--- a/revenue-view/output/Nasam_Revenue_View.xlsx
+++ b/revenue-view/output/Nasam_Revenue_View.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="0 ReadMe" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1 Revenue Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2 Brand-Channel Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3 SaaS Subscriptions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0 ReadMe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Revenue Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Brand-Channel Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 SaaS Subscriptions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -683,10 +683,10 @@
         <v>32429.34</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>48659.57</v>
+        <v>81506.23</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>916092.61</v>
+        <v>948939.27</v>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
@@ -728,10 +728,10 @@
         <v>6574.55</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>10561.81</v>
+        <v>13262.63</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>65363.24</v>
+        <v>68064.06</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -765,10 +765,10 @@
         <v>219280.29</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>434058.05</v>
+        <v>522496.35</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>942058.9300000001</v>
+        <v>1030497.23</v>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
         <v>258284.18</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>493279.43</v>
+        <v>617265.21</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>1923514.78</v>
+        <v>2047500.56</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -862,10 +862,10 @@
         <v>231860.15</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>58943.41</v>
+        <v>101242.49</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>564475.38</v>
+        <v>606774.46</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
         <v>4994.34</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>6498.9</v>
+        <v>10140.29</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>17844.76</v>
+        <v>21486.15</v>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
         <v>1289.44</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>125.64</v>
+        <v>376.91</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>1907.86</v>
+        <v>2159.13</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -961,10 +961,10 @@
         <v>3704.9</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>6373.26</v>
+        <v>9763.379999999999</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>15936.9</v>
+        <v>19327.02</v>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         <v>20454.68</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>11500.3</v>
+        <v>22906.52</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>96703.22</v>
+        <v>108109.44</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         <v>5179</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>2753.1</v>
+        <v>4650.6</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>39006.58</v>
+        <v>40904.08</v>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="n">
-        <v>310.87</v>
+        <v>478.87</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>310.87</v>
+        <v>478.87</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         <v>14094.94</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>2616.85</v>
+        <v>3183.28</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>39495.27</v>
+        <v>40061.7</v>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
@@ -1150,10 +1150,10 @@
         <v>1180.74</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>5819.48</v>
+        <v>14593.77</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>17890.5</v>
+        <v>26664.79</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         <v>200728.24</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>33449.86</v>
+        <v>57241.01</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>421017.51</v>
+        <v>444808.66</v>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         <v>441.7</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>759.6</v>
+        <v>1184.4</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>18353.7</v>
+        <v>18778.5</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
       </c>
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n">
-        <v>933.62</v>
+        <v>1429.94</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>8933.58</v>
+        <v>9429.9</v>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         <v>199016.56</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>23055.07</v>
+        <v>37023.19</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>364739.32</v>
+        <v>378707.44</v>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
         <v>1269.98</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>8701.57</v>
+        <v>17603.48</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>28104.58</v>
+        <v>37006.49</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
         <v>5682.89</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>7494.35</v>
+        <v>10954.67</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>28909.89</v>
+        <v>32370.21</v>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
       <c r="J24" s="5" t="n"/>
       <c r="K24" s="5" t="n"/>
       <c r="L24" s="5" t="n">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         <v>4879.35</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>808.79</v>
+        <v>1314.77</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>13486.44</v>
+        <v>13992.42</v>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         <v>803.54</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>6632.56</v>
+        <v>9480.9</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>15370.45</v>
+        <v>18218.79</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -1555,10 +1555,10 @@
         <v>19709.28</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>17425.33</v>
+        <v>24732.68</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>246346.53</v>
+        <v>253653.88</v>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         <v>12498.2</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>8443.65</v>
+        <v>13587.8</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>136743.31</v>
+        <v>141887.46</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         <v>4265</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>8981.68</v>
+        <v>10880.16</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>57976.41</v>
+        <v>59874.89</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -1718,9 +1718,11 @@
       <c r="K31" s="5" t="n">
         <v>2867.08</v>
       </c>
-      <c r="L31" s="5" t="n"/>
+      <c r="L31" s="5" t="n">
+        <v>264.72</v>
+      </c>
       <c r="M31" s="5" t="n">
-        <v>51415.81</v>
+        <v>51680.53</v>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
@@ -1762,10 +1764,10 @@
         <v>4560.75</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>2229.73</v>
+        <v>3084.06</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>49942.39</v>
+        <v>50796.72</v>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
@@ -1807,10 +1809,10 @@
         <v>2668.25</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>1026.02</v>
+        <v>1403.67</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>27010.02</v>
+        <v>27387.67</v>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
@@ -1852,10 +1854,10 @@
         <v>1892.5</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>957.71</v>
+        <v>1434.39</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>10441.04</v>
+        <v>10917.72</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -1967,10 +1969,10 @@
         <v>2154</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>7229.26</v>
+        <v>7607.78</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>10482.76</v>
+        <v>10861.28</v>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
@@ -2023,10 +2025,10 @@
       <c r="J39" s="5" t="n"/>
       <c r="K39" s="5" t="n"/>
       <c r="L39" s="5" t="n">
-        <v>6050.96</v>
+        <v>6429.48</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>6050.96</v>
+        <v>6429.48</v>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
@@ -2085,10 +2087,10 @@
       <c r="J41" s="5" t="n"/>
       <c r="K41" s="5" t="n"/>
       <c r="L41" s="5" t="n">
-        <v>407451.7</v>
+        <v>480598.2</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>407451.7</v>
+        <v>480598.2</v>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
@@ -4119,10 +4121,10 @@
       <c r="J100" s="5" t="n"/>
       <c r="K100" s="5" t="n"/>
       <c r="L100" s="5" t="n">
-        <v>2</v>
+        <v>17.14</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>2</v>
+        <v>17.14</v>
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
@@ -4276,10 +4278,10 @@
         <v>7298.95</v>
       </c>
       <c r="L105" s="7" t="n">
-        <v>3532.67</v>
+        <v>3547.81</v>
       </c>
       <c r="M105" s="7" t="n">
-        <v>203561.68</v>
+        <v>203576.81</v>
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
@@ -4792,7 +4794,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R185"/>
+  <dimension ref="A1:R186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4996,10 +4998,10 @@
         <v>4994.34</v>
       </c>
       <c r="P3" s="12" t="n">
-        <v>6498.9</v>
+        <v>10140.29</v>
       </c>
       <c r="Q3" s="12" t="n">
-        <v>17844.76</v>
+        <v>21486.15</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
@@ -5054,10 +5056,10 @@
         <v>1289.44</v>
       </c>
       <c r="P4" s="12" t="n">
-        <v>125.64</v>
+        <v>376.91</v>
       </c>
       <c r="Q4" s="12" t="n">
-        <v>1907.86</v>
+        <v>2159.13</v>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
@@ -5108,10 +5110,10 @@
         <v>3704.9</v>
       </c>
       <c r="P5" s="12" t="n">
-        <v>6373.26</v>
+        <v>9763.379999999999</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>15936.9</v>
+        <v>19327.02</v>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
@@ -5222,10 +5224,10 @@
         <v>20454.68</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>11500.3</v>
+        <v>22906.52</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>96703.22</v>
+        <v>108109.44</v>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
@@ -5288,10 +5290,10 @@
         <v>5179</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>2753.1</v>
+        <v>4650.6</v>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>39006.58</v>
+        <v>40904.08</v>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
@@ -5336,10 +5338,10 @@
       <c r="N9" s="12" t="n"/>
       <c r="O9" s="12" t="n"/>
       <c r="P9" s="12" t="n">
-        <v>310.87</v>
+        <v>478.87</v>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>310.87</v>
+        <v>478.87</v>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
@@ -5396,10 +5398,10 @@
         <v>14094.94</v>
       </c>
       <c r="P10" s="12" t="n">
-        <v>2616.85</v>
+        <v>3183.28</v>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>39495.27</v>
+        <v>40061.7</v>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
@@ -5454,10 +5456,10 @@
         <v>1180.74</v>
       </c>
       <c r="P11" s="12" t="n">
-        <v>5819.48</v>
+        <v>14593.77</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>17890.5</v>
+        <v>26664.79</v>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
@@ -5572,10 +5574,10 @@
         <v>200728.24</v>
       </c>
       <c r="P13" s="12" t="n">
-        <v>33449.86</v>
+        <v>57241.01</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>421017.51</v>
+        <v>444808.66</v>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
@@ -5638,10 +5640,10 @@
         <v>441.7</v>
       </c>
       <c r="P14" s="12" t="n">
-        <v>759.6</v>
+        <v>1184.4</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>18353.7</v>
+        <v>18778.5</v>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
@@ -5794,10 +5796,10 @@
       </c>
       <c r="O17" s="12" t="n"/>
       <c r="P17" s="12" t="n">
-        <v>933.62</v>
+        <v>1429.94</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>8933.58</v>
+        <v>9429.9</v>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
@@ -5910,10 +5912,10 @@
         <v>199016.56</v>
       </c>
       <c r="P19" s="12" t="n">
-        <v>23055.07</v>
+        <v>37023.19</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>364739.32</v>
+        <v>378707.44</v>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
@@ -5974,10 +5976,10 @@
         <v>1269.98</v>
       </c>
       <c r="P20" s="12" t="n">
-        <v>8701.57</v>
+        <v>17603.48</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>28104.58</v>
+        <v>37006.49</v>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
@@ -6088,10 +6090,10 @@
         <v>5682.89</v>
       </c>
       <c r="P22" s="12" t="n">
-        <v>7494.35</v>
+        <v>10954.67</v>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>28909.89</v>
+        <v>32370.21</v>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
@@ -6136,10 +6138,10 @@
       <c r="N23" s="12" t="n"/>
       <c r="O23" s="12" t="n"/>
       <c r="P23" s="12" t="n">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
@@ -6196,10 +6198,10 @@
         <v>4879.35</v>
       </c>
       <c r="P24" s="12" t="n">
-        <v>808.79</v>
+        <v>1314.77</v>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>13486.44</v>
+        <v>13992.42</v>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
@@ -6250,10 +6252,10 @@
         <v>803.54</v>
       </c>
       <c r="P25" s="12" t="n">
-        <v>6632.56</v>
+        <v>9480.9</v>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>15370.45</v>
+        <v>18218.79</v>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
@@ -6582,10 +6584,10 @@
         <v>12498.2</v>
       </c>
       <c r="P32" s="12" t="n">
-        <v>8443.65</v>
+        <v>13587.8</v>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>136743.31</v>
+        <v>141887.46</v>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
@@ -6820,10 +6822,10 @@
         <v>4265</v>
       </c>
       <c r="P36" s="12" t="n">
-        <v>8981.68</v>
+        <v>10880.16</v>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>57976.41</v>
+        <v>59874.89</v>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
@@ -6953,9 +6955,11 @@
       <c r="O38" s="12" t="n">
         <v>2867.08</v>
       </c>
-      <c r="P38" s="12" t="n"/>
+      <c r="P38" s="12" t="n">
+        <v>264.72</v>
+      </c>
       <c r="Q38" s="12" t="n">
-        <v>51415.81</v>
+        <v>51680.53</v>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
@@ -7194,10 +7198,10 @@
         <v>2668.25</v>
       </c>
       <c r="P43" s="12" t="n">
-        <v>1026.02</v>
+        <v>1403.67</v>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>27010.02</v>
+        <v>27387.67</v>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
@@ -7328,10 +7332,10 @@
         <v>1892.5</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>957.71</v>
+        <v>1434.39</v>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>10441.04</v>
+        <v>10917.72</v>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
@@ -7934,10 +7938,10 @@
       <c r="N57" s="12" t="n"/>
       <c r="O57" s="12" t="n"/>
       <c r="P57" s="12" t="n">
-        <v>6050.96</v>
+        <v>6429.48</v>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>6050.96</v>
+        <v>6429.48</v>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
@@ -7996,116 +8000,110 @@
       </c>
     </row>
     <row r="59" outlineLevel="1">
-      <c r="A59" s="11" t="inlineStr">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>Wadi Halfa</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>Wadi Halfa</t>
         </is>
       </c>
-      <c r="C59" s="11" t="inlineStr">
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>Ninja Retail</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>Commission (to invoice)</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="n"/>
+      <c r="H59" s="17" t="n"/>
+      <c r="I59" s="17" t="n"/>
+      <c r="J59" s="17" t="n"/>
+      <c r="K59" s="17" t="n"/>
+      <c r="L59" s="17" t="n"/>
+      <c r="M59" s="17" t="n"/>
+      <c r="N59" s="17" t="n"/>
+      <c r="O59" s="17" t="n"/>
+      <c r="P59" s="17" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="Q59" s="17" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>Nasam platform — closed POs — net of billed; on received value</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" outlineLevel="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>Wadi Halfa</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Wadi Halfa</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="D60" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E59" s="11" t="inlineStr">
+      <c r="E60" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F59" s="11" t="n"/>
-      <c r="G59" s="12" t="n"/>
-      <c r="H59" s="12" t="n"/>
-      <c r="I59" s="12" t="n"/>
-      <c r="J59" s="12" t="n"/>
-      <c r="K59" s="12" t="n"/>
-      <c r="L59" s="12" t="n">
+      <c r="F60" s="11" t="n"/>
+      <c r="G60" s="12" t="n"/>
+      <c r="H60" s="12" t="n"/>
+      <c r="I60" s="12" t="n"/>
+      <c r="J60" s="12" t="n"/>
+      <c r="K60" s="12" t="n"/>
+      <c r="L60" s="12" t="n">
         <v>199</v>
       </c>
-      <c r="M59" s="12" t="n">
+      <c r="M60" s="12" t="n">
         <v>534.25</v>
       </c>
-      <c r="N59" s="12" t="n">
+      <c r="N60" s="12" t="n">
         <v>366.25</v>
       </c>
-      <c r="O59" s="12" t="n">
+      <c r="O60" s="12" t="n">
         <v>1200.15</v>
       </c>
-      <c r="P59" s="12" t="n">
+      <c r="P60" s="12" t="n">
         <v>180.15</v>
       </c>
-      <c r="Q59" s="12" t="n">
+      <c r="Q60" s="12" t="n">
         <v>2479.8</v>
       </c>
-      <c r="R59" s="3" t="inlineStr">
+      <c r="R60" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" outlineLevel="1">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>Wadi Halfa</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>Wadi Halfa</t>
-        </is>
-      </c>
-      <c r="C60" s="13" t="inlineStr">
-        <is>
-          <t>Trendyol</t>
-        </is>
-      </c>
-      <c r="D60" s="13" t="inlineStr">
-        <is>
-          <t>Commission (billed)</t>
-        </is>
-      </c>
-      <c r="E60" s="13" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F60" s="13" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="G60" s="14" t="n"/>
-      <c r="H60" s="14" t="n"/>
-      <c r="I60" s="14" t="n"/>
-      <c r="J60" s="14" t="n"/>
-      <c r="K60" s="14" t="n"/>
-      <c r="L60" s="14" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="M60" s="14" t="n">
-        <v>24.04</v>
-      </c>
-      <c r="N60" s="14" t="n">
-        <v>16.48</v>
-      </c>
-      <c r="O60" s="14" t="n">
-        <v>54.01</v>
-      </c>
-      <c r="P60" s="14" t="n"/>
-      <c r="Q60" s="14" t="n">
-        <v>103.49</v>
-      </c>
-      <c r="R60" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
@@ -8117,43 +8115,53 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="n"/>
+          <t>Wadi Halfa</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>Trendyol</t>
+        </is>
+      </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="n"/>
-      <c r="F61" s="13" t="n"/>
+          <t>Commission (billed)</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="G61" s="14" t="n"/>
       <c r="H61" s="14" t="n"/>
       <c r="I61" s="14" t="n"/>
       <c r="J61" s="14" t="n"/>
-      <c r="K61" s="14" t="n">
-        <v>1290.32</v>
-      </c>
+      <c r="K61" s="14" t="n"/>
       <c r="L61" s="14" t="n">
-        <v>2000</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M61" s="14" t="n">
-        <v>2000</v>
+        <v>24.04</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>2000</v>
+        <v>16.48</v>
       </c>
       <c r="O61" s="14" t="n">
-        <v>600</v>
+        <v>54.01</v>
       </c>
       <c r="P61" s="14" t="n"/>
       <c r="Q61" s="14" t="n">
-        <v>7890.32</v>
+        <v>103.49</v>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>Wafeq invoice export · Temporary support discount (supply issues); card fee 2,000</t>
+          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8179,7 @@
       <c r="C62" s="13" t="n"/>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>Setup / one-time</t>
+          <t>Monthly fee</t>
         </is>
       </c>
       <c r="E62" s="13" t="n"/>
@@ -8181,19 +8189,27 @@
       <c r="I62" s="14" t="n"/>
       <c r="J62" s="14" t="n"/>
       <c r="K62" s="14" t="n">
+        <v>1290.32</v>
+      </c>
+      <c r="L62" s="14" t="n">
         <v>2000</v>
       </c>
-      <c r="L62" s="14" t="n"/>
-      <c r="M62" s="14" t="n"/>
-      <c r="N62" s="14" t="n"/>
-      <c r="O62" s="14" t="n"/>
+      <c r="M62" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N62" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O62" s="14" t="n">
+        <v>600</v>
+      </c>
       <c r="P62" s="14" t="n"/>
       <c r="Q62" s="14" t="n">
-        <v>2000</v>
+        <v>7890.32</v>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>Wafeq invoice export</t>
+          <t>Wafeq invoice export · Temporary support discount (supply issues); card fee 2,000</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8227,7 @@
       <c r="C63" s="13" t="n"/>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>Setup / one-time</t>
         </is>
       </c>
       <c r="E63" s="13" t="n"/>
@@ -8220,158 +8236,148 @@
       <c r="H63" s="14" t="n"/>
       <c r="I63" s="14" t="n"/>
       <c r="J63" s="14" t="n"/>
-      <c r="K63" s="14" t="n"/>
-      <c r="L63" s="14" t="n">
-        <v>-2000</v>
-      </c>
+      <c r="K63" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L63" s="14" t="n"/>
       <c r="M63" s="14" t="n"/>
       <c r="N63" s="14" t="n"/>
       <c r="O63" s="14" t="n"/>
       <c r="P63" s="14" t="n"/>
       <c r="Q63" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" outlineLevel="1">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>Wadi Halfa</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="n"/>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="n"/>
+      <c r="F64" s="13" t="n"/>
+      <c r="G64" s="14" t="n"/>
+      <c r="H64" s="14" t="n"/>
+      <c r="I64" s="14" t="n"/>
+      <c r="J64" s="14" t="n"/>
+      <c r="K64" s="14" t="n"/>
+      <c r="L64" s="14" t="n">
         <v>-2000</v>
       </c>
-      <c r="R63" s="3" t="inlineStr">
+      <c r="M64" s="14" t="n"/>
+      <c r="N64" s="14" t="n"/>
+      <c r="O64" s="14" t="n"/>
+      <c r="P64" s="14" t="n"/>
+      <c r="Q64" s="14" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="R64" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · setup-period 50% AM fee / agreed reduction / pricing error</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>Dar Sonbol</t>
         </is>
       </c>
-      <c r="B65" s="9" t="n"/>
-      <c r="C65" s="9" t="n"/>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E65" s="9" t="n"/>
-      <c r="F65" s="9" t="n"/>
-      <c r="G65" s="10" t="n"/>
-      <c r="H65" s="10" t="n"/>
-      <c r="I65" s="10" t="n"/>
-      <c r="J65" s="10" t="n"/>
-      <c r="K65" s="10" t="n"/>
-      <c r="L65" s="10" t="n"/>
-      <c r="M65" s="10" t="n"/>
-      <c r="N65" s="10" t="n">
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n"/>
+      <c r="J66" s="10" t="n"/>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n">
         <v>4000</v>
       </c>
-      <c r="O65" s="10" t="n"/>
-      <c r="P65" s="10" t="n"/>
-      <c r="Q65" s="10" t="n">
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n">
         <v>4000</v>
       </c>
-      <c r="R65" s="3" t="inlineStr">
+      <c r="R66" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="66" outlineLevel="1">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="67" outlineLevel="1">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>Dar Sonbol</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>Sonbol (سنبل)</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr">
+      <c r="E67" s="11" t="inlineStr">
         <is>
           <t>SaaS</t>
         </is>
       </c>
-      <c r="F66" s="11" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G66" s="12" t="n"/>
-      <c r="H66" s="12" t="n"/>
-      <c r="I66" s="12" t="n"/>
-      <c r="J66" s="12" t="n"/>
-      <c r="K66" s="12" t="n"/>
-      <c r="L66" s="12" t="n"/>
-      <c r="M66" s="12" t="n"/>
-      <c r="N66" s="12" t="n"/>
-      <c r="O66" s="12" t="n"/>
-      <c r="P66" s="12" t="n">
-        <v>407451.7</v>
-      </c>
-      <c r="Q66" s="12" t="n">
-        <v>407451.7</v>
-      </c>
-      <c r="R66" s="3" t="inlineStr">
+      <c r="G67" s="12" t="n"/>
+      <c r="H67" s="12" t="n"/>
+      <c r="I67" s="12" t="n"/>
+      <c r="J67" s="12" t="n"/>
+      <c r="K67" s="12" t="n"/>
+      <c r="L67" s="12" t="n"/>
+      <c r="M67" s="12" t="n"/>
+      <c r="N67" s="12" t="n"/>
+      <c r="O67" s="12" t="n"/>
+      <c r="P67" s="12" t="n">
+        <v>480598.2</v>
+      </c>
+      <c r="Q67" s="12" t="n">
+        <v>480598.2</v>
+      </c>
+      <c r="R67" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view (from 13 Aug 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" outlineLevel="1">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Dar Sonbol</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Sonbol (سنبل)</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Mapping</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G67" s="15" t="n"/>
-      <c r="H67" s="15" t="n"/>
-      <c r="I67" s="15" t="n"/>
-      <c r="J67" s="15" t="n"/>
-      <c r="K67" s="15" t="n"/>
-      <c r="L67" s="15" t="n"/>
-      <c r="M67" s="15" t="n"/>
-      <c r="N67" s="15" t="n"/>
-      <c r="O67" s="15" t="n"/>
-      <c r="P67" s="15" t="n"/>
-      <c r="Q67" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" s="3" t="inlineStr">
-        <is>
-          <t>Rate card (Tarik) — in setup, channel being built</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8394,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Noon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -8438,7 +8444,7 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Trendyol</t>
+          <t>Noon</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -8488,7 +8494,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>aivi</t>
+          <t>Trendyol</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -8521,7 +8527,7 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>Rate card (Tarik) — integration WIP</t>
+          <t>Rate card (Tarik) — in setup, channel being built</t>
         </is>
       </c>
     </row>
@@ -8533,19 +8539,27 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="n"/>
+          <t>Sonbol (سنبل)</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>aivi</t>
+        </is>
+      </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n"/>
+          <t>Mapping</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G71" s="15" t="n"/>
@@ -8563,175 +8577,165 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
+          <t>Rate card (Tarik) — integration WIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" outlineLevel="1">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Dar Sonbol</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Monthly fee</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="n"/>
+      <c r="H72" s="15" t="n"/>
+      <c r="I72" s="15" t="n"/>
+      <c r="J72" s="15" t="n"/>
+      <c r="K72" s="15" t="n"/>
+      <c r="L72" s="15" t="n"/>
+      <c r="M72" s="15" t="n"/>
+      <c r="N72" s="15" t="n"/>
+      <c r="O72" s="15" t="n"/>
+      <c r="P72" s="15" t="n"/>
+      <c r="Q72" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3" t="inlineStr">
+        <is>
           <t>Rate card (Tarik) · Card: FAM 2% + 5,000/mo — 50% at 1st live managed channel, 100% from 2nd (FAM only). Salla SaaS = separate added deal.</t>
         </is>
       </c>
     </row>
-    <row r="72" outlineLevel="1">
-      <c r="A72" s="13" t="inlineStr">
+    <row r="73" outlineLevel="1">
+      <c r="A73" s="13" t="inlineStr">
         <is>
           <t>Dar Sonbol</t>
         </is>
       </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="B73" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C72" s="13" t="n"/>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="C73" s="13" t="n"/>
+      <c r="D73" s="13" t="inlineStr">
         <is>
           <t>Setup / one-time</t>
         </is>
       </c>
-      <c r="E72" s="13" t="n"/>
-      <c r="F72" s="13" t="n"/>
-      <c r="G72" s="14" t="n"/>
-      <c r="H72" s="14" t="n"/>
-      <c r="I72" s="14" t="n"/>
-      <c r="J72" s="14" t="n"/>
-      <c r="K72" s="14" t="n"/>
-      <c r="L72" s="14" t="n"/>
-      <c r="M72" s="14" t="n"/>
-      <c r="N72" s="14" t="n">
+      <c r="E73" s="13" t="n"/>
+      <c r="F73" s="13" t="n"/>
+      <c r="G73" s="14" t="n"/>
+      <c r="H73" s="14" t="n"/>
+      <c r="I73" s="14" t="n"/>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="14" t="n"/>
+      <c r="L73" s="14" t="n"/>
+      <c r="M73" s="14" t="n"/>
+      <c r="N73" s="14" t="n">
         <v>4000</v>
       </c>
-      <c r="O72" s="14" t="n"/>
-      <c r="P72" s="14" t="n"/>
-      <c r="Q72" s="14" t="n">
+      <c r="O73" s="14" t="n"/>
+      <c r="P73" s="14" t="n"/>
+      <c r="Q73" s="14" t="n">
         <v>4000</v>
       </c>
-      <c r="R72" s="3" t="inlineStr">
+      <c r="R73" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>Two United  (churned 2026-05)</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n"/>
-      <c r="C74" s="9" t="n"/>
-      <c r="D74" s="9" t="inlineStr">
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E74" s="9" t="n"/>
-      <c r="F74" s="9" t="n"/>
-      <c r="G74" s="10" t="n">
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="H74" s="10" t="n">
+      <c r="H75" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="I74" s="10" t="n">
+      <c r="I75" s="10" t="n">
         <v>3606.59</v>
       </c>
-      <c r="J74" s="10" t="n">
+      <c r="J75" s="10" t="n">
         <v>2747.96</v>
       </c>
-      <c r="K74" s="10" t="n">
+      <c r="K75" s="10" t="n">
         <v>5631.76</v>
       </c>
-      <c r="L74" s="10" t="n">
+      <c r="L75" s="10" t="n">
         <v>5324.76</v>
       </c>
-      <c r="M74" s="10" t="n">
+      <c r="M75" s="10" t="n">
         <v>5462.25</v>
       </c>
-      <c r="N74" s="10" t="n"/>
-      <c r="O74" s="10" t="n"/>
-      <c r="P74" s="10" t="n"/>
-      <c r="Q74" s="10" t="n">
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="10" t="n">
         <v>32773.32</v>
       </c>
-      <c r="R74" s="3" t="inlineStr">
+      <c r="R75" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · Card: MP 2% / Retail 1.5% + 5,000/mo</t>
         </is>
       </c>
     </row>
-    <row r="75" outlineLevel="1">
-      <c r="A75" s="11" t="inlineStr">
+    <row r="76" outlineLevel="1">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>Bonita</t>
         </is>
       </c>
-      <c r="C75" s="11" t="n"/>
-      <c r="D75" s="11" t="inlineStr">
+      <c r="C76" s="11" t="n"/>
+      <c r="D76" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E75" s="11" t="n"/>
-      <c r="F75" s="11" t="n"/>
-      <c r="G75" s="12" t="n"/>
-      <c r="H75" s="12" t="n">
-        <v>449.56</v>
-      </c>
-      <c r="I75" s="12" t="n">
-        <v>1196.25</v>
-      </c>
-      <c r="J75" s="12" t="n"/>
-      <c r="K75" s="12" t="n">
-        <v>487.96</v>
-      </c>
-      <c r="L75" s="12" t="n"/>
-      <c r="M75" s="12" t="n"/>
-      <c r="N75" s="12" t="n"/>
-      <c r="O75" s="12" t="n"/>
-      <c r="P75" s="12" t="n"/>
-      <c r="Q75" s="12" t="n">
-        <v>2133.77</v>
-      </c>
-      <c r="R75" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" outlineLevel="2">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="inlineStr">
-        <is>
-          <t>Bonita</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E76" s="11" t="n"/>
       <c r="F76" s="11" t="n"/>
       <c r="G76" s="12" t="n"/>
       <c r="H76" s="12" t="n">
         <v>449.56</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>1079.25</v>
+        <v>1196.25</v>
       </c>
       <c r="J76" s="12" t="n"/>
       <c r="K76" s="12" t="n">
@@ -8743,244 +8747,238 @@
       <c r="O76" s="12" t="n"/>
       <c r="P76" s="12" t="n"/>
       <c r="Q76" s="12" t="n">
+        <v>2133.77</v>
+      </c>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" outlineLevel="2">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>Bonita</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>Jahez</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="n"/>
+      <c r="G77" s="12" t="n"/>
+      <c r="H77" s="12" t="n">
+        <v>449.56</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <v>1079.25</v>
+      </c>
+      <c r="J77" s="12" t="n"/>
+      <c r="K77" s="12" t="n">
+        <v>487.96</v>
+      </c>
+      <c r="L77" s="12" t="n"/>
+      <c r="M77" s="12" t="n"/>
+      <c r="N77" s="12" t="n"/>
+      <c r="O77" s="12" t="n"/>
+      <c r="P77" s="12" t="n"/>
+      <c r="Q77" s="12" t="n">
         <v>2016.77</v>
       </c>
-      <c r="R76" s="3" t="inlineStr">
+      <c r="R77" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="77" outlineLevel="2">
-      <c r="A77" s="13" t="inlineStr">
+    <row r="78" outlineLevel="2">
+      <c r="A78" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B77" s="13" t="inlineStr">
+      <c r="B78" s="13" t="inlineStr">
         <is>
           <t>Bonita ≈</t>
         </is>
       </c>
-      <c r="C77" s="13" t="inlineStr">
+      <c r="C78" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D77" s="13" t="inlineStr">
+      <c r="D78" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E77" s="13" t="inlineStr">
+      <c r="E78" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F77" s="13" t="inlineStr">
+      <c r="F78" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G77" s="14" t="n"/>
-      <c r="H77" s="14" t="n"/>
-      <c r="I77" s="14" t="n">
+      <c r="G78" s="14" t="n"/>
+      <c r="H78" s="14" t="n"/>
+      <c r="I78" s="14" t="n">
         <v>22.83</v>
       </c>
-      <c r="J77" s="14" t="n"/>
-      <c r="K77" s="14" t="n">
+      <c r="J78" s="14" t="n"/>
+      <c r="K78" s="14" t="n">
         <v>9.76</v>
       </c>
-      <c r="L77" s="14" t="n"/>
-      <c r="M77" s="14" t="n"/>
-      <c r="N77" s="14" t="n"/>
-      <c r="O77" s="14" t="n"/>
-      <c r="P77" s="14" t="n"/>
-      <c r="Q77" s="14" t="n">
+      <c r="L78" s="14" t="n"/>
+      <c r="M78" s="14" t="n"/>
+      <c r="N78" s="14" t="n"/>
+      <c r="O78" s="14" t="n"/>
+      <c r="P78" s="14" t="n"/>
+      <c r="Q78" s="14" t="n">
         <v>32.59</v>
       </c>
-      <c r="R77" s="3" t="inlineStr">
+      <c r="R78" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="78" outlineLevel="2">
-      <c r="A78" s="11" t="inlineStr">
+    <row r="79" outlineLevel="2">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>Bonita</t>
         </is>
       </c>
-      <c r="C78" s="11" t="inlineStr">
+      <c r="C79" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D78" s="11" t="inlineStr">
+      <c r="D79" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E78" s="11" t="inlineStr">
+      <c r="E79" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F78" s="11" t="n"/>
-      <c r="G78" s="12" t="n"/>
-      <c r="H78" s="12" t="n"/>
-      <c r="I78" s="12" t="n">
+      <c r="F79" s="11" t="n"/>
+      <c r="G79" s="12" t="n"/>
+      <c r="H79" s="12" t="n"/>
+      <c r="I79" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="J78" s="12" t="n"/>
-      <c r="K78" s="12" t="n"/>
-      <c r="L78" s="12" t="n"/>
-      <c r="M78" s="12" t="n"/>
-      <c r="N78" s="12" t="n"/>
-      <c r="O78" s="12" t="n"/>
-      <c r="P78" s="12" t="n"/>
-      <c r="Q78" s="12" t="n">
+      <c r="J79" s="12" t="n"/>
+      <c r="K79" s="12" t="n"/>
+      <c r="L79" s="12" t="n"/>
+      <c r="M79" s="12" t="n"/>
+      <c r="N79" s="12" t="n"/>
+      <c r="O79" s="12" t="n"/>
+      <c r="P79" s="12" t="n"/>
+      <c r="Q79" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="R78" s="3" t="inlineStr">
+      <c r="R79" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="79" outlineLevel="2">
-      <c r="A79" s="13" t="inlineStr">
+    <row r="80" outlineLevel="2">
+      <c r="A80" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B79" s="13" t="inlineStr">
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>Bonita ≈</t>
         </is>
       </c>
-      <c r="C79" s="13" t="inlineStr">
+      <c r="C80" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D79" s="13" t="inlineStr">
+      <c r="D80" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E79" s="13" t="inlineStr">
+      <c r="E80" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F79" s="13" t="inlineStr">
+      <c r="F80" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G79" s="14" t="n"/>
-      <c r="H79" s="14" t="n"/>
-      <c r="I79" s="14" t="n">
+      <c r="G80" s="14" t="n"/>
+      <c r="H80" s="14" t="n"/>
+      <c r="I80" s="14" t="n">
         <v>3.03</v>
       </c>
-      <c r="J79" s="14" t="n"/>
-      <c r="K79" s="14" t="n"/>
-      <c r="L79" s="14" t="n"/>
-      <c r="M79" s="14" t="n"/>
-      <c r="N79" s="14" t="n"/>
-      <c r="O79" s="14" t="n"/>
-      <c r="P79" s="14" t="n"/>
-      <c r="Q79" s="14" t="n">
+      <c r="J80" s="14" t="n"/>
+      <c r="K80" s="14" t="n"/>
+      <c r="L80" s="14" t="n"/>
+      <c r="M80" s="14" t="n"/>
+      <c r="N80" s="14" t="n"/>
+      <c r="O80" s="14" t="n"/>
+      <c r="P80" s="14" t="n"/>
+      <c r="Q80" s="14" t="n">
         <v>3.03</v>
       </c>
-      <c r="R79" s="3" t="inlineStr">
+      <c r="R80" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="80" outlineLevel="1">
-      <c r="A80" s="11" t="inlineStr">
+    <row r="81" outlineLevel="1">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>Feel</t>
         </is>
       </c>
-      <c r="C80" s="11" t="n"/>
-      <c r="D80" s="11" t="inlineStr">
+      <c r="C81" s="11" t="n"/>
+      <c r="D81" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E80" s="11" t="n"/>
-      <c r="F80" s="11" t="n"/>
-      <c r="G80" s="12" t="n"/>
-      <c r="H80" s="12" t="n">
-        <v>801.75</v>
-      </c>
-      <c r="I80" s="12" t="n">
-        <v>1047</v>
-      </c>
-      <c r="J80" s="12" t="n">
-        <v>1068</v>
-      </c>
-      <c r="K80" s="12" t="n">
-        <v>3214</v>
-      </c>
-      <c r="L80" s="12" t="n">
-        <v>1219</v>
-      </c>
-      <c r="M80" s="12" t="n">
-        <v>1193</v>
-      </c>
-      <c r="N80" s="12" t="n"/>
-      <c r="O80" s="12" t="n"/>
-      <c r="P80" s="12" t="n"/>
-      <c r="Q80" s="12" t="n">
-        <v>8542.75</v>
-      </c>
-      <c r="R80" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" outlineLevel="2">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B81" s="11" t="inlineStr">
-        <is>
-          <t>Feel</t>
-        </is>
-      </c>
-      <c r="C81" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E81" s="11" t="n"/>
       <c r="F81" s="11" t="n"/>
       <c r="G81" s="12" t="n"/>
       <c r="H81" s="12" t="n">
@@ -9009,432 +9007,436 @@
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" outlineLevel="2">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>Feel</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>Jahez</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="n"/>
+      <c r="G82" s="12" t="n"/>
+      <c r="H82" s="12" t="n">
+        <v>801.75</v>
+      </c>
+      <c r="I82" s="12" t="n">
+        <v>1047</v>
+      </c>
+      <c r="J82" s="12" t="n">
+        <v>1068</v>
+      </c>
+      <c r="K82" s="12" t="n">
+        <v>3214</v>
+      </c>
+      <c r="L82" s="12" t="n">
+        <v>1219</v>
+      </c>
+      <c r="M82" s="12" t="n">
+        <v>1193</v>
+      </c>
+      <c r="N82" s="12" t="n"/>
+      <c r="O82" s="12" t="n"/>
+      <c r="P82" s="12" t="n"/>
+      <c r="Q82" s="12" t="n">
+        <v>8542.75</v>
+      </c>
+      <c r="R82" s="3" t="inlineStr">
+        <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="82" outlineLevel="2">
-      <c r="A82" s="13" t="inlineStr">
+    <row r="83" outlineLevel="2">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="B83" s="13" t="inlineStr">
         <is>
           <t>Feel ≈</t>
         </is>
       </c>
-      <c r="C82" s="13" t="inlineStr">
+      <c r="C83" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="D83" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E82" s="13" t="inlineStr">
+      <c r="E83" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F82" s="13" t="inlineStr">
+      <c r="F83" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G82" s="14" t="n"/>
-      <c r="H82" s="14" t="n"/>
-      <c r="I82" s="14" t="n">
+      <c r="G83" s="14" t="n"/>
+      <c r="H83" s="14" t="n"/>
+      <c r="I83" s="14" t="n">
         <v>22.14</v>
       </c>
-      <c r="J82" s="14" t="n">
+      <c r="J83" s="14" t="n">
         <v>21.36</v>
       </c>
-      <c r="K82" s="14" t="n">
+      <c r="K83" s="14" t="n">
         <v>64.28</v>
       </c>
-      <c r="L82" s="14" t="n">
+      <c r="L83" s="14" t="n">
         <v>23.58</v>
       </c>
-      <c r="M82" s="14" t="n">
+      <c r="M83" s="14" t="n">
         <v>24.46</v>
       </c>
-      <c r="N82" s="14" t="n"/>
-      <c r="O82" s="14" t="n"/>
-      <c r="P82" s="14" t="n"/>
-      <c r="Q82" s="14" t="n">
+      <c r="N83" s="14" t="n"/>
+      <c r="O83" s="14" t="n"/>
+      <c r="P83" s="14" t="n"/>
+      <c r="Q83" s="14" t="n">
         <v>155.82</v>
       </c>
-      <c r="R82" s="3" t="inlineStr">
+      <c r="R83" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="83" outlineLevel="1">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="84" outlineLevel="1">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>Reefi</t>
         </is>
       </c>
-      <c r="C83" s="11" t="n"/>
-      <c r="D83" s="11" t="inlineStr">
+      <c r="C84" s="11" t="n"/>
+      <c r="D84" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E83" s="11" t="n"/>
-      <c r="F83" s="11" t="n"/>
-      <c r="G83" s="12" t="n">
+      <c r="E84" s="11" t="n"/>
+      <c r="F84" s="11" t="n"/>
+      <c r="G84" s="12" t="n">
         <v>1949.46</v>
       </c>
-      <c r="H83" s="12" t="n">
+      <c r="H84" s="12" t="n">
         <v>11692.19</v>
       </c>
-      <c r="I83" s="12" t="n">
+      <c r="I84" s="12" t="n">
         <v>17810.99</v>
       </c>
-      <c r="J83" s="12" t="n">
+      <c r="J84" s="12" t="n">
         <v>8609.1</v>
       </c>
-      <c r="K83" s="12" t="n">
+      <c r="K84" s="12" t="n">
         <v>18582.9</v>
       </c>
-      <c r="L83" s="12" t="n">
+      <c r="L84" s="12" t="n">
         <v>11841.5</v>
       </c>
-      <c r="M83" s="12" t="n">
+      <c r="M84" s="12" t="n">
         <v>17164.82</v>
-      </c>
-      <c r="N83" s="12" t="n"/>
-      <c r="O83" s="12" t="n"/>
-      <c r="P83" s="12" t="n"/>
-      <c r="Q83" s="12" t="n">
-        <v>87650.96000000001</v>
-      </c>
-      <c r="R83" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" outlineLevel="2">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B84" s="11" t="inlineStr">
-        <is>
-          <t>Reefi</t>
-        </is>
-      </c>
-      <c r="C84" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F84" s="11" t="n"/>
-      <c r="G84" s="12" t="n"/>
-      <c r="H84" s="12" t="n">
-        <v>7960.01</v>
-      </c>
-      <c r="I84" s="12" t="n">
-        <v>16919.59</v>
-      </c>
-      <c r="J84" s="12" t="n">
-        <v>7725</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>17372.35</v>
-      </c>
-      <c r="L84" s="12" t="n">
-        <v>7113</v>
-      </c>
-      <c r="M84" s="12" t="n">
-        <v>10864.82</v>
       </c>
       <c r="N84" s="12" t="n"/>
       <c r="O84" s="12" t="n"/>
       <c r="P84" s="12" t="n"/>
       <c r="Q84" s="12" t="n">
+        <v>87650.96000000001</v>
+      </c>
+      <c r="R84" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" outlineLevel="2">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>Reefi</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>Jahez</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="n"/>
+      <c r="G85" s="12" t="n"/>
+      <c r="H85" s="12" t="n">
+        <v>7960.01</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>16919.59</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>7725</v>
+      </c>
+      <c r="K85" s="12" t="n">
+        <v>17372.35</v>
+      </c>
+      <c r="L85" s="12" t="n">
+        <v>7113</v>
+      </c>
+      <c r="M85" s="12" t="n">
+        <v>10864.82</v>
+      </c>
+      <c r="N85" s="12" t="n"/>
+      <c r="O85" s="12" t="n"/>
+      <c r="P85" s="12" t="n"/>
+      <c r="Q85" s="12" t="n">
         <v>67954.77</v>
       </c>
-      <c r="R84" s="3" t="inlineStr">
+      <c r="R85" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="85" outlineLevel="2">
-      <c r="A85" s="13" t="inlineStr">
+    <row r="86" outlineLevel="2">
+      <c r="A86" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B85" s="13" t="inlineStr">
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>Reefi ≈</t>
         </is>
       </c>
-      <c r="C85" s="13" t="inlineStr">
+      <c r="C86" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D85" s="13" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E85" s="13" t="inlineStr">
+      <c r="E86" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F85" s="13" t="inlineStr">
+      <c r="F86" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G85" s="14" t="n"/>
-      <c r="H85" s="14" t="n"/>
-      <c r="I85" s="14" t="n">
+      <c r="G86" s="14" t="n"/>
+      <c r="H86" s="14" t="n"/>
+      <c r="I86" s="14" t="n">
         <v>357.85</v>
       </c>
-      <c r="J85" s="14" t="n">
+      <c r="J86" s="14" t="n">
         <v>154.5</v>
       </c>
-      <c r="K85" s="14" t="n">
+      <c r="K86" s="14" t="n">
         <v>347.45</v>
       </c>
-      <c r="L85" s="14" t="n">
+      <c r="L86" s="14" t="n">
         <v>137.56</v>
       </c>
-      <c r="M85" s="14" t="n">
+      <c r="M86" s="14" t="n">
         <v>222.77</v>
       </c>
-      <c r="N85" s="14" t="n"/>
-      <c r="O85" s="14" t="n"/>
-      <c r="P85" s="14" t="n"/>
-      <c r="Q85" s="14" t="n">
+      <c r="N86" s="14" t="n"/>
+      <c r="O86" s="14" t="n"/>
+      <c r="P86" s="14" t="n"/>
+      <c r="Q86" s="14" t="n">
         <v>1220.13</v>
       </c>
-      <c r="R85" s="3" t="inlineStr">
+      <c r="R86" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="86" outlineLevel="2">
-      <c r="A86" s="11" t="inlineStr">
+    <row r="87" outlineLevel="2">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>Reefi</t>
         </is>
       </c>
-      <c r="C86" s="11" t="inlineStr">
+      <c r="C87" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D86" s="11" t="inlineStr">
+      <c r="D87" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E86" s="11" t="inlineStr">
+      <c r="E87" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F86" s="11" t="n"/>
-      <c r="G86" s="12" t="n">
+      <c r="F87" s="11" t="n"/>
+      <c r="G87" s="12" t="n">
         <v>1949.46</v>
       </c>
-      <c r="H86" s="12" t="n">
+      <c r="H87" s="12" t="n">
         <v>3732.18</v>
       </c>
-      <c r="I86" s="12" t="n">
+      <c r="I87" s="12" t="n">
         <v>891.4</v>
       </c>
-      <c r="J86" s="12" t="n">
+      <c r="J87" s="12" t="n">
         <v>884.1</v>
       </c>
-      <c r="K86" s="12" t="n">
+      <c r="K87" s="12" t="n">
         <v>1210.55</v>
       </c>
-      <c r="L86" s="12" t="n">
+      <c r="L87" s="12" t="n">
         <v>4728.5</v>
       </c>
-      <c r="M86" s="12" t="n">
+      <c r="M87" s="12" t="n">
         <v>6300</v>
       </c>
-      <c r="N86" s="12" t="n"/>
-      <c r="O86" s="12" t="n"/>
-      <c r="P86" s="12" t="n"/>
-      <c r="Q86" s="12" t="n">
+      <c r="N87" s="12" t="n"/>
+      <c r="O87" s="12" t="n"/>
+      <c r="P87" s="12" t="n"/>
+      <c r="Q87" s="12" t="n">
         <v>19696.19</v>
       </c>
-      <c r="R86" s="3" t="inlineStr">
+      <c r="R87" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="87" outlineLevel="2">
-      <c r="A87" s="13" t="inlineStr">
+    <row r="88" outlineLevel="2">
+      <c r="A88" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B87" s="13" t="inlineStr">
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>Reefi ≈</t>
         </is>
       </c>
-      <c r="C87" s="13" t="inlineStr">
+      <c r="C88" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D87" s="13" t="inlineStr">
+      <c r="D88" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E87" s="13" t="inlineStr">
+      <c r="E88" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F87" s="13" t="inlineStr">
+      <c r="F88" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G87" s="14" t="n"/>
-      <c r="H87" s="14" t="n"/>
-      <c r="I87" s="14" t="n">
+      <c r="G88" s="14" t="n"/>
+      <c r="H88" s="14" t="n"/>
+      <c r="I88" s="14" t="n">
         <v>23.07</v>
       </c>
-      <c r="J87" s="14" t="n">
+      <c r="J88" s="14" t="n">
         <v>53.14</v>
       </c>
-      <c r="K87" s="14" t="n">
+      <c r="K88" s="14" t="n">
         <v>25.79</v>
       </c>
-      <c r="L87" s="14" t="n">
+      <c r="L88" s="14" t="n">
         <v>89.58</v>
       </c>
-      <c r="M87" s="14" t="n">
+      <c r="M88" s="14" t="n">
         <v>127.37</v>
       </c>
-      <c r="N87" s="14" t="n"/>
-      <c r="O87" s="14" t="n"/>
-      <c r="P87" s="14" t="n"/>
-      <c r="Q87" s="14" t="n">
+      <c r="N88" s="14" t="n"/>
+      <c r="O88" s="14" t="n"/>
+      <c r="P88" s="14" t="n"/>
+      <c r="Q88" s="14" t="n">
         <v>318.95</v>
       </c>
-      <c r="R87" s="3" t="inlineStr">
+      <c r="R88" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="88" outlineLevel="1">
-      <c r="A88" s="11" t="inlineStr">
+    <row r="89" outlineLevel="1">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>brio</t>
         </is>
       </c>
-      <c r="C88" s="11" t="n"/>
-      <c r="D88" s="11" t="inlineStr">
+      <c r="C89" s="11" t="n"/>
+      <c r="D89" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E88" s="11" t="n"/>
-      <c r="F88" s="11" t="n"/>
-      <c r="G88" s="12" t="n"/>
-      <c r="H88" s="12" t="n">
-        <v>1343.45</v>
-      </c>
-      <c r="I88" s="12" t="n">
-        <v>2456.81</v>
-      </c>
-      <c r="J88" s="12" t="n"/>
-      <c r="K88" s="12" t="n">
-        <v>1677.37</v>
-      </c>
-      <c r="L88" s="12" t="n"/>
-      <c r="M88" s="12" t="n">
-        <v>896.39</v>
-      </c>
-      <c r="N88" s="12" t="n"/>
-      <c r="O88" s="12" t="n"/>
-      <c r="P88" s="12" t="n"/>
-      <c r="Q88" s="12" t="n">
-        <v>6374.02</v>
-      </c>
-      <c r="R88" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" outlineLevel="2">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t>brio</t>
-        </is>
-      </c>
-      <c r="C89" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E89" s="11" t="n"/>
       <c r="F89" s="11" t="n"/>
       <c r="G89" s="12" t="n"/>
       <c r="H89" s="12" t="n">
@@ -9448,249 +9450,245 @@
         <v>1677.37</v>
       </c>
       <c r="L89" s="12" t="n"/>
-      <c r="M89" s="12" t="n"/>
+      <c r="M89" s="12" t="n">
+        <v>896.39</v>
+      </c>
       <c r="N89" s="12" t="n"/>
       <c r="O89" s="12" t="n"/>
       <c r="P89" s="12" t="n"/>
       <c r="Q89" s="12" t="n">
+        <v>6374.02</v>
+      </c>
+      <c r="R89" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" outlineLevel="2">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>brio</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>Jahez</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="n"/>
+      <c r="G90" s="12" t="n"/>
+      <c r="H90" s="12" t="n">
+        <v>1343.45</v>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>2456.81</v>
+      </c>
+      <c r="J90" s="12" t="n"/>
+      <c r="K90" s="12" t="n">
+        <v>1677.37</v>
+      </c>
+      <c r="L90" s="12" t="n"/>
+      <c r="M90" s="12" t="n"/>
+      <c r="N90" s="12" t="n"/>
+      <c r="O90" s="12" t="n"/>
+      <c r="P90" s="12" t="n"/>
+      <c r="Q90" s="12" t="n">
         <v>5477.63</v>
       </c>
-      <c r="R89" s="3" t="inlineStr">
+      <c r="R90" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="90" outlineLevel="2">
-      <c r="A90" s="13" t="inlineStr">
+    <row r="91" outlineLevel="2">
+      <c r="A91" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B90" s="13" t="inlineStr">
+      <c r="B91" s="13" t="inlineStr">
         <is>
           <t>brio ≈</t>
         </is>
       </c>
-      <c r="C90" s="13" t="inlineStr">
+      <c r="C91" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D90" s="13" t="inlineStr">
+      <c r="D91" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E90" s="13" t="inlineStr">
+      <c r="E91" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F90" s="13" t="inlineStr">
+      <c r="F91" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G90" s="14" t="n"/>
-      <c r="H90" s="14" t="n"/>
-      <c r="I90" s="14" t="n">
+      <c r="G91" s="14" t="n"/>
+      <c r="H91" s="14" t="n"/>
+      <c r="I91" s="14" t="n">
         <v>51.96</v>
       </c>
-      <c r="J90" s="14" t="n"/>
-      <c r="K90" s="14" t="n">
+      <c r="J91" s="14" t="n"/>
+      <c r="K91" s="14" t="n">
         <v>33.55</v>
       </c>
-      <c r="L90" s="14" t="n"/>
-      <c r="M90" s="14" t="n"/>
-      <c r="N90" s="14" t="n"/>
-      <c r="O90" s="14" t="n"/>
-      <c r="P90" s="14" t="n"/>
-      <c r="Q90" s="14" t="n">
+      <c r="L91" s="14" t="n"/>
+      <c r="M91" s="14" t="n"/>
+      <c r="N91" s="14" t="n"/>
+      <c r="O91" s="14" t="n"/>
+      <c r="P91" s="14" t="n"/>
+      <c r="Q91" s="14" t="n">
         <v>85.51000000000001</v>
       </c>
-      <c r="R90" s="3" t="inlineStr">
+      <c r="R91" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="91" outlineLevel="2">
-      <c r="A91" s="11" t="inlineStr">
+    <row r="92" outlineLevel="2">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>brio</t>
         </is>
       </c>
-      <c r="C91" s="11" t="inlineStr">
+      <c r="C92" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D91" s="11" t="inlineStr">
+      <c r="D92" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E91" s="11" t="inlineStr">
+      <c r="E92" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F91" s="11" t="n"/>
-      <c r="G91" s="12" t="n"/>
-      <c r="H91" s="12" t="n"/>
-      <c r="I91" s="12" t="n"/>
-      <c r="J91" s="12" t="n"/>
-      <c r="K91" s="12" t="n"/>
-      <c r="L91" s="12" t="n"/>
-      <c r="M91" s="12" t="n">
+      <c r="F92" s="11" t="n"/>
+      <c r="G92" s="12" t="n"/>
+      <c r="H92" s="12" t="n"/>
+      <c r="I92" s="12" t="n"/>
+      <c r="J92" s="12" t="n"/>
+      <c r="K92" s="12" t="n"/>
+      <c r="L92" s="12" t="n"/>
+      <c r="M92" s="12" t="n">
         <v>896.39</v>
       </c>
-      <c r="N91" s="12" t="n"/>
-      <c r="O91" s="12" t="n"/>
-      <c r="P91" s="12" t="n"/>
-      <c r="Q91" s="12" t="n">
+      <c r="N92" s="12" t="n"/>
+      <c r="O92" s="12" t="n"/>
+      <c r="P92" s="12" t="n"/>
+      <c r="Q92" s="12" t="n">
         <v>896.39</v>
       </c>
-      <c r="R91" s="3" t="inlineStr">
+      <c r="R92" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="92" outlineLevel="2">
-      <c r="A92" s="13" t="inlineStr">
+    <row r="93" outlineLevel="2">
+      <c r="A93" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B92" s="13" t="inlineStr">
+      <c r="B93" s="13" t="inlineStr">
         <is>
           <t>brio ≈</t>
         </is>
       </c>
-      <c r="C92" s="13" t="inlineStr">
+      <c r="C93" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D92" s="13" t="inlineStr">
+      <c r="D93" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E92" s="13" t="inlineStr">
+      <c r="E93" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F92" s="13" t="inlineStr">
+      <c r="F93" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G92" s="14" t="n"/>
-      <c r="H92" s="14" t="n"/>
-      <c r="I92" s="14" t="n"/>
-      <c r="J92" s="14" t="n"/>
-      <c r="K92" s="14" t="n"/>
-      <c r="L92" s="14" t="n"/>
-      <c r="M92" s="14" t="n">
+      <c r="G93" s="14" t="n"/>
+      <c r="H93" s="14" t="n"/>
+      <c r="I93" s="14" t="n"/>
+      <c r="J93" s="14" t="n"/>
+      <c r="K93" s="14" t="n"/>
+      <c r="L93" s="14" t="n"/>
+      <c r="M93" s="14" t="n">
         <v>18.12</v>
       </c>
-      <c r="N92" s="14" t="n"/>
-      <c r="O92" s="14" t="n"/>
-      <c r="P92" s="14" t="n"/>
-      <c r="Q92" s="14" t="n">
+      <c r="N93" s="14" t="n"/>
+      <c r="O93" s="14" t="n"/>
+      <c r="P93" s="14" t="n"/>
+      <c r="Q93" s="14" t="n">
         <v>18.12</v>
       </c>
-      <c r="R92" s="3" t="inlineStr">
+      <c r="R93" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="93" outlineLevel="1">
-      <c r="A93" s="11" t="inlineStr">
+    <row r="94" outlineLevel="1">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B93" s="11" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>circles</t>
         </is>
       </c>
-      <c r="C93" s="11" t="n"/>
-      <c r="D93" s="11" t="inlineStr">
+      <c r="C94" s="11" t="n"/>
+      <c r="D94" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E93" s="11" t="n"/>
-      <c r="F93" s="11" t="n"/>
-      <c r="G93" s="12" t="n"/>
-      <c r="H93" s="12" t="n">
-        <v>269.57</v>
-      </c>
-      <c r="I93" s="12" t="n">
-        <v>310</v>
-      </c>
-      <c r="J93" s="12" t="n">
-        <v>300</v>
-      </c>
-      <c r="K93" s="12" t="n">
-        <v>330</v>
-      </c>
-      <c r="L93" s="12" t="n">
-        <v>426</v>
-      </c>
-      <c r="M93" s="12" t="n">
-        <v>668</v>
-      </c>
-      <c r="N93" s="12" t="n"/>
-      <c r="O93" s="12" t="n"/>
-      <c r="P93" s="12" t="n"/>
-      <c r="Q93" s="12" t="n">
-        <v>2303.57</v>
-      </c>
-      <c r="R93" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" outlineLevel="2">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="inlineStr">
-        <is>
-          <t>circles</t>
-        </is>
-      </c>
-      <c r="C94" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D94" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E94" s="11" t="n"/>
       <c r="F94" s="11" t="n"/>
       <c r="G94" s="12" t="n"/>
       <c r="H94" s="12" t="n">
@@ -9706,7 +9704,7 @@
         <v>330</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="M94" s="12" t="n">
         <v>668</v>
@@ -9715,256 +9713,256 @@
       <c r="O94" s="12" t="n"/>
       <c r="P94" s="12" t="n"/>
       <c r="Q94" s="12" t="n">
+        <v>2303.57</v>
+      </c>
+      <c r="R94" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" outlineLevel="2">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>circles</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>Jahez</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="n"/>
+      <c r="G95" s="12" t="n"/>
+      <c r="H95" s="12" t="n">
+        <v>269.57</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <v>310</v>
+      </c>
+      <c r="J95" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="K95" s="12" t="n">
+        <v>330</v>
+      </c>
+      <c r="L95" s="12" t="n">
+        <v>378</v>
+      </c>
+      <c r="M95" s="12" t="n">
+        <v>668</v>
+      </c>
+      <c r="N95" s="12" t="n"/>
+      <c r="O95" s="12" t="n"/>
+      <c r="P95" s="12" t="n"/>
+      <c r="Q95" s="12" t="n">
         <v>2255.57</v>
       </c>
-      <c r="R94" s="3" t="inlineStr">
+      <c r="R95" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="95" outlineLevel="2">
-      <c r="A95" s="13" t="inlineStr">
+    <row r="96" outlineLevel="2">
+      <c r="A96" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B95" s="13" t="inlineStr">
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>circles ≈</t>
         </is>
       </c>
-      <c r="C95" s="13" t="inlineStr">
+      <c r="C96" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D95" s="13" t="inlineStr">
+      <c r="D96" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E95" s="13" t="inlineStr">
+      <c r="E96" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F95" s="13" t="inlineStr">
+      <c r="F96" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G95" s="14" t="n"/>
-      <c r="H95" s="14" t="n"/>
-      <c r="I95" s="14" t="n">
+      <c r="G96" s="14" t="n"/>
+      <c r="H96" s="14" t="n"/>
+      <c r="I96" s="14" t="n">
         <v>6.56</v>
       </c>
-      <c r="J95" s="14" t="n">
+      <c r="J96" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="K95" s="14" t="n">
+      <c r="K96" s="14" t="n">
         <v>6.6</v>
       </c>
-      <c r="L95" s="14" t="n">
+      <c r="L96" s="14" t="n">
         <v>7.31</v>
       </c>
-      <c r="M95" s="14" t="n">
+      <c r="M96" s="14" t="n">
         <v>13.7</v>
       </c>
-      <c r="N95" s="14" t="n"/>
-      <c r="O95" s="14" t="n"/>
-      <c r="P95" s="14" t="n"/>
-      <c r="Q95" s="14" t="n">
+      <c r="N96" s="14" t="n"/>
+      <c r="O96" s="14" t="n"/>
+      <c r="P96" s="14" t="n"/>
+      <c r="Q96" s="14" t="n">
         <v>40.16</v>
       </c>
-      <c r="R95" s="3" t="inlineStr">
+      <c r="R96" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="96" outlineLevel="2">
-      <c r="A96" s="11" t="inlineStr">
+    <row r="97" outlineLevel="2">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>circles</t>
         </is>
       </c>
-      <c r="C96" s="11" t="inlineStr">
+      <c r="C97" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D96" s="11" t="inlineStr">
+      <c r="D97" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E96" s="11" t="inlineStr">
+      <c r="E97" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F96" s="11" t="n"/>
-      <c r="G96" s="12" t="n"/>
-      <c r="H96" s="12" t="n"/>
-      <c r="I96" s="12" t="n"/>
-      <c r="J96" s="12" t="n"/>
-      <c r="K96" s="12" t="n"/>
-      <c r="L96" s="12" t="n">
+      <c r="F97" s="11" t="n"/>
+      <c r="G97" s="12" t="n"/>
+      <c r="H97" s="12" t="n"/>
+      <c r="I97" s="12" t="n"/>
+      <c r="J97" s="12" t="n"/>
+      <c r="K97" s="12" t="n"/>
+      <c r="L97" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="M96" s="12" t="n"/>
-      <c r="N96" s="12" t="n"/>
-      <c r="O96" s="12" t="n"/>
-      <c r="P96" s="12" t="n"/>
-      <c r="Q96" s="12" t="n">
+      <c r="M97" s="12" t="n"/>
+      <c r="N97" s="12" t="n"/>
+      <c r="O97" s="12" t="n"/>
+      <c r="P97" s="12" t="n"/>
+      <c r="Q97" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="R96" s="3" t="inlineStr">
+      <c r="R97" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="97" outlineLevel="2">
-      <c r="A97" s="13" t="inlineStr">
+    <row r="98" outlineLevel="2">
+      <c r="A98" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B97" s="13" t="inlineStr">
+      <c r="B98" s="13" t="inlineStr">
         <is>
           <t>circles ≈</t>
         </is>
       </c>
-      <c r="C97" s="13" t="inlineStr">
+      <c r="C98" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D97" s="13" t="inlineStr">
+      <c r="D98" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E97" s="13" t="inlineStr">
+      <c r="E98" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F97" s="13" t="inlineStr">
+      <c r="F98" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G97" s="14" t="n"/>
-      <c r="H97" s="14" t="n"/>
-      <c r="I97" s="14" t="n"/>
-      <c r="J97" s="14" t="n"/>
-      <c r="K97" s="14" t="n"/>
-      <c r="L97" s="14" t="n">
+      <c r="G98" s="14" t="n"/>
+      <c r="H98" s="14" t="n"/>
+      <c r="I98" s="14" t="n"/>
+      <c r="J98" s="14" t="n"/>
+      <c r="K98" s="14" t="n"/>
+      <c r="L98" s="14" t="n">
         <v>0.91</v>
       </c>
-      <c r="M97" s="14" t="n"/>
-      <c r="N97" s="14" t="n"/>
-      <c r="O97" s="14" t="n"/>
-      <c r="P97" s="14" t="n"/>
-      <c r="Q97" s="14" t="n">
+      <c r="M98" s="14" t="n"/>
+      <c r="N98" s="14" t="n"/>
+      <c r="O98" s="14" t="n"/>
+      <c r="P98" s="14" t="n"/>
+      <c r="Q98" s="14" t="n">
         <v>0.91</v>
       </c>
-      <c r="R97" s="3" t="inlineStr">
+      <c r="R98" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="98" outlineLevel="1">
-      <c r="A98" s="11" t="inlineStr">
+    <row r="99" outlineLevel="1">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>labelle</t>
         </is>
       </c>
-      <c r="C98" s="11" t="n"/>
-      <c r="D98" s="11" t="inlineStr">
+      <c r="C99" s="11" t="n"/>
+      <c r="D99" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E98" s="11" t="n"/>
-      <c r="F98" s="11" t="n"/>
-      <c r="G98" s="12" t="n">
+      <c r="E99" s="11" t="n"/>
+      <c r="F99" s="11" t="n"/>
+      <c r="G99" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="H98" s="12" t="n">
+      <c r="H99" s="12" t="n">
         <v>7203.2</v>
-      </c>
-      <c r="I98" s="12" t="n">
-        <v>8006.86</v>
-      </c>
-      <c r="J98" s="12" t="n">
-        <v>647.96</v>
-      </c>
-      <c r="K98" s="12" t="n">
-        <v>7216.83</v>
-      </c>
-      <c r="L98" s="12" t="n">
-        <v>3410.26</v>
-      </c>
-      <c r="M98" s="12" t="n">
-        <v>2723</v>
-      </c>
-      <c r="N98" s="12" t="n"/>
-      <c r="O98" s="12" t="n"/>
-      <c r="P98" s="12" t="n"/>
-      <c r="Q98" s="12" t="n">
-        <v>29406.11</v>
-      </c>
-      <c r="R98" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" outlineLevel="2">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B99" s="11" t="inlineStr">
-        <is>
-          <t>labelle</t>
-        </is>
-      </c>
-      <c r="C99" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D99" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E99" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F99" s="11" t="n"/>
-      <c r="G99" s="12" t="n"/>
-      <c r="H99" s="12" t="n">
-        <v>5377.58</v>
       </c>
       <c r="I99" s="12" t="n">
         <v>8006.86</v>
@@ -9976,7 +9974,7 @@
         <v>7216.83</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>3072</v>
+        <v>3410.26</v>
       </c>
       <c r="M99" s="12" t="n">
         <v>2723</v>
@@ -9985,227 +9983,233 @@
       <c r="O99" s="12" t="n"/>
       <c r="P99" s="12" t="n"/>
       <c r="Q99" s="12" t="n">
+        <v>29406.11</v>
+      </c>
+      <c r="R99" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" outlineLevel="2">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>labelle</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>Jahez</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="n"/>
+      <c r="G100" s="12" t="n"/>
+      <c r="H100" s="12" t="n">
+        <v>5377.58</v>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>8006.86</v>
+      </c>
+      <c r="J100" s="12" t="n">
+        <v>647.96</v>
+      </c>
+      <c r="K100" s="12" t="n">
+        <v>7216.83</v>
+      </c>
+      <c r="L100" s="12" t="n">
+        <v>3072</v>
+      </c>
+      <c r="M100" s="12" t="n">
+        <v>2723</v>
+      </c>
+      <c r="N100" s="12" t="n"/>
+      <c r="O100" s="12" t="n"/>
+      <c r="P100" s="12" t="n"/>
+      <c r="Q100" s="12" t="n">
         <v>27044.23</v>
       </c>
-      <c r="R99" s="3" t="inlineStr">
+      <c r="R100" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="100" outlineLevel="2">
-      <c r="A100" s="13" t="inlineStr">
+    <row r="101" outlineLevel="2">
+      <c r="A101" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B100" s="13" t="inlineStr">
+      <c r="B101" s="13" t="inlineStr">
         <is>
           <t>labelle ≈</t>
         </is>
       </c>
-      <c r="C100" s="13" t="inlineStr">
+      <c r="C101" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D100" s="13" t="inlineStr">
+      <c r="D101" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E100" s="13" t="inlineStr">
+      <c r="E101" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F100" s="13" t="inlineStr">
+      <c r="F101" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G100" s="14" t="n"/>
-      <c r="H100" s="14" t="n"/>
-      <c r="I100" s="14" t="n">
+      <c r="G101" s="14" t="n"/>
+      <c r="H101" s="14" t="n"/>
+      <c r="I101" s="14" t="n">
         <v>169.35</v>
       </c>
-      <c r="J100" s="14" t="n">
+      <c r="J101" s="14" t="n">
         <v>12.96</v>
       </c>
-      <c r="K100" s="14" t="n">
+      <c r="K101" s="14" t="n">
         <v>144.34</v>
       </c>
-      <c r="L100" s="14" t="n">
+      <c r="L101" s="14" t="n">
         <v>59.41</v>
       </c>
-      <c r="M100" s="14" t="n">
+      <c r="M101" s="14" t="n">
         <v>55.83</v>
       </c>
-      <c r="N100" s="14" t="n"/>
-      <c r="O100" s="14" t="n"/>
-      <c r="P100" s="14" t="n"/>
-      <c r="Q100" s="14" t="n">
+      <c r="N101" s="14" t="n"/>
+      <c r="O101" s="14" t="n"/>
+      <c r="P101" s="14" t="n"/>
+      <c r="Q101" s="14" t="n">
         <v>441.89</v>
       </c>
-      <c r="R100" s="3" t="inlineStr">
+      <c r="R101" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="101" outlineLevel="2">
-      <c r="A101" s="11" t="inlineStr">
+    <row r="102" outlineLevel="2">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>labelle</t>
         </is>
       </c>
-      <c r="C101" s="11" t="inlineStr">
+      <c r="C102" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D101" s="11" t="inlineStr">
+      <c r="D102" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E101" s="11" t="inlineStr">
+      <c r="E102" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F101" s="11" t="n"/>
-      <c r="G101" s="12" t="n">
+      <c r="F102" s="11" t="n"/>
+      <c r="G102" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="H101" s="12" t="n">
+      <c r="H102" s="12" t="n">
         <v>1825.62</v>
       </c>
-      <c r="I101" s="12" t="n"/>
-      <c r="J101" s="12" t="n"/>
-      <c r="K101" s="12" t="n"/>
-      <c r="L101" s="12" t="n">
+      <c r="I102" s="12" t="n"/>
+      <c r="J102" s="12" t="n"/>
+      <c r="K102" s="12" t="n"/>
+      <c r="L102" s="12" t="n">
         <v>338.26</v>
       </c>
-      <c r="M101" s="12" t="n"/>
-      <c r="N101" s="12" t="n"/>
-      <c r="O101" s="12" t="n"/>
-      <c r="P101" s="12" t="n"/>
-      <c r="Q101" s="12" t="n">
+      <c r="M102" s="12" t="n"/>
+      <c r="N102" s="12" t="n"/>
+      <c r="O102" s="12" t="n"/>
+      <c r="P102" s="12" t="n"/>
+      <c r="Q102" s="12" t="n">
         <v>2361.88</v>
       </c>
-      <c r="R101" s="3" t="inlineStr">
+      <c r="R102" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="102" outlineLevel="2">
-      <c r="A102" s="13" t="inlineStr">
+    <row r="103" outlineLevel="2">
+      <c r="A103" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B102" s="13" t="inlineStr">
+      <c r="B103" s="13" t="inlineStr">
         <is>
           <t>labelle ≈</t>
         </is>
       </c>
-      <c r="C102" s="13" t="inlineStr">
+      <c r="C103" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D102" s="13" t="inlineStr">
+      <c r="D103" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E102" s="13" t="inlineStr">
+      <c r="E103" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F102" s="13" t="inlineStr">
+      <c r="F103" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G102" s="14" t="n"/>
-      <c r="H102" s="14" t="n"/>
-      <c r="I102" s="14" t="n"/>
-      <c r="J102" s="14" t="n"/>
-      <c r="K102" s="14" t="n"/>
-      <c r="L102" s="14" t="n">
+      <c r="G103" s="14" t="n"/>
+      <c r="H103" s="14" t="n"/>
+      <c r="I103" s="14" t="n"/>
+      <c r="J103" s="14" t="n"/>
+      <c r="K103" s="14" t="n"/>
+      <c r="L103" s="14" t="n">
         <v>6.41</v>
       </c>
-      <c r="M102" s="14" t="n"/>
-      <c r="N102" s="14" t="n"/>
-      <c r="O102" s="14" t="n"/>
-      <c r="P102" s="14" t="n"/>
-      <c r="Q102" s="14" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="R102" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" outlineLevel="1">
-      <c r="A103" s="13" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B103" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C103" s="13" t="n"/>
-      <c r="D103" s="13" t="inlineStr">
-        <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E103" s="13" t="n"/>
-      <c r="F103" s="13" t="n"/>
-      <c r="G103" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H103" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I103" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J103" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="K103" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L103" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M103" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="M103" s="14" t="n"/>
       <c r="N103" s="14" t="n"/>
       <c r="O103" s="14" t="n"/>
       <c r="P103" s="14" t="n"/>
       <c r="Q103" s="14" t="n">
-        <v>35000</v>
+        <v>6.41</v>
       </c>
       <c r="R103" s="3" t="inlineStr">
         <is>
-          <t>Wafeq invoice export</t>
+          <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
@@ -10223,983 +10227,977 @@
       <c r="C104" s="13" t="n"/>
       <c r="D104" s="13" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>Monthly fee</t>
         </is>
       </c>
       <c r="E104" s="13" t="n"/>
       <c r="F104" s="13" t="n"/>
-      <c r="G104" s="14" t="n"/>
-      <c r="H104" s="14" t="n"/>
+      <c r="G104" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H104" s="14" t="n">
+        <v>5000</v>
+      </c>
       <c r="I104" s="14" t="n">
-        <v>-2050.2</v>
+        <v>5000</v>
       </c>
       <c r="J104" s="14" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="K104" s="14" t="n"/>
-      <c r="L104" s="14" t="n"/>
-      <c r="M104" s="14" t="n"/>
+        <v>5000</v>
+      </c>
+      <c r="K104" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L104" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M104" s="14" t="n">
+        <v>5000</v>
+      </c>
       <c r="N104" s="14" t="n"/>
       <c r="O104" s="14" t="n"/>
       <c r="P104" s="14" t="n"/>
       <c r="Q104" s="14" t="n">
+        <v>35000</v>
+      </c>
+      <c r="R104" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" outlineLevel="1">
+      <c r="A105" s="13" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C105" s="13" t="n"/>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="n"/>
+      <c r="F105" s="13" t="n"/>
+      <c r="G105" s="14" t="n"/>
+      <c r="H105" s="14" t="n"/>
+      <c r="I105" s="14" t="n">
+        <v>-2050.2</v>
+      </c>
+      <c r="J105" s="14" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="K105" s="14" t="n"/>
+      <c r="L105" s="14" t="n"/>
+      <c r="M105" s="14" t="n"/>
+      <c r="N105" s="14" t="n"/>
+      <c r="O105" s="14" t="n"/>
+      <c r="P105" s="14" t="n"/>
+      <c r="Q105" s="14" t="n">
         <v>-4550.2</v>
       </c>
-      <c r="R104" s="3" t="inlineStr">
+      <c r="R105" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · setup-period 50% AM fee / agreed reduction / pricing error</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
         <is>
           <t>Rimath  (churned 2026-06)</t>
         </is>
       </c>
-      <c r="B106" s="9" t="n"/>
-      <c r="C106" s="9" t="n"/>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="B107" s="9" t="n"/>
+      <c r="C107" s="9" t="n"/>
+      <c r="D107" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E106" s="9" t="n"/>
-      <c r="F106" s="9" t="n"/>
-      <c r="G106" s="10" t="n">
+      <c r="E107" s="9" t="n"/>
+      <c r="F107" s="9" t="n"/>
+      <c r="G107" s="10" t="n">
         <v>3743.36</v>
       </c>
-      <c r="H106" s="10" t="n">
+      <c r="H107" s="10" t="n">
         <v>2998.75</v>
       </c>
-      <c r="I106" s="10" t="n">
+      <c r="I107" s="10" t="n">
         <v>3561.57</v>
       </c>
-      <c r="J106" s="10" t="n">
+      <c r="J107" s="10" t="n">
         <v>4753.24</v>
       </c>
-      <c r="K106" s="10" t="n">
+      <c r="K107" s="10" t="n">
         <v>3970.51</v>
       </c>
-      <c r="L106" s="10" t="n">
+      <c r="L107" s="10" t="n">
         <v>3649.59</v>
       </c>
-      <c r="M106" s="10" t="n">
+      <c r="M107" s="10" t="n">
         <v>3044.62</v>
       </c>
-      <c r="N106" s="10" t="n">
+      <c r="N107" s="10" t="n">
         <v>2819.43</v>
       </c>
-      <c r="O106" s="10" t="n"/>
-      <c r="P106" s="10" t="n"/>
-      <c r="Q106" s="10" t="n">
+      <c r="O107" s="10" t="n"/>
+      <c r="P107" s="10" t="n"/>
+      <c r="Q107" s="10" t="n">
         <v>28541.07</v>
       </c>
-      <c r="R106" s="3" t="inlineStr">
+      <c r="R107" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="107" outlineLevel="1">
-      <c r="A107" s="11" t="inlineStr">
+    <row r="108" outlineLevel="1">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C107" s="11" t="n"/>
-      <c r="D107" s="11" t="inlineStr">
+      <c r="C108" s="11" t="n"/>
+      <c r="D108" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E107" s="11" t="n"/>
-      <c r="F107" s="11" t="n"/>
-      <c r="G107" s="12" t="n">
-        <v>2261.24</v>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>1589.06</v>
-      </c>
-      <c r="I107" s="12" t="n">
-        <v>972.27</v>
-      </c>
-      <c r="J107" s="12" t="n">
-        <v>1792.37</v>
-      </c>
-      <c r="K107" s="12" t="n">
-        <v>2105.88</v>
-      </c>
-      <c r="L107" s="12" t="n">
-        <v>1333.37</v>
-      </c>
-      <c r="M107" s="12" t="n">
-        <v>249.01</v>
-      </c>
-      <c r="N107" s="12" t="n">
-        <v>189</v>
-      </c>
-      <c r="O107" s="12" t="n"/>
-      <c r="P107" s="12" t="n"/>
-      <c r="Q107" s="12" t="n">
-        <v>10492.2</v>
-      </c>
-      <c r="R107" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" outlineLevel="2">
-      <c r="A108" s="11" t="inlineStr">
-        <is>
-          <t>Rimath</t>
-        </is>
-      </c>
-      <c r="B108" s="11" t="inlineStr">
-        <is>
-          <t>O'SO</t>
-        </is>
-      </c>
-      <c r="C108" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D108" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E108" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E108" s="11" t="n"/>
       <c r="F108" s="11" t="n"/>
       <c r="G108" s="12" t="n">
-        <v>1137</v>
+        <v>2261.24</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>327</v>
+        <v>1589.06</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>363.99</v>
+        <v>972.27</v>
       </c>
       <c r="J108" s="12" t="n">
-        <v>681.71</v>
+        <v>1792.37</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>577.73</v>
+        <v>2105.88</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>446.94</v>
+        <v>1333.37</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>129</v>
-      </c>
-      <c r="N108" s="12" t="n"/>
+        <v>249.01</v>
+      </c>
+      <c r="N108" s="12" t="n">
+        <v>189</v>
+      </c>
       <c r="O108" s="12" t="n"/>
       <c r="P108" s="12" t="n"/>
       <c r="Q108" s="12" t="n">
+        <v>10492.2</v>
+      </c>
+      <c r="R108" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" outlineLevel="2">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>Rimath</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>O'SO</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="n"/>
+      <c r="G109" s="12" t="n">
+        <v>1137</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>327</v>
+      </c>
+      <c r="I109" s="12" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="J109" s="12" t="n">
+        <v>681.71</v>
+      </c>
+      <c r="K109" s="12" t="n">
+        <v>577.73</v>
+      </c>
+      <c r="L109" s="12" t="n">
+        <v>446.94</v>
+      </c>
+      <c r="M109" s="12" t="n">
+        <v>129</v>
+      </c>
+      <c r="N109" s="12" t="n"/>
+      <c r="O109" s="12" t="n"/>
+      <c r="P109" s="12" t="n"/>
+      <c r="Q109" s="12" t="n">
         <v>3663.37</v>
       </c>
-      <c r="R108" s="3" t="inlineStr">
+      <c r="R109" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="109" outlineLevel="2">
-      <c r="A109" s="13" t="inlineStr">
+    <row r="110" outlineLevel="2">
+      <c r="A110" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B109" s="13" t="inlineStr">
+      <c r="B110" s="13" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C109" s="13" t="inlineStr">
+      <c r="C110" s="13" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D109" s="13" t="inlineStr">
+      <c r="D110" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E109" s="13" t="inlineStr">
+      <c r="E110" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F109" s="13" t="inlineStr">
+      <c r="F110" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G109" s="14" t="n">
+      <c r="G110" s="14" t="n">
         <v>84.91</v>
       </c>
-      <c r="H109" s="14" t="n">
+      <c r="H110" s="14" t="n">
         <v>22.89</v>
       </c>
-      <c r="I109" s="14" t="n">
+      <c r="I110" s="14" t="n">
         <v>25.48</v>
       </c>
-      <c r="J109" s="14" t="n">
+      <c r="J110" s="14" t="n">
         <v>47.72</v>
       </c>
-      <c r="K109" s="14" t="n">
+      <c r="K110" s="14" t="n">
         <v>41.7</v>
       </c>
-      <c r="L109" s="14" t="n">
+      <c r="L110" s="14" t="n">
         <v>31.29</v>
       </c>
-      <c r="M109" s="14" t="n">
+      <c r="M110" s="14" t="n">
         <v>9.029999999999999</v>
       </c>
-      <c r="N109" s="14" t="n"/>
-      <c r="O109" s="14" t="n"/>
-      <c r="P109" s="14" t="n"/>
-      <c r="Q109" s="14" t="n">
+      <c r="N110" s="14" t="n"/>
+      <c r="O110" s="14" t="n"/>
+      <c r="P110" s="14" t="n"/>
+      <c r="Q110" s="14" t="n">
         <v>263.02</v>
       </c>
-      <c r="R109" s="3" t="inlineStr">
+      <c r="R110" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="110" outlineLevel="2">
-      <c r="A110" s="11" t="inlineStr">
+    <row r="111" outlineLevel="2">
+      <c r="A111" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C110" s="11" t="inlineStr">
+      <c r="C111" s="11" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D110" s="11" t="inlineStr">
+      <c r="D111" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E110" s="11" t="inlineStr">
+      <c r="E111" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F110" s="11" t="n"/>
-      <c r="G110" s="12" t="n">
+      <c r="F111" s="11" t="n"/>
+      <c r="G111" s="12" t="n">
         <v>665.5</v>
       </c>
-      <c r="H110" s="12" t="n">
+      <c r="H111" s="12" t="n">
         <v>670</v>
       </c>
-      <c r="I110" s="12" t="n">
+      <c r="I111" s="12" t="n">
         <v>503.86</v>
       </c>
-      <c r="J110" s="12" t="n">
+      <c r="J111" s="12" t="n">
         <v>161.88</v>
       </c>
-      <c r="K110" s="12" t="n">
+      <c r="K111" s="12" t="n">
         <v>548</v>
       </c>
-      <c r="L110" s="12" t="n">
+      <c r="L111" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="M110" s="12" t="n">
+      <c r="M111" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="N110" s="12" t="n">
+      <c r="N111" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="O110" s="12" t="n"/>
-      <c r="P110" s="12" t="n"/>
-      <c r="Q110" s="12" t="n">
+      <c r="O111" s="12" t="n"/>
+      <c r="P111" s="12" t="n"/>
+      <c r="Q111" s="12" t="n">
         <v>2728.24</v>
       </c>
-      <c r="R110" s="3" t="inlineStr">
+      <c r="R111" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="111" outlineLevel="2">
-      <c r="A111" s="13" t="inlineStr">
+    <row r="112" outlineLevel="2">
+      <c r="A112" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B111" s="13" t="inlineStr">
+      <c r="B112" s="13" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C111" s="13" t="inlineStr">
+      <c r="C112" s="13" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D111" s="13" t="inlineStr">
+      <c r="D112" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E111" s="13" t="inlineStr">
+      <c r="E112" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F111" s="13" t="inlineStr">
+      <c r="F112" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G111" s="14" t="n">
+      <c r="G112" s="14" t="n">
         <v>48.83</v>
       </c>
-      <c r="H111" s="14" t="n">
+      <c r="H112" s="14" t="n">
         <v>46.9</v>
       </c>
-      <c r="I111" s="14" t="n">
+      <c r="I112" s="14" t="n">
         <v>31.49</v>
       </c>
-      <c r="J111" s="14" t="n">
+      <c r="J112" s="14" t="n">
         <v>11.33</v>
       </c>
-      <c r="K111" s="14" t="n">
+      <c r="K112" s="14" t="n">
         <v>38.36</v>
       </c>
-      <c r="L111" s="14" t="n">
+      <c r="L112" s="14" t="n">
         <v>6.51</v>
       </c>
-      <c r="M111" s="14" t="n">
+      <c r="M112" s="14" t="n">
         <v>3.78</v>
       </c>
-      <c r="N111" s="14" t="n">
+      <c r="N112" s="14" t="n">
         <v>1.12</v>
       </c>
-      <c r="O111" s="14" t="n"/>
-      <c r="P111" s="14" t="n"/>
-      <c r="Q111" s="14" t="n">
+      <c r="O112" s="14" t="n"/>
+      <c r="P112" s="14" t="n"/>
+      <c r="Q112" s="14" t="n">
         <v>188.32</v>
       </c>
-      <c r="R111" s="3" t="inlineStr">
+      <c r="R112" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="112" outlineLevel="2">
-      <c r="A112" s="11" t="inlineStr">
+    <row r="113" outlineLevel="2">
+      <c r="A113" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C112" s="11" t="inlineStr">
+      <c r="C113" s="11" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D112" s="11" t="inlineStr">
+      <c r="D113" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E112" s="11" t="inlineStr">
+      <c r="E113" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F112" s="11" t="n"/>
-      <c r="G112" s="12" t="n">
+      <c r="F113" s="11" t="n"/>
+      <c r="G113" s="12" t="n">
         <v>351.34</v>
       </c>
-      <c r="H112" s="12" t="n">
+      <c r="H113" s="12" t="n">
         <v>468.88</v>
       </c>
-      <c r="I112" s="12" t="n">
+      <c r="I113" s="12" t="n">
         <v>104.42</v>
       </c>
-      <c r="J112" s="12" t="n">
+      <c r="J113" s="12" t="n">
         <v>948.78</v>
       </c>
-      <c r="K112" s="12" t="n">
+      <c r="K113" s="12" t="n">
         <v>980.15</v>
       </c>
-      <c r="L112" s="12" t="n">
+      <c r="L113" s="12" t="n">
         <v>405.99</v>
       </c>
-      <c r="M112" s="12" t="n">
+      <c r="M113" s="12" t="n">
         <v>66.01000000000001</v>
       </c>
-      <c r="N112" s="12" t="n"/>
-      <c r="O112" s="12" t="n"/>
-      <c r="P112" s="12" t="n"/>
-      <c r="Q112" s="12" t="n">
+      <c r="N113" s="12" t="n"/>
+      <c r="O113" s="12" t="n"/>
+      <c r="P113" s="12" t="n"/>
+      <c r="Q113" s="12" t="n">
         <v>3325.57</v>
       </c>
-      <c r="R112" s="3" t="inlineStr">
+      <c r="R113" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="113" outlineLevel="2">
-      <c r="A113" s="13" t="inlineStr">
+    <row r="114" outlineLevel="2">
+      <c r="A114" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B113" s="13" t="inlineStr">
+      <c r="B114" s="13" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C113" s="13" t="inlineStr">
+      <c r="C114" s="13" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D113" s="13" t="inlineStr">
+      <c r="D114" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E113" s="13" t="inlineStr">
+      <c r="E114" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F113" s="13" t="inlineStr">
+      <c r="F114" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G113" s="14" t="n">
+      <c r="G114" s="14" t="n">
         <v>24.59</v>
       </c>
-      <c r="H113" s="14" t="n">
+      <c r="H114" s="14" t="n">
         <v>32.83</v>
       </c>
-      <c r="I113" s="14" t="n">
+      <c r="I114" s="14" t="n">
         <v>7.31</v>
       </c>
-      <c r="J113" s="14" t="n">
+      <c r="J114" s="14" t="n">
         <v>66.41</v>
       </c>
-      <c r="K113" s="14" t="n">
+      <c r="K114" s="14" t="n">
         <v>68.62</v>
       </c>
-      <c r="L113" s="14" t="n">
+      <c r="L114" s="14" t="n">
         <v>28.42</v>
       </c>
-      <c r="M113" s="14" t="n">
+      <c r="M114" s="14" t="n">
         <v>16.83</v>
       </c>
-      <c r="N113" s="14" t="n">
+      <c r="N114" s="14" t="n">
         <v>17.95</v>
       </c>
-      <c r="O113" s="14" t="n"/>
-      <c r="P113" s="14" t="n"/>
-      <c r="Q113" s="14" t="n">
+      <c r="O114" s="14" t="n"/>
+      <c r="P114" s="14" t="n"/>
+      <c r="Q114" s="14" t="n">
         <v>262.96</v>
       </c>
-      <c r="R113" s="3" t="inlineStr">
+      <c r="R114" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="114" outlineLevel="2">
-      <c r="A114" s="11" t="inlineStr">
+    <row r="115" outlineLevel="2">
+      <c r="A115" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C114" s="11" t="inlineStr">
+      <c r="C115" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D114" s="11" t="inlineStr">
+      <c r="D115" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E114" s="11" t="inlineStr">
+      <c r="E115" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F114" s="11" t="n"/>
-      <c r="G114" s="12" t="n">
+      <c r="F115" s="11" t="n"/>
+      <c r="G115" s="12" t="n">
         <v>107.4</v>
       </c>
-      <c r="H114" s="12" t="n">
+      <c r="H115" s="12" t="n">
         <v>123.18</v>
       </c>
-      <c r="I114" s="12" t="n"/>
-      <c r="J114" s="12" t="n"/>
-      <c r="K114" s="12" t="n"/>
-      <c r="L114" s="12" t="n">
+      <c r="I115" s="12" t="n"/>
+      <c r="J115" s="12" t="n"/>
+      <c r="K115" s="12" t="n"/>
+      <c r="L115" s="12" t="n">
         <v>387.44</v>
       </c>
-      <c r="M114" s="12" t="n"/>
-      <c r="N114" s="12" t="n">
+      <c r="M115" s="12" t="n"/>
+      <c r="N115" s="12" t="n">
         <v>157</v>
       </c>
-      <c r="O114" s="12" t="n"/>
-      <c r="P114" s="12" t="n"/>
-      <c r="Q114" s="12" t="n">
+      <c r="O115" s="12" t="n"/>
+      <c r="P115" s="12" t="n"/>
+      <c r="Q115" s="12" t="n">
         <v>775.02</v>
       </c>
-      <c r="R114" s="3" t="inlineStr">
+      <c r="R115" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="115" outlineLevel="2">
-      <c r="A115" s="13" t="inlineStr">
+    <row r="116" outlineLevel="2">
+      <c r="A116" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B115" s="13" t="inlineStr">
+      <c r="B116" s="13" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C115" s="13" t="inlineStr">
+      <c r="C116" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D115" s="13" t="inlineStr">
+      <c r="D116" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E115" s="13" t="inlineStr">
+      <c r="E116" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F115" s="13" t="inlineStr">
+      <c r="F116" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G115" s="14" t="n">
+      <c r="G116" s="14" t="n">
         <v>14.07</v>
       </c>
-      <c r="H115" s="14" t="n">
+      <c r="H116" s="14" t="n">
         <v>11.27</v>
       </c>
-      <c r="I115" s="14" t="n">
+      <c r="I116" s="14" t="n">
         <v>2.24</v>
       </c>
-      <c r="J115" s="14" t="n"/>
-      <c r="K115" s="14" t="n">
+      <c r="J116" s="14" t="n"/>
+      <c r="K116" s="14" t="n">
         <v>20.24</v>
       </c>
-      <c r="L115" s="14" t="n">
+      <c r="L116" s="14" t="n">
         <v>30.2</v>
       </c>
-      <c r="M115" s="14" t="n"/>
-      <c r="N115" s="14" t="n">
+      <c r="M116" s="14" t="n"/>
+      <c r="N116" s="14" t="n">
         <v>14.35</v>
       </c>
-      <c r="O115" s="14" t="n"/>
-      <c r="P115" s="14" t="n"/>
-      <c r="Q115" s="14" t="n">
+      <c r="O116" s="14" t="n"/>
+      <c r="P116" s="14" t="n"/>
+      <c r="Q116" s="14" t="n">
         <v>92.37</v>
       </c>
-      <c r="R115" s="3" t="inlineStr">
+      <c r="R116" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="116" outlineLevel="1">
-      <c r="A116" s="11" t="inlineStr">
+    <row r="117" outlineLevel="1">
+      <c r="A117" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C116" s="11" t="n"/>
-      <c r="D116" s="11" t="inlineStr">
+      <c r="C117" s="11" t="n"/>
+      <c r="D117" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E116" s="11" t="n"/>
-      <c r="F116" s="11" t="n"/>
-      <c r="G116" s="12" t="n">
-        <v>11744.34</v>
-      </c>
-      <c r="H116" s="12" t="n">
-        <v>7456.05</v>
-      </c>
-      <c r="I116" s="12" t="n">
-        <v>9033.969999999999</v>
-      </c>
-      <c r="J116" s="12" t="n">
-        <v>26081.7</v>
-      </c>
-      <c r="K116" s="12" t="n">
-        <v>17923.14</v>
-      </c>
-      <c r="L116" s="12" t="n">
-        <v>14640.4</v>
-      </c>
-      <c r="M116" s="12" t="n">
-        <v>6386.02</v>
-      </c>
-      <c r="N116" s="12" t="n">
-        <v>2254</v>
-      </c>
-      <c r="O116" s="12" t="n"/>
-      <c r="P116" s="12" t="n"/>
-      <c r="Q116" s="12" t="n">
-        <v>95519.62</v>
-      </c>
-      <c r="R116" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" outlineLevel="2">
-      <c r="A117" s="11" t="inlineStr">
-        <is>
-          <t>Rimath</t>
-        </is>
-      </c>
-      <c r="B117" s="11" t="inlineStr">
-        <is>
-          <t>Thannah</t>
-        </is>
-      </c>
-      <c r="C117" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D117" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E117" s="11" t="n"/>
       <c r="F117" s="11" t="n"/>
       <c r="G117" s="12" t="n">
-        <v>3133</v>
+        <v>11744.34</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>2398.8</v>
+        <v>7456.05</v>
       </c>
       <c r="I117" s="12" t="n">
-        <v>1021.2</v>
+        <v>9033.969999999999</v>
       </c>
       <c r="J117" s="12" t="n">
-        <v>966.8</v>
+        <v>26081.7</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>3279.4</v>
+        <v>17923.14</v>
       </c>
       <c r="L117" s="12" t="n">
-        <v>2579</v>
+        <v>14640.4</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>3199</v>
+        <v>6386.02</v>
       </c>
       <c r="N117" s="12" t="n">
-        <v>1381</v>
+        <v>2254</v>
       </c>
       <c r="O117" s="12" t="n"/>
       <c r="P117" s="12" t="n"/>
       <c r="Q117" s="12" t="n">
+        <v>95519.62</v>
+      </c>
+      <c r="R117" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" outlineLevel="2">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>Rimath</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>Thannah</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="n"/>
+      <c r="G118" s="12" t="n">
+        <v>3133</v>
+      </c>
+      <c r="H118" s="12" t="n">
+        <v>2398.8</v>
+      </c>
+      <c r="I118" s="12" t="n">
+        <v>1021.2</v>
+      </c>
+      <c r="J118" s="12" t="n">
+        <v>966.8</v>
+      </c>
+      <c r="K118" s="12" t="n">
+        <v>3279.4</v>
+      </c>
+      <c r="L118" s="12" t="n">
+        <v>2579</v>
+      </c>
+      <c r="M118" s="12" t="n">
+        <v>3199</v>
+      </c>
+      <c r="N118" s="12" t="n">
+        <v>1381</v>
+      </c>
+      <c r="O118" s="12" t="n"/>
+      <c r="P118" s="12" t="n"/>
+      <c r="Q118" s="12" t="n">
         <v>17958.2</v>
       </c>
-      <c r="R117" s="3" t="inlineStr">
+      <c r="R118" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="118" outlineLevel="2">
-      <c r="A118" s="13" t="inlineStr">
+    <row r="119" outlineLevel="2">
+      <c r="A119" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B118" s="13" t="inlineStr">
+      <c r="B119" s="13" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C118" s="13" t="inlineStr">
+      <c r="C119" s="13" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D118" s="13" t="inlineStr">
+      <c r="D119" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E118" s="13" t="inlineStr">
+      <c r="E119" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F118" s="13" t="inlineStr">
+      <c r="F119" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G118" s="14" t="n">
+      <c r="G119" s="14" t="n">
         <v>219.87</v>
       </c>
-      <c r="H118" s="14" t="n">
+      <c r="H119" s="14" t="n">
         <v>169.76</v>
       </c>
-      <c r="I118" s="14" t="n">
+      <c r="I119" s="14" t="n">
         <v>71.48</v>
       </c>
-      <c r="J118" s="14" t="n">
+      <c r="J119" s="14" t="n">
         <v>67.63</v>
       </c>
-      <c r="K118" s="14" t="n">
+      <c r="K119" s="14" t="n">
         <v>226.55</v>
       </c>
-      <c r="L118" s="14" t="n">
+      <c r="L119" s="14" t="n">
         <v>183.54</v>
       </c>
-      <c r="M118" s="14" t="n">
+      <c r="M119" s="14" t="n">
         <v>223.93</v>
       </c>
-      <c r="N118" s="14" t="n">
+      <c r="N119" s="14" t="n">
         <v>75.31999999999999</v>
       </c>
-      <c r="O118" s="14" t="n"/>
-      <c r="P118" s="14" t="n"/>
-      <c r="Q118" s="14" t="n">
+      <c r="O119" s="14" t="n"/>
+      <c r="P119" s="14" t="n"/>
+      <c r="Q119" s="14" t="n">
         <v>1238.08</v>
       </c>
-      <c r="R118" s="3" t="inlineStr">
+      <c r="R119" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="119" outlineLevel="2">
-      <c r="A119" s="11" t="inlineStr">
+    <row r="120" outlineLevel="2">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B119" s="11" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C119" s="11" t="inlineStr">
+      <c r="C120" s="11" t="inlineStr">
         <is>
           <t>Hungerstation</t>
         </is>
       </c>
-      <c r="D119" s="11" t="inlineStr">
+      <c r="D120" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E119" s="11" t="inlineStr">
+      <c r="E120" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F119" s="11" t="n"/>
-      <c r="G119" s="12" t="n">
+      <c r="F120" s="11" t="n"/>
+      <c r="G120" s="12" t="n">
         <v>714</v>
       </c>
-      <c r="H119" s="12" t="n">
+      <c r="H120" s="12" t="n">
         <v>339</v>
       </c>
-      <c r="I119" s="12" t="n">
+      <c r="I120" s="12" t="n">
         <v>595</v>
       </c>
-      <c r="J119" s="12" t="n"/>
-      <c r="K119" s="12" t="n"/>
-      <c r="L119" s="12" t="n"/>
-      <c r="M119" s="12" t="n"/>
-      <c r="N119" s="12" t="n"/>
-      <c r="O119" s="12" t="n"/>
-      <c r="P119" s="12" t="n"/>
-      <c r="Q119" s="12" t="n">
+      <c r="J120" s="12" t="n"/>
+      <c r="K120" s="12" t="n"/>
+      <c r="L120" s="12" t="n"/>
+      <c r="M120" s="12" t="n"/>
+      <c r="N120" s="12" t="n"/>
+      <c r="O120" s="12" t="n"/>
+      <c r="P120" s="12" t="n"/>
+      <c r="Q120" s="12" t="n">
         <v>1648</v>
       </c>
-      <c r="R119" s="3" t="inlineStr">
+      <c r="R120" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="120" outlineLevel="2">
-      <c r="A120" s="13" t="inlineStr">
+    <row r="121" outlineLevel="2">
+      <c r="A121" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B120" s="13" t="inlineStr">
+      <c r="B121" s="13" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C120" s="13" t="inlineStr">
+      <c r="C121" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D120" s="13" t="inlineStr">
+      <c r="D121" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E120" s="13" t="inlineStr">
+      <c r="E121" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F120" s="13" t="inlineStr">
+      <c r="F121" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G120" s="14" t="n">
+      <c r="G121" s="14" t="n">
         <v>162.47</v>
       </c>
-      <c r="H120" s="14" t="n">
+      <c r="H121" s="14" t="n">
         <v>101.5</v>
       </c>
-      <c r="I120" s="14" t="n">
+      <c r="I121" s="14" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="J120" s="14" t="n">
+      <c r="J121" s="14" t="n">
         <v>15.6</v>
       </c>
-      <c r="K120" s="14" t="n"/>
-      <c r="L120" s="14" t="n">
+      <c r="K121" s="14" t="n"/>
+      <c r="L121" s="14" t="n">
         <v>6.74</v>
       </c>
-      <c r="M120" s="14" t="n">
+      <c r="M121" s="14" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="N120" s="14" t="n"/>
-      <c r="O120" s="14" t="n"/>
-      <c r="P120" s="14" t="n"/>
-      <c r="Q120" s="14" t="n">
+      <c r="N121" s="14" t="n"/>
+      <c r="O121" s="14" t="n"/>
+      <c r="P121" s="14" t="n"/>
+      <c r="Q121" s="14" t="n">
         <v>369.95</v>
       </c>
-      <c r="R120" s="3" t="inlineStr">
+      <c r="R121" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" outlineLevel="2">
-      <c r="A121" s="11" t="inlineStr">
-        <is>
-          <t>Rimath</t>
-        </is>
-      </c>
-      <c r="B121" s="11" t="inlineStr">
-        <is>
-          <t>Thannah</t>
-        </is>
-      </c>
-      <c r="C121" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F121" s="11" t="n"/>
-      <c r="G121" s="12" t="n">
-        <v>1601</v>
-      </c>
-      <c r="H121" s="12" t="n">
-        <v>869</v>
-      </c>
-      <c r="I121" s="12" t="n">
-        <v>465</v>
-      </c>
-      <c r="J121" s="12" t="n">
-        <v>222.88</v>
-      </c>
-      <c r="K121" s="12" t="n"/>
-      <c r="L121" s="12" t="n">
-        <v>96.31999999999999</v>
-      </c>
-      <c r="M121" s="12" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="N121" s="12" t="n"/>
-      <c r="O121" s="12" t="n"/>
-      <c r="P121" s="12" t="n"/>
-      <c r="Q121" s="12" t="n">
-        <v>3369</v>
-      </c>
-      <c r="R121" s="3" t="inlineStr">
-        <is>
-          <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11214,7 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Noon</t>
+          <t>Jahez</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
@@ -11231,1421 +11229,1427 @@
       </c>
       <c r="F122" s="11" t="n"/>
       <c r="G122" s="12" t="n">
-        <v>43</v>
+        <v>1601</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>666</v>
+        <v>869</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>316</v>
+        <v>465</v>
       </c>
       <c r="J122" s="12" t="n">
-        <v>1320.29</v>
-      </c>
-      <c r="K122" s="12" t="n">
-        <v>166</v>
-      </c>
+        <v>222.88</v>
+      </c>
+      <c r="K122" s="12" t="n"/>
       <c r="L122" s="12" t="n">
-        <v>200</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>338.8</v>
-      </c>
-      <c r="N122" s="12" t="n">
-        <v>467</v>
-      </c>
+        <v>114.8</v>
+      </c>
+      <c r="N122" s="12" t="n"/>
       <c r="O122" s="12" t="n"/>
       <c r="P122" s="12" t="n"/>
       <c r="Q122" s="12" t="n">
+        <v>3369</v>
+      </c>
+      <c r="R122" s="3" t="inlineStr">
+        <is>
+          <t>Nasam platform — revenue view</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" outlineLevel="2">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>Rimath</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>Thannah</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>Noon</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="n"/>
+      <c r="G123" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="H123" s="12" t="n">
+        <v>666</v>
+      </c>
+      <c r="I123" s="12" t="n">
+        <v>316</v>
+      </c>
+      <c r="J123" s="12" t="n">
+        <v>1320.29</v>
+      </c>
+      <c r="K123" s="12" t="n">
+        <v>166</v>
+      </c>
+      <c r="L123" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="M123" s="12" t="n">
+        <v>338.8</v>
+      </c>
+      <c r="N123" s="12" t="n">
+        <v>467</v>
+      </c>
+      <c r="O123" s="12" t="n"/>
+      <c r="P123" s="12" t="n"/>
+      <c r="Q123" s="12" t="n">
         <v>3517.09</v>
       </c>
-      <c r="R122" s="3" t="inlineStr">
+      <c r="R123" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="123" outlineLevel="2">
-      <c r="A123" s="13" t="inlineStr">
+    <row r="124" outlineLevel="2">
+      <c r="A124" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B123" s="13" t="inlineStr">
+      <c r="B124" s="13" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C123" s="13" t="inlineStr">
+      <c r="C124" s="13" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D123" s="13" t="inlineStr">
+      <c r="D124" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E123" s="13" t="inlineStr">
+      <c r="E124" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F123" s="13" t="inlineStr">
+      <c r="F124" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G123" s="14" t="n">
+      <c r="G124" s="14" t="n">
         <v>3.01</v>
       </c>
-      <c r="H123" s="14" t="n">
+      <c r="H124" s="14" t="n">
         <v>46.62</v>
       </c>
-      <c r="I123" s="14" t="n">
+      <c r="I124" s="14" t="n">
         <v>19.6</v>
       </c>
-      <c r="J123" s="14" t="n">
+      <c r="J124" s="14" t="n">
         <v>92.42</v>
       </c>
-      <c r="K123" s="14" t="n">
+      <c r="K124" s="14" t="n">
         <v>20.44</v>
       </c>
-      <c r="L123" s="14" t="n">
+      <c r="L124" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="M123" s="14" t="n">
+      <c r="M124" s="14" t="n">
         <v>26.31</v>
       </c>
-      <c r="N123" s="14" t="n">
+      <c r="N124" s="14" t="n">
         <v>23.8</v>
       </c>
-      <c r="O123" s="14" t="n"/>
-      <c r="P123" s="14" t="n"/>
-      <c r="Q123" s="14" t="n">
+      <c r="O124" s="14" t="n"/>
+      <c r="P124" s="14" t="n"/>
+      <c r="Q124" s="14" t="n">
         <v>246.2</v>
       </c>
-      <c r="R123" s="3" t="inlineStr">
+      <c r="R124" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="124" outlineLevel="2">
-      <c r="A124" s="11" t="inlineStr">
+    <row r="125" outlineLevel="2">
+      <c r="A125" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C124" s="11" t="inlineStr">
+      <c r="C125" s="11" t="inlineStr">
         <is>
           <t>NoonFood</t>
         </is>
       </c>
-      <c r="D124" s="11" t="inlineStr">
+      <c r="D125" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E124" s="11" t="inlineStr">
+      <c r="E125" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F124" s="11" t="n"/>
-      <c r="G124" s="12" t="n"/>
-      <c r="H124" s="12" t="n">
+      <c r="F125" s="11" t="n"/>
+      <c r="G125" s="12" t="n"/>
+      <c r="H125" s="12" t="n">
         <v>242</v>
       </c>
-      <c r="I124" s="12" t="n"/>
-      <c r="J124" s="12" t="n"/>
-      <c r="K124" s="12" t="n"/>
-      <c r="L124" s="12" t="n"/>
-      <c r="M124" s="12" t="n"/>
-      <c r="N124" s="12" t="n"/>
-      <c r="O124" s="12" t="n"/>
-      <c r="P124" s="12" t="n"/>
-      <c r="Q124" s="12" t="n">
+      <c r="I125" s="12" t="n"/>
+      <c r="J125" s="12" t="n"/>
+      <c r="K125" s="12" t="n"/>
+      <c r="L125" s="12" t="n"/>
+      <c r="M125" s="12" t="n"/>
+      <c r="N125" s="12" t="n"/>
+      <c r="O125" s="12" t="n"/>
+      <c r="P125" s="12" t="n"/>
+      <c r="Q125" s="12" t="n">
         <v>242</v>
       </c>
-      <c r="R124" s="3" t="inlineStr">
+      <c r="R125" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="125" outlineLevel="2">
-      <c r="A125" s="13" t="inlineStr">
+    <row r="126" outlineLevel="2">
+      <c r="A126" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B125" s="13" t="inlineStr">
+      <c r="B126" s="13" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C125" s="13" t="inlineStr">
+      <c r="C126" s="13" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="D125" s="13" t="inlineStr">
+      <c r="D126" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E125" s="13" t="inlineStr">
+      <c r="E126" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F125" s="13" t="inlineStr"/>
-      <c r="G125" s="14" t="n"/>
-      <c r="H125" s="14" t="n"/>
-      <c r="I125" s="14" t="n"/>
-      <c r="J125" s="14" t="n"/>
-      <c r="K125" s="14" t="n"/>
-      <c r="L125" s="14" t="n"/>
-      <c r="M125" s="14" t="n"/>
-      <c r="N125" s="14" t="n">
+      <c r="F126" s="13" t="inlineStr"/>
+      <c r="G126" s="14" t="n"/>
+      <c r="H126" s="14" t="n"/>
+      <c r="I126" s="14" t="n"/>
+      <c r="J126" s="14" t="n"/>
+      <c r="K126" s="14" t="n"/>
+      <c r="L126" s="14" t="n"/>
+      <c r="M126" s="14" t="n"/>
+      <c r="N126" s="14" t="n">
         <v>862.6799999999999</v>
       </c>
-      <c r="O125" s="14" t="n"/>
-      <c r="P125" s="14" t="n"/>
-      <c r="Q125" s="14" t="n">
+      <c r="O126" s="14" t="n"/>
+      <c r="P126" s="14" t="n"/>
+      <c r="Q126" s="14" t="n">
         <v>862.6799999999999</v>
       </c>
-      <c r="R125" s="3" t="inlineStr">
+      <c r="R126" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="126" outlineLevel="2">
-      <c r="A126" s="11" t="inlineStr">
+    <row r="127" outlineLevel="2">
+      <c r="A127" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr">
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C126" s="11" t="inlineStr">
+      <c r="C127" s="11" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D126" s="11" t="inlineStr">
+      <c r="D127" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E126" s="11" t="inlineStr">
+      <c r="E127" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F126" s="11" t="n"/>
-      <c r="G126" s="12" t="n">
+      <c r="F127" s="11" t="n"/>
+      <c r="G127" s="12" t="n">
         <v>4949.84</v>
       </c>
-      <c r="H126" s="12" t="n">
+      <c r="H127" s="12" t="n">
         <v>2430.39</v>
       </c>
-      <c r="I126" s="12" t="n">
+      <c r="I127" s="12" t="n">
         <v>6636.77</v>
       </c>
-      <c r="J126" s="12" t="n">
+      <c r="J127" s="12" t="n">
         <v>23571.73</v>
       </c>
-      <c r="K126" s="12" t="n">
+      <c r="K127" s="12" t="n">
         <v>14335.79</v>
       </c>
-      <c r="L126" s="12" t="n">
+      <c r="L127" s="12" t="n">
         <v>11615.48</v>
       </c>
-      <c r="M126" s="12" t="n">
+      <c r="M127" s="12" t="n">
         <v>2340.42</v>
       </c>
-      <c r="N126" s="12" t="n"/>
-      <c r="O126" s="12" t="n"/>
-      <c r="P126" s="12" t="n"/>
-      <c r="Q126" s="12" t="n">
+      <c r="N127" s="12" t="n"/>
+      <c r="O127" s="12" t="n"/>
+      <c r="P127" s="12" t="n"/>
+      <c r="Q127" s="12" t="n">
         <v>65880.42</v>
       </c>
-      <c r="R126" s="3" t="inlineStr">
+      <c r="R127" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="127" outlineLevel="2">
-      <c r="A127" s="13" t="inlineStr">
+    <row r="128" outlineLevel="2">
+      <c r="A128" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B127" s="13" t="inlineStr">
+      <c r="B128" s="13" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C127" s="13" t="inlineStr">
+      <c r="C128" s="13" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D127" s="13" t="inlineStr">
+      <c r="D128" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E127" s="13" t="inlineStr">
+      <c r="E128" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F127" s="13" t="inlineStr">
+      <c r="F128" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G127" s="14" t="n">
+      <c r="G128" s="14" t="n">
         <v>346.49</v>
       </c>
-      <c r="H127" s="14" t="n">
+      <c r="H128" s="14" t="n">
         <v>170.13</v>
       </c>
-      <c r="I127" s="14" t="n">
+      <c r="I128" s="14" t="n">
         <v>464.57</v>
       </c>
-      <c r="J127" s="14" t="n">
+      <c r="J128" s="14" t="n">
         <v>1633.71</v>
       </c>
-      <c r="K127" s="14" t="n">
+      <c r="K128" s="14" t="n">
         <v>1003.51</v>
       </c>
-      <c r="L127" s="14" t="n">
+      <c r="L128" s="14" t="n">
         <v>813.08</v>
       </c>
-      <c r="M127" s="14" t="n">
+      <c r="M128" s="14" t="n">
         <v>288.49</v>
       </c>
-      <c r="N127" s="14" t="n">
+      <c r="N128" s="14" t="n">
         <v>226.89</v>
       </c>
-      <c r="O127" s="14" t="n"/>
-      <c r="P127" s="14" t="n"/>
-      <c r="Q127" s="14" t="n">
+      <c r="O128" s="14" t="n"/>
+      <c r="P128" s="14" t="n"/>
+      <c r="Q128" s="14" t="n">
         <v>4946.87</v>
       </c>
-      <c r="R127" s="3" t="inlineStr">
+      <c r="R128" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="128" outlineLevel="2">
-      <c r="A128" s="11" t="inlineStr">
+    <row r="129" outlineLevel="2">
+      <c r="A129" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C128" s="11" t="inlineStr">
+      <c r="C129" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D128" s="11" t="inlineStr">
+      <c r="D129" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E128" s="11" t="inlineStr">
+      <c r="E129" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F128" s="11" t="n"/>
-      <c r="G128" s="12" t="n">
+      <c r="F129" s="11" t="n"/>
+      <c r="G129" s="12" t="n">
         <v>1303.5</v>
       </c>
-      <c r="H128" s="12" t="n">
+      <c r="H129" s="12" t="n">
         <v>510.86</v>
       </c>
-      <c r="I128" s="12" t="n"/>
-      <c r="J128" s="12" t="n"/>
-      <c r="K128" s="12" t="n">
+      <c r="I129" s="12" t="n"/>
+      <c r="J129" s="12" t="n"/>
+      <c r="K129" s="12" t="n">
         <v>141.95</v>
       </c>
-      <c r="L128" s="12" t="n">
+      <c r="L129" s="12" t="n">
         <v>149.6</v>
       </c>
-      <c r="M128" s="12" t="n">
+      <c r="M129" s="12" t="n">
         <v>393</v>
       </c>
-      <c r="N128" s="12" t="n">
+      <c r="N129" s="12" t="n">
         <v>406</v>
       </c>
-      <c r="O128" s="12" t="n"/>
-      <c r="P128" s="12" t="n"/>
-      <c r="Q128" s="12" t="n">
+      <c r="O129" s="12" t="n"/>
+      <c r="P129" s="12" t="n"/>
+      <c r="Q129" s="12" t="n">
         <v>2904.91</v>
       </c>
-      <c r="R128" s="3" t="inlineStr">
+      <c r="R129" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="129" outlineLevel="2">
-      <c r="A129" s="13" t="inlineStr">
+    <row r="130" outlineLevel="2">
+      <c r="A130" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B129" s="13" t="inlineStr">
+      <c r="B130" s="13" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C129" s="13" t="inlineStr">
+      <c r="C130" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D129" s="13" t="inlineStr">
+      <c r="D130" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E129" s="13" t="inlineStr">
+      <c r="E130" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F129" s="13" t="inlineStr">
+      <c r="F130" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G129" s="14" t="n">
+      <c r="G130" s="14" t="n">
         <v>98.39</v>
       </c>
-      <c r="H129" s="14" t="n">
+      <c r="H130" s="14" t="n">
         <v>41.79</v>
       </c>
-      <c r="I129" s="14" t="n"/>
-      <c r="J129" s="14" t="n"/>
-      <c r="K129" s="14" t="n">
+      <c r="I130" s="14" t="n"/>
+      <c r="J130" s="14" t="n"/>
+      <c r="K130" s="14" t="n">
         <v>9.93</v>
       </c>
-      <c r="L129" s="14" t="n">
+      <c r="L130" s="14" t="n">
         <v>10.47</v>
       </c>
-      <c r="M129" s="14" t="n">
+      <c r="M130" s="14" t="n">
         <v>27.51</v>
       </c>
-      <c r="N129" s="14" t="n">
+      <c r="N130" s="14" t="n">
         <v>28.07</v>
       </c>
-      <c r="O129" s="14" t="n"/>
-      <c r="P129" s="14" t="n"/>
-      <c r="Q129" s="14" t="n">
+      <c r="O130" s="14" t="n"/>
+      <c r="P130" s="14" t="n"/>
+      <c r="Q130" s="14" t="n">
         <v>216.16</v>
       </c>
-      <c r="R129" s="3" t="inlineStr">
+      <c r="R130" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="130" outlineLevel="1">
-      <c r="A130" s="11" t="inlineStr">
+    <row r="131" outlineLevel="1">
+      <c r="A131" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr">
+      <c r="B131" s="11" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C130" s="11" t="n"/>
-      <c r="D130" s="11" t="inlineStr">
+      <c r="C131" s="11" t="n"/>
+      <c r="D131" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E130" s="11" t="n"/>
-      <c r="F130" s="11" t="n"/>
-      <c r="G130" s="12" t="n">
-        <v>17966.96</v>
-      </c>
-      <c r="H130" s="12" t="n">
-        <v>12215.09</v>
-      </c>
-      <c r="I130" s="12" t="n">
-        <v>19733.81</v>
-      </c>
-      <c r="J130" s="12" t="n">
-        <v>19995.25</v>
-      </c>
-      <c r="K130" s="12" t="n">
-        <v>14622.86</v>
-      </c>
-      <c r="L130" s="12" t="n">
-        <v>15131.7</v>
-      </c>
-      <c r="M130" s="12" t="n">
-        <v>6146.65</v>
-      </c>
-      <c r="N130" s="12" t="n">
-        <v>2282</v>
-      </c>
-      <c r="O130" s="12" t="n"/>
-      <c r="P130" s="12" t="n"/>
-      <c r="Q130" s="12" t="n">
-        <v>108094.32</v>
-      </c>
-      <c r="R130" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" outlineLevel="2">
-      <c r="A131" s="11" t="inlineStr">
-        <is>
-          <t>Rimath</t>
-        </is>
-      </c>
-      <c r="B131" s="11" t="inlineStr">
-        <is>
-          <t>iOUD</t>
-        </is>
-      </c>
-      <c r="C131" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D131" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E131" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E131" s="11" t="n"/>
       <c r="F131" s="11" t="n"/>
       <c r="G131" s="12" t="n">
-        <v>2893.12</v>
+        <v>17966.96</v>
       </c>
       <c r="H131" s="12" t="n">
-        <v>805.8</v>
+        <v>12215.09</v>
       </c>
       <c r="I131" s="12" t="n">
-        <v>1930.64</v>
+        <v>19733.81</v>
       </c>
       <c r="J131" s="12" t="n">
-        <v>2215.64</v>
+        <v>19995.25</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>496.92</v>
+        <v>14622.86</v>
       </c>
       <c r="L131" s="12" t="n">
-        <v>1919</v>
-      </c>
-      <c r="M131" s="12" t="n"/>
+        <v>15131.7</v>
+      </c>
+      <c r="M131" s="12" t="n">
+        <v>6146.65</v>
+      </c>
       <c r="N131" s="12" t="n">
-        <v>378</v>
+        <v>2282</v>
       </c>
       <c r="O131" s="12" t="n"/>
       <c r="P131" s="12" t="n"/>
       <c r="Q131" s="12" t="n">
+        <v>108094.32</v>
+      </c>
+      <c r="R131" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" outlineLevel="2">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>Rimath</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>iOUD</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="n"/>
+      <c r="G132" s="12" t="n">
+        <v>2893.12</v>
+      </c>
+      <c r="H132" s="12" t="n">
+        <v>805.8</v>
+      </c>
+      <c r="I132" s="12" t="n">
+        <v>1930.64</v>
+      </c>
+      <c r="J132" s="12" t="n">
+        <v>2215.64</v>
+      </c>
+      <c r="K132" s="12" t="n">
+        <v>496.92</v>
+      </c>
+      <c r="L132" s="12" t="n">
+        <v>1919</v>
+      </c>
+      <c r="M132" s="12" t="n"/>
+      <c r="N132" s="12" t="n">
+        <v>378</v>
+      </c>
+      <c r="O132" s="12" t="n"/>
+      <c r="P132" s="12" t="n"/>
+      <c r="Q132" s="12" t="n">
         <v>10639.12</v>
       </c>
-      <c r="R131" s="3" t="inlineStr">
+      <c r="R132" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="132" outlineLevel="2">
-      <c r="A132" s="13" t="inlineStr">
+    <row r="133" outlineLevel="2">
+      <c r="A133" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B132" s="13" t="inlineStr">
+      <c r="B133" s="13" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C132" s="13" t="inlineStr">
+      <c r="C133" s="13" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D132" s="13" t="inlineStr">
+      <c r="D133" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E132" s="13" t="inlineStr">
+      <c r="E133" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F132" s="13" t="inlineStr">
+      <c r="F133" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G132" s="14" t="n">
+      <c r="G133" s="14" t="n">
         <v>176.96</v>
       </c>
-      <c r="H132" s="14" t="n">
+      <c r="H133" s="14" t="n">
         <v>56.41</v>
       </c>
-      <c r="I132" s="14" t="n">
+      <c r="I133" s="14" t="n">
         <v>135.14</v>
       </c>
-      <c r="J132" s="14" t="n">
+      <c r="J133" s="14" t="n">
         <v>154.82</v>
       </c>
-      <c r="K132" s="14" t="n">
+      <c r="K133" s="14" t="n">
         <v>52.34</v>
       </c>
-      <c r="L132" s="14" t="n">
+      <c r="L133" s="14" t="n">
         <v>134.33</v>
       </c>
-      <c r="M132" s="14" t="n"/>
-      <c r="N132" s="14" t="n">
+      <c r="M133" s="14" t="n"/>
+      <c r="N133" s="14" t="n">
         <v>17.85</v>
       </c>
-      <c r="O132" s="14" t="n"/>
-      <c r="P132" s="14" t="n"/>
-      <c r="Q132" s="14" t="n">
+      <c r="O133" s="14" t="n"/>
+      <c r="P133" s="14" t="n"/>
+      <c r="Q133" s="14" t="n">
         <v>727.85</v>
       </c>
-      <c r="R132" s="3" t="inlineStr">
+      <c r="R133" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="133" outlineLevel="2">
-      <c r="A133" s="11" t="inlineStr">
+    <row r="134" outlineLevel="2">
+      <c r="A134" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B134" s="11" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C133" s="11" t="inlineStr">
+      <c r="C134" s="11" t="inlineStr">
         <is>
           <t>Jahez</t>
         </is>
       </c>
-      <c r="D133" s="11" t="inlineStr">
+      <c r="D134" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E133" s="11" t="inlineStr">
+      <c r="E134" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F133" s="11" t="n"/>
-      <c r="G133" s="12" t="n"/>
-      <c r="H133" s="12" t="n"/>
-      <c r="I133" s="12" t="n"/>
-      <c r="J133" s="12" t="n"/>
-      <c r="K133" s="12" t="n"/>
-      <c r="L133" s="12" t="n">
+      <c r="F134" s="11" t="n"/>
+      <c r="G134" s="12" t="n"/>
+      <c r="H134" s="12" t="n"/>
+      <c r="I134" s="12" t="n"/>
+      <c r="J134" s="12" t="n"/>
+      <c r="K134" s="12" t="n"/>
+      <c r="L134" s="12" t="n">
         <v>306</v>
       </c>
-      <c r="M133" s="12" t="n"/>
-      <c r="N133" s="12" t="n"/>
-      <c r="O133" s="12" t="n"/>
-      <c r="P133" s="12" t="n"/>
-      <c r="Q133" s="12" t="n">
+      <c r="M134" s="12" t="n"/>
+      <c r="N134" s="12" t="n"/>
+      <c r="O134" s="12" t="n"/>
+      <c r="P134" s="12" t="n"/>
+      <c r="Q134" s="12" t="n">
         <v>306</v>
       </c>
-      <c r="R133" s="3" t="inlineStr">
+      <c r="R134" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="134" outlineLevel="2">
-      <c r="A134" s="13" t="inlineStr">
+    <row r="135" outlineLevel="2">
+      <c r="A135" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B134" s="13" t="inlineStr">
+      <c r="B135" s="13" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C134" s="13" t="inlineStr">
+      <c r="C135" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D134" s="13" t="inlineStr">
+      <c r="D135" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E134" s="13" t="inlineStr">
+      <c r="E135" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F134" s="13" t="inlineStr">
+      <c r="F135" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G134" s="14" t="n"/>
-      <c r="H134" s="14" t="n"/>
-      <c r="I134" s="14" t="n"/>
-      <c r="J134" s="14" t="n"/>
-      <c r="K134" s="14" t="n"/>
-      <c r="L134" s="14" t="n">
+      <c r="G135" s="14" t="n"/>
+      <c r="H135" s="14" t="n"/>
+      <c r="I135" s="14" t="n"/>
+      <c r="J135" s="14" t="n"/>
+      <c r="K135" s="14" t="n"/>
+      <c r="L135" s="14" t="n">
         <v>21.42</v>
       </c>
-      <c r="M134" s="14" t="n"/>
-      <c r="N134" s="14" t="n"/>
-      <c r="O134" s="14" t="n"/>
-      <c r="P134" s="14" t="n"/>
-      <c r="Q134" s="14" t="n">
+      <c r="M135" s="14" t="n"/>
+      <c r="N135" s="14" t="n"/>
+      <c r="O135" s="14" t="n"/>
+      <c r="P135" s="14" t="n"/>
+      <c r="Q135" s="14" t="n">
         <v>21.42</v>
       </c>
-      <c r="R134" s="3" t="inlineStr">
+      <c r="R135" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="135" outlineLevel="2">
-      <c r="A135" s="11" t="inlineStr">
+    <row r="136" outlineLevel="2">
+      <c r="A136" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B135" s="11" t="inlineStr">
+      <c r="B136" s="11" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C135" s="11" t="inlineStr">
+      <c r="C136" s="11" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D135" s="11" t="inlineStr">
+      <c r="D136" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E135" s="11" t="inlineStr">
+      <c r="E136" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F135" s="11" t="n"/>
-      <c r="G135" s="12" t="n">
+      <c r="F136" s="11" t="n"/>
+      <c r="G136" s="12" t="n">
         <v>1930.6</v>
       </c>
-      <c r="H135" s="12" t="n">
+      <c r="H136" s="12" t="n">
         <v>1857</v>
       </c>
-      <c r="I135" s="12" t="n">
+      <c r="I136" s="12" t="n">
         <v>1037.52</v>
       </c>
-      <c r="J135" s="12" t="n">
+      <c r="J136" s="12" t="n">
         <v>2488.96</v>
       </c>
-      <c r="K135" s="12" t="n">
+      <c r="K136" s="12" t="n">
         <v>1688</v>
       </c>
-      <c r="L135" s="12" t="n">
+      <c r="L136" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="M135" s="12" t="n">
+      <c r="M136" s="12" t="n">
         <v>283</v>
       </c>
-      <c r="N135" s="12" t="n">
+      <c r="N136" s="12" t="n">
         <v>1904</v>
       </c>
-      <c r="O135" s="12" t="n"/>
-      <c r="P135" s="12" t="n"/>
-      <c r="Q135" s="12" t="n">
+      <c r="O136" s="12" t="n"/>
+      <c r="P136" s="12" t="n"/>
+      <c r="Q136" s="12" t="n">
         <v>11349.08</v>
       </c>
-      <c r="R135" s="3" t="inlineStr">
+      <c r="R136" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="136" outlineLevel="2">
-      <c r="A136" s="13" t="inlineStr">
+    <row r="137" outlineLevel="2">
+      <c r="A137" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B136" s="13" t="inlineStr">
+      <c r="B137" s="13" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C136" s="13" t="inlineStr">
+      <c r="C137" s="13" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D136" s="13" t="inlineStr">
+      <c r="D137" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E136" s="13" t="inlineStr">
+      <c r="E137" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F136" s="13" t="inlineStr">
+      <c r="F137" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G136" s="14" t="n">
+      <c r="G137" s="14" t="n">
         <v>135.14</v>
       </c>
-      <c r="H136" s="14" t="n">
+      <c r="H137" s="14" t="n">
         <v>129.99</v>
       </c>
-      <c r="I136" s="14" t="n">
+      <c r="I137" s="14" t="n">
         <v>55.06</v>
       </c>
-      <c r="J136" s="14" t="n">
+      <c r="J137" s="14" t="n">
         <v>165.62</v>
       </c>
-      <c r="K136" s="14" t="n">
+      <c r="K137" s="14" t="n">
         <v>118.16</v>
       </c>
-      <c r="L136" s="14" t="n">
+      <c r="L137" s="14" t="n">
         <v>11.2</v>
       </c>
-      <c r="M136" s="14" t="n">
+      <c r="M137" s="14" t="n">
         <v>19.81</v>
       </c>
-      <c r="N136" s="14" t="n">
+      <c r="N137" s="14" t="n">
         <v>117.53</v>
       </c>
-      <c r="O136" s="14" t="n"/>
-      <c r="P136" s="14" t="n"/>
-      <c r="Q136" s="14" t="n">
+      <c r="O137" s="14" t="n"/>
+      <c r="P137" s="14" t="n"/>
+      <c r="Q137" s="14" t="n">
         <v>752.51</v>
       </c>
-      <c r="R136" s="3" t="inlineStr">
+      <c r="R137" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="137" outlineLevel="2">
-      <c r="A137" s="11" t="inlineStr">
+    <row r="138" outlineLevel="2">
+      <c r="A138" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr">
+      <c r="B138" s="11" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C137" s="11" t="inlineStr">
+      <c r="C138" s="11" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D137" s="11" t="inlineStr">
+      <c r="D138" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E137" s="11" t="inlineStr">
+      <c r="E138" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F137" s="11" t="n"/>
-      <c r="G137" s="12" t="n">
+      <c r="F138" s="11" t="n"/>
+      <c r="G138" s="12" t="n">
         <v>11857.63</v>
       </c>
-      <c r="H137" s="12" t="n">
+      <c r="H138" s="12" t="n">
         <v>9312.950000000001</v>
       </c>
-      <c r="I137" s="12" t="n">
+      <c r="I138" s="12" t="n">
         <v>16765.65</v>
       </c>
-      <c r="J137" s="12" t="n">
+      <c r="J138" s="12" t="n">
         <v>15290.65</v>
       </c>
-      <c r="K137" s="12" t="n">
+      <c r="K138" s="12" t="n">
         <v>11946.93</v>
       </c>
-      <c r="L137" s="12" t="n">
+      <c r="L138" s="12" t="n">
         <v>12677.13</v>
       </c>
-      <c r="M137" s="12" t="n">
+      <c r="M138" s="12" t="n">
         <v>5740.65</v>
       </c>
-      <c r="N137" s="12" t="n"/>
-      <c r="O137" s="12" t="n"/>
-      <c r="P137" s="12" t="n"/>
-      <c r="Q137" s="12" t="n">
+      <c r="N138" s="12" t="n"/>
+      <c r="O138" s="12" t="n"/>
+      <c r="P138" s="12" t="n"/>
+      <c r="Q138" s="12" t="n">
         <v>83591.59</v>
       </c>
-      <c r="R137" s="3" t="inlineStr">
+      <c r="R138" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="138" outlineLevel="2">
-      <c r="A138" s="13" t="inlineStr">
+    <row r="139" outlineLevel="2">
+      <c r="A139" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B138" s="13" t="inlineStr">
+      <c r="B139" s="13" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C138" s="13" t="inlineStr">
+      <c r="C139" s="13" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D138" s="13" t="inlineStr">
+      <c r="D139" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E138" s="13" t="inlineStr">
+      <c r="E139" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F138" s="13" t="inlineStr">
+      <c r="F139" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G138" s="14" t="n">
+      <c r="G139" s="14" t="n">
         <v>830.03</v>
       </c>
-      <c r="H138" s="14" t="n">
+      <c r="H139" s="14" t="n">
         <v>651.91</v>
       </c>
-      <c r="I138" s="14" t="n">
+      <c r="I139" s="14" t="n">
         <v>1173.6</v>
       </c>
-      <c r="J138" s="14" t="n">
+      <c r="J139" s="14" t="n">
         <v>997.98</v>
       </c>
-      <c r="K138" s="14" t="n">
+      <c r="K139" s="14" t="n">
         <v>836.29</v>
       </c>
-      <c r="L138" s="14" t="n">
+      <c r="L139" s="14" t="n">
         <v>853.52</v>
       </c>
-      <c r="M138" s="14" t="n">
+      <c r="M139" s="14" t="n">
         <v>912.28</v>
       </c>
-      <c r="N138" s="14" t="n">
+      <c r="N139" s="14" t="n">
         <v>283.88</v>
       </c>
-      <c r="O138" s="14" t="n"/>
-      <c r="P138" s="14" t="n"/>
-      <c r="Q138" s="14" t="n">
+      <c r="O139" s="14" t="n"/>
+      <c r="P139" s="14" t="n"/>
+      <c r="Q139" s="14" t="n">
         <v>6539.49</v>
       </c>
-      <c r="R138" s="3" t="inlineStr">
+      <c r="R139" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="139" outlineLevel="2">
-      <c r="A139" s="11" t="inlineStr">
+    <row r="140" outlineLevel="2">
+      <c r="A140" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C139" s="11" t="inlineStr">
+      <c r="C140" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D139" s="11" t="inlineStr">
+      <c r="D140" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E139" s="11" t="inlineStr">
+      <c r="E140" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F139" s="11" t="n"/>
-      <c r="G139" s="12" t="n">
+      <c r="F140" s="11" t="n"/>
+      <c r="G140" s="12" t="n">
         <v>1285.61</v>
       </c>
-      <c r="H139" s="12" t="n">
+      <c r="H140" s="12" t="n">
         <v>239.34</v>
       </c>
-      <c r="I139" s="12" t="n"/>
-      <c r="J139" s="12" t="n"/>
-      <c r="K139" s="12" t="n">
+      <c r="I140" s="12" t="n"/>
+      <c r="J140" s="12" t="n"/>
+      <c r="K140" s="12" t="n">
         <v>491.01</v>
       </c>
-      <c r="L139" s="12" t="n">
+      <c r="L140" s="12" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="M139" s="12" t="n">
+      <c r="M140" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="N139" s="12" t="n"/>
-      <c r="O139" s="12" t="n"/>
-      <c r="P139" s="12" t="n"/>
-      <c r="Q139" s="12" t="n">
+      <c r="N140" s="12" t="n"/>
+      <c r="O140" s="12" t="n"/>
+      <c r="P140" s="12" t="n"/>
+      <c r="Q140" s="12" t="n">
         <v>2208.53</v>
       </c>
-      <c r="R139" s="3" t="inlineStr">
+      <c r="R140" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="140" outlineLevel="2">
-      <c r="A140" s="13" t="inlineStr">
+    <row r="141" outlineLevel="2">
+      <c r="A141" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B140" s="13" t="inlineStr">
+      <c r="B141" s="13" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C140" s="13" t="inlineStr">
+      <c r="C141" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D140" s="13" t="inlineStr">
+      <c r="D141" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E140" s="13" t="inlineStr">
+      <c r="E141" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F140" s="13" t="inlineStr">
+      <c r="F141" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G140" s="14" t="n">
+      <c r="G141" s="14" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="H140" s="14" t="n">
+      <c r="H141" s="14" t="n">
         <v>16.75</v>
       </c>
-      <c r="I140" s="14" t="n"/>
-      <c r="J140" s="14" t="n"/>
-      <c r="K140" s="14" t="n">
+      <c r="I141" s="14" t="n"/>
+      <c r="J141" s="14" t="n"/>
+      <c r="K141" s="14" t="n">
         <v>34.37</v>
       </c>
-      <c r="L140" s="14" t="n">
+      <c r="L141" s="14" t="n">
         <v>4.87</v>
       </c>
-      <c r="M140" s="14" t="n">
+      <c r="M141" s="14" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="N140" s="14" t="n"/>
-      <c r="O140" s="14" t="n"/>
-      <c r="P140" s="14" t="n"/>
-      <c r="Q140" s="14" t="n">
-        <v>163.2</v>
-      </c>
-      <c r="R140" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" outlineLevel="1">
-      <c r="A141" s="13" t="inlineStr">
-        <is>
-          <t>Rimath</t>
-        </is>
-      </c>
-      <c r="B141" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C141" s="13" t="n"/>
-      <c r="D141" s="13" t="inlineStr">
-        <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E141" s="13" t="n"/>
-      <c r="F141" s="13" t="n"/>
-      <c r="G141" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H141" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I141" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J141" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K141" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L141" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="M141" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="N141" s="14" t="n">
-        <v>1149.99</v>
-      </c>
+      <c r="N141" s="14" t="n"/>
       <c r="O141" s="14" t="n"/>
       <c r="P141" s="14" t="n"/>
       <c r="Q141" s="14" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="R141" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" outlineLevel="1">
+      <c r="A142" s="13" t="inlineStr">
+        <is>
+          <t>Rimath</t>
+        </is>
+      </c>
+      <c r="B142" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C142" s="13" t="n"/>
+      <c r="D142" s="13" t="inlineStr">
+        <is>
+          <t>Monthly fee</t>
+        </is>
+      </c>
+      <c r="E142" s="13" t="n"/>
+      <c r="F142" s="13" t="n"/>
+      <c r="G142" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H142" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I142" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J142" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K142" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L142" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M142" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N142" s="14" t="n">
+        <v>1149.99</v>
+      </c>
+      <c r="O142" s="14" t="n"/>
+      <c r="P142" s="14" t="n"/>
+      <c r="Q142" s="14" t="n">
         <v>11649.99</v>
       </c>
-      <c r="R141" s="3" t="inlineStr">
+      <c r="R142" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · Card 1,500 = 500 × 3 brands</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="9" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya  (churned 2026-05)</t>
         </is>
       </c>
-      <c r="B143" s="9" t="n"/>
-      <c r="C143" s="9" t="n"/>
-      <c r="D143" s="9" t="inlineStr">
+      <c r="B144" s="9" t="n"/>
+      <c r="C144" s="9" t="n"/>
+      <c r="D144" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E143" s="9" t="n"/>
-      <c r="F143" s="9" t="n"/>
-      <c r="G143" s="10" t="n">
+      <c r="E144" s="9" t="n"/>
+      <c r="F144" s="9" t="n"/>
+      <c r="G144" s="10" t="n">
         <v>3041.76</v>
       </c>
-      <c r="H143" s="10" t="n">
+      <c r="H144" s="10" t="n">
         <v>2097.12</v>
       </c>
-      <c r="I143" s="10" t="n">
+      <c r="I144" s="10" t="n">
         <v>2292.39</v>
       </c>
-      <c r="J143" s="10" t="n">
+      <c r="J144" s="10" t="n">
         <v>2880.71</v>
       </c>
-      <c r="K143" s="10" t="n">
+      <c r="K144" s="10" t="n">
         <v>2981.2</v>
       </c>
-      <c r="L143" s="10" t="n">
+      <c r="L144" s="10" t="n">
         <v>2360.37</v>
       </c>
-      <c r="M143" s="10" t="n">
+      <c r="M144" s="10" t="n">
         <v>1670.7</v>
       </c>
-      <c r="N143" s="10" t="n"/>
-      <c r="O143" s="10" t="n"/>
-      <c r="P143" s="10" t="n"/>
-      <c r="Q143" s="10" t="n">
+      <c r="N144" s="10" t="n"/>
+      <c r="O144" s="10" t="n"/>
+      <c r="P144" s="10" t="n"/>
+      <c r="Q144" s="10" t="n">
         <v>17324.25</v>
       </c>
-      <c r="R143" s="3" t="inlineStr">
+      <c r="R144" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · Card: 4% + 1,500/mo</t>
         </is>
       </c>
     </row>
-    <row r="144" outlineLevel="1">
-      <c r="A144" s="11" t="inlineStr">
+    <row r="145" outlineLevel="1">
+      <c r="A145" s="11" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="B144" s="11" t="inlineStr">
+      <c r="B145" s="11" t="inlineStr">
         <is>
           <t>Ancy</t>
         </is>
       </c>
-      <c r="C144" s="11" t="n"/>
-      <c r="D144" s="11" t="inlineStr">
+      <c r="C145" s="11" t="n"/>
+      <c r="D145" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E144" s="11" t="n"/>
-      <c r="F144" s="11" t="n"/>
-      <c r="G144" s="12" t="n">
-        <v>20126.2</v>
-      </c>
-      <c r="H144" s="12" t="n">
-        <v>11164.52</v>
-      </c>
-      <c r="I144" s="12" t="n">
-        <v>11654.13</v>
-      </c>
-      <c r="J144" s="12" t="n">
-        <v>10923.98</v>
-      </c>
-      <c r="K144" s="12" t="n">
-        <v>14516.31</v>
-      </c>
-      <c r="L144" s="12" t="n">
-        <v>13262.43</v>
-      </c>
-      <c r="M144" s="12" t="n">
-        <v>80462.35000000001</v>
-      </c>
-      <c r="N144" s="12" t="n"/>
-      <c r="O144" s="12" t="n"/>
-      <c r="P144" s="12" t="n"/>
-      <c r="Q144" s="12" t="n">
-        <v>162109.92</v>
-      </c>
-      <c r="R144" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" outlineLevel="2">
-      <c r="A145" s="11" t="inlineStr">
-        <is>
-          <t>Ancy &amp; Shaya</t>
-        </is>
-      </c>
-      <c r="B145" s="11" t="inlineStr">
-        <is>
-          <t>Ancy</t>
-        </is>
-      </c>
-      <c r="C145" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D145" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E145" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E145" s="11" t="n"/>
       <c r="F145" s="11" t="n"/>
       <c r="G145" s="12" t="n">
-        <v>199</v>
+        <v>20126.2</v>
       </c>
       <c r="H145" s="12" t="n">
-        <v>4577</v>
+        <v>11164.52</v>
       </c>
       <c r="I145" s="12" t="n">
-        <v>6507</v>
+        <v>11654.13</v>
       </c>
       <c r="J145" s="12" t="n">
         <v>10923.98</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>12112.97</v>
+        <v>14516.31</v>
       </c>
       <c r="L145" s="12" t="n">
-        <v>12715.8</v>
+        <v>13262.43</v>
       </c>
       <c r="M145" s="12" t="n">
-        <v>8243.5</v>
+        <v>80462.35000000001</v>
       </c>
       <c r="N145" s="12" t="n"/>
       <c r="O145" s="12" t="n"/>
       <c r="P145" s="12" t="n"/>
       <c r="Q145" s="12" t="n">
+        <v>162109.92</v>
+      </c>
+      <c r="R145" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" outlineLevel="2">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>Ancy &amp; Shaya</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>Ancy</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="n"/>
+      <c r="G146" s="12" t="n">
+        <v>199</v>
+      </c>
+      <c r="H146" s="12" t="n">
+        <v>4577</v>
+      </c>
+      <c r="I146" s="12" t="n">
+        <v>6507</v>
+      </c>
+      <c r="J146" s="12" t="n">
+        <v>10923.98</v>
+      </c>
+      <c r="K146" s="12" t="n">
+        <v>12112.97</v>
+      </c>
+      <c r="L146" s="12" t="n">
+        <v>12715.8</v>
+      </c>
+      <c r="M146" s="12" t="n">
+        <v>8243.5</v>
+      </c>
+      <c r="N146" s="12" t="n"/>
+      <c r="O146" s="12" t="n"/>
+      <c r="P146" s="12" t="n"/>
+      <c r="Q146" s="12" t="n">
         <v>55279.25</v>
       </c>
-      <c r="R145" s="3" t="inlineStr">
+      <c r="R146" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="146" outlineLevel="2">
-      <c r="A146" s="13" t="inlineStr">
+    <row r="147" outlineLevel="2">
+      <c r="A147" s="13" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="B146" s="13" t="inlineStr">
+      <c r="B147" s="13" t="inlineStr">
         <is>
           <t>Ancy ≈</t>
         </is>
       </c>
-      <c r="C146" s="13" t="inlineStr">
+      <c r="C147" s="13" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D146" s="13" t="inlineStr">
+      <c r="D147" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E146" s="13" t="inlineStr">
+      <c r="E147" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F146" s="13" t="inlineStr">
+      <c r="F147" s="13" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="G146" s="14" t="n"/>
-      <c r="H146" s="14" t="n">
+      <c r="G147" s="14" t="n"/>
+      <c r="H147" s="14" t="n">
         <v>183.08</v>
       </c>
-      <c r="I146" s="14" t="n">
+      <c r="I147" s="14" t="n">
         <v>260.28</v>
       </c>
-      <c r="J146" s="14" t="n">
+      <c r="J147" s="14" t="n">
         <v>437.78</v>
       </c>
-      <c r="K146" s="14" t="n">
+      <c r="K147" s="14" t="n">
         <v>475.14</v>
       </c>
-      <c r="L146" s="14" t="n">
+      <c r="L147" s="14" t="n">
         <v>521.03</v>
       </c>
-      <c r="M146" s="14" t="n">
+      <c r="M147" s="14" t="n">
         <v>328.37</v>
       </c>
-      <c r="N146" s="14" t="n"/>
-      <c r="O146" s="14" t="n"/>
-      <c r="P146" s="14" t="n"/>
-      <c r="Q146" s="14" t="n">
+      <c r="N147" s="14" t="n"/>
+      <c r="O147" s="14" t="n"/>
+      <c r="P147" s="14" t="n"/>
+      <c r="Q147" s="14" t="n">
         <v>2205.69</v>
       </c>
-      <c r="R146" s="3" t="inlineStr">
+      <c r="R147" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" outlineLevel="2">
-      <c r="A147" s="11" t="inlineStr">
-        <is>
-          <t>Ancy &amp; Shaya</t>
-        </is>
-      </c>
-      <c r="B147" s="11" t="inlineStr">
-        <is>
-          <t>Ancy</t>
-        </is>
-      </c>
-      <c r="C147" s="11" t="inlineStr">
-        <is>
-          <t>Noon</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E147" s="11" t="inlineStr">
-        <is>
-          <t>SaaS</t>
-        </is>
-      </c>
-      <c r="F147" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G147" s="12" t="n"/>
-      <c r="H147" s="12" t="n"/>
-      <c r="I147" s="12" t="n"/>
-      <c r="J147" s="12" t="n"/>
-      <c r="K147" s="12" t="n"/>
-      <c r="L147" s="12" t="n"/>
-      <c r="M147" s="12" t="n">
-        <v>70029.97</v>
-      </c>
-      <c r="N147" s="12" t="n"/>
-      <c r="O147" s="12" t="n"/>
-      <c r="P147" s="12" t="n"/>
-      <c r="Q147" s="12" t="n">
-        <v>70029.97</v>
-      </c>
-      <c r="R147" s="3" t="inlineStr">
-        <is>
-          <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
@@ -12662,7 +12666,7 @@
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Trendyol</t>
+          <t>Noon</t>
         </is>
       </c>
       <c r="D148" s="11" t="inlineStr">
@@ -12672,320 +12676,320 @@
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F148" s="11" t="n"/>
-      <c r="G148" s="12" t="n">
-        <v>19927.2</v>
-      </c>
-      <c r="H148" s="12" t="n">
-        <v>6587.52</v>
-      </c>
-      <c r="I148" s="12" t="n">
-        <v>5147.13</v>
-      </c>
+          <t>SaaS</t>
+        </is>
+      </c>
+      <c r="F148" s="11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G148" s="12" t="n"/>
+      <c r="H148" s="12" t="n"/>
+      <c r="I148" s="12" t="n"/>
       <c r="J148" s="12" t="n"/>
-      <c r="K148" s="12" t="n">
-        <v>2403.34</v>
-      </c>
-      <c r="L148" s="12" t="n">
-        <v>546.63</v>
-      </c>
+      <c r="K148" s="12" t="n"/>
+      <c r="L148" s="12" t="n"/>
       <c r="M148" s="12" t="n">
-        <v>2188.88</v>
+        <v>70029.97</v>
       </c>
       <c r="N148" s="12" t="n"/>
       <c r="O148" s="12" t="n"/>
       <c r="P148" s="12" t="n"/>
       <c r="Q148" s="12" t="n">
+        <v>70029.97</v>
+      </c>
+      <c r="R148" s="3" t="inlineStr">
+        <is>
+          <t>Nasam platform — revenue view</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" outlineLevel="2">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>Ancy &amp; Shaya</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>Ancy</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr">
+        <is>
+          <t>Trendyol</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F149" s="11" t="n"/>
+      <c r="G149" s="12" t="n">
+        <v>19927.2</v>
+      </c>
+      <c r="H149" s="12" t="n">
+        <v>6587.52</v>
+      </c>
+      <c r="I149" s="12" t="n">
+        <v>5147.13</v>
+      </c>
+      <c r="J149" s="12" t="n"/>
+      <c r="K149" s="12" t="n">
+        <v>2403.34</v>
+      </c>
+      <c r="L149" s="12" t="n">
+        <v>546.63</v>
+      </c>
+      <c r="M149" s="12" t="n">
+        <v>2188.88</v>
+      </c>
+      <c r="N149" s="12" t="n"/>
+      <c r="O149" s="12" t="n"/>
+      <c r="P149" s="12" t="n"/>
+      <c r="Q149" s="12" t="n">
         <v>36800.7</v>
       </c>
-      <c r="R148" s="3" t="inlineStr">
+      <c r="R149" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="149" outlineLevel="2">
-      <c r="A149" s="13" t="inlineStr">
+    <row r="150" outlineLevel="2">
+      <c r="A150" s="13" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="B149" s="13" t="inlineStr">
+      <c r="B150" s="13" t="inlineStr">
         <is>
           <t>Ancy ≈</t>
         </is>
       </c>
-      <c r="C149" s="13" t="inlineStr">
+      <c r="C150" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D149" s="13" t="inlineStr">
+      <c r="D150" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E149" s="13" t="inlineStr">
+      <c r="E150" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F149" s="13" t="inlineStr">
+      <c r="F150" s="13" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="G149" s="14" t="n">
+      <c r="G150" s="14" t="n">
         <v>795.64</v>
       </c>
-      <c r="H149" s="14" t="n">
+      <c r="H150" s="14" t="n">
         <v>263.5</v>
       </c>
-      <c r="I149" s="14" t="n">
+      <c r="I150" s="14" t="n">
         <v>272.5</v>
       </c>
-      <c r="J149" s="14" t="n"/>
-      <c r="K149" s="14" t="n">
+      <c r="J150" s="14" t="n"/>
+      <c r="K150" s="14" t="n">
         <v>101.98</v>
       </c>
-      <c r="L149" s="14" t="n">
+      <c r="L150" s="14" t="n">
         <v>22.22</v>
       </c>
-      <c r="M149" s="14" t="n">
+      <c r="M150" s="14" t="n">
         <v>97.12</v>
       </c>
-      <c r="N149" s="14" t="n"/>
-      <c r="O149" s="14" t="n"/>
-      <c r="P149" s="14" t="n"/>
-      <c r="Q149" s="14" t="n">
+      <c r="N150" s="14" t="n"/>
+      <c r="O150" s="14" t="n"/>
+      <c r="P150" s="14" t="n"/>
+      <c r="Q150" s="14" t="n">
         <v>1552.96</v>
       </c>
-      <c r="R149" s="3" t="inlineStr">
+      <c r="R150" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="150" outlineLevel="1">
-      <c r="A150" s="11" t="inlineStr">
+    <row r="151" outlineLevel="1">
+      <c r="A151" s="11" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="B150" s="11" t="inlineStr">
+      <c r="B151" s="11" t="inlineStr">
         <is>
           <t>Shaya</t>
         </is>
       </c>
-      <c r="C150" s="11" t="n"/>
-      <c r="D150" s="11" t="inlineStr">
+      <c r="C151" s="11" t="n"/>
+      <c r="D151" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E150" s="11" t="n"/>
-      <c r="F150" s="11" t="n"/>
-      <c r="G150" s="12" t="n">
+      <c r="E151" s="11" t="n"/>
+      <c r="F151" s="11" t="n"/>
+      <c r="G151" s="12" t="n">
         <v>16003.24</v>
       </c>
-      <c r="H150" s="12" t="n">
+      <c r="H151" s="12" t="n">
         <v>3763.58</v>
       </c>
-      <c r="I150" s="12" t="n">
+      <c r="I151" s="12" t="n">
         <v>5839.63</v>
       </c>
-      <c r="J150" s="12" t="n">
+      <c r="J151" s="12" t="n">
         <v>13744.33</v>
       </c>
-      <c r="K150" s="12" t="n">
+      <c r="K151" s="12" t="n">
         <v>21709.24</v>
       </c>
-      <c r="L150" s="12" t="n">
+      <c r="L151" s="12" t="n">
         <v>7779.17</v>
       </c>
-      <c r="M150" s="12" t="n">
+      <c r="M151" s="12" t="n">
         <v>52659.24</v>
-      </c>
-      <c r="N150" s="12" t="n"/>
-      <c r="O150" s="12" t="n"/>
-      <c r="P150" s="12" t="n"/>
-      <c r="Q150" s="12" t="n">
-        <v>121498.43</v>
-      </c>
-      <c r="R150" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" outlineLevel="2">
-      <c r="A151" s="11" t="inlineStr">
-        <is>
-          <t>Ancy &amp; Shaya</t>
-        </is>
-      </c>
-      <c r="B151" s="11" t="inlineStr">
-        <is>
-          <t>Shaya</t>
-        </is>
-      </c>
-      <c r="C151" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D151" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E151" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F151" s="11" t="n"/>
-      <c r="G151" s="12" t="n"/>
-      <c r="H151" s="12" t="n"/>
-      <c r="I151" s="12" t="n">
-        <v>3829</v>
-      </c>
-      <c r="J151" s="12" t="n">
-        <v>9830.799999999999</v>
-      </c>
-      <c r="K151" s="12" t="n">
-        <v>5344.2</v>
-      </c>
-      <c r="L151" s="12" t="n">
-        <v>2746</v>
-      </c>
-      <c r="M151" s="12" t="n">
-        <v>3585</v>
       </c>
       <c r="N151" s="12" t="n"/>
       <c r="O151" s="12" t="n"/>
       <c r="P151" s="12" t="n"/>
       <c r="Q151" s="12" t="n">
+        <v>121498.43</v>
+      </c>
+      <c r="R151" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" outlineLevel="2">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>Ancy &amp; Shaya</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>Shaya</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="n"/>
+      <c r="G152" s="12" t="n"/>
+      <c r="H152" s="12" t="n"/>
+      <c r="I152" s="12" t="n">
+        <v>3829</v>
+      </c>
+      <c r="J152" s="12" t="n">
+        <v>9830.799999999999</v>
+      </c>
+      <c r="K152" s="12" t="n">
+        <v>5344.2</v>
+      </c>
+      <c r="L152" s="12" t="n">
+        <v>2746</v>
+      </c>
+      <c r="M152" s="12" t="n">
+        <v>3585</v>
+      </c>
+      <c r="N152" s="12" t="n"/>
+      <c r="O152" s="12" t="n"/>
+      <c r="P152" s="12" t="n"/>
+      <c r="Q152" s="12" t="n">
         <v>25335</v>
       </c>
-      <c r="R151" s="3" t="inlineStr">
+      <c r="R152" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="152" outlineLevel="2">
-      <c r="A152" s="13" t="inlineStr">
+    <row r="153" outlineLevel="2">
+      <c r="A153" s="13" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="B152" s="13" t="inlineStr">
+      <c r="B153" s="13" t="inlineStr">
         <is>
           <t>Shaya ≈</t>
         </is>
       </c>
-      <c r="C152" s="13" t="inlineStr">
+      <c r="C153" s="13" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D152" s="13" t="inlineStr">
+      <c r="D153" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E152" s="13" t="inlineStr">
+      <c r="E153" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F152" s="13" t="inlineStr">
+      <c r="F153" s="13" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="G152" s="14" t="n"/>
-      <c r="H152" s="14" t="n"/>
-      <c r="I152" s="14" t="n">
+      <c r="G153" s="14" t="n"/>
+      <c r="H153" s="14" t="n"/>
+      <c r="I153" s="14" t="n">
         <v>153.16</v>
       </c>
-      <c r="J152" s="14" t="n">
+      <c r="J153" s="14" t="n">
         <v>393.98</v>
       </c>
-      <c r="K152" s="14" t="n">
+      <c r="K153" s="14" t="n">
         <v>209.63</v>
       </c>
-      <c r="L152" s="14" t="n">
+      <c r="L153" s="14" t="n">
         <v>112.52</v>
       </c>
-      <c r="M152" s="14" t="n">
+      <c r="M153" s="14" t="n">
         <v>142.81</v>
       </c>
-      <c r="N152" s="14" t="n"/>
-      <c r="O152" s="14" t="n"/>
-      <c r="P152" s="14" t="n"/>
-      <c r="Q152" s="14" t="n">
+      <c r="N153" s="14" t="n"/>
+      <c r="O153" s="14" t="n"/>
+      <c r="P153" s="14" t="n"/>
+      <c r="Q153" s="14" t="n">
         <v>1012.09</v>
       </c>
-      <c r="R152" s="3" t="inlineStr">
+      <c r="R153" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" outlineLevel="2">
-      <c r="A153" s="11" t="inlineStr">
-        <is>
-          <t>Ancy &amp; Shaya</t>
-        </is>
-      </c>
-      <c r="B153" s="11" t="inlineStr">
-        <is>
-          <t>Shaya</t>
-        </is>
-      </c>
-      <c r="C153" s="11" t="inlineStr">
-        <is>
-          <t>Noon</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E153" s="11" t="inlineStr">
-        <is>
-          <t>SaaS</t>
-        </is>
-      </c>
-      <c r="F153" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G153" s="12" t="n"/>
-      <c r="H153" s="12" t="n"/>
-      <c r="I153" s="12" t="n"/>
-      <c r="J153" s="12" t="n"/>
-      <c r="K153" s="12" t="n"/>
-      <c r="L153" s="12" t="n"/>
-      <c r="M153" s="12" t="n">
-        <v>44948.37</v>
-      </c>
-      <c r="N153" s="12" t="n"/>
-      <c r="O153" s="12" t="n"/>
-      <c r="P153" s="12" t="n"/>
-      <c r="Q153" s="12" t="n">
-        <v>44948.37</v>
-      </c>
-      <c r="R153" s="3" t="inlineStr">
-        <is>
-          <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13006,7 @@
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>Trendyol</t>
+          <t>Noon</t>
         </is>
       </c>
       <c r="D154" s="11" t="inlineStr">
@@ -13012,152 +13016,156 @@
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F154" s="11" t="n"/>
-      <c r="G154" s="12" t="n">
-        <v>16003.24</v>
-      </c>
-      <c r="H154" s="12" t="n">
-        <v>3763.58</v>
-      </c>
-      <c r="I154" s="12" t="n">
-        <v>2010.63</v>
-      </c>
-      <c r="J154" s="12" t="n">
-        <v>3913.53</v>
-      </c>
-      <c r="K154" s="12" t="n">
-        <v>16365.04</v>
-      </c>
-      <c r="L154" s="12" t="n">
-        <v>5033.17</v>
-      </c>
+          <t>SaaS</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G154" s="12" t="n"/>
+      <c r="H154" s="12" t="n"/>
+      <c r="I154" s="12" t="n"/>
+      <c r="J154" s="12" t="n"/>
+      <c r="K154" s="12" t="n"/>
+      <c r="L154" s="12" t="n"/>
       <c r="M154" s="12" t="n">
-        <v>4125.87</v>
+        <v>44948.37</v>
       </c>
       <c r="N154" s="12" t="n"/>
       <c r="O154" s="12" t="n"/>
       <c r="P154" s="12" t="n"/>
       <c r="Q154" s="12" t="n">
+        <v>44948.37</v>
+      </c>
+      <c r="R154" s="3" t="inlineStr">
+        <is>
+          <t>Nasam platform — revenue view</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" outlineLevel="2">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>Ancy &amp; Shaya</t>
+        </is>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>Shaya</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr">
+        <is>
+          <t>Trendyol</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="n"/>
+      <c r="G155" s="12" t="n">
+        <v>16003.24</v>
+      </c>
+      <c r="H155" s="12" t="n">
+        <v>3763.58</v>
+      </c>
+      <c r="I155" s="12" t="n">
+        <v>2010.63</v>
+      </c>
+      <c r="J155" s="12" t="n">
+        <v>3913.53</v>
+      </c>
+      <c r="K155" s="12" t="n">
+        <v>16365.04</v>
+      </c>
+      <c r="L155" s="12" t="n">
+        <v>5033.17</v>
+      </c>
+      <c r="M155" s="12" t="n">
+        <v>4125.87</v>
+      </c>
+      <c r="N155" s="12" t="n"/>
+      <c r="O155" s="12" t="n"/>
+      <c r="P155" s="12" t="n"/>
+      <c r="Q155" s="12" t="n">
         <v>51215.06</v>
       </c>
-      <c r="R154" s="3" t="inlineStr">
+      <c r="R155" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="155" outlineLevel="2">
-      <c r="A155" s="13" t="inlineStr">
+    <row r="156" outlineLevel="2">
+      <c r="A156" s="13" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="B155" s="13" t="inlineStr">
+      <c r="B156" s="13" t="inlineStr">
         <is>
           <t>Shaya ≈</t>
         </is>
       </c>
-      <c r="C155" s="13" t="inlineStr">
+      <c r="C156" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D155" s="13" t="inlineStr">
+      <c r="D156" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E155" s="13" t="inlineStr">
+      <c r="E156" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F155" s="13" t="inlineStr">
+      <c r="F156" s="13" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="G155" s="14" t="n">
+      <c r="G156" s="14" t="n">
         <v>638.97</v>
       </c>
-      <c r="H155" s="14" t="n">
+      <c r="H156" s="14" t="n">
         <v>150.54</v>
       </c>
-      <c r="I155" s="14" t="n">
+      <c r="I156" s="14" t="n">
         <v>106.45</v>
       </c>
-      <c r="J155" s="14" t="n">
+      <c r="J156" s="14" t="n">
         <v>548.95</v>
       </c>
-      <c r="K155" s="14" t="n">
+      <c r="K156" s="14" t="n">
         <v>694.45</v>
       </c>
-      <c r="L155" s="14" t="n">
+      <c r="L156" s="14" t="n">
         <v>204.6</v>
       </c>
-      <c r="M155" s="14" t="n">
+      <c r="M156" s="14" t="n">
         <v>183.05</v>
       </c>
-      <c r="N155" s="14" t="n"/>
-      <c r="O155" s="14" t="n"/>
-      <c r="P155" s="14" t="n"/>
-      <c r="Q155" s="14" t="n">
-        <v>2527.01</v>
-      </c>
-      <c r="R155" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" outlineLevel="1">
-      <c r="A156" s="13" t="inlineStr">
-        <is>
-          <t>Ancy &amp; Shaya</t>
-        </is>
-      </c>
-      <c r="B156" s="13" t="inlineStr">
-        <is>
-          <t>— all brands</t>
-        </is>
-      </c>
-      <c r="C156" s="13" t="inlineStr">
-        <is>
-          <t>Amazon Retail</t>
-        </is>
-      </c>
-      <c r="D156" s="13" t="inlineStr">
-        <is>
-          <t>Commission (billed)</t>
-        </is>
-      </c>
-      <c r="E156" s="13" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F156" s="13" t="inlineStr"/>
-      <c r="G156" s="14" t="n">
-        <v>107.15</v>
-      </c>
-      <c r="H156" s="14" t="n"/>
-      <c r="I156" s="14" t="n"/>
-      <c r="J156" s="14" t="n"/>
-      <c r="K156" s="14" t="n"/>
-      <c r="L156" s="14" t="n"/>
-      <c r="M156" s="14" t="n"/>
       <c r="N156" s="14" t="n"/>
       <c r="O156" s="14" t="n"/>
       <c r="P156" s="14" t="n"/>
       <c r="Q156" s="14" t="n">
-        <v>107.15</v>
+        <v>2527.01</v>
       </c>
       <c r="R156" s="3" t="inlineStr">
         <is>
-          <t>Wafeq invoice export</t>
+          <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
@@ -13169,147 +13177,137 @@
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C157" s="13" t="n"/>
+          <t>— all brands</t>
+        </is>
+      </c>
+      <c r="C157" s="13" t="inlineStr">
+        <is>
+          <t>Amazon Retail</t>
+        </is>
+      </c>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E157" s="13" t="n"/>
-      <c r="F157" s="13" t="n"/>
+          <t>Commission (billed)</t>
+        </is>
+      </c>
+      <c r="E157" s="13" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F157" s="13" t="inlineStr"/>
       <c r="G157" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H157" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I157" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J157" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K157" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L157" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="M157" s="14" t="n">
-        <v>919.35</v>
-      </c>
+        <v>107.15</v>
+      </c>
+      <c r="H157" s="14" t="n"/>
+      <c r="I157" s="14" t="n"/>
+      <c r="J157" s="14" t="n"/>
+      <c r="K157" s="14" t="n"/>
+      <c r="L157" s="14" t="n"/>
+      <c r="M157" s="14" t="n"/>
       <c r="N157" s="14" t="n"/>
       <c r="O157" s="14" t="n"/>
       <c r="P157" s="14" t="n"/>
       <c r="Q157" s="14" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="R157" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" outlineLevel="1">
+      <c r="A158" s="13" t="inlineStr">
+        <is>
+          <t>Ancy &amp; Shaya</t>
+        </is>
+      </c>
+      <c r="B158" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C158" s="13" t="n"/>
+      <c r="D158" s="13" t="inlineStr">
+        <is>
+          <t>Monthly fee</t>
+        </is>
+      </c>
+      <c r="E158" s="13" t="n"/>
+      <c r="F158" s="13" t="n"/>
+      <c r="G158" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H158" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I158" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J158" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K158" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L158" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M158" s="14" t="n">
+        <v>919.35</v>
+      </c>
+      <c r="N158" s="14" t="n"/>
+      <c r="O158" s="14" t="n"/>
+      <c r="P158" s="14" t="n"/>
+      <c r="Q158" s="14" t="n">
         <v>9919.35</v>
       </c>
-      <c r="R157" s="3" t="inlineStr">
+      <c r="R158" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="9" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
         <is>
           <t>Gamesir  (churned 2026-02)</t>
         </is>
       </c>
-      <c r="B159" s="9" t="n"/>
-      <c r="C159" s="9" t="n"/>
-      <c r="D159" s="9" t="inlineStr">
+      <c r="B160" s="9" t="n"/>
+      <c r="C160" s="9" t="n"/>
+      <c r="D160" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E159" s="9" t="n"/>
-      <c r="F159" s="9" t="n"/>
-      <c r="G159" s="10" t="n">
+      <c r="E160" s="9" t="n"/>
+      <c r="F160" s="9" t="n"/>
+      <c r="G160" s="10" t="n">
         <v>3161.37</v>
       </c>
-      <c r="H159" s="10" t="n">
+      <c r="H160" s="10" t="n">
         <v>2732.77</v>
       </c>
-      <c r="I159" s="10" t="n">
+      <c r="I160" s="10" t="n">
         <v>5143.07</v>
       </c>
-      <c r="J159" s="10" t="n">
+      <c r="J160" s="10" t="n">
         <v>512.96</v>
       </c>
-      <c r="K159" s="10" t="n"/>
-      <c r="L159" s="10" t="n"/>
-      <c r="M159" s="10" t="n"/>
-      <c r="N159" s="10" t="n"/>
-      <c r="O159" s="10" t="n"/>
-      <c r="P159" s="10" t="n"/>
-      <c r="Q159" s="10" t="n">
+      <c r="K160" s="10" t="n"/>
+      <c r="L160" s="10" t="n"/>
+      <c r="M160" s="10" t="n"/>
+      <c r="N160" s="10" t="n"/>
+      <c r="O160" s="10" t="n"/>
+      <c r="P160" s="10" t="n"/>
+      <c r="Q160" s="10" t="n">
         <v>11550.17</v>
       </c>
-      <c r="R159" s="3" t="inlineStr">
+      <c r="R160" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · Card: 1.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" outlineLevel="1">
-      <c r="A160" s="13" t="inlineStr">
-        <is>
-          <t>Gamesir</t>
-        </is>
-      </c>
-      <c r="B160" s="13" t="inlineStr">
-        <is>
-          <t>— (no platform brand)</t>
-        </is>
-      </c>
-      <c r="C160" s="13" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D160" s="13" t="inlineStr">
-        <is>
-          <t>Commission (billed)</t>
-        </is>
-      </c>
-      <c r="E160" s="13" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F160" s="13" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G160" s="14" t="n">
-        <v>141.12</v>
-      </c>
-      <c r="H160" s="14" t="n">
-        <v>497.2</v>
-      </c>
-      <c r="I160" s="14" t="n">
-        <v>3143.07</v>
-      </c>
-      <c r="J160" s="14" t="n">
-        <v>227.25</v>
-      </c>
-      <c r="K160" s="14" t="n"/>
-      <c r="L160" s="14" t="n"/>
-      <c r="M160" s="14" t="n"/>
-      <c r="N160" s="14" t="n"/>
-      <c r="O160" s="14" t="n"/>
-      <c r="P160" s="14" t="n"/>
-      <c r="Q160" s="14" t="n">
-        <v>4008.64</v>
-      </c>
-      <c r="R160" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
@@ -13326,7 +13324,7 @@
       </c>
       <c r="C161" s="13" t="inlineStr">
         <is>
-          <t>Noon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D161" s="13" t="inlineStr">
@@ -13339,15 +13337,23 @@
           <t>FAM</t>
         </is>
       </c>
-      <c r="F161" s="13" t="inlineStr"/>
+      <c r="F161" s="13" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
       <c r="G161" s="14" t="n">
-        <v>53.58</v>
+        <v>141.12</v>
       </c>
       <c r="H161" s="14" t="n">
-        <v>235.57</v>
-      </c>
-      <c r="I161" s="14" t="n"/>
-      <c r="J161" s="14" t="n"/>
+        <v>497.2</v>
+      </c>
+      <c r="I161" s="14" t="n">
+        <v>3143.07</v>
+      </c>
+      <c r="J161" s="14" t="n">
+        <v>227.25</v>
+      </c>
       <c r="K161" s="14" t="n"/>
       <c r="L161" s="14" t="n"/>
       <c r="M161" s="14" t="n"/>
@@ -13355,7 +13361,7 @@
       <c r="O161" s="14" t="n"/>
       <c r="P161" s="14" t="n"/>
       <c r="Q161" s="14" t="n">
-        <v>289.15</v>
+        <v>4008.64</v>
       </c>
       <c r="R161" s="3" t="inlineStr">
         <is>
@@ -13371,29 +13377,33 @@
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C162" s="13" t="n"/>
+          <t>— (no platform brand)</t>
+        </is>
+      </c>
+      <c r="C162" s="13" t="inlineStr">
+        <is>
+          <t>Noon</t>
+        </is>
+      </c>
       <c r="D162" s="13" t="inlineStr">
         <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E162" s="13" t="n"/>
-      <c r="F162" s="13" t="n"/>
+          <t>Commission (billed)</t>
+        </is>
+      </c>
+      <c r="E162" s="13" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F162" s="13" t="inlineStr"/>
       <c r="G162" s="14" t="n">
-        <v>2466.67</v>
+        <v>53.58</v>
       </c>
       <c r="H162" s="14" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I162" s="14" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J162" s="14" t="n">
-        <v>285.71</v>
-      </c>
+        <v>235.57</v>
+      </c>
+      <c r="I162" s="14" t="n"/>
+      <c r="J162" s="14" t="n"/>
       <c r="K162" s="14" t="n"/>
       <c r="L162" s="14" t="n"/>
       <c r="M162" s="14" t="n"/>
@@ -13401,7 +13411,7 @@
       <c r="O162" s="14" t="n"/>
       <c r="P162" s="14" t="n"/>
       <c r="Q162" s="14" t="n">
-        <v>6752.38</v>
+        <v>289.15</v>
       </c>
       <c r="R162" s="3" t="inlineStr">
         <is>
@@ -13423,17 +13433,23 @@
       <c r="C163" s="13" t="n"/>
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>Setup / one-time</t>
+          <t>Monthly fee</t>
         </is>
       </c>
       <c r="E163" s="13" t="n"/>
       <c r="F163" s="13" t="n"/>
       <c r="G163" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="H163" s="14" t="n"/>
-      <c r="I163" s="14" t="n"/>
-      <c r="J163" s="14" t="n"/>
+        <v>2466.67</v>
+      </c>
+      <c r="H163" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I163" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J163" s="14" t="n">
+        <v>285.71</v>
+      </c>
       <c r="K163" s="14" t="n"/>
       <c r="L163" s="14" t="n"/>
       <c r="M163" s="14" t="n"/>
@@ -13441,165 +13457,147 @@
       <c r="O163" s="14" t="n"/>
       <c r="P163" s="14" t="n"/>
       <c r="Q163" s="14" t="n">
+        <v>6752.38</v>
+      </c>
+      <c r="R163" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" outlineLevel="1">
+      <c r="A164" s="13" t="inlineStr">
+        <is>
+          <t>Gamesir</t>
+        </is>
+      </c>
+      <c r="B164" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C164" s="13" t="n"/>
+      <c r="D164" s="13" t="inlineStr">
+        <is>
+          <t>Setup / one-time</t>
+        </is>
+      </c>
+      <c r="E164" s="13" t="n"/>
+      <c r="F164" s="13" t="n"/>
+      <c r="G164" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="R163" s="3" t="inlineStr">
+      <c r="H164" s="14" t="n"/>
+      <c r="I164" s="14" t="n"/>
+      <c r="J164" s="14" t="n"/>
+      <c r="K164" s="14" t="n"/>
+      <c r="L164" s="14" t="n"/>
+      <c r="M164" s="14" t="n"/>
+      <c r="N164" s="14" t="n"/>
+      <c r="O164" s="14" t="n"/>
+      <c r="P164" s="14" t="n"/>
+      <c r="Q164" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="R164" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="9" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
         <is>
           <t>Safwat Aljouf  (churned 2026-02)</t>
         </is>
       </c>
-      <c r="B165" s="9" t="n"/>
-      <c r="C165" s="9" t="n"/>
-      <c r="D165" s="9" t="inlineStr">
+      <c r="B166" s="9" t="n"/>
+      <c r="C166" s="9" t="n"/>
+      <c r="D166" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E165" s="9" t="n"/>
-      <c r="F165" s="9" t="n"/>
-      <c r="G165" s="10" t="n">
+      <c r="E166" s="9" t="n"/>
+      <c r="F166" s="9" t="n"/>
+      <c r="G166" s="10" t="n">
         <v>3585.43</v>
       </c>
-      <c r="H165" s="10" t="n">
+      <c r="H166" s="10" t="n">
         <v>2564.26</v>
       </c>
-      <c r="I165" s="10" t="n">
+      <c r="I166" s="10" t="n">
         <v>2607.58</v>
       </c>
-      <c r="J165" s="10" t="n">
+      <c r="J166" s="10" t="n">
         <v>837.29</v>
       </c>
-      <c r="K165" s="10" t="n"/>
-      <c r="L165" s="10" t="n"/>
-      <c r="M165" s="10" t="n"/>
-      <c r="N165" s="10" t="n"/>
-      <c r="O165" s="10" t="n"/>
-      <c r="P165" s="10" t="n"/>
-      <c r="Q165" s="10" t="n">
+      <c r="K166" s="10" t="n"/>
+      <c r="L166" s="10" t="n"/>
+      <c r="M166" s="10" t="n"/>
+      <c r="N166" s="10" t="n"/>
+      <c r="O166" s="10" t="n"/>
+      <c r="P166" s="10" t="n"/>
+      <c r="Q166" s="10" t="n">
         <v>9594.559999999999</v>
       </c>
-      <c r="R165" s="3" t="inlineStr">
+      <c r="R166" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · Card: 6%</t>
         </is>
       </c>
     </row>
-    <row r="166" outlineLevel="1">
-      <c r="A166" s="11" t="inlineStr">
+    <row r="167" outlineLevel="1">
+      <c r="A167" s="11" t="inlineStr">
         <is>
           <t>Safwat Aljouf</t>
         </is>
       </c>
-      <c r="B166" s="11" t="inlineStr">
+      <c r="B167" s="11" t="inlineStr">
         <is>
           <t>Safwat Aljawf</t>
         </is>
       </c>
-      <c r="C166" s="11" t="inlineStr">
+      <c r="C167" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D166" s="11" t="inlineStr">
+      <c r="D167" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E166" s="11" t="inlineStr">
+      <c r="E167" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F166" s="11" t="n"/>
-      <c r="G166" s="12" t="n">
+      <c r="F167" s="11" t="n"/>
+      <c r="G167" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="H166" s="12" t="n">
+      <c r="H167" s="12" t="n">
         <v>1071</v>
       </c>
-      <c r="I166" s="12" t="n">
+      <c r="I167" s="12" t="n">
         <v>2033</v>
       </c>
-      <c r="J166" s="12" t="n">
+      <c r="J167" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="K166" s="12" t="n"/>
-      <c r="L166" s="12" t="n"/>
-      <c r="M166" s="12" t="n"/>
-      <c r="N166" s="12" t="n"/>
-      <c r="O166" s="12" t="n"/>
-      <c r="P166" s="12" t="n"/>
-      <c r="Q166" s="12" t="n">
+      <c r="K167" s="12" t="n"/>
+      <c r="L167" s="12" t="n"/>
+      <c r="M167" s="12" t="n"/>
+      <c r="N167" s="12" t="n"/>
+      <c r="O167" s="12" t="n"/>
+      <c r="P167" s="12" t="n"/>
+      <c r="Q167" s="12" t="n">
         <v>3205</v>
       </c>
-      <c r="R166" s="3" t="inlineStr">
+      <c r="R167" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" outlineLevel="1">
-      <c r="A167" s="13" t="inlineStr">
-        <is>
-          <t>Safwat Aljouf</t>
-        </is>
-      </c>
-      <c r="B167" s="13" t="inlineStr">
-        <is>
-          <t>Safwat Aljawf</t>
-        </is>
-      </c>
-      <c r="C167" s="13" t="inlineStr">
-        <is>
-          <t>Trendyol</t>
-        </is>
-      </c>
-      <c r="D167" s="13" t="inlineStr">
-        <is>
-          <t>Commission (billed)</t>
-        </is>
-      </c>
-      <c r="E167" s="13" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F167" s="13" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="G167" s="14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H167" s="14" t="n">
-        <v>64.26000000000001</v>
-      </c>
-      <c r="I167" s="14" t="n">
-        <v>107.58</v>
-      </c>
-      <c r="J167" s="14" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="K167" s="14" t="n"/>
-      <c r="L167" s="14" t="n"/>
-      <c r="M167" s="14" t="n"/>
-      <c r="N167" s="14" t="n"/>
-      <c r="O167" s="14" t="n"/>
-      <c r="P167" s="14" t="n"/>
-      <c r="Q167" s="14" t="n">
-        <v>177.9</v>
-      </c>
-      <c r="R167" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
@@ -13611,28 +13609,40 @@
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C168" s="13" t="n"/>
+          <t>Safwat Aljawf</t>
+        </is>
+      </c>
+      <c r="C168" s="13" t="inlineStr">
+        <is>
+          <t>Trendyol</t>
+        </is>
+      </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E168" s="13" t="n"/>
-      <c r="F168" s="13" t="n"/>
+          <t>Commission (billed)</t>
+        </is>
+      </c>
+      <c r="E168" s="13" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F168" s="13" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
       <c r="G168" s="14" t="n">
-        <v>1083.33</v>
+        <v>2.1</v>
       </c>
       <c r="H168" s="14" t="n">
-        <v>2500</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I168" s="14" t="n">
-        <v>2500</v>
+        <v>107.58</v>
       </c>
       <c r="J168" s="14" t="n">
-        <v>833.33</v>
+        <v>3.96</v>
       </c>
       <c r="K168" s="14" t="n"/>
       <c r="L168" s="14" t="n"/>
@@ -13641,7 +13651,7 @@
       <c r="O168" s="14" t="n"/>
       <c r="P168" s="14" t="n"/>
       <c r="Q168" s="14" t="n">
-        <v>6916.66</v>
+        <v>177.9</v>
       </c>
       <c r="R168" s="3" t="inlineStr">
         <is>
@@ -13663,17 +13673,23 @@
       <c r="C169" s="13" t="n"/>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>Setup / one-time</t>
+          <t>Monthly fee</t>
         </is>
       </c>
       <c r="E169" s="13" t="n"/>
       <c r="F169" s="13" t="n"/>
       <c r="G169" s="14" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="H169" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="H169" s="14" t="n"/>
-      <c r="I169" s="14" t="n"/>
-      <c r="J169" s="14" t="n"/>
+      <c r="I169" s="14" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J169" s="14" t="n">
+        <v>833.33</v>
+      </c>
       <c r="K169" s="14" t="n"/>
       <c r="L169" s="14" t="n"/>
       <c r="M169" s="14" t="n"/>
@@ -13681,271 +13697,253 @@
       <c r="O169" s="14" t="n"/>
       <c r="P169" s="14" t="n"/>
       <c r="Q169" s="14" t="n">
+        <v>6916.66</v>
+      </c>
+      <c r="R169" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" outlineLevel="1">
+      <c r="A170" s="13" t="inlineStr">
+        <is>
+          <t>Safwat Aljouf</t>
+        </is>
+      </c>
+      <c r="B170" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C170" s="13" t="n"/>
+      <c r="D170" s="13" t="inlineStr">
+        <is>
+          <t>Setup / one-time</t>
+        </is>
+      </c>
+      <c r="E170" s="13" t="n"/>
+      <c r="F170" s="13" t="n"/>
+      <c r="G170" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="R169" s="3" t="inlineStr">
+      <c r="H170" s="14" t="n"/>
+      <c r="I170" s="14" t="n"/>
+      <c r="J170" s="14" t="n"/>
+      <c r="K170" s="14" t="n"/>
+      <c r="L170" s="14" t="n"/>
+      <c r="M170" s="14" t="n"/>
+      <c r="N170" s="14" t="n"/>
+      <c r="O170" s="14" t="n"/>
+      <c r="P170" s="14" t="n"/>
+      <c r="Q170" s="14" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R170" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="9" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="9" t="inlineStr">
         <is>
           <t>Reetal  (churned 2026-06)</t>
         </is>
       </c>
-      <c r="B171" s="9" t="n"/>
-      <c r="C171" s="9" t="n"/>
-      <c r="D171" s="9" t="inlineStr">
+      <c r="B172" s="9" t="n"/>
+      <c r="C172" s="9" t="n"/>
+      <c r="D172" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E171" s="9" t="n"/>
-      <c r="F171" s="9" t="n"/>
-      <c r="G171" s="10" t="n"/>
-      <c r="H171" s="10" t="n"/>
-      <c r="I171" s="10" t="n"/>
-      <c r="J171" s="10" t="n"/>
-      <c r="K171" s="10" t="n">
+      <c r="E172" s="9" t="n"/>
+      <c r="F172" s="9" t="n"/>
+      <c r="G172" s="10" t="n"/>
+      <c r="H172" s="10" t="n"/>
+      <c r="I172" s="10" t="n"/>
+      <c r="J172" s="10" t="n"/>
+      <c r="K172" s="10" t="n">
         <v>4492.3</v>
       </c>
-      <c r="L171" s="10" t="n">
+      <c r="L172" s="10" t="n">
         <v>1033.1</v>
       </c>
-      <c r="M171" s="10" t="n">
+      <c r="M172" s="10" t="n">
         <v>1799.32</v>
       </c>
-      <c r="N171" s="10" t="n">
+      <c r="N172" s="10" t="n">
         <v>684.49</v>
       </c>
-      <c r="O171" s="10" t="n"/>
-      <c r="P171" s="10" t="n"/>
-      <c r="Q171" s="10" t="n">
+      <c r="O172" s="10" t="n"/>
+      <c r="P172" s="10" t="n"/>
+      <c r="Q172" s="10" t="n">
         <v>8009.21</v>
       </c>
-      <c r="R171" s="3" t="inlineStr">
+      <c r="R172" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="172" outlineLevel="1">
-      <c r="A172" s="11" t="inlineStr">
+    <row r="173" outlineLevel="1">
+      <c r="A173" s="11" t="inlineStr">
         <is>
           <t>Reetal</t>
         </is>
       </c>
-      <c r="B172" s="11" t="inlineStr">
+      <c r="B173" s="11" t="inlineStr">
         <is>
           <t>Reetal</t>
         </is>
       </c>
-      <c r="C172" s="11" t="inlineStr">
+      <c r="C173" s="11" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D172" s="11" t="inlineStr">
+      <c r="D173" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E172" s="11" t="inlineStr">
+      <c r="E173" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F172" s="11" t="n"/>
-      <c r="G172" s="12" t="n"/>
-      <c r="H172" s="12" t="n"/>
-      <c r="I172" s="12" t="n"/>
-      <c r="J172" s="12" t="n"/>
-      <c r="K172" s="12" t="n"/>
-      <c r="L172" s="12" t="n">
+      <c r="F173" s="11" t="n"/>
+      <c r="G173" s="12" t="n"/>
+      <c r="H173" s="12" t="n"/>
+      <c r="I173" s="12" t="n"/>
+      <c r="J173" s="12" t="n"/>
+      <c r="K173" s="12" t="n"/>
+      <c r="L173" s="12" t="n">
         <v>280</v>
       </c>
-      <c r="M172" s="12" t="n">
+      <c r="M173" s="12" t="n">
         <v>4670</v>
       </c>
-      <c r="N172" s="12" t="n">
+      <c r="N173" s="12" t="n">
         <v>1150</v>
       </c>
-      <c r="O172" s="12" t="n"/>
-      <c r="P172" s="12" t="n"/>
-      <c r="Q172" s="12" t="n">
+      <c r="O173" s="12" t="n"/>
+      <c r="P173" s="12" t="n"/>
+      <c r="Q173" s="12" t="n">
         <v>6100</v>
       </c>
-      <c r="R172" s="3" t="inlineStr">
+      <c r="R173" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="173" outlineLevel="1">
-      <c r="A173" s="13" t="inlineStr">
+    <row r="174" outlineLevel="1">
+      <c r="A174" s="13" t="inlineStr">
         <is>
           <t>Reetal</t>
         </is>
       </c>
-      <c r="B173" s="13" t="inlineStr">
+      <c r="B174" s="13" t="inlineStr">
         <is>
           <t>Reetal</t>
         </is>
       </c>
-      <c r="C173" s="13" t="inlineStr">
+      <c r="C174" s="13" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D173" s="13" t="inlineStr">
+      <c r="D174" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E173" s="13" t="inlineStr">
+      <c r="E174" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F173" s="13" t="inlineStr">
+      <c r="F174" s="13" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="G173" s="14" t="n"/>
-      <c r="H173" s="14" t="n"/>
-      <c r="I173" s="14" t="n"/>
-      <c r="J173" s="14" t="n"/>
-      <c r="K173" s="14" t="n"/>
-      <c r="L173" s="14" t="n">
+      <c r="G174" s="14" t="n"/>
+      <c r="H174" s="14" t="n"/>
+      <c r="I174" s="14" t="n"/>
+      <c r="J174" s="14" t="n"/>
+      <c r="K174" s="14" t="n"/>
+      <c r="L174" s="14" t="n">
         <v>11.2</v>
       </c>
-      <c r="M173" s="14" t="n">
+      <c r="M174" s="14" t="n">
         <v>189.8</v>
       </c>
-      <c r="N173" s="14" t="n">
+      <c r="N174" s="14" t="n">
         <v>72.5</v>
       </c>
-      <c r="O173" s="14" t="n"/>
-      <c r="P173" s="14" t="n"/>
-      <c r="Q173" s="14" t="n">
+      <c r="O174" s="14" t="n"/>
+      <c r="P174" s="14" t="n"/>
+      <c r="Q174" s="14" t="n">
         <v>273.5</v>
       </c>
-      <c r="R173" s="3" t="inlineStr">
+      <c r="R174" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="174" outlineLevel="1">
-      <c r="A174" s="11" t="inlineStr">
+    <row r="175" outlineLevel="1">
+      <c r="A175" s="11" t="inlineStr">
         <is>
           <t>Reetal</t>
         </is>
       </c>
-      <c r="B174" s="11" t="inlineStr">
+      <c r="B175" s="11" t="inlineStr">
         <is>
           <t>Reetal</t>
         </is>
       </c>
-      <c r="C174" s="11" t="inlineStr">
+      <c r="C175" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D174" s="11" t="inlineStr">
+      <c r="D175" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E174" s="11" t="inlineStr">
+      <c r="E175" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F174" s="11" t="n"/>
-      <c r="G174" s="12" t="n"/>
-      <c r="H174" s="12" t="n"/>
-      <c r="I174" s="12" t="n"/>
-      <c r="J174" s="12" t="n"/>
-      <c r="K174" s="12" t="n"/>
-      <c r="L174" s="12" t="n">
+      <c r="F175" s="11" t="n"/>
+      <c r="G175" s="12" t="n"/>
+      <c r="H175" s="12" t="n"/>
+      <c r="I175" s="12" t="n"/>
+      <c r="J175" s="12" t="n"/>
+      <c r="K175" s="12" t="n"/>
+      <c r="L175" s="12" t="n">
         <v>547.46</v>
       </c>
-      <c r="M174" s="12" t="n">
+      <c r="M175" s="12" t="n">
         <v>614.85</v>
       </c>
-      <c r="N174" s="12" t="n">
+      <c r="N175" s="12" t="n">
         <v>223.04</v>
       </c>
-      <c r="O174" s="12" t="n"/>
-      <c r="P174" s="12" t="n"/>
-      <c r="Q174" s="12" t="n">
+      <c r="O175" s="12" t="n"/>
+      <c r="P175" s="12" t="n"/>
+      <c r="Q175" s="12" t="n">
         <v>1385.35</v>
       </c>
-      <c r="R174" s="3" t="inlineStr">
+      <c r="R175" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" outlineLevel="1">
-      <c r="A175" s="13" t="inlineStr">
-        <is>
-          <t>Reetal</t>
-        </is>
-      </c>
-      <c r="B175" s="13" t="inlineStr">
-        <is>
-          <t>Reetal</t>
-        </is>
-      </c>
-      <c r="C175" s="13" t="inlineStr">
-        <is>
-          <t>Trendyol</t>
-        </is>
-      </c>
-      <c r="D175" s="13" t="inlineStr">
-        <is>
-          <t>Commission (billed)</t>
-        </is>
-      </c>
-      <c r="E175" s="13" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F175" s="13" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="G175" s="14" t="n"/>
-      <c r="H175" s="14" t="n"/>
-      <c r="I175" s="14" t="n"/>
-      <c r="J175" s="14" t="n"/>
-      <c r="K175" s="14" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="L175" s="14" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M175" s="14" t="n">
-        <v>28.92</v>
-      </c>
-      <c r="N175" s="14" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="O175" s="14" t="n"/>
-      <c r="P175" s="14" t="n"/>
-      <c r="Q175" s="14" t="n">
-        <v>71.23999999999999</v>
-      </c>
-      <c r="R175" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
@@ -13957,41 +13955,53 @@
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C176" s="13" t="n"/>
+          <t>Reetal</t>
+        </is>
+      </c>
+      <c r="C176" s="13" t="inlineStr">
+        <is>
+          <t>Trendyol</t>
+        </is>
+      </c>
       <c r="D176" s="13" t="inlineStr">
         <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E176" s="13" t="n"/>
-      <c r="F176" s="13" t="n"/>
+          <t>Commission (billed)</t>
+        </is>
+      </c>
+      <c r="E176" s="13" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F176" s="13" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="G176" s="14" t="n"/>
       <c r="H176" s="14" t="n"/>
       <c r="I176" s="14" t="n"/>
       <c r="J176" s="14" t="n"/>
       <c r="K176" s="14" t="n">
-        <v>1483.87</v>
+        <v>8.43</v>
       </c>
       <c r="L176" s="14" t="n">
-        <v>2000</v>
+        <v>21.9</v>
       </c>
       <c r="M176" s="14" t="n">
-        <v>1580.6</v>
+        <v>28.92</v>
       </c>
       <c r="N176" s="14" t="n">
-        <v>600</v>
+        <v>11.99</v>
       </c>
       <c r="O176" s="14" t="n"/>
       <c r="P176" s="14" t="n"/>
       <c r="Q176" s="14" t="n">
-        <v>5664.47</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="R176" s="3" t="inlineStr">
         <is>
-          <t>Wafeq invoice export · Card 5% + 1,000; billed 4% + 2,000 under setup-period arrangement</t>
+          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
@@ -14009,7 +14019,7 @@
       <c r="C177" s="13" t="n"/>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>Setup / one-time</t>
+          <t>Monthly fee</t>
         </is>
       </c>
       <c r="E177" s="13" t="n"/>
@@ -14019,19 +14029,25 @@
       <c r="I177" s="14" t="n"/>
       <c r="J177" s="14" t="n"/>
       <c r="K177" s="14" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L177" s="14" t="n"/>
-      <c r="M177" s="14" t="n"/>
-      <c r="N177" s="14" t="n"/>
+        <v>1483.87</v>
+      </c>
+      <c r="L177" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M177" s="14" t="n">
+        <v>1580.6</v>
+      </c>
+      <c r="N177" s="14" t="n">
+        <v>600</v>
+      </c>
       <c r="O177" s="14" t="n"/>
       <c r="P177" s="14" t="n"/>
       <c r="Q177" s="14" t="n">
-        <v>3000</v>
+        <v>5664.47</v>
       </c>
       <c r="R177" s="3" t="inlineStr">
         <is>
-          <t>Wafeq invoice export</t>
+          <t>Wafeq invoice export · Card 5% + 1,000; billed 4% + 2,000 under setup-period arrangement</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14065,7 @@
       <c r="C178" s="13" t="n"/>
       <c r="D178" s="13" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>Setup / one-time</t>
         </is>
       </c>
       <c r="E178" s="13" t="n"/>
@@ -14058,242 +14074,282 @@
       <c r="H178" s="14" t="n"/>
       <c r="I178" s="14" t="n"/>
       <c r="J178" s="14" t="n"/>
-      <c r="K178" s="14" t="n"/>
-      <c r="L178" s="14" t="n">
-        <v>-1000</v>
-      </c>
+      <c r="K178" s="14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L178" s="14" t="n"/>
       <c r="M178" s="14" t="n"/>
       <c r="N178" s="14" t="n"/>
       <c r="O178" s="14" t="n"/>
       <c r="P178" s="14" t="n"/>
       <c r="Q178" s="14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="R178" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" outlineLevel="1">
+      <c r="A179" s="13" t="inlineStr">
+        <is>
+          <t>Reetal</t>
+        </is>
+      </c>
+      <c r="B179" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C179" s="13" t="n"/>
+      <c r="D179" s="13" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="E179" s="13" t="n"/>
+      <c r="F179" s="13" t="n"/>
+      <c r="G179" s="14" t="n"/>
+      <c r="H179" s="14" t="n"/>
+      <c r="I179" s="14" t="n"/>
+      <c r="J179" s="14" t="n"/>
+      <c r="K179" s="14" t="n"/>
+      <c r="L179" s="14" t="n">
         <v>-1000</v>
       </c>
-      <c r="R178" s="3" t="inlineStr">
+      <c r="M179" s="14" t="n"/>
+      <c r="N179" s="14" t="n"/>
+      <c r="O179" s="14" t="n"/>
+      <c r="P179" s="14" t="n"/>
+      <c r="Q179" s="14" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="R179" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · setup-period 50% AM fee / agreed reduction / pricing error</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="9" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="9" t="inlineStr">
         <is>
           <t>House Mart  (churned 2026-04)</t>
         </is>
       </c>
-      <c r="B180" s="9" t="n"/>
-      <c r="C180" s="9" t="n"/>
-      <c r="D180" s="9" t="inlineStr">
+      <c r="B181" s="9" t="n"/>
+      <c r="C181" s="9" t="n"/>
+      <c r="D181" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E180" s="9" t="n"/>
-      <c r="F180" s="9" t="n"/>
-      <c r="G180" s="10" t="n">
+      <c r="E181" s="9" t="n"/>
+      <c r="F181" s="9" t="n"/>
+      <c r="G181" s="10" t="n">
         <v>6750</v>
       </c>
-      <c r="H180" s="10" t="n"/>
-      <c r="I180" s="10" t="n"/>
-      <c r="J180" s="10" t="n"/>
-      <c r="K180" s="10" t="n"/>
-      <c r="L180" s="10" t="n">
+      <c r="H181" s="10" t="n"/>
+      <c r="I181" s="10" t="n"/>
+      <c r="J181" s="10" t="n"/>
+      <c r="K181" s="10" t="n"/>
+      <c r="L181" s="10" t="n">
         <v>8800.5</v>
       </c>
-      <c r="M180" s="10" t="n"/>
-      <c r="N180" s="10" t="n"/>
-      <c r="O180" s="10" t="n"/>
-      <c r="P180" s="10" t="n"/>
-      <c r="Q180" s="10" t="n">
+      <c r="M181" s="10" t="n"/>
+      <c r="N181" s="10" t="n"/>
+      <c r="O181" s="10" t="n"/>
+      <c r="P181" s="10" t="n"/>
+      <c r="Q181" s="10" t="n">
         <v>15550.5</v>
       </c>
-      <c r="R180" s="3" t="inlineStr">
+      <c r="R181" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="181" outlineLevel="1">
-      <c r="A181" s="13" t="inlineStr">
+    <row r="182" outlineLevel="1">
+      <c r="A182" s="13" t="inlineStr">
         <is>
           <t>House Mart</t>
         </is>
       </c>
-      <c r="B181" s="13" t="inlineStr">
+      <c r="B182" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C181" s="13" t="n"/>
-      <c r="D181" s="13" t="inlineStr">
+      <c r="C182" s="13" t="n"/>
+      <c r="D182" s="13" t="inlineStr">
         <is>
           <t>Setup / one-time</t>
         </is>
       </c>
-      <c r="E181" s="13" t="n"/>
-      <c r="F181" s="13" t="n"/>
-      <c r="G181" s="14" t="n">
+      <c r="E182" s="13" t="n"/>
+      <c r="F182" s="13" t="n"/>
+      <c r="G182" s="14" t="n">
         <v>6750</v>
       </c>
-      <c r="H181" s="14" t="n"/>
-      <c r="I181" s="14" t="n"/>
-      <c r="J181" s="14" t="n"/>
-      <c r="K181" s="14" t="n"/>
-      <c r="L181" s="14" t="n">
+      <c r="H182" s="14" t="n"/>
+      <c r="I182" s="14" t="n"/>
+      <c r="J182" s="14" t="n"/>
+      <c r="K182" s="14" t="n"/>
+      <c r="L182" s="14" t="n">
         <v>8800.5</v>
       </c>
-      <c r="M181" s="14" t="n"/>
-      <c r="N181" s="14" t="n"/>
-      <c r="O181" s="14" t="n"/>
-      <c r="P181" s="14" t="n"/>
-      <c r="Q181" s="14" t="n">
+      <c r="M182" s="14" t="n"/>
+      <c r="N182" s="14" t="n"/>
+      <c r="O182" s="14" t="n"/>
+      <c r="P182" s="14" t="n"/>
+      <c r="Q182" s="14" t="n">
         <v>15550.5</v>
       </c>
-      <c r="R181" s="3" t="inlineStr">
+      <c r="R182" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="6" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
         <is>
           <t>ALL CLIENTS</t>
         </is>
       </c>
-      <c r="B183" s="6" t="n"/>
-      <c r="C183" s="6" t="n"/>
-      <c r="D183" s="6" t="inlineStr">
+      <c r="B184" s="6" t="n"/>
+      <c r="C184" s="6" t="n"/>
+      <c r="D184" s="6" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E183" s="6" t="n"/>
-      <c r="F183" s="6" t="n"/>
-      <c r="G183" s="18" t="n">
+      <c r="E184" s="6" t="n"/>
+      <c r="F184" s="6" t="n"/>
+      <c r="G184" s="18" t="n">
         <v>31390.44</v>
       </c>
-      <c r="H183" s="18" t="n">
+      <c r="H184" s="18" t="n">
         <v>21947.73</v>
       </c>
-      <c r="I183" s="18" t="n">
+      <c r="I184" s="18" t="n">
         <v>26212.8</v>
       </c>
-      <c r="J183" s="18" t="n">
+      <c r="J184" s="18" t="n">
         <v>19517.67</v>
       </c>
-      <c r="K183" s="18" t="n">
+      <c r="K184" s="18" t="n">
         <v>27125.53</v>
       </c>
-      <c r="L183" s="18" t="n">
+      <c r="L184" s="18" t="n">
         <v>27486.22</v>
       </c>
-      <c r="M183" s="18" t="n">
+      <c r="M184" s="18" t="n">
         <v>21956.43</v>
       </c>
-      <c r="N183" s="18" t="n">
+      <c r="N184" s="18" t="n">
         <v>16243.45</v>
       </c>
-      <c r="O183" s="18" t="n">
+      <c r="O184" s="18" t="n">
         <v>7298.95</v>
       </c>
-      <c r="P183" s="18" t="n">
+      <c r="P184" s="18" t="n">
         <v>2680.88</v>
       </c>
-      <c r="Q183" s="18" t="n">
+      <c r="Q184" s="18" t="n">
         <v>201860.1</v>
       </c>
-      <c r="R183" s="3" t="inlineStr">
+      <c r="R184" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="16" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="16" t="inlineStr">
         <is>
           <t>ALL CLIENTS</t>
         </is>
       </c>
-      <c r="B184" s="16" t="n"/>
-      <c r="C184" s="16" t="n"/>
-      <c r="D184" s="16" t="inlineStr">
+      <c r="B185" s="16" t="n"/>
+      <c r="C185" s="16" t="n"/>
+      <c r="D185" s="16" t="inlineStr">
         <is>
           <t>Commission (to invoice)</t>
         </is>
       </c>
-      <c r="E184" s="16" t="n"/>
-      <c r="F184" s="16" t="n"/>
-      <c r="G184" s="17" t="n"/>
-      <c r="H184" s="17" t="n"/>
-      <c r="I184" s="17" t="n"/>
-      <c r="J184" s="17" t="n"/>
-      <c r="K184" s="17" t="n"/>
-      <c r="L184" s="17" t="n"/>
-      <c r="M184" s="17" t="n"/>
-      <c r="N184" s="17" t="n"/>
-      <c r="O184" s="17" t="n"/>
-      <c r="P184" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q184" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R184" s="3" t="inlineStr">
+      <c r="E185" s="16" t="n"/>
+      <c r="F185" s="16" t="n"/>
+      <c r="G185" s="17" t="n"/>
+      <c r="H185" s="17" t="n"/>
+      <c r="I185" s="17" t="n"/>
+      <c r="J185" s="17" t="n"/>
+      <c r="K185" s="17" t="n"/>
+      <c r="L185" s="17" t="n"/>
+      <c r="M185" s="17" t="n"/>
+      <c r="N185" s="17" t="n"/>
+      <c r="O185" s="17" t="n"/>
+      <c r="P185" s="17" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="Q185" s="17" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="R185" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — closed POs</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="6" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
         <is>
           <t>ALL CLIENTS</t>
         </is>
       </c>
-      <c r="B185" s="6" t="n"/>
-      <c r="C185" s="6" t="n"/>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="B186" s="6" t="n"/>
+      <c r="C186" s="6" t="n"/>
+      <c r="D186" s="6" t="inlineStr">
         <is>
           <t>TOTAL incl. to-invoice</t>
         </is>
       </c>
-      <c r="E185" s="6" t="n"/>
-      <c r="F185" s="6" t="n"/>
-      <c r="G185" s="18" t="n">
+      <c r="E186" s="6" t="n"/>
+      <c r="F186" s="6" t="n"/>
+      <c r="G186" s="18" t="n">
         <v>31390.44</v>
       </c>
-      <c r="H185" s="18" t="n">
+      <c r="H186" s="18" t="n">
         <v>21947.73</v>
       </c>
-      <c r="I185" s="18" t="n">
+      <c r="I186" s="18" t="n">
         <v>26212.8</v>
       </c>
-      <c r="J185" s="18" t="n">
+      <c r="J186" s="18" t="n">
         <v>19517.67</v>
       </c>
-      <c r="K185" s="18" t="n">
+      <c r="K186" s="18" t="n">
         <v>27125.53</v>
       </c>
-      <c r="L185" s="18" t="n">
+      <c r="L186" s="18" t="n">
         <v>27486.22</v>
       </c>
-      <c r="M185" s="18" t="n">
+      <c r="M186" s="18" t="n">
         <v>21956.43</v>
       </c>
-      <c r="N185" s="18" t="n">
+      <c r="N186" s="18" t="n">
         <v>16243.45</v>
       </c>
-      <c r="O185" s="18" t="n">
+      <c r="O186" s="18" t="n">
         <v>7298.95</v>
       </c>
-      <c r="P185" s="18" t="n">
-        <v>2682.88</v>
-      </c>
-      <c r="Q185" s="18" t="n">
-        <v>201862.1</v>
-      </c>
-      <c r="R185" s="3" t="inlineStr">
+      <c r="P186" s="18" t="n">
+        <v>2698.02</v>
+      </c>
+      <c r="Q186" s="18" t="n">
+        <v>201877.24</v>
+      </c>
+      <c r="R186" s="3" t="inlineStr">
         <is>
           <t>Billed + closed-PO commission</t>
         </is>

--- a/revenue-view/output/Nasam_Revenue_View.xlsx
+++ b/revenue-view/output/Nasam_Revenue_View.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N120"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4148,12 +4148,14 @@
         <v>999.75</v>
       </c>
       <c r="J101" s="5" t="n"/>
-      <c r="K101" s="5" t="n"/>
+      <c r="K101" s="5" t="n">
+        <v>449</v>
+      </c>
       <c r="L101" s="5" t="n">
         <v>999.75</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>1999.5</v>
+        <v>2448.5</v>
       </c>
       <c r="N101" s="3" t="inlineStr">
         <is>
@@ -4191,7 +4193,7 @@
     <row r="103" outlineLevel="1">
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SONDOS — annual, paid Aug 2026</t>
+          <t xml:space="preserve">    SONDOS — monthly, paid Jul 2026</t>
         </is>
       </c>
       <c r="C103" s="5" t="n"/>
@@ -4202,12 +4204,12 @@
       <c r="H103" s="5" t="n"/>
       <c r="I103" s="5" t="n"/>
       <c r="J103" s="5" t="n"/>
-      <c r="K103" s="5" t="n"/>
-      <c r="L103" s="5" t="n">
-        <v>999.75</v>
-      </c>
+      <c r="K103" s="5" t="n">
+        <v>449</v>
+      </c>
+      <c r="L103" s="5" t="n"/>
       <c r="M103" s="5" t="n">
-        <v>999.75</v>
+        <v>449</v>
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
@@ -4215,10 +4217,10 @@
         </is>
       </c>
     </row>
-    <row r="104">
+    <row r="104" outlineLevel="1">
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>less: Salla share (15%)</t>
+          <t xml:space="preserve">    SONDOS — annual, paid Aug 2026</t>
         </is>
       </c>
       <c r="C104" s="5" t="n"/>
@@ -4227,156 +4229,142 @@
       <c r="F104" s="5" t="n"/>
       <c r="G104" s="5" t="n"/>
       <c r="H104" s="5" t="n"/>
-      <c r="I104" s="5" t="n">
-        <v>-149.96</v>
-      </c>
+      <c r="I104" s="5" t="n"/>
       <c r="J104" s="5" t="n"/>
       <c r="K104" s="5" t="n"/>
       <c r="L104" s="5" t="n">
+        <v>999.75</v>
+      </c>
+      <c r="M104" s="5" t="n">
+        <v>999.75</v>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>less: Salla share (15%)</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="n"/>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="5" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="5" t="n"/>
+      <c r="I105" s="5" t="n">
         <v>-149.96</v>
       </c>
-      <c r="M104" s="5" t="n">
-        <v>-299.93</v>
-      </c>
-      <c r="N104" s="3" t="inlineStr">
+      <c r="J105" s="5" t="n"/>
+      <c r="K105" s="5" t="n">
+        <v>-67.34999999999999</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>-149.96</v>
+      </c>
+      <c r="M105" s="5" t="n">
+        <v>-367.27</v>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
         <is>
           <t>15% per Tarik — not pullable from Salla</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="B105" s="6" t="inlineStr">
+    <row r="106">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="C105" s="7" t="n">
+      <c r="C106" s="7" t="n">
         <v>31390.44</v>
       </c>
-      <c r="D105" s="7" t="n">
+      <c r="D106" s="7" t="n">
         <v>21947.73</v>
       </c>
-      <c r="E105" s="7" t="n">
+      <c r="E106" s="7" t="n">
         <v>26212.8</v>
       </c>
-      <c r="F105" s="7" t="n">
+      <c r="F106" s="7" t="n">
         <v>19517.67</v>
       </c>
-      <c r="G105" s="7" t="n">
+      <c r="G106" s="7" t="n">
         <v>27125.53</v>
       </c>
-      <c r="H105" s="7" t="n">
+      <c r="H106" s="7" t="n">
         <v>27486.22</v>
       </c>
-      <c r="I105" s="7" t="n">
+      <c r="I106" s="7" t="n">
         <v>22806.22</v>
       </c>
-      <c r="J105" s="7" t="n">
+      <c r="J106" s="7" t="n">
         <v>16243.45</v>
       </c>
-      <c r="K105" s="7" t="n">
-        <v>7298.95</v>
-      </c>
-      <c r="L105" s="7" t="n">
+      <c r="K106" s="7" t="n">
+        <v>7680.6</v>
+      </c>
+      <c r="L106" s="7" t="n">
         <v>3547.81</v>
       </c>
-      <c r="M105" s="7" t="n">
-        <v>203576.81</v>
-      </c>
-      <c r="N105" s="3" t="inlineStr">
+      <c r="M106" s="7" t="n">
+        <v>203958.46</v>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
         <is>
           <t>Billed + to-invoice + SaaS net of Salla share</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="B107" s="1" t="inlineStr">
+    <row r="108">
+      <c r="B108" s="1" t="inlineStr">
         <is>
           <t>BY CLIENT (billed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>Alfaris Group</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D108" s="5" t="n">
-        <v>2717.44</v>
-      </c>
-      <c r="E108" s="5" t="n">
-        <v>5230.11</v>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>3123.95</v>
-      </c>
-      <c r="G108" s="5" t="n">
-        <v>2640.55</v>
-      </c>
-      <c r="H108" s="5" t="n">
-        <v>2840.27</v>
-      </c>
-      <c r="I108" s="5" t="n">
-        <v>4081.37</v>
-      </c>
-      <c r="J108" s="5" t="n">
-        <v>3921.48</v>
-      </c>
-      <c r="K108" s="5" t="n">
-        <v>3290.53</v>
-      </c>
-      <c r="L108" s="5" t="n">
-        <v>2513.78</v>
-      </c>
-      <c r="M108" s="5" t="n">
-        <v>32859.48</v>
-      </c>
-      <c r="N108" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Inivita</t>
+          <t>Alfaris Group</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>3269.61</v>
+        <v>2500</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>3598.8</v>
+        <v>2717.44</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>3591.47</v>
+        <v>5230.11</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>4252.12</v>
+        <v>3123.95</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>3792.64</v>
+        <v>2640.55</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>3047.98</v>
+        <v>2840.27</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>3218.29</v>
+        <v>4081.37</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>2377.85</v>
+        <v>3921.48</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>2884.13</v>
-      </c>
-      <c r="L109" s="5" t="n"/>
+        <v>3290.53</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>2513.78</v>
+      </c>
       <c r="M109" s="5" t="n">
-        <v>30032.89</v>
+        <v>32859.48</v>
       </c>
       <c r="N109" s="3" t="inlineStr">
         <is>
@@ -4387,39 +4375,39 @@
     <row r="110">
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Nokush</t>
+          <t>Inivita</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
-        <v>338.91</v>
+        <v>3269.61</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>238.59</v>
+        <v>3598.8</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>180.02</v>
+        <v>3591.47</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>409.44</v>
+        <v>4252.12</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>326.25</v>
+        <v>3792.64</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>420.69</v>
+        <v>3047.98</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>655.84</v>
+        <v>3218.29</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>423.72</v>
+        <v>2377.85</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>319.26</v>
+        <v>2884.13</v>
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="5" t="n">
-        <v>3312.72</v>
+        <v>30032.89</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -4430,33 +4418,39 @@
     <row r="111">
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Wadi Halfa</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="n"/>
-      <c r="D111" s="5" t="n"/>
-      <c r="E111" s="5" t="n"/>
-      <c r="F111" s="5" t="n"/>
+          <t>Nokush</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>338.91</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>238.59</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>180.02</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>409.44</v>
+      </c>
       <c r="G111" s="5" t="n">
-        <v>3290.32</v>
+        <v>326.25</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>8.960000000000001</v>
+        <v>420.69</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>2024.04</v>
+        <v>655.84</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>2016.48</v>
+        <v>423.72</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>805.03</v>
-      </c>
-      <c r="L111" s="5" t="n">
-        <v>167.1</v>
-      </c>
+        <v>319.26</v>
+      </c>
+      <c r="L111" s="5" t="n"/>
       <c r="M111" s="5" t="n">
-        <v>8311.93</v>
+        <v>3312.72</v>
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
@@ -4467,23 +4461,33 @@
     <row r="112">
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Dar Sonbol</t>
+          <t>Wadi Halfa</t>
         </is>
       </c>
       <c r="C112" s="5" t="n"/>
       <c r="D112" s="5" t="n"/>
       <c r="E112" s="5" t="n"/>
       <c r="F112" s="5" t="n"/>
-      <c r="G112" s="5" t="n"/>
-      <c r="H112" s="5" t="n"/>
-      <c r="I112" s="5" t="n"/>
+      <c r="G112" s="5" t="n">
+        <v>3290.32</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>2024.04</v>
+      </c>
       <c r="J112" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="K112" s="5" t="n"/>
-      <c r="L112" s="5" t="n"/>
+        <v>2016.48</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>805.03</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>167.1</v>
+      </c>
       <c r="M112" s="5" t="n">
-        <v>4000</v>
+        <v>8311.93</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -4494,35 +4498,23 @@
     <row r="113">
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Two United  (churned 2026-05)</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D113" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E113" s="5" t="n">
-        <v>3606.59</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>2747.96</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>5631.76</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>5324.76</v>
-      </c>
-      <c r="I113" s="5" t="n">
-        <v>5462.25</v>
-      </c>
-      <c r="J113" s="5" t="n"/>
+          <t>Dar Sonbol</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n"/>
+      <c r="D113" s="5" t="n"/>
+      <c r="E113" s="5" t="n"/>
+      <c r="F113" s="5" t="n"/>
+      <c r="G113" s="5" t="n"/>
+      <c r="H113" s="5" t="n"/>
+      <c r="I113" s="5" t="n"/>
+      <c r="J113" s="5" t="n">
+        <v>4000</v>
+      </c>
       <c r="K113" s="5" t="n"/>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="5" t="n">
-        <v>32773.32</v>
+        <v>4000</v>
       </c>
       <c r="N113" s="3" t="inlineStr">
         <is>
@@ -4533,37 +4525,35 @@
     <row r="114">
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Rimath  (churned 2026-06)</t>
+          <t>Two United  (churned 2026-05)</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
-        <v>3743.36</v>
+        <v>5000</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>2998.75</v>
+        <v>5000</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>3561.57</v>
+        <v>3606.59</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>4753.24</v>
+        <v>2747.96</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>3970.51</v>
+        <v>5631.76</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>3649.59</v>
+        <v>5324.76</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>3044.62</v>
-      </c>
-      <c r="J114" s="5" t="n">
-        <v>2819.43</v>
-      </c>
+        <v>5462.25</v>
+      </c>
+      <c r="J114" s="5" t="n"/>
       <c r="K114" s="5" t="n"/>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="5" t="n">
-        <v>28541.07</v>
+        <v>32773.32</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -4574,35 +4564,37 @@
     <row r="115">
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Ancy &amp; Shaya  (churned 2026-05)</t>
+          <t>Rimath  (churned 2026-06)</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>3041.76</v>
+        <v>3743.36</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>2097.12</v>
+        <v>2998.75</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>2292.39</v>
+        <v>3561.57</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>2880.71</v>
+        <v>4753.24</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>2981.2</v>
+        <v>3970.51</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>2360.37</v>
+        <v>3649.59</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>1670.7</v>
-      </c>
-      <c r="J115" s="5" t="n"/>
+        <v>3044.62</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>2819.43</v>
+      </c>
       <c r="K115" s="5" t="n"/>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="5" t="n">
-        <v>17324.25</v>
+        <v>28541.07</v>
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
@@ -4613,29 +4605,35 @@
     <row r="116">
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Gamesir  (churned 2026-02)</t>
+          <t>Ancy &amp; Shaya  (churned 2026-05)</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
-        <v>3161.37</v>
+        <v>3041.76</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>2732.77</v>
+        <v>2097.12</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>5143.07</v>
+        <v>2292.39</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>512.96</v>
-      </c>
-      <c r="G116" s="5" t="n"/>
-      <c r="H116" s="5" t="n"/>
-      <c r="I116" s="5" t="n"/>
+        <v>2880.71</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>2981.2</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>2360.37</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>1670.7</v>
+      </c>
       <c r="J116" s="5" t="n"/>
       <c r="K116" s="5" t="n"/>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="5" t="n">
-        <v>11550.17</v>
+        <v>17324.25</v>
       </c>
       <c r="N116" s="3" t="inlineStr">
         <is>
@@ -4646,20 +4644,20 @@
     <row r="117">
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Safwat Aljouf  (churned 2026-02)</t>
+          <t>Gamesir  (churned 2026-02)</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>3585.43</v>
+        <v>3161.37</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>2564.26</v>
+        <v>2732.77</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2607.58</v>
+        <v>5143.07</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>837.29</v>
+        <v>512.96</v>
       </c>
       <c r="G117" s="5" t="n"/>
       <c r="H117" s="5" t="n"/>
@@ -4668,7 +4666,7 @@
       <c r="K117" s="5" t="n"/>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="5" t="n">
-        <v>9594.559999999999</v>
+        <v>11550.17</v>
       </c>
       <c r="N117" s="3" t="inlineStr">
         <is>
@@ -4679,29 +4677,29 @@
     <row r="118">
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Reetal  (churned 2026-06)</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="n"/>
-      <c r="D118" s="5" t="n"/>
-      <c r="E118" s="5" t="n"/>
-      <c r="F118" s="5" t="n"/>
-      <c r="G118" s="5" t="n">
-        <v>4492.3</v>
-      </c>
-      <c r="H118" s="5" t="n">
-        <v>1033.1</v>
-      </c>
-      <c r="I118" s="5" t="n">
-        <v>1799.32</v>
-      </c>
-      <c r="J118" s="5" t="n">
-        <v>684.49</v>
-      </c>
+          <t>Safwat Aljouf  (churned 2026-02)</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>3585.43</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>2564.26</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>2607.58</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>837.29</v>
+      </c>
+      <c r="G118" s="5" t="n"/>
+      <c r="H118" s="5" t="n"/>
+      <c r="I118" s="5" t="n"/>
+      <c r="J118" s="5" t="n"/>
       <c r="K118" s="5" t="n"/>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="5" t="n">
-        <v>8009.21</v>
+        <v>9594.559999999999</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -4712,72 +4710,105 @@
     <row r="119">
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>House Mart  (churned 2026-04)</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="n">
-        <v>6750</v>
-      </c>
+          <t>Reetal  (churned 2026-06)</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n"/>
       <c r="D119" s="5" t="n"/>
       <c r="E119" s="5" t="n"/>
       <c r="F119" s="5" t="n"/>
-      <c r="G119" s="5" t="n"/>
+      <c r="G119" s="5" t="n">
+        <v>4492.3</v>
+      </c>
       <c r="H119" s="5" t="n">
-        <v>8800.5</v>
-      </c>
-      <c r="I119" s="5" t="n"/>
-      <c r="J119" s="5" t="n"/>
+        <v>1033.1</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>1799.32</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>684.49</v>
+      </c>
       <c r="K119" s="5" t="n"/>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="5" t="n">
+        <v>8009.21</v>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>House Mart  (churned 2026-04)</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>6750</v>
+      </c>
+      <c r="D120" s="5" t="n"/>
+      <c r="E120" s="5" t="n"/>
+      <c r="F120" s="5" t="n"/>
+      <c r="G120" s="5" t="n"/>
+      <c r="H120" s="5" t="n">
+        <v>8800.5</v>
+      </c>
+      <c r="I120" s="5" t="n"/>
+      <c r="J120" s="5" t="n"/>
+      <c r="K120" s="5" t="n"/>
+      <c r="L120" s="5" t="n"/>
+      <c r="M120" s="5" t="n">
         <v>15550.5</v>
       </c>
-      <c r="N119" s="3" t="inlineStr">
+      <c r="N120" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="B120" s="6" t="inlineStr">
+    <row r="121">
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C120" s="7" t="n">
+      <c r="C121" s="7" t="n">
         <v>31390.44</v>
       </c>
-      <c r="D120" s="7" t="n">
+      <c r="D121" s="7" t="n">
         <v>21947.73</v>
       </c>
-      <c r="E120" s="7" t="n">
+      <c r="E121" s="7" t="n">
         <v>26212.8</v>
       </c>
-      <c r="F120" s="7" t="n">
+      <c r="F121" s="7" t="n">
         <v>19517.67</v>
       </c>
-      <c r="G120" s="7" t="n">
+      <c r="G121" s="7" t="n">
         <v>27125.53</v>
       </c>
-      <c r="H120" s="7" t="n">
+      <c r="H121" s="7" t="n">
         <v>27486.22</v>
       </c>
-      <c r="I120" s="7" t="n">
+      <c r="I121" s="7" t="n">
         <v>21956.43</v>
       </c>
-      <c r="J120" s="7" t="n">
+      <c r="J121" s="7" t="n">
         <v>16243.45</v>
       </c>
-      <c r="K120" s="7" t="n">
+      <c r="K121" s="7" t="n">
         <v>7298.95</v>
       </c>
-      <c r="L120" s="7" t="n">
+      <c r="L121" s="7" t="n">
         <v>2680.88</v>
       </c>
-      <c r="M120" s="7" t="n">
+      <c r="M121" s="7" t="n">
         <v>201860.1</v>
       </c>
-      <c r="N120" s="3" t="inlineStr">
+      <c r="N121" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
@@ -14366,7 +14397,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14519,36 +14550,36 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Annual</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2027-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G3" s="15" t="n">
-        <v>3999</v>
+        <v>449</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>999.75</v>
+        <v>449</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>1149.71</v>
+        <v>516.35</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>SPNS75 (−75%)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Paid — active</t>
+          <t>Paid — ended, replaced by annual</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -14560,17 +14591,17 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sonbol (سنبل)</t>
+          <t>SONDOS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Dar Sonbol</t>
+          <t>Alfaris Group</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>773002475</t>
+          <t>1052755076</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -14580,29 +14611,31 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n"/>
+          <t>2027-08-09</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>3999</v>
+      </c>
       <c r="H4" s="15" t="n">
-        <v>0</v>
+        <v>999.75</v>
       </c>
       <c r="I4" s="15" t="n">
-        <v>0</v>
+        <v>1149.71</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SPNS75 (−75%)</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Trial until 20 Aug</t>
+          <t>Paid — active</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -14614,49 +14647,51 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Pearly touch</t>
+          <t>Sonbol (سنبل)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>— new lead</t>
+          <t>Dar Sonbol</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>458981891</t>
+          <t>1773002475</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="n"/>
+          <t>2027-08-20</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>3999</v>
+      </c>
       <c r="H5" s="15" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>0</v>
+        <v>4598.85</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>— (full price)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Trial until 22 Aug</t>
+          <t>CANCELLED — confirm paid/refunded</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -14668,7 +14703,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>شركة جرافيتي ريزن</t>
+          <t>Hattrick - هاتريك</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -14678,7 +14713,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>825450288</t>
+          <t>789609037</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -14688,12 +14723,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G6" s="3" t="n"/>
@@ -14710,7 +14745,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Trial until 19 Aug</t>
+          <t>Trial — live to 6 Sep</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -14720,15 +14755,1149 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Erbi3a'a3228</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>— new lead</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>1695233027</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Trial — live to 4 Sep</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>المها | ALMAHA</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>— new lead</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>559840089</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Trial — live to 2 Sep</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>HANAY ABAYA</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>— new lead</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>1852978713</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Trial — live to 31 Aug</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sonbol (سنبل)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Dar Sonbol</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>1773002475</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Trial — converted 20 Aug</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SONDOS</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Alfaris Group</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>1052755076</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Trial — converted 2 Jul</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>محمصة نقوش (Nokush)</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Nokush</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>317767866</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Trial — converted 14 May</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>جوهرة الروح</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>524997780</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>جزيرة رجوة</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>1398934210</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Pearly touch</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>1458981891</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>شركة جرافيتي ريزن</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>825450288</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>لوتانا بوتيك Lotana</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>277377837</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>سنديان Seindyan</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>1870570337</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>فيلور للأناقة</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>1289067859</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>ANARCHI</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>1771117031</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>كودك ستور</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>7315862</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>مذهلة</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>816144827</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>العيسائي - موندو توندو</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>1439457817</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>المبخرة الحجازية | Hejaz Oud</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>498974673</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>شروق تأنّ</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>1553526899</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>أضواء ADWAA</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>91801065</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>إتحاد اللياقة</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>— lapsed</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>1146172804</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Trial — lapsed</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>TOTAL PAID (ex-VAT)</t>
         </is>
       </c>
-      <c r="H7" s="18" t="n">
-        <v>1999.5</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="H28" s="18" t="n">
+        <v>2448.5</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>Salla Partners export</t>
         </is>

--- a/revenue-view/output/Nasam_Revenue_View.xlsx
+++ b/revenue-view/output/Nasam_Revenue_View.xlsx
@@ -14686,12 +14686,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>— (full price)</t>
+          <t>none — coupon missed</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>CANCELLED — confirm paid/refunded</t>
+          <t>Cancelled via Salla — re-subscribing with SPNS75</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">

--- a/revenue-view/output/Nasam_Revenue_View.xlsx
+++ b/revenue-view/output/Nasam_Revenue_View.xlsx
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Nasam Revenue View — weekly run · 23 Aug 2026</t>
+          <t>Nasam Revenue View — weekly run · 6 Sep 2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>First automated Sunday run. Billing source switched to the WAFEQ API (reconciled against the 17-Aug manual export before switching). Retail reads closed POs directly from the platform (values live since 20 Aug), netted against retail invoices already raised in Wafeq. Sonbol was renamed in the platform ('Sonbol') and its from-integration sales refreshed.</t>
+          <t>Third automated Sunday run. Wafeq pulled via API on 6 Sep (164 invoices): no new invoices issued since 30 Aug; four August monthly invoices are drafted (31 Aug, 12,013.72) and enter billed once sent; five invoices moved to PAID (Alfaris May–Jul, Inivita Jul, INV-000151). The platform read layer was unavailable this run, so platform sales, purchase orders and Sonbol's from-integration figure are carried from the 30 Aug pull (August through 30 Aug; no September GMV yet). The six duplicated Alfaris retail invoices (INV-000169/170/171/181/182/183, 739.48) are still SENT in Wafeq with no credit note, so the Dec–Feb over-billing is still shown.</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Wafeq API snapshot 23 Aug (160 invoices) · platform revenue + purchase orders pulled 23 Aug · churned-brand snapshots 15 Aug (the read layer does not serve deactivated brands) · Salla Partners export 18 Aug (manual) · rate card 17 Aug.</t>
+          <t>Wafeq API snapshot 6 Sep (164 invoices) · platform revenue + purchase orders pulled 30 Aug (not refreshed this run) · churned-brand snapshots 15 Aug (the read layer does not serve deactivated brands) · Salla Partners export 30 Aug (manual, 26 records) · rate card 17 Aug.</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N121"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4108,7 +4108,7 @@
     <row r="100">
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Retail commission — closed POs, to invoice</t>
+          <t>Memo: drafted in Wafeq, not yet issued (not in billed)</t>
         </is>
       </c>
       <c r="C100" s="5" t="n"/>
@@ -4121,21 +4121,21 @@
       <c r="J100" s="5" t="n"/>
       <c r="K100" s="5" t="n"/>
       <c r="L100" s="5" t="n">
-        <v>17.14</v>
+        <v>12013.72</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>17.14</v>
+        <v>12013.72</v>
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>Nasam platform — closed POs — net of retail already billed in Wafeq</t>
+          <t>Wafeq invoice export — DRAFT status; enters billed once sent</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>SaaS subscriptions (Salla App Store, gross)</t>
+          <t>Retail commission — closed POs, to invoice</t>
         </is>
       </c>
       <c r="C101" s="5" t="n"/>
@@ -4144,29 +4144,25 @@
       <c r="F101" s="5" t="n"/>
       <c r="G101" s="5" t="n"/>
       <c r="H101" s="5" t="n"/>
-      <c r="I101" s="5" t="n">
-        <v>999.75</v>
-      </c>
+      <c r="I101" s="5" t="n"/>
       <c r="J101" s="5" t="n"/>
-      <c r="K101" s="5" t="n">
-        <v>449</v>
-      </c>
+      <c r="K101" s="5" t="n"/>
       <c r="L101" s="5" t="n">
-        <v>999.75</v>
+        <v>17.14</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>2448.5</v>
+        <v>17.14</v>
       </c>
       <c r="N101" s="3" t="inlineStr">
         <is>
-          <t>Salla Partners export</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" outlineLevel="1">
+          <t>Nasam platform — closed POs — net of retail already billed in Wafeq</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    محمصة نقوش (Nokush) — annual, paid May 2026</t>
+          <t>SaaS subscriptions (Salla App Store, gross)</t>
         </is>
       </c>
       <c r="C102" s="5" t="n"/>
@@ -4179,10 +4175,14 @@
         <v>999.75</v>
       </c>
       <c r="J102" s="5" t="n"/>
-      <c r="K102" s="5" t="n"/>
-      <c r="L102" s="5" t="n"/>
+      <c r="K102" s="5" t="n">
+        <v>449</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>999.75</v>
+      </c>
       <c r="M102" s="5" t="n">
-        <v>999.75</v>
+        <v>2448.5</v>
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
     <row r="103" outlineLevel="1">
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SONDOS — monthly, paid Jul 2026</t>
+          <t xml:space="preserve">    محمصة نقوش (Nokush) — annual, paid May 2026</t>
         </is>
       </c>
       <c r="C103" s="5" t="n"/>
@@ -4202,14 +4202,14 @@
       <c r="F103" s="5" t="n"/>
       <c r="G103" s="5" t="n"/>
       <c r="H103" s="5" t="n"/>
-      <c r="I103" s="5" t="n"/>
+      <c r="I103" s="5" t="n">
+        <v>999.75</v>
+      </c>
       <c r="J103" s="5" t="n"/>
-      <c r="K103" s="5" t="n">
-        <v>449</v>
-      </c>
+      <c r="K103" s="5" t="n"/>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="5" t="n">
-        <v>449</v>
+        <v>999.75</v>
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
     <row r="104" outlineLevel="1">
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SONDOS — annual, paid Aug 2026</t>
+          <t xml:space="preserve">    SONDOS — monthly, paid Jul 2026</t>
         </is>
       </c>
       <c r="C104" s="5" t="n"/>
@@ -4231,12 +4231,12 @@
       <c r="H104" s="5" t="n"/>
       <c r="I104" s="5" t="n"/>
       <c r="J104" s="5" t="n"/>
-      <c r="K104" s="5" t="n"/>
-      <c r="L104" s="5" t="n">
-        <v>999.75</v>
-      </c>
+      <c r="K104" s="5" t="n">
+        <v>449</v>
+      </c>
+      <c r="L104" s="5" t="n"/>
       <c r="M104" s="5" t="n">
-        <v>999.75</v>
+        <v>449</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
     </row>
-    <row r="105">
+    <row r="105" outlineLevel="1">
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>less: Salla share (15%)</t>
+          <t xml:space="preserve">    SONDOS — annual, paid Aug 2026</t>
         </is>
       </c>
       <c r="C105" s="5" t="n"/>
@@ -4256,158 +4256,142 @@
       <c r="F105" s="5" t="n"/>
       <c r="G105" s="5" t="n"/>
       <c r="H105" s="5" t="n"/>
-      <c r="I105" s="5" t="n">
+      <c r="I105" s="5" t="n"/>
+      <c r="J105" s="5" t="n"/>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n">
+        <v>999.75</v>
+      </c>
+      <c r="M105" s="5" t="n">
+        <v>999.75</v>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
+          <t>Salla Partners export</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>less: Salla share (15%)</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="n"/>
+      <c r="D106" s="5" t="n"/>
+      <c r="E106" s="5" t="n"/>
+      <c r="F106" s="5" t="n"/>
+      <c r="G106" s="5" t="n"/>
+      <c r="H106" s="5" t="n"/>
+      <c r="I106" s="5" t="n">
         <v>-149.96</v>
       </c>
-      <c r="J105" s="5" t="n"/>
-      <c r="K105" s="5" t="n">
+      <c r="J106" s="5" t="n"/>
+      <c r="K106" s="5" t="n">
         <v>-67.34999999999999</v>
       </c>
-      <c r="L105" s="5" t="n">
+      <c r="L106" s="5" t="n">
         <v>-149.96</v>
       </c>
-      <c r="M105" s="5" t="n">
+      <c r="M106" s="5" t="n">
         <v>-367.27</v>
       </c>
-      <c r="N105" s="3" t="inlineStr">
+      <c r="N106" s="3" t="inlineStr">
         <is>
           <t>15% per Tarik — not pullable from Salla</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="B106" s="6" t="inlineStr">
+    <row r="107">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="C106" s="7" t="n">
+      <c r="C107" s="7" t="n">
         <v>31390.44</v>
       </c>
-      <c r="D106" s="7" t="n">
+      <c r="D107" s="7" t="n">
         <v>21947.73</v>
       </c>
-      <c r="E106" s="7" t="n">
+      <c r="E107" s="7" t="n">
         <v>26212.8</v>
       </c>
-      <c r="F106" s="7" t="n">
+      <c r="F107" s="7" t="n">
         <v>19517.67</v>
       </c>
-      <c r="G106" s="7" t="n">
+      <c r="G107" s="7" t="n">
         <v>27125.53</v>
       </c>
-      <c r="H106" s="7" t="n">
+      <c r="H107" s="7" t="n">
         <v>27486.22</v>
       </c>
-      <c r="I106" s="7" t="n">
+      <c r="I107" s="7" t="n">
         <v>22806.22</v>
       </c>
-      <c r="J106" s="7" t="n">
+      <c r="J107" s="7" t="n">
         <v>16243.45</v>
       </c>
-      <c r="K106" s="7" t="n">
+      <c r="K107" s="7" t="n">
         <v>7680.6</v>
       </c>
-      <c r="L106" s="7" t="n">
+      <c r="L107" s="7" t="n">
         <v>3547.81</v>
       </c>
-      <c r="M106" s="7" t="n">
+      <c r="M107" s="7" t="n">
         <v>203958.46</v>
       </c>
-      <c r="N106" s="3" t="inlineStr">
+      <c r="N107" s="3" t="inlineStr">
         <is>
           <t>Billed + to-invoice + SaaS net of Salla share</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="B108" s="1" t="inlineStr">
+    <row r="109">
+      <c r="B109" s="1" t="inlineStr">
         <is>
           <t>BY CLIENT (billed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>Alfaris Group</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D109" s="5" t="n">
-        <v>2717.44</v>
-      </c>
-      <c r="E109" s="5" t="n">
-        <v>5230.11</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>3123.95</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>2640.55</v>
-      </c>
-      <c r="H109" s="5" t="n">
-        <v>2840.27</v>
-      </c>
-      <c r="I109" s="5" t="n">
-        <v>4081.37</v>
-      </c>
-      <c r="J109" s="5" t="n">
-        <v>3921.48</v>
-      </c>
-      <c r="K109" s="5" t="n">
-        <v>3290.53</v>
-      </c>
-      <c r="L109" s="5" t="n">
-        <v>2513.78</v>
-      </c>
-      <c r="M109" s="5" t="n">
-        <v>32859.48</v>
-      </c>
-      <c r="N109" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Inivita</t>
+          <t>Alfaris Group</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
-        <v>3269.61</v>
+        <v>2500</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>3598.8</v>
+        <v>2717.44</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>3591.47</v>
+        <v>5230.11</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>4252.12</v>
+        <v>3123.95</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>3792.64</v>
+        <v>2640.55</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>3047.98</v>
+        <v>2840.27</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>3218.29</v>
+        <v>4081.37</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>2377.85</v>
+        <v>3921.48</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>2884.13</v>
-      </c>
-      <c r="L110" s="5" t="n"/>
+        <v>3290.53</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>2513.78</v>
+      </c>
       <c r="M110" s="5" t="n">
-        <v>30032.89</v>
+        <v>32859.48</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -4418,39 +4402,39 @@
     <row r="111">
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Nokush</t>
+          <t>Inivita</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>338.91</v>
+        <v>3269.61</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>238.59</v>
+        <v>3598.8</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>180.02</v>
+        <v>3591.47</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>409.44</v>
+        <v>4252.12</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>326.25</v>
+        <v>3792.64</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>420.69</v>
+        <v>3047.98</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>655.84</v>
+        <v>3218.29</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>423.72</v>
+        <v>2377.85</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>319.26</v>
+        <v>2884.13</v>
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="5" t="n">
-        <v>3312.72</v>
+        <v>30032.89</v>
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
@@ -4461,33 +4445,39 @@
     <row r="112">
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Wadi Halfa</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="n"/>
-      <c r="D112" s="5" t="n"/>
-      <c r="E112" s="5" t="n"/>
-      <c r="F112" s="5" t="n"/>
+          <t>Nokush</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>338.91</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>238.59</v>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>180.02</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>409.44</v>
+      </c>
       <c r="G112" s="5" t="n">
-        <v>3290.32</v>
+        <v>326.25</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>8.960000000000001</v>
+        <v>420.69</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>2024.04</v>
+        <v>655.84</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>2016.48</v>
+        <v>423.72</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>805.03</v>
-      </c>
-      <c r="L112" s="5" t="n">
-        <v>167.1</v>
-      </c>
+        <v>319.26</v>
+      </c>
+      <c r="L112" s="5" t="n"/>
       <c r="M112" s="5" t="n">
-        <v>8311.93</v>
+        <v>3312.72</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -4498,23 +4488,33 @@
     <row r="113">
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Dar Sonbol</t>
+          <t>Wadi Halfa</t>
         </is>
       </c>
       <c r="C113" s="5" t="n"/>
       <c r="D113" s="5" t="n"/>
       <c r="E113" s="5" t="n"/>
       <c r="F113" s="5" t="n"/>
-      <c r="G113" s="5" t="n"/>
-      <c r="H113" s="5" t="n"/>
-      <c r="I113" s="5" t="n"/>
+      <c r="G113" s="5" t="n">
+        <v>3290.32</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>2024.04</v>
+      </c>
       <c r="J113" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="K113" s="5" t="n"/>
-      <c r="L113" s="5" t="n"/>
+        <v>2016.48</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>805.03</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>167.1</v>
+      </c>
       <c r="M113" s="5" t="n">
-        <v>4000</v>
+        <v>8311.93</v>
       </c>
       <c r="N113" s="3" t="inlineStr">
         <is>
@@ -4525,35 +4525,23 @@
     <row r="114">
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Two United  (churned 2026-05)</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D114" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E114" s="5" t="n">
-        <v>3606.59</v>
-      </c>
-      <c r="F114" s="5" t="n">
-        <v>2747.96</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>5631.76</v>
-      </c>
-      <c r="H114" s="5" t="n">
-        <v>5324.76</v>
-      </c>
-      <c r="I114" s="5" t="n">
-        <v>5462.25</v>
-      </c>
-      <c r="J114" s="5" t="n"/>
+          <t>Dar Sonbol</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="5" t="n"/>
+      <c r="F114" s="5" t="n"/>
+      <c r="G114" s="5" t="n"/>
+      <c r="H114" s="5" t="n"/>
+      <c r="I114" s="5" t="n"/>
+      <c r="J114" s="5" t="n">
+        <v>4000</v>
+      </c>
       <c r="K114" s="5" t="n"/>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="5" t="n">
-        <v>32773.32</v>
+        <v>4000</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -4564,37 +4552,35 @@
     <row r="115">
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Rimath  (churned 2026-06)</t>
+          <t>Two United  (churned 2026-05)</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>3743.36</v>
+        <v>5000</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>2998.75</v>
+        <v>5000</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>3561.57</v>
+        <v>3606.59</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>4753.24</v>
+        <v>2747.96</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>3970.51</v>
+        <v>5631.76</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>3649.59</v>
+        <v>5324.76</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>3044.62</v>
-      </c>
-      <c r="J115" s="5" t="n">
-        <v>2819.43</v>
-      </c>
+        <v>5462.25</v>
+      </c>
+      <c r="J115" s="5" t="n"/>
       <c r="K115" s="5" t="n"/>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="5" t="n">
-        <v>28541.07</v>
+        <v>32773.32</v>
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
@@ -4605,35 +4591,37 @@
     <row r="116">
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Ancy &amp; Shaya  (churned 2026-05)</t>
+          <t>Rimath  (churned 2026-06)</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
-        <v>3041.76</v>
+        <v>3743.36</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>2097.12</v>
+        <v>2998.75</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2292.39</v>
+        <v>3561.57</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>2880.71</v>
+        <v>4753.24</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>2981.2</v>
+        <v>3970.51</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>2360.37</v>
+        <v>3649.59</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>1670.7</v>
-      </c>
-      <c r="J116" s="5" t="n"/>
+        <v>3044.62</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>2819.43</v>
+      </c>
       <c r="K116" s="5" t="n"/>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="5" t="n">
-        <v>17324.25</v>
+        <v>28541.07</v>
       </c>
       <c r="N116" s="3" t="inlineStr">
         <is>
@@ -4644,29 +4632,35 @@
     <row r="117">
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Gamesir  (churned 2026-02)</t>
+          <t>Ancy &amp; Shaya  (churned 2026-05)</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>3161.37</v>
+        <v>3041.76</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>2732.77</v>
+        <v>2097.12</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>5143.07</v>
+        <v>2292.39</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>512.96</v>
-      </c>
-      <c r="G117" s="5" t="n"/>
-      <c r="H117" s="5" t="n"/>
-      <c r="I117" s="5" t="n"/>
+        <v>2880.71</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>2981.2</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>2360.37</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>1670.7</v>
+      </c>
       <c r="J117" s="5" t="n"/>
       <c r="K117" s="5" t="n"/>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="5" t="n">
-        <v>11550.17</v>
+        <v>17324.25</v>
       </c>
       <c r="N117" s="3" t="inlineStr">
         <is>
@@ -4677,20 +4671,20 @@
     <row r="118">
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Safwat Aljouf  (churned 2026-02)</t>
+          <t>Gamesir  (churned 2026-02)</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
-        <v>3585.43</v>
+        <v>3161.37</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>2564.26</v>
+        <v>2732.77</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2607.58</v>
+        <v>5143.07</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>837.29</v>
+        <v>512.96</v>
       </c>
       <c r="G118" s="5" t="n"/>
       <c r="H118" s="5" t="n"/>
@@ -4699,7 +4693,7 @@
       <c r="K118" s="5" t="n"/>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="5" t="n">
-        <v>9594.559999999999</v>
+        <v>11550.17</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -4710,29 +4704,29 @@
     <row r="119">
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Reetal  (churned 2026-06)</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="n"/>
-      <c r="D119" s="5" t="n"/>
-      <c r="E119" s="5" t="n"/>
-      <c r="F119" s="5" t="n"/>
-      <c r="G119" s="5" t="n">
-        <v>4492.3</v>
-      </c>
-      <c r="H119" s="5" t="n">
-        <v>1033.1</v>
-      </c>
-      <c r="I119" s="5" t="n">
-        <v>1799.32</v>
-      </c>
-      <c r="J119" s="5" t="n">
-        <v>684.49</v>
-      </c>
+          <t>Safwat Aljouf  (churned 2026-02)</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>3585.43</v>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>2564.26</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>2607.58</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>837.29</v>
+      </c>
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="5" t="n"/>
+      <c r="I119" s="5" t="n"/>
+      <c r="J119" s="5" t="n"/>
       <c r="K119" s="5" t="n"/>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="5" t="n">
-        <v>8009.21</v>
+        <v>9594.559999999999</v>
       </c>
       <c r="N119" s="3" t="inlineStr">
         <is>
@@ -4743,72 +4737,105 @@
     <row r="120">
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>House Mart  (churned 2026-04)</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="n">
-        <v>6750</v>
-      </c>
+          <t>Reetal  (churned 2026-06)</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="n"/>
       <c r="D120" s="5" t="n"/>
       <c r="E120" s="5" t="n"/>
       <c r="F120" s="5" t="n"/>
-      <c r="G120" s="5" t="n"/>
+      <c r="G120" s="5" t="n">
+        <v>4492.3</v>
+      </c>
       <c r="H120" s="5" t="n">
-        <v>8800.5</v>
-      </c>
-      <c r="I120" s="5" t="n"/>
-      <c r="J120" s="5" t="n"/>
+        <v>1033.1</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>1799.32</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>684.49</v>
+      </c>
       <c r="K120" s="5" t="n"/>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="5" t="n">
+        <v>8009.21</v>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>House Mart  (churned 2026-04)</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>6750</v>
+      </c>
+      <c r="D121" s="5" t="n"/>
+      <c r="E121" s="5" t="n"/>
+      <c r="F121" s="5" t="n"/>
+      <c r="G121" s="5" t="n"/>
+      <c r="H121" s="5" t="n">
+        <v>8800.5</v>
+      </c>
+      <c r="I121" s="5" t="n"/>
+      <c r="J121" s="5" t="n"/>
+      <c r="K121" s="5" t="n"/>
+      <c r="L121" s="5" t="n"/>
+      <c r="M121" s="5" t="n">
         <v>15550.5</v>
       </c>
-      <c r="N120" s="3" t="inlineStr">
+      <c r="N121" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="B121" s="6" t="inlineStr">
+    <row r="122">
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C121" s="7" t="n">
+      <c r="C122" s="7" t="n">
         <v>31390.44</v>
       </c>
-      <c r="D121" s="7" t="n">
+      <c r="D122" s="7" t="n">
         <v>21947.73</v>
       </c>
-      <c r="E121" s="7" t="n">
+      <c r="E122" s="7" t="n">
         <v>26212.8</v>
       </c>
-      <c r="F121" s="7" t="n">
+      <c r="F122" s="7" t="n">
         <v>19517.67</v>
       </c>
-      <c r="G121" s="7" t="n">
+      <c r="G122" s="7" t="n">
         <v>27125.53</v>
       </c>
-      <c r="H121" s="7" t="n">
+      <c r="H122" s="7" t="n">
         <v>27486.22</v>
       </c>
-      <c r="I121" s="7" t="n">
+      <c r="I122" s="7" t="n">
         <v>21956.43</v>
       </c>
-      <c r="J121" s="7" t="n">
+      <c r="J122" s="7" t="n">
         <v>16243.45</v>
       </c>
-      <c r="K121" s="7" t="n">
+      <c r="K122" s="7" t="n">
         <v>7298.95</v>
       </c>
-      <c r="L121" s="7" t="n">
+      <c r="L122" s="7" t="n">
         <v>2680.88</v>
       </c>
-      <c r="M121" s="7" t="n">
+      <c r="M122" s="7" t="n">
         <v>201860.1</v>
       </c>
-      <c r="N121" s="3" t="inlineStr">
+      <c r="N122" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>

--- a/revenue-view/output/Nasam_Revenue_View.xlsx
+++ b/revenue-view/output/Nasam_Revenue_View.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Window Nov 2025+ (current model) · GMV post-Nasam only (Sonbol from 13 Aug 2026) · post-churn months excluded · SaaS brand-channels 0% · SaaS subscriptions net of Salla 15% · retail commission on the RECEIVED value of closed POs · pass-throughs (3,355.01) excluded · all figures SAR ex-VAT.</t>
+          <t>Window Nov 2025+ (current model) · GMV post-Nasam only (Sonbol from 13 Aug 2026) · post-churn months excluded · SaaS brand-channels 0% · SaaS subscriptions net of Salla 15% · retail commission on the RECEIVED value of closed POs · pass-throughs excluded: Cloud Shelf recharges (3,355.01 in window) and marketing rebilled to a client at cost (INV-000137, 16,534.40, Oct 2025 — outside the window) · only the management fee on such work is revenue, and there was none on that invoice · all figures SAR ex-VAT.</t>
         </is>
       </c>
     </row>

--- a/revenue-view/output/Nasam_Revenue_View.xlsx
+++ b/revenue-view/output/Nasam_Revenue_View.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Nasam Revenue View — run of 9 Sep 2026 · August monthly close</t>
+          <t>Nasam Revenue View — weekly run · 13 Sep 2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -510,7 +510,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Monthly close for August, off the accounting drop Tarik shared on 9 Sep (data to 8 Sep). The four August invoices drafted on 31 Aug are now issued, so 10,013.72 moves from the memo line into billed — Wadi Halfa's released invoice is 8.11, not 2,008.11, because the 2,000 monthly fee was dropped while the shipping disruption lasts. New sheet 4 Cost &amp; Break-even carries the expense side for the first time: salaries and bills against revenue, what was spent on clients' behalf, how the gap was funded, and receivables reconciled against the accountant's statement. Platform sales, purchase orders and Sonbol's from-integration figure are still the 30 Aug pull (the read layer is offline).</t>
+          <t>A quiet week: no invoice was issued, paid or changed since 9 Sep, so billed, receivables and every total are unchanged. Wafeq was re-pulled today and matches the 9 Sep state exactly. One forward signal: a new billing item, عمولة مبيعات - نمشي (Namshi sales commission), was created in Wafeq on 10 Sep — the channel is now mapped here so the first Namshi invoice classifies correctly instead of falling into Other. Platform sales, purchase orders and Sonbol's from-integration figure are still the 30 Aug pull; the platform read layer needs re-authorising.</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Wafeq API snapshot 9 Sep (164 invoices) · Wafeq accounting exports 8 Sep: purchase bills, journal entries, customer-balances statement · platform revenue + purchase orders pulled 30 Aug (not refreshed) · churned-brand snapshots 15 Aug · Salla Partners export 30 Aug (manual, 26 records) · rate card 17 Aug.</t>
+          <t>Wafeq API snapshot 13 Sep (164 invoices) · Wafeq accounting exports 8 Sep: purchase bills, journal entries, customer-balances statement · platform revenue + purchase orders pulled 30 Aug (14 days old) · churned-brand snapshots 15 Aug · Salla Partners export 30 Aug (14 days old — the four trials live then have all since expired) · closed-PO export 17 Aug · rate card 17 Aug.</t>
         </is>
       </c>
     </row>

--- a/revenue-view/output/Nasam_Revenue_View.xlsx
+++ b/revenue-view/output/Nasam_Revenue_View.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>A quiet week: no invoice was issued, paid or changed since 9 Sep, so billed, receivables and every total are unchanged. Wafeq was re-pulled today and matches the 9 Sep state exactly. One forward signal: a new billing item, عمولة مبيعات - نمشي (Namshi sales commission), was created in Wafeq on 10 Sep — the channel is now mapped here so the first Namshi invoice classifies correctly instead of falling into Other. Platform sales, purchase orders and Sonbol's from-integration figure are still the 30 Aug pull; the platform read layer needs re-authorising.</t>
+          <t>Nasam has fixed the per-channel commission mapping in the platform, so the platform's own toggle — not the rate card — now decides whether a channel is invoiced. That mapping is held in mapping.py and checked against the billing every run; see PLATFORM MAPPING CHECK at the foot of this sheet. Sonbol is read in from the organization dialog: Amazon, Namshi, Noon and Trendyol commission-active, Salla بلا عمولة (which matches how Salla was already treated), monthly fee 8,000. The check raises one thing to decide — that 8,000 has never been billed — and confirms Salla carries no commission by design. Nothing else moved: no invoice was issued, paid or changed since 9 Sep, so billed, receivables and every total are unchanged. The live platform read layer is still unauthorised, so the other 20 brands remain on rate-card defaults and are listed as unconfirmed rather than shown as verified.</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Wafeq API snapshot 13 Sep (164 invoices) · Wafeq accounting exports 8 Sep: purchase bills, journal entries, customer-balances statement · platform revenue + purchase orders pulled 30 Aug (14 days old) · churned-brand snapshots 15 Aug · Salla Partners export 30 Aug (14 days old — the four trials live then have all since expired) · closed-PO export 17 Aug · rate card 17 Aug.</t>
+          <t>Wafeq API snapshot 13 Sep (164 invoices) · platform channel mapping and monthly fees read 13 Sep (Sonbol only) · Wafeq accounting exports 8 Sep: purchase bills, journal entries, customer-balances statement · platform revenue + purchase orders pulled 30 Aug (14 days old) · churned-brand snapshots 15 Aug · Salla Partners export 30 Aug (14 days old — the four trials live then have all since expired) · closed-PO export 17 Aug · rate card 17 Aug.</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Window Nov 2025+ (current model) · GMV post-Nasam only (Sonbol from 13 Aug 2026) · post-churn months excluded · SaaS brand-channels 0% · SaaS subscriptions net of Salla 15% · retail commission on the RECEIVED value of closed POs · pass-throughs excluded: Cloud Shelf recharges (3,355.01 in window) and marketing rebilled to a client at cost (INV-000137, 16,534.40, Oct 2025 — outside the window) · only the management fee on such work is revenue, and there was none on that invoice · all figures SAR ex-VAT.</t>
+          <t>Window Nov 2025+ (current model) · GMV post-Nasam only (Sonbol from 13 Aug 2026) · post-churn months excluded · a channel is commissioned only if the platform says so (بلا عمولة = 0%, orders still sync and still show in sales); brands not yet read off the platform fall back to the rate card and SaaS brand-channels stay 0% · SaaS subscriptions net of Salla 15% · retail commission on the RECEIVED value of closed POs · pass-throughs excluded: Cloud Shelf recharges (3,355.01 in window) and marketing rebilled to a client at cost (INV-000137, 16,534.40, Oct 2025 — outside the window) · only the management fee on such work is revenue, and there was none on that invoice · all figures SAR ex-VAT.</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Automatic: Wafeq API, platform sales, platform POs, rebuild + verification. Manual: only the Salla Partners subscriptions export — share it whenever it changes.</t>
+          <t>Automatic: Wafeq API, platform sales, platform POs, platform channel mapping and monthly fees, rebuild + verification + mapping check. Manual: only the Salla Partners subscriptions export — share it whenever it changes.</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:N131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4863,6 +4863,97 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>PLATFORM MAPPING CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Read 2026-09-13 · 1 of 21 brands confirmed against the platform</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
+          <t>Nasam platform — تعديل المنظمة (per-channel commission toggle + الرسوم الشهرية)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Note: Sonbol · Amazon</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
+          <t>mapped and commission active on the platform, but no sales and no invoice yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Note: Sonbol · Namshi</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
+          <t>mapped and commission active on the platform, but no sales and no invoice yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Note: Sonbol · Noon</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
+          <t>mapped and commission active on the platform, but no sales and no invoice yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Note: Sonbol · Trendyol</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
+          <t>mapped and commission active on the platform, but no sales and no invoice yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>Decide: Sonbol</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
+          <t>platform monthly fee 8,000 is not billed in 2026-08 — never billed in the window</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Note: Ancy, Arabesque, Bonita, Feel, Invita, Marah, Nokush, O'SO, Reefi, Reetal, SONDOS, Safwat Aljawf, Sense, Shaya, Thannah, Wadi Halfa, brio, circles, iOUD, labelle</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
+          <t>not read off the platform yet — still on rate-card defaults</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4874,7 +4965,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R188"/>
+  <dimension ref="A1:R189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8593,7 +8684,7 @@
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>Nasam platform — revenue view (from 13 Aug 2026)</t>
+          <t>Nasam platform — revenue view (from 13 Aug 2026) · platform mapping: بلا عمولة — commission off, orders still sync</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8734,7 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>Rate card (Tarik) — in setup, channel being built</t>
+          <t>Nasam platform — revenue view — mapped, no sales and no invoice yet · platform mapping: العمولة سارية — commission active</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8751,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Noon</t>
+          <t>Namshi</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -8693,7 +8784,7 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>Rate card (Tarik) — in setup, channel being built</t>
+          <t>Nasam platform — revenue view — mapped, no sales and no invoice yet · platform mapping: العمولة سارية — commission active</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8801,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Trendyol</t>
+          <t>Noon</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -8743,7 +8834,7 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>Rate card (Tarik) — in setup, channel being built</t>
+          <t>Nasam platform — revenue view — mapped, no sales and no invoice yet · platform mapping: العمولة سارية — commission active</t>
         </is>
       </c>
     </row>
@@ -8760,7 +8851,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>aivi</t>
+          <t>Trendyol</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -8793,7 +8884,7 @@
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>Rate card (Tarik) — integration WIP</t>
+          <t>Nasam platform — revenue view — mapped, no sales and no invoice yet · platform mapping: العمولة سارية — commission active</t>
         </is>
       </c>
     </row>
@@ -8805,19 +8896,27 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="n"/>
+          <t>Sonbol (سنبل)</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>aivi</t>
+        </is>
+      </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="n"/>
+          <t>Mapping</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G74" s="15" t="n"/>
@@ -8835,175 +8934,165 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>Rate card (Tarik) · Card: FAM 2% + 5,000/mo — 50% at 1st live managed channel, 100% from 2nd (FAM only). Salla SaaS = separate added deal.</t>
+          <t>Rate card (Tarik) — integration WIP, not a platform channel</t>
         </is>
       </c>
     </row>
     <row r="75" outlineLevel="1">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Dar Sonbol</t>
         </is>
       </c>
-      <c r="B75" s="13" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C75" s="13" t="n"/>
-      <c r="D75" s="13" t="inlineStr">
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Monthly fee</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="15" t="n"/>
+      <c r="H75" s="15" t="n"/>
+      <c r="I75" s="15" t="n"/>
+      <c r="J75" s="15" t="n"/>
+      <c r="K75" s="15" t="n"/>
+      <c r="L75" s="15" t="n"/>
+      <c r="M75" s="15" t="n"/>
+      <c r="N75" s="15" t="n"/>
+      <c r="O75" s="15" t="n"/>
+      <c r="P75" s="15" t="n"/>
+      <c r="Q75" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>Rate card (Tarik) · Platform: 8,000/mo set on the organization, not billed in any month here. Card: FAM 2% + 5,000/mo — 50% at 1st live managed channel, 100% from 2nd (FAM only). Salla SaaS = separate added deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" outlineLevel="1">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>Dar Sonbol</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="n"/>
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>Setup / one-time</t>
         </is>
       </c>
-      <c r="E75" s="13" t="n"/>
-      <c r="F75" s="13" t="n"/>
-      <c r="G75" s="14" t="n"/>
-      <c r="H75" s="14" t="n"/>
-      <c r="I75" s="14" t="n"/>
-      <c r="J75" s="14" t="n"/>
-      <c r="K75" s="14" t="n"/>
-      <c r="L75" s="14" t="n"/>
-      <c r="M75" s="14" t="n"/>
-      <c r="N75" s="14" t="n">
+      <c r="E76" s="13" t="n"/>
+      <c r="F76" s="13" t="n"/>
+      <c r="G76" s="14" t="n"/>
+      <c r="H76" s="14" t="n"/>
+      <c r="I76" s="14" t="n"/>
+      <c r="J76" s="14" t="n"/>
+      <c r="K76" s="14" t="n"/>
+      <c r="L76" s="14" t="n"/>
+      <c r="M76" s="14" t="n"/>
+      <c r="N76" s="14" t="n">
         <v>4000</v>
       </c>
-      <c r="O75" s="14" t="n"/>
-      <c r="P75" s="14" t="n"/>
-      <c r="Q75" s="14" t="n">
+      <c r="O76" s="14" t="n"/>
+      <c r="P76" s="14" t="n"/>
+      <c r="Q76" s="14" t="n">
         <v>4000</v>
       </c>
-      <c r="R75" s="3" t="inlineStr">
+      <c r="R76" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>Two United  (churned 2026-05)</t>
         </is>
       </c>
-      <c r="B77" s="9" t="n"/>
-      <c r="C77" s="9" t="n"/>
-      <c r="D77" s="9" t="inlineStr">
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E77" s="9" t="n"/>
-      <c r="F77" s="9" t="n"/>
-      <c r="G77" s="10" t="n">
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="9" t="n"/>
+      <c r="G78" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="H77" s="10" t="n">
+      <c r="H78" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="I77" s="10" t="n">
+      <c r="I78" s="10" t="n">
         <v>3606.59</v>
       </c>
-      <c r="J77" s="10" t="n">
+      <c r="J78" s="10" t="n">
         <v>2747.96</v>
       </c>
-      <c r="K77" s="10" t="n">
+      <c r="K78" s="10" t="n">
         <v>5631.76</v>
       </c>
-      <c r="L77" s="10" t="n">
+      <c r="L78" s="10" t="n">
         <v>5324.76</v>
       </c>
-      <c r="M77" s="10" t="n">
+      <c r="M78" s="10" t="n">
         <v>5462.25</v>
       </c>
-      <c r="N77" s="10" t="n"/>
-      <c r="O77" s="10" t="n"/>
-      <c r="P77" s="10" t="n"/>
-      <c r="Q77" s="10" t="n">
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="10" t="n">
         <v>32773.32</v>
       </c>
-      <c r="R77" s="3" t="inlineStr">
+      <c r="R78" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · Card: MP 2% / Retail 1.5% + 5,000/mo</t>
         </is>
       </c>
     </row>
-    <row r="78" outlineLevel="1">
-      <c r="A78" s="11" t="inlineStr">
+    <row r="79" outlineLevel="1">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>Bonita</t>
         </is>
       </c>
-      <c r="C78" s="11" t="n"/>
-      <c r="D78" s="11" t="inlineStr">
+      <c r="C79" s="11" t="n"/>
+      <c r="D79" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E78" s="11" t="n"/>
-      <c r="F78" s="11" t="n"/>
-      <c r="G78" s="12" t="n"/>
-      <c r="H78" s="12" t="n">
-        <v>449.56</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>1196.25</v>
-      </c>
-      <c r="J78" s="12" t="n"/>
-      <c r="K78" s="12" t="n">
-        <v>487.96</v>
-      </c>
-      <c r="L78" s="12" t="n"/>
-      <c r="M78" s="12" t="n"/>
-      <c r="N78" s="12" t="n"/>
-      <c r="O78" s="12" t="n"/>
-      <c r="P78" s="12" t="n"/>
-      <c r="Q78" s="12" t="n">
-        <v>2133.77</v>
-      </c>
-      <c r="R78" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" outlineLevel="2">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t>Bonita</t>
-        </is>
-      </c>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E79" s="11" t="n"/>
       <c r="F79" s="11" t="n"/>
       <c r="G79" s="12" t="n"/>
       <c r="H79" s="12" t="n">
         <v>449.56</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>1079.25</v>
+        <v>1196.25</v>
       </c>
       <c r="J79" s="12" t="n"/>
       <c r="K79" s="12" t="n">
@@ -9015,244 +9104,238 @@
       <c r="O79" s="12" t="n"/>
       <c r="P79" s="12" t="n"/>
       <c r="Q79" s="12" t="n">
+        <v>2133.77</v>
+      </c>
+      <c r="R79" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" outlineLevel="2">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>Bonita</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>Jahez</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="n"/>
+      <c r="G80" s="12" t="n"/>
+      <c r="H80" s="12" t="n">
+        <v>449.56</v>
+      </c>
+      <c r="I80" s="12" t="n">
+        <v>1079.25</v>
+      </c>
+      <c r="J80" s="12" t="n"/>
+      <c r="K80" s="12" t="n">
+        <v>487.96</v>
+      </c>
+      <c r="L80" s="12" t="n"/>
+      <c r="M80" s="12" t="n"/>
+      <c r="N80" s="12" t="n"/>
+      <c r="O80" s="12" t="n"/>
+      <c r="P80" s="12" t="n"/>
+      <c r="Q80" s="12" t="n">
         <v>2016.77</v>
       </c>
-      <c r="R79" s="3" t="inlineStr">
+      <c r="R80" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="80" outlineLevel="2">
-      <c r="A80" s="13" t="inlineStr">
+    <row r="81" outlineLevel="2">
+      <c r="A81" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B80" s="13" t="inlineStr">
+      <c r="B81" s="13" t="inlineStr">
         <is>
           <t>Bonita ≈</t>
         </is>
       </c>
-      <c r="C80" s="13" t="inlineStr">
+      <c r="C81" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="D81" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E80" s="13" t="inlineStr">
+      <c r="E81" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F80" s="13" t="inlineStr">
+      <c r="F81" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G80" s="14" t="n"/>
-      <c r="H80" s="14" t="n"/>
-      <c r="I80" s="14" t="n">
+      <c r="G81" s="14" t="n"/>
+      <c r="H81" s="14" t="n"/>
+      <c r="I81" s="14" t="n">
         <v>22.83</v>
       </c>
-      <c r="J80" s="14" t="n"/>
-      <c r="K80" s="14" t="n">
+      <c r="J81" s="14" t="n"/>
+      <c r="K81" s="14" t="n">
         <v>9.76</v>
       </c>
-      <c r="L80" s="14" t="n"/>
-      <c r="M80" s="14" t="n"/>
-      <c r="N80" s="14" t="n"/>
-      <c r="O80" s="14" t="n"/>
-      <c r="P80" s="14" t="n"/>
-      <c r="Q80" s="14" t="n">
+      <c r="L81" s="14" t="n"/>
+      <c r="M81" s="14" t="n"/>
+      <c r="N81" s="14" t="n"/>
+      <c r="O81" s="14" t="n"/>
+      <c r="P81" s="14" t="n"/>
+      <c r="Q81" s="14" t="n">
         <v>32.59</v>
       </c>
-      <c r="R80" s="3" t="inlineStr">
+      <c r="R81" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="81" outlineLevel="2">
-      <c r="A81" s="11" t="inlineStr">
+    <row r="82" outlineLevel="2">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>Bonita</t>
         </is>
       </c>
-      <c r="C81" s="11" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D81" s="11" t="inlineStr">
+      <c r="D82" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E81" s="11" t="inlineStr">
+      <c r="E82" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F81" s="11" t="n"/>
-      <c r="G81" s="12" t="n"/>
-      <c r="H81" s="12" t="n"/>
-      <c r="I81" s="12" t="n">
+      <c r="F82" s="11" t="n"/>
+      <c r="G82" s="12" t="n"/>
+      <c r="H82" s="12" t="n"/>
+      <c r="I82" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="J81" s="12" t="n"/>
-      <c r="K81" s="12" t="n"/>
-      <c r="L81" s="12" t="n"/>
-      <c r="M81" s="12" t="n"/>
-      <c r="N81" s="12" t="n"/>
-      <c r="O81" s="12" t="n"/>
-      <c r="P81" s="12" t="n"/>
-      <c r="Q81" s="12" t="n">
+      <c r="J82" s="12" t="n"/>
+      <c r="K82" s="12" t="n"/>
+      <c r="L82" s="12" t="n"/>
+      <c r="M82" s="12" t="n"/>
+      <c r="N82" s="12" t="n"/>
+      <c r="O82" s="12" t="n"/>
+      <c r="P82" s="12" t="n"/>
+      <c r="Q82" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="R81" s="3" t="inlineStr">
+      <c r="R82" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="82" outlineLevel="2">
-      <c r="A82" s="13" t="inlineStr">
+    <row r="83" outlineLevel="2">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="B83" s="13" t="inlineStr">
         <is>
           <t>Bonita ≈</t>
         </is>
       </c>
-      <c r="C82" s="13" t="inlineStr">
+      <c r="C83" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="D83" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E82" s="13" t="inlineStr">
+      <c r="E83" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F82" s="13" t="inlineStr">
+      <c r="F83" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G82" s="14" t="n"/>
-      <c r="H82" s="14" t="n"/>
-      <c r="I82" s="14" t="n">
+      <c r="G83" s="14" t="n"/>
+      <c r="H83" s="14" t="n"/>
+      <c r="I83" s="14" t="n">
         <v>3.03</v>
       </c>
-      <c r="J82" s="14" t="n"/>
-      <c r="K82" s="14" t="n"/>
-      <c r="L82" s="14" t="n"/>
-      <c r="M82" s="14" t="n"/>
-      <c r="N82" s="14" t="n"/>
-      <c r="O82" s="14" t="n"/>
-      <c r="P82" s="14" t="n"/>
-      <c r="Q82" s="14" t="n">
+      <c r="J83" s="14" t="n"/>
+      <c r="K83" s="14" t="n"/>
+      <c r="L83" s="14" t="n"/>
+      <c r="M83" s="14" t="n"/>
+      <c r="N83" s="14" t="n"/>
+      <c r="O83" s="14" t="n"/>
+      <c r="P83" s="14" t="n"/>
+      <c r="Q83" s="14" t="n">
         <v>3.03</v>
       </c>
-      <c r="R82" s="3" t="inlineStr">
+      <c r="R83" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="83" outlineLevel="1">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="84" outlineLevel="1">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>Feel</t>
         </is>
       </c>
-      <c r="C83" s="11" t="n"/>
-      <c r="D83" s="11" t="inlineStr">
+      <c r="C84" s="11" t="n"/>
+      <c r="D84" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E83" s="11" t="n"/>
-      <c r="F83" s="11" t="n"/>
-      <c r="G83" s="12" t="n"/>
-      <c r="H83" s="12" t="n">
-        <v>801.75</v>
-      </c>
-      <c r="I83" s="12" t="n">
-        <v>1047</v>
-      </c>
-      <c r="J83" s="12" t="n">
-        <v>1068</v>
-      </c>
-      <c r="K83" s="12" t="n">
-        <v>3214</v>
-      </c>
-      <c r="L83" s="12" t="n">
-        <v>1219</v>
-      </c>
-      <c r="M83" s="12" t="n">
-        <v>1193</v>
-      </c>
-      <c r="N83" s="12" t="n"/>
-      <c r="O83" s="12" t="n"/>
-      <c r="P83" s="12" t="n"/>
-      <c r="Q83" s="12" t="n">
-        <v>8542.75</v>
-      </c>
-      <c r="R83" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" outlineLevel="2">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B84" s="11" t="inlineStr">
-        <is>
-          <t>Feel</t>
-        </is>
-      </c>
-      <c r="C84" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E84" s="11" t="n"/>
       <c r="F84" s="11" t="n"/>
       <c r="G84" s="12" t="n"/>
       <c r="H84" s="12" t="n">
@@ -9281,432 +9364,436 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" outlineLevel="2">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>Feel</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>Jahez</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="n"/>
+      <c r="G85" s="12" t="n"/>
+      <c r="H85" s="12" t="n">
+        <v>801.75</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>1047</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>1068</v>
+      </c>
+      <c r="K85" s="12" t="n">
+        <v>3214</v>
+      </c>
+      <c r="L85" s="12" t="n">
+        <v>1219</v>
+      </c>
+      <c r="M85" s="12" t="n">
+        <v>1193</v>
+      </c>
+      <c r="N85" s="12" t="n"/>
+      <c r="O85" s="12" t="n"/>
+      <c r="P85" s="12" t="n"/>
+      <c r="Q85" s="12" t="n">
+        <v>8542.75</v>
+      </c>
+      <c r="R85" s="3" t="inlineStr">
+        <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="85" outlineLevel="2">
-      <c r="A85" s="13" t="inlineStr">
+    <row r="86" outlineLevel="2">
+      <c r="A86" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B85" s="13" t="inlineStr">
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>Feel ≈</t>
         </is>
       </c>
-      <c r="C85" s="13" t="inlineStr">
+      <c r="C86" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D85" s="13" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E85" s="13" t="inlineStr">
+      <c r="E86" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F85" s="13" t="inlineStr">
+      <c r="F86" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G85" s="14" t="n"/>
-      <c r="H85" s="14" t="n"/>
-      <c r="I85" s="14" t="n">
+      <c r="G86" s="14" t="n"/>
+      <c r="H86" s="14" t="n"/>
+      <c r="I86" s="14" t="n">
         <v>22.14</v>
       </c>
-      <c r="J85" s="14" t="n">
+      <c r="J86" s="14" t="n">
         <v>21.36</v>
       </c>
-      <c r="K85" s="14" t="n">
+      <c r="K86" s="14" t="n">
         <v>64.28</v>
       </c>
-      <c r="L85" s="14" t="n">
+      <c r="L86" s="14" t="n">
         <v>23.58</v>
       </c>
-      <c r="M85" s="14" t="n">
+      <c r="M86" s="14" t="n">
         <v>24.46</v>
       </c>
-      <c r="N85" s="14" t="n"/>
-      <c r="O85" s="14" t="n"/>
-      <c r="P85" s="14" t="n"/>
-      <c r="Q85" s="14" t="n">
+      <c r="N86" s="14" t="n"/>
+      <c r="O86" s="14" t="n"/>
+      <c r="P86" s="14" t="n"/>
+      <c r="Q86" s="14" t="n">
         <v>155.82</v>
       </c>
-      <c r="R85" s="3" t="inlineStr">
+      <c r="R86" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="86" outlineLevel="1">
-      <c r="A86" s="11" t="inlineStr">
+    <row r="87" outlineLevel="1">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>Reefi</t>
         </is>
       </c>
-      <c r="C86" s="11" t="n"/>
-      <c r="D86" s="11" t="inlineStr">
+      <c r="C87" s="11" t="n"/>
+      <c r="D87" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E86" s="11" t="n"/>
-      <c r="F86" s="11" t="n"/>
-      <c r="G86" s="12" t="n">
+      <c r="E87" s="11" t="n"/>
+      <c r="F87" s="11" t="n"/>
+      <c r="G87" s="12" t="n">
         <v>1949.46</v>
       </c>
-      <c r="H86" s="12" t="n">
+      <c r="H87" s="12" t="n">
         <v>11692.19</v>
       </c>
-      <c r="I86" s="12" t="n">
+      <c r="I87" s="12" t="n">
         <v>17810.99</v>
       </c>
-      <c r="J86" s="12" t="n">
+      <c r="J87" s="12" t="n">
         <v>8609.1</v>
       </c>
-      <c r="K86" s="12" t="n">
+      <c r="K87" s="12" t="n">
         <v>18582.9</v>
       </c>
-      <c r="L86" s="12" t="n">
+      <c r="L87" s="12" t="n">
         <v>11841.5</v>
       </c>
-      <c r="M86" s="12" t="n">
+      <c r="M87" s="12" t="n">
         <v>17164.82</v>
-      </c>
-      <c r="N86" s="12" t="n"/>
-      <c r="O86" s="12" t="n"/>
-      <c r="P86" s="12" t="n"/>
-      <c r="Q86" s="12" t="n">
-        <v>87650.96000000001</v>
-      </c>
-      <c r="R86" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" outlineLevel="2">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t>Reefi</t>
-        </is>
-      </c>
-      <c r="C87" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F87" s="11" t="n"/>
-      <c r="G87" s="12" t="n"/>
-      <c r="H87" s="12" t="n">
-        <v>7960.01</v>
-      </c>
-      <c r="I87" s="12" t="n">
-        <v>16919.59</v>
-      </c>
-      <c r="J87" s="12" t="n">
-        <v>7725</v>
-      </c>
-      <c r="K87" s="12" t="n">
-        <v>17372.35</v>
-      </c>
-      <c r="L87" s="12" t="n">
-        <v>7113</v>
-      </c>
-      <c r="M87" s="12" t="n">
-        <v>10864.82</v>
       </c>
       <c r="N87" s="12" t="n"/>
       <c r="O87" s="12" t="n"/>
       <c r="P87" s="12" t="n"/>
       <c r="Q87" s="12" t="n">
+        <v>87650.96000000001</v>
+      </c>
+      <c r="R87" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" outlineLevel="2">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>Reefi</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>Jahez</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="n"/>
+      <c r="G88" s="12" t="n"/>
+      <c r="H88" s="12" t="n">
+        <v>7960.01</v>
+      </c>
+      <c r="I88" s="12" t="n">
+        <v>16919.59</v>
+      </c>
+      <c r="J88" s="12" t="n">
+        <v>7725</v>
+      </c>
+      <c r="K88" s="12" t="n">
+        <v>17372.35</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>7113</v>
+      </c>
+      <c r="M88" s="12" t="n">
+        <v>10864.82</v>
+      </c>
+      <c r="N88" s="12" t="n"/>
+      <c r="O88" s="12" t="n"/>
+      <c r="P88" s="12" t="n"/>
+      <c r="Q88" s="12" t="n">
         <v>67954.77</v>
       </c>
-      <c r="R87" s="3" t="inlineStr">
+      <c r="R88" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="88" outlineLevel="2">
-      <c r="A88" s="13" t="inlineStr">
+    <row r="89" outlineLevel="2">
+      <c r="A89" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B88" s="13" t="inlineStr">
+      <c r="B89" s="13" t="inlineStr">
         <is>
           <t>Reefi ≈</t>
         </is>
       </c>
-      <c r="C88" s="13" t="inlineStr">
+      <c r="C89" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D88" s="13" t="inlineStr">
+      <c r="D89" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E88" s="13" t="inlineStr">
+      <c r="E89" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F88" s="13" t="inlineStr">
+      <c r="F89" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G88" s="14" t="n"/>
-      <c r="H88" s="14" t="n"/>
-      <c r="I88" s="14" t="n">
+      <c r="G89" s="14" t="n"/>
+      <c r="H89" s="14" t="n"/>
+      <c r="I89" s="14" t="n">
         <v>357.85</v>
       </c>
-      <c r="J88" s="14" t="n">
+      <c r="J89" s="14" t="n">
         <v>154.5</v>
       </c>
-      <c r="K88" s="14" t="n">
+      <c r="K89" s="14" t="n">
         <v>347.45</v>
       </c>
-      <c r="L88" s="14" t="n">
+      <c r="L89" s="14" t="n">
         <v>137.56</v>
       </c>
-      <c r="M88" s="14" t="n">
+      <c r="M89" s="14" t="n">
         <v>222.77</v>
       </c>
-      <c r="N88" s="14" t="n"/>
-      <c r="O88" s="14" t="n"/>
-      <c r="P88" s="14" t="n"/>
-      <c r="Q88" s="14" t="n">
+      <c r="N89" s="14" t="n"/>
+      <c r="O89" s="14" t="n"/>
+      <c r="P89" s="14" t="n"/>
+      <c r="Q89" s="14" t="n">
         <v>1220.13</v>
       </c>
-      <c r="R88" s="3" t="inlineStr">
+      <c r="R89" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="89" outlineLevel="2">
-      <c r="A89" s="11" t="inlineStr">
+    <row r="90" outlineLevel="2">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>Reefi</t>
         </is>
       </c>
-      <c r="C89" s="11" t="inlineStr">
+      <c r="C90" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D89" s="11" t="inlineStr">
+      <c r="D90" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E89" s="11" t="inlineStr">
+      <c r="E90" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F89" s="11" t="n"/>
-      <c r="G89" s="12" t="n">
+      <c r="F90" s="11" t="n"/>
+      <c r="G90" s="12" t="n">
         <v>1949.46</v>
       </c>
-      <c r="H89" s="12" t="n">
+      <c r="H90" s="12" t="n">
         <v>3732.18</v>
       </c>
-      <c r="I89" s="12" t="n">
+      <c r="I90" s="12" t="n">
         <v>891.4</v>
       </c>
-      <c r="J89" s="12" t="n">
+      <c r="J90" s="12" t="n">
         <v>884.1</v>
       </c>
-      <c r="K89" s="12" t="n">
+      <c r="K90" s="12" t="n">
         <v>1210.55</v>
       </c>
-      <c r="L89" s="12" t="n">
+      <c r="L90" s="12" t="n">
         <v>4728.5</v>
       </c>
-      <c r="M89" s="12" t="n">
+      <c r="M90" s="12" t="n">
         <v>6300</v>
       </c>
-      <c r="N89" s="12" t="n"/>
-      <c r="O89" s="12" t="n"/>
-      <c r="P89" s="12" t="n"/>
-      <c r="Q89" s="12" t="n">
+      <c r="N90" s="12" t="n"/>
+      <c r="O90" s="12" t="n"/>
+      <c r="P90" s="12" t="n"/>
+      <c r="Q90" s="12" t="n">
         <v>19696.19</v>
       </c>
-      <c r="R89" s="3" t="inlineStr">
+      <c r="R90" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="90" outlineLevel="2">
-      <c r="A90" s="13" t="inlineStr">
+    <row r="91" outlineLevel="2">
+      <c r="A91" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B90" s="13" t="inlineStr">
+      <c r="B91" s="13" t="inlineStr">
         <is>
           <t>Reefi ≈</t>
         </is>
       </c>
-      <c r="C90" s="13" t="inlineStr">
+      <c r="C91" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D90" s="13" t="inlineStr">
+      <c r="D91" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E90" s="13" t="inlineStr">
+      <c r="E91" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F90" s="13" t="inlineStr">
+      <c r="F91" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G90" s="14" t="n"/>
-      <c r="H90" s="14" t="n"/>
-      <c r="I90" s="14" t="n">
+      <c r="G91" s="14" t="n"/>
+      <c r="H91" s="14" t="n"/>
+      <c r="I91" s="14" t="n">
         <v>23.07</v>
       </c>
-      <c r="J90" s="14" t="n">
+      <c r="J91" s="14" t="n">
         <v>53.14</v>
       </c>
-      <c r="K90" s="14" t="n">
+      <c r="K91" s="14" t="n">
         <v>25.79</v>
       </c>
-      <c r="L90" s="14" t="n">
+      <c r="L91" s="14" t="n">
         <v>89.58</v>
       </c>
-      <c r="M90" s="14" t="n">
+      <c r="M91" s="14" t="n">
         <v>127.37</v>
       </c>
-      <c r="N90" s="14" t="n"/>
-      <c r="O90" s="14" t="n"/>
-      <c r="P90" s="14" t="n"/>
-      <c r="Q90" s="14" t="n">
+      <c r="N91" s="14" t="n"/>
+      <c r="O91" s="14" t="n"/>
+      <c r="P91" s="14" t="n"/>
+      <c r="Q91" s="14" t="n">
         <v>318.95</v>
       </c>
-      <c r="R90" s="3" t="inlineStr">
+      <c r="R91" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="91" outlineLevel="1">
-      <c r="A91" s="11" t="inlineStr">
+    <row r="92" outlineLevel="1">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>brio</t>
         </is>
       </c>
-      <c r="C91" s="11" t="n"/>
-      <c r="D91" s="11" t="inlineStr">
+      <c r="C92" s="11" t="n"/>
+      <c r="D92" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E91" s="11" t="n"/>
-      <c r="F91" s="11" t="n"/>
-      <c r="G91" s="12" t="n"/>
-      <c r="H91" s="12" t="n">
-        <v>1343.45</v>
-      </c>
-      <c r="I91" s="12" t="n">
-        <v>2456.81</v>
-      </c>
-      <c r="J91" s="12" t="n"/>
-      <c r="K91" s="12" t="n">
-        <v>1677.37</v>
-      </c>
-      <c r="L91" s="12" t="n"/>
-      <c r="M91" s="12" t="n">
-        <v>896.39</v>
-      </c>
-      <c r="N91" s="12" t="n"/>
-      <c r="O91" s="12" t="n"/>
-      <c r="P91" s="12" t="n"/>
-      <c r="Q91" s="12" t="n">
-        <v>6374.02</v>
-      </c>
-      <c r="R91" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" outlineLevel="2">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B92" s="11" t="inlineStr">
-        <is>
-          <t>brio</t>
-        </is>
-      </c>
-      <c r="C92" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D92" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E92" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E92" s="11" t="n"/>
       <c r="F92" s="11" t="n"/>
       <c r="G92" s="12" t="n"/>
       <c r="H92" s="12" t="n">
@@ -9720,249 +9807,245 @@
         <v>1677.37</v>
       </c>
       <c r="L92" s="12" t="n"/>
-      <c r="M92" s="12" t="n"/>
+      <c r="M92" s="12" t="n">
+        <v>896.39</v>
+      </c>
       <c r="N92" s="12" t="n"/>
       <c r="O92" s="12" t="n"/>
       <c r="P92" s="12" t="n"/>
       <c r="Q92" s="12" t="n">
+        <v>6374.02</v>
+      </c>
+      <c r="R92" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" outlineLevel="2">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>brio</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>Jahez</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="n"/>
+      <c r="G93" s="12" t="n"/>
+      <c r="H93" s="12" t="n">
+        <v>1343.45</v>
+      </c>
+      <c r="I93" s="12" t="n">
+        <v>2456.81</v>
+      </c>
+      <c r="J93" s="12" t="n"/>
+      <c r="K93" s="12" t="n">
+        <v>1677.37</v>
+      </c>
+      <c r="L93" s="12" t="n"/>
+      <c r="M93" s="12" t="n"/>
+      <c r="N93" s="12" t="n"/>
+      <c r="O93" s="12" t="n"/>
+      <c r="P93" s="12" t="n"/>
+      <c r="Q93" s="12" t="n">
         <v>5477.63</v>
       </c>
-      <c r="R92" s="3" t="inlineStr">
+      <c r="R93" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="93" outlineLevel="2">
-      <c r="A93" s="13" t="inlineStr">
+    <row r="94" outlineLevel="2">
+      <c r="A94" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B93" s="13" t="inlineStr">
+      <c r="B94" s="13" t="inlineStr">
         <is>
           <t>brio ≈</t>
         </is>
       </c>
-      <c r="C93" s="13" t="inlineStr">
+      <c r="C94" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D93" s="13" t="inlineStr">
+      <c r="D94" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E93" s="13" t="inlineStr">
+      <c r="E94" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F93" s="13" t="inlineStr">
+      <c r="F94" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G93" s="14" t="n"/>
-      <c r="H93" s="14" t="n"/>
-      <c r="I93" s="14" t="n">
+      <c r="G94" s="14" t="n"/>
+      <c r="H94" s="14" t="n"/>
+      <c r="I94" s="14" t="n">
         <v>51.96</v>
       </c>
-      <c r="J93" s="14" t="n"/>
-      <c r="K93" s="14" t="n">
+      <c r="J94" s="14" t="n"/>
+      <c r="K94" s="14" t="n">
         <v>33.55</v>
       </c>
-      <c r="L93" s="14" t="n"/>
-      <c r="M93" s="14" t="n"/>
-      <c r="N93" s="14" t="n"/>
-      <c r="O93" s="14" t="n"/>
-      <c r="P93" s="14" t="n"/>
-      <c r="Q93" s="14" t="n">
+      <c r="L94" s="14" t="n"/>
+      <c r="M94" s="14" t="n"/>
+      <c r="N94" s="14" t="n"/>
+      <c r="O94" s="14" t="n"/>
+      <c r="P94" s="14" t="n"/>
+      <c r="Q94" s="14" t="n">
         <v>85.51000000000001</v>
       </c>
-      <c r="R93" s="3" t="inlineStr">
+      <c r="R94" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="94" outlineLevel="2">
-      <c r="A94" s="11" t="inlineStr">
+    <row r="95" outlineLevel="2">
+      <c r="A95" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>brio</t>
         </is>
       </c>
-      <c r="C94" s="11" t="inlineStr">
+      <c r="C95" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D94" s="11" t="inlineStr">
+      <c r="D95" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E94" s="11" t="inlineStr">
+      <c r="E95" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F94" s="11" t="n"/>
-      <c r="G94" s="12" t="n"/>
-      <c r="H94" s="12" t="n"/>
-      <c r="I94" s="12" t="n"/>
-      <c r="J94" s="12" t="n"/>
-      <c r="K94" s="12" t="n"/>
-      <c r="L94" s="12" t="n"/>
-      <c r="M94" s="12" t="n">
+      <c r="F95" s="11" t="n"/>
+      <c r="G95" s="12" t="n"/>
+      <c r="H95" s="12" t="n"/>
+      <c r="I95" s="12" t="n"/>
+      <c r="J95" s="12" t="n"/>
+      <c r="K95" s="12" t="n"/>
+      <c r="L95" s="12" t="n"/>
+      <c r="M95" s="12" t="n">
         <v>896.39</v>
       </c>
-      <c r="N94" s="12" t="n"/>
-      <c r="O94" s="12" t="n"/>
-      <c r="P94" s="12" t="n"/>
-      <c r="Q94" s="12" t="n">
+      <c r="N95" s="12" t="n"/>
+      <c r="O95" s="12" t="n"/>
+      <c r="P95" s="12" t="n"/>
+      <c r="Q95" s="12" t="n">
         <v>896.39</v>
       </c>
-      <c r="R94" s="3" t="inlineStr">
+      <c r="R95" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="95" outlineLevel="2">
-      <c r="A95" s="13" t="inlineStr">
+    <row r="96" outlineLevel="2">
+      <c r="A96" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B95" s="13" t="inlineStr">
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>brio ≈</t>
         </is>
       </c>
-      <c r="C95" s="13" t="inlineStr">
+      <c r="C96" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D95" s="13" t="inlineStr">
+      <c r="D96" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E95" s="13" t="inlineStr">
+      <c r="E96" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F95" s="13" t="inlineStr">
+      <c r="F96" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G95" s="14" t="n"/>
-      <c r="H95" s="14" t="n"/>
-      <c r="I95" s="14" t="n"/>
-      <c r="J95" s="14" t="n"/>
-      <c r="K95" s="14" t="n"/>
-      <c r="L95" s="14" t="n"/>
-      <c r="M95" s="14" t="n">
+      <c r="G96" s="14" t="n"/>
+      <c r="H96" s="14" t="n"/>
+      <c r="I96" s="14" t="n"/>
+      <c r="J96" s="14" t="n"/>
+      <c r="K96" s="14" t="n"/>
+      <c r="L96" s="14" t="n"/>
+      <c r="M96" s="14" t="n">
         <v>18.12</v>
       </c>
-      <c r="N95" s="14" t="n"/>
-      <c r="O95" s="14" t="n"/>
-      <c r="P95" s="14" t="n"/>
-      <c r="Q95" s="14" t="n">
+      <c r="N96" s="14" t="n"/>
+      <c r="O96" s="14" t="n"/>
+      <c r="P96" s="14" t="n"/>
+      <c r="Q96" s="14" t="n">
         <v>18.12</v>
       </c>
-      <c r="R95" s="3" t="inlineStr">
+      <c r="R96" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="96" outlineLevel="1">
-      <c r="A96" s="11" t="inlineStr">
+    <row r="97" outlineLevel="1">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>circles</t>
         </is>
       </c>
-      <c r="C96" s="11" t="n"/>
-      <c r="D96" s="11" t="inlineStr">
+      <c r="C97" s="11" t="n"/>
+      <c r="D97" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E96" s="11" t="n"/>
-      <c r="F96" s="11" t="n"/>
-      <c r="G96" s="12" t="n"/>
-      <c r="H96" s="12" t="n">
-        <v>269.57</v>
-      </c>
-      <c r="I96" s="12" t="n">
-        <v>310</v>
-      </c>
-      <c r="J96" s="12" t="n">
-        <v>300</v>
-      </c>
-      <c r="K96" s="12" t="n">
-        <v>330</v>
-      </c>
-      <c r="L96" s="12" t="n">
-        <v>426</v>
-      </c>
-      <c r="M96" s="12" t="n">
-        <v>668</v>
-      </c>
-      <c r="N96" s="12" t="n"/>
-      <c r="O96" s="12" t="n"/>
-      <c r="P96" s="12" t="n"/>
-      <c r="Q96" s="12" t="n">
-        <v>2303.57</v>
-      </c>
-      <c r="R96" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" outlineLevel="2">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t>circles</t>
-        </is>
-      </c>
-      <c r="C97" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D97" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E97" s="11" t="n"/>
       <c r="F97" s="11" t="n"/>
       <c r="G97" s="12" t="n"/>
       <c r="H97" s="12" t="n">
@@ -9978,7 +10061,7 @@
         <v>330</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="M97" s="12" t="n">
         <v>668</v>
@@ -9987,256 +10070,256 @@
       <c r="O97" s="12" t="n"/>
       <c r="P97" s="12" t="n"/>
       <c r="Q97" s="12" t="n">
+        <v>2303.57</v>
+      </c>
+      <c r="R97" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" outlineLevel="2">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>circles</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>Jahez</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="n"/>
+      <c r="G98" s="12" t="n"/>
+      <c r="H98" s="12" t="n">
+        <v>269.57</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>310</v>
+      </c>
+      <c r="J98" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>330</v>
+      </c>
+      <c r="L98" s="12" t="n">
+        <v>378</v>
+      </c>
+      <c r="M98" s="12" t="n">
+        <v>668</v>
+      </c>
+      <c r="N98" s="12" t="n"/>
+      <c r="O98" s="12" t="n"/>
+      <c r="P98" s="12" t="n"/>
+      <c r="Q98" s="12" t="n">
         <v>2255.57</v>
       </c>
-      <c r="R97" s="3" t="inlineStr">
+      <c r="R98" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="98" outlineLevel="2">
-      <c r="A98" s="13" t="inlineStr">
+    <row r="99" outlineLevel="2">
+      <c r="A99" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B98" s="13" t="inlineStr">
+      <c r="B99" s="13" t="inlineStr">
         <is>
           <t>circles ≈</t>
         </is>
       </c>
-      <c r="C98" s="13" t="inlineStr">
+      <c r="C99" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D98" s="13" t="inlineStr">
+      <c r="D99" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E98" s="13" t="inlineStr">
+      <c r="E99" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F98" s="13" t="inlineStr">
+      <c r="F99" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G98" s="14" t="n"/>
-      <c r="H98" s="14" t="n"/>
-      <c r="I98" s="14" t="n">
+      <c r="G99" s="14" t="n"/>
+      <c r="H99" s="14" t="n"/>
+      <c r="I99" s="14" t="n">
         <v>6.56</v>
       </c>
-      <c r="J98" s="14" t="n">
+      <c r="J99" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="K98" s="14" t="n">
+      <c r="K99" s="14" t="n">
         <v>6.6</v>
       </c>
-      <c r="L98" s="14" t="n">
+      <c r="L99" s="14" t="n">
         <v>7.31</v>
       </c>
-      <c r="M98" s="14" t="n">
+      <c r="M99" s="14" t="n">
         <v>13.7</v>
       </c>
-      <c r="N98" s="14" t="n"/>
-      <c r="O98" s="14" t="n"/>
-      <c r="P98" s="14" t="n"/>
-      <c r="Q98" s="14" t="n">
+      <c r="N99" s="14" t="n"/>
+      <c r="O99" s="14" t="n"/>
+      <c r="P99" s="14" t="n"/>
+      <c r="Q99" s="14" t="n">
         <v>40.16</v>
       </c>
-      <c r="R98" s="3" t="inlineStr">
+      <c r="R99" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="99" outlineLevel="2">
-      <c r="A99" s="11" t="inlineStr">
+    <row r="100" outlineLevel="2">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>circles</t>
         </is>
       </c>
-      <c r="C99" s="11" t="inlineStr">
+      <c r="C100" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D99" s="11" t="inlineStr">
+      <c r="D100" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E99" s="11" t="inlineStr">
+      <c r="E100" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F99" s="11" t="n"/>
-      <c r="G99" s="12" t="n"/>
-      <c r="H99" s="12" t="n"/>
-      <c r="I99" s="12" t="n"/>
-      <c r="J99" s="12" t="n"/>
-      <c r="K99" s="12" t="n"/>
-      <c r="L99" s="12" t="n">
+      <c r="F100" s="11" t="n"/>
+      <c r="G100" s="12" t="n"/>
+      <c r="H100" s="12" t="n"/>
+      <c r="I100" s="12" t="n"/>
+      <c r="J100" s="12" t="n"/>
+      <c r="K100" s="12" t="n"/>
+      <c r="L100" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="M99" s="12" t="n"/>
-      <c r="N99" s="12" t="n"/>
-      <c r="O99" s="12" t="n"/>
-      <c r="P99" s="12" t="n"/>
-      <c r="Q99" s="12" t="n">
+      <c r="M100" s="12" t="n"/>
+      <c r="N100" s="12" t="n"/>
+      <c r="O100" s="12" t="n"/>
+      <c r="P100" s="12" t="n"/>
+      <c r="Q100" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="R99" s="3" t="inlineStr">
+      <c r="R100" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="100" outlineLevel="2">
-      <c r="A100" s="13" t="inlineStr">
+    <row r="101" outlineLevel="2">
+      <c r="A101" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B100" s="13" t="inlineStr">
+      <c r="B101" s="13" t="inlineStr">
         <is>
           <t>circles ≈</t>
         </is>
       </c>
-      <c r="C100" s="13" t="inlineStr">
+      <c r="C101" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D100" s="13" t="inlineStr">
+      <c r="D101" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E100" s="13" t="inlineStr">
+      <c r="E101" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F100" s="13" t="inlineStr">
+      <c r="F101" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G100" s="14" t="n"/>
-      <c r="H100" s="14" t="n"/>
-      <c r="I100" s="14" t="n"/>
-      <c r="J100" s="14" t="n"/>
-      <c r="K100" s="14" t="n"/>
-      <c r="L100" s="14" t="n">
+      <c r="G101" s="14" t="n"/>
+      <c r="H101" s="14" t="n"/>
+      <c r="I101" s="14" t="n"/>
+      <c r="J101" s="14" t="n"/>
+      <c r="K101" s="14" t="n"/>
+      <c r="L101" s="14" t="n">
         <v>0.91</v>
       </c>
-      <c r="M100" s="14" t="n"/>
-      <c r="N100" s="14" t="n"/>
-      <c r="O100" s="14" t="n"/>
-      <c r="P100" s="14" t="n"/>
-      <c r="Q100" s="14" t="n">
+      <c r="M101" s="14" t="n"/>
+      <c r="N101" s="14" t="n"/>
+      <c r="O101" s="14" t="n"/>
+      <c r="P101" s="14" t="n"/>
+      <c r="Q101" s="14" t="n">
         <v>0.91</v>
       </c>
-      <c r="R100" s="3" t="inlineStr">
+      <c r="R101" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="101" outlineLevel="1">
-      <c r="A101" s="11" t="inlineStr">
+    <row r="102" outlineLevel="1">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>labelle</t>
         </is>
       </c>
-      <c r="C101" s="11" t="n"/>
-      <c r="D101" s="11" t="inlineStr">
+      <c r="C102" s="11" t="n"/>
+      <c r="D102" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E101" s="11" t="n"/>
-      <c r="F101" s="11" t="n"/>
-      <c r="G101" s="12" t="n">
+      <c r="E102" s="11" t="n"/>
+      <c r="F102" s="11" t="n"/>
+      <c r="G102" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="H101" s="12" t="n">
+      <c r="H102" s="12" t="n">
         <v>7203.2</v>
-      </c>
-      <c r="I101" s="12" t="n">
-        <v>8006.86</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>647.96</v>
-      </c>
-      <c r="K101" s="12" t="n">
-        <v>7216.83</v>
-      </c>
-      <c r="L101" s="12" t="n">
-        <v>3410.26</v>
-      </c>
-      <c r="M101" s="12" t="n">
-        <v>2723</v>
-      </c>
-      <c r="N101" s="12" t="n"/>
-      <c r="O101" s="12" t="n"/>
-      <c r="P101" s="12" t="n"/>
-      <c r="Q101" s="12" t="n">
-        <v>29406.11</v>
-      </c>
-      <c r="R101" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" outlineLevel="2">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="inlineStr">
-        <is>
-          <t>labelle</t>
-        </is>
-      </c>
-      <c r="C102" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E102" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F102" s="11" t="n"/>
-      <c r="G102" s="12" t="n"/>
-      <c r="H102" s="12" t="n">
-        <v>5377.58</v>
       </c>
       <c r="I102" s="12" t="n">
         <v>8006.86</v>
@@ -10248,7 +10331,7 @@
         <v>7216.83</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>3072</v>
+        <v>3410.26</v>
       </c>
       <c r="M102" s="12" t="n">
         <v>2723</v>
@@ -10257,227 +10340,233 @@
       <c r="O102" s="12" t="n"/>
       <c r="P102" s="12" t="n"/>
       <c r="Q102" s="12" t="n">
+        <v>29406.11</v>
+      </c>
+      <c r="R102" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" outlineLevel="2">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>labelle</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>Jahez</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="n"/>
+      <c r="G103" s="12" t="n"/>
+      <c r="H103" s="12" t="n">
+        <v>5377.58</v>
+      </c>
+      <c r="I103" s="12" t="n">
+        <v>8006.86</v>
+      </c>
+      <c r="J103" s="12" t="n">
+        <v>647.96</v>
+      </c>
+      <c r="K103" s="12" t="n">
+        <v>7216.83</v>
+      </c>
+      <c r="L103" s="12" t="n">
+        <v>3072</v>
+      </c>
+      <c r="M103" s="12" t="n">
+        <v>2723</v>
+      </c>
+      <c r="N103" s="12" t="n"/>
+      <c r="O103" s="12" t="n"/>
+      <c r="P103" s="12" t="n"/>
+      <c r="Q103" s="12" t="n">
         <v>27044.23</v>
       </c>
-      <c r="R102" s="3" t="inlineStr">
+      <c r="R103" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="103" outlineLevel="2">
-      <c r="A103" s="13" t="inlineStr">
+    <row r="104" outlineLevel="2">
+      <c r="A104" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B103" s="13" t="inlineStr">
+      <c r="B104" s="13" t="inlineStr">
         <is>
           <t>labelle ≈</t>
         </is>
       </c>
-      <c r="C103" s="13" t="inlineStr">
+      <c r="C104" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D103" s="13" t="inlineStr">
+      <c r="D104" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E103" s="13" t="inlineStr">
+      <c r="E104" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F103" s="13" t="inlineStr">
+      <c r="F104" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G103" s="14" t="n"/>
-      <c r="H103" s="14" t="n"/>
-      <c r="I103" s="14" t="n">
+      <c r="G104" s="14" t="n"/>
+      <c r="H104" s="14" t="n"/>
+      <c r="I104" s="14" t="n">
         <v>169.35</v>
       </c>
-      <c r="J103" s="14" t="n">
+      <c r="J104" s="14" t="n">
         <v>12.96</v>
       </c>
-      <c r="K103" s="14" t="n">
+      <c r="K104" s="14" t="n">
         <v>144.34</v>
       </c>
-      <c r="L103" s="14" t="n">
+      <c r="L104" s="14" t="n">
         <v>59.41</v>
       </c>
-      <c r="M103" s="14" t="n">
+      <c r="M104" s="14" t="n">
         <v>55.83</v>
       </c>
-      <c r="N103" s="14" t="n"/>
-      <c r="O103" s="14" t="n"/>
-      <c r="P103" s="14" t="n"/>
-      <c r="Q103" s="14" t="n">
+      <c r="N104" s="14" t="n"/>
+      <c r="O104" s="14" t="n"/>
+      <c r="P104" s="14" t="n"/>
+      <c r="Q104" s="14" t="n">
         <v>441.89</v>
       </c>
-      <c r="R103" s="3" t="inlineStr">
+      <c r="R104" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="104" outlineLevel="2">
-      <c r="A104" s="11" t="inlineStr">
+    <row r="105" outlineLevel="2">
+      <c r="A105" s="11" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>labelle</t>
         </is>
       </c>
-      <c r="C104" s="11" t="inlineStr">
+      <c r="C105" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D104" s="11" t="inlineStr">
+      <c r="D105" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E104" s="11" t="inlineStr">
+      <c r="E105" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F104" s="11" t="n"/>
-      <c r="G104" s="12" t="n">
+      <c r="F105" s="11" t="n"/>
+      <c r="G105" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="H104" s="12" t="n">
+      <c r="H105" s="12" t="n">
         <v>1825.62</v>
       </c>
-      <c r="I104" s="12" t="n"/>
-      <c r="J104" s="12" t="n"/>
-      <c r="K104" s="12" t="n"/>
-      <c r="L104" s="12" t="n">
+      <c r="I105" s="12" t="n"/>
+      <c r="J105" s="12" t="n"/>
+      <c r="K105" s="12" t="n"/>
+      <c r="L105" s="12" t="n">
         <v>338.26</v>
       </c>
-      <c r="M104" s="12" t="n"/>
-      <c r="N104" s="12" t="n"/>
-      <c r="O104" s="12" t="n"/>
-      <c r="P104" s="12" t="n"/>
-      <c r="Q104" s="12" t="n">
+      <c r="M105" s="12" t="n"/>
+      <c r="N105" s="12" t="n"/>
+      <c r="O105" s="12" t="n"/>
+      <c r="P105" s="12" t="n"/>
+      <c r="Q105" s="12" t="n">
         <v>2361.88</v>
       </c>
-      <c r="R104" s="3" t="inlineStr">
+      <c r="R105" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — orders view</t>
         </is>
       </c>
     </row>
-    <row r="105" outlineLevel="2">
-      <c r="A105" s="13" t="inlineStr">
+    <row r="106" outlineLevel="2">
+      <c r="A106" s="13" t="inlineStr">
         <is>
           <t>Two United</t>
         </is>
       </c>
-      <c r="B105" s="13" t="inlineStr">
+      <c r="B106" s="13" t="inlineStr">
         <is>
           <t>labelle ≈</t>
         </is>
       </c>
-      <c r="C105" s="13" t="inlineStr">
+      <c r="C106" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D105" s="13" t="inlineStr">
+      <c r="D106" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E105" s="13" t="inlineStr">
+      <c r="E106" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F105" s="13" t="inlineStr">
+      <c r="F106" s="13" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G105" s="14" t="n"/>
-      <c r="H105" s="14" t="n"/>
-      <c r="I105" s="14" t="n"/>
-      <c r="J105" s="14" t="n"/>
-      <c r="K105" s="14" t="n"/>
-      <c r="L105" s="14" t="n">
+      <c r="G106" s="14" t="n"/>
+      <c r="H106" s="14" t="n"/>
+      <c r="I106" s="14" t="n"/>
+      <c r="J106" s="14" t="n"/>
+      <c r="K106" s="14" t="n"/>
+      <c r="L106" s="14" t="n">
         <v>6.41</v>
       </c>
-      <c r="M105" s="14" t="n"/>
-      <c r="N105" s="14" t="n"/>
-      <c r="O105" s="14" t="n"/>
-      <c r="P105" s="14" t="n"/>
-      <c r="Q105" s="14" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="R105" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" outlineLevel="1">
-      <c r="A106" s="13" t="inlineStr">
-        <is>
-          <t>Two United</t>
-        </is>
-      </c>
-      <c r="B106" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C106" s="13" t="n"/>
-      <c r="D106" s="13" t="inlineStr">
-        <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E106" s="13" t="n"/>
-      <c r="F106" s="13" t="n"/>
-      <c r="G106" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H106" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I106" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J106" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="K106" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L106" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M106" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="M106" s="14" t="n"/>
       <c r="N106" s="14" t="n"/>
       <c r="O106" s="14" t="n"/>
       <c r="P106" s="14" t="n"/>
       <c r="Q106" s="14" t="n">
-        <v>35000</v>
+        <v>6.41</v>
       </c>
       <c r="R106" s="3" t="inlineStr">
         <is>
-          <t>Wafeq invoice export</t>
+          <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
@@ -10495,983 +10584,977 @@
       <c r="C107" s="13" t="n"/>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>Monthly fee</t>
         </is>
       </c>
       <c r="E107" s="13" t="n"/>
       <c r="F107" s="13" t="n"/>
-      <c r="G107" s="14" t="n"/>
-      <c r="H107" s="14" t="n"/>
+      <c r="G107" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H107" s="14" t="n">
+        <v>5000</v>
+      </c>
       <c r="I107" s="14" t="n">
-        <v>-2050.2</v>
+        <v>5000</v>
       </c>
       <c r="J107" s="14" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="K107" s="14" t="n"/>
-      <c r="L107" s="14" t="n"/>
-      <c r="M107" s="14" t="n"/>
+        <v>5000</v>
+      </c>
+      <c r="K107" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L107" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M107" s="14" t="n">
+        <v>5000</v>
+      </c>
       <c r="N107" s="14" t="n"/>
       <c r="O107" s="14" t="n"/>
       <c r="P107" s="14" t="n"/>
       <c r="Q107" s="14" t="n">
+        <v>35000</v>
+      </c>
+      <c r="R107" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" outlineLevel="1">
+      <c r="A108" s="13" t="inlineStr">
+        <is>
+          <t>Two United</t>
+        </is>
+      </c>
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C108" s="13" t="n"/>
+      <c r="D108" s="13" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="n"/>
+      <c r="F108" s="13" t="n"/>
+      <c r="G108" s="14" t="n"/>
+      <c r="H108" s="14" t="n"/>
+      <c r="I108" s="14" t="n">
+        <v>-2050.2</v>
+      </c>
+      <c r="J108" s="14" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="K108" s="14" t="n"/>
+      <c r="L108" s="14" t="n"/>
+      <c r="M108" s="14" t="n"/>
+      <c r="N108" s="14" t="n"/>
+      <c r="O108" s="14" t="n"/>
+      <c r="P108" s="14" t="n"/>
+      <c r="Q108" s="14" t="n">
         <v>-4550.2</v>
       </c>
-      <c r="R107" s="3" t="inlineStr">
+      <c r="R108" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · setup-period 50% AM fee / agreed reduction / pricing error</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
         <is>
           <t>Rimath  (churned 2026-06)</t>
         </is>
       </c>
-      <c r="B109" s="9" t="n"/>
-      <c r="C109" s="9" t="n"/>
-      <c r="D109" s="9" t="inlineStr">
+      <c r="B110" s="9" t="n"/>
+      <c r="C110" s="9" t="n"/>
+      <c r="D110" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E109" s="9" t="n"/>
-      <c r="F109" s="9" t="n"/>
-      <c r="G109" s="10" t="n">
+      <c r="E110" s="9" t="n"/>
+      <c r="F110" s="9" t="n"/>
+      <c r="G110" s="10" t="n">
         <v>3743.36</v>
       </c>
-      <c r="H109" s="10" t="n">
+      <c r="H110" s="10" t="n">
         <v>2998.75</v>
       </c>
-      <c r="I109" s="10" t="n">
+      <c r="I110" s="10" t="n">
         <v>3561.57</v>
       </c>
-      <c r="J109" s="10" t="n">
+      <c r="J110" s="10" t="n">
         <v>4753.24</v>
       </c>
-      <c r="K109" s="10" t="n">
+      <c r="K110" s="10" t="n">
         <v>3970.51</v>
       </c>
-      <c r="L109" s="10" t="n">
+      <c r="L110" s="10" t="n">
         <v>3649.59</v>
       </c>
-      <c r="M109" s="10" t="n">
+      <c r="M110" s="10" t="n">
         <v>3044.62</v>
       </c>
-      <c r="N109" s="10" t="n">
+      <c r="N110" s="10" t="n">
         <v>2819.43</v>
       </c>
-      <c r="O109" s="10" t="n"/>
-      <c r="P109" s="10" t="n"/>
-      <c r="Q109" s="10" t="n">
+      <c r="O110" s="10" t="n"/>
+      <c r="P110" s="10" t="n"/>
+      <c r="Q110" s="10" t="n">
         <v>28541.07</v>
       </c>
-      <c r="R109" s="3" t="inlineStr">
+      <c r="R110" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="110" outlineLevel="1">
-      <c r="A110" s="11" t="inlineStr">
+    <row r="111" outlineLevel="1">
+      <c r="A111" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C110" s="11" t="n"/>
-      <c r="D110" s="11" t="inlineStr">
+      <c r="C111" s="11" t="n"/>
+      <c r="D111" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E110" s="11" t="n"/>
-      <c r="F110" s="11" t="n"/>
-      <c r="G110" s="12" t="n">
-        <v>2261.24</v>
-      </c>
-      <c r="H110" s="12" t="n">
-        <v>1589.06</v>
-      </c>
-      <c r="I110" s="12" t="n">
-        <v>972.27</v>
-      </c>
-      <c r="J110" s="12" t="n">
-        <v>1792.37</v>
-      </c>
-      <c r="K110" s="12" t="n">
-        <v>2105.88</v>
-      </c>
-      <c r="L110" s="12" t="n">
-        <v>1333.37</v>
-      </c>
-      <c r="M110" s="12" t="n">
-        <v>249.01</v>
-      </c>
-      <c r="N110" s="12" t="n">
-        <v>189</v>
-      </c>
-      <c r="O110" s="12" t="n"/>
-      <c r="P110" s="12" t="n"/>
-      <c r="Q110" s="12" t="n">
-        <v>10492.2</v>
-      </c>
-      <c r="R110" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" outlineLevel="2">
-      <c r="A111" s="11" t="inlineStr">
-        <is>
-          <t>Rimath</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="inlineStr">
-        <is>
-          <t>O'SO</t>
-        </is>
-      </c>
-      <c r="C111" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D111" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E111" s="11" t="n"/>
       <c r="F111" s="11" t="n"/>
       <c r="G111" s="12" t="n">
-        <v>1137</v>
+        <v>2261.24</v>
       </c>
       <c r="H111" s="12" t="n">
-        <v>327</v>
+        <v>1589.06</v>
       </c>
       <c r="I111" s="12" t="n">
-        <v>363.99</v>
+        <v>972.27</v>
       </c>
       <c r="J111" s="12" t="n">
-        <v>681.71</v>
+        <v>1792.37</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>577.73</v>
+        <v>2105.88</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>446.94</v>
+        <v>1333.37</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>129</v>
-      </c>
-      <c r="N111" s="12" t="n"/>
+        <v>249.01</v>
+      </c>
+      <c r="N111" s="12" t="n">
+        <v>189</v>
+      </c>
       <c r="O111" s="12" t="n"/>
       <c r="P111" s="12" t="n"/>
       <c r="Q111" s="12" t="n">
+        <v>10492.2</v>
+      </c>
+      <c r="R111" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" outlineLevel="2">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>Rimath</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>O'SO</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="n"/>
+      <c r="G112" s="12" t="n">
+        <v>1137</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>327</v>
+      </c>
+      <c r="I112" s="12" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="J112" s="12" t="n">
+        <v>681.71</v>
+      </c>
+      <c r="K112" s="12" t="n">
+        <v>577.73</v>
+      </c>
+      <c r="L112" s="12" t="n">
+        <v>446.94</v>
+      </c>
+      <c r="M112" s="12" t="n">
+        <v>129</v>
+      </c>
+      <c r="N112" s="12" t="n"/>
+      <c r="O112" s="12" t="n"/>
+      <c r="P112" s="12" t="n"/>
+      <c r="Q112" s="12" t="n">
         <v>3663.37</v>
       </c>
-      <c r="R111" s="3" t="inlineStr">
+      <c r="R112" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="112" outlineLevel="2">
-      <c r="A112" s="13" t="inlineStr">
+    <row r="113" outlineLevel="2">
+      <c r="A113" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B112" s="13" t="inlineStr">
+      <c r="B113" s="13" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C112" s="13" t="inlineStr">
+      <c r="C113" s="13" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D112" s="13" t="inlineStr">
+      <c r="D113" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E112" s="13" t="inlineStr">
+      <c r="E113" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F112" s="13" t="inlineStr">
+      <c r="F113" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G112" s="14" t="n">
+      <c r="G113" s="14" t="n">
         <v>84.91</v>
       </c>
-      <c r="H112" s="14" t="n">
+      <c r="H113" s="14" t="n">
         <v>22.89</v>
       </c>
-      <c r="I112" s="14" t="n">
+      <c r="I113" s="14" t="n">
         <v>25.48</v>
       </c>
-      <c r="J112" s="14" t="n">
+      <c r="J113" s="14" t="n">
         <v>47.72</v>
       </c>
-      <c r="K112" s="14" t="n">
+      <c r="K113" s="14" t="n">
         <v>41.7</v>
       </c>
-      <c r="L112" s="14" t="n">
+      <c r="L113" s="14" t="n">
         <v>31.29</v>
       </c>
-      <c r="M112" s="14" t="n">
+      <c r="M113" s="14" t="n">
         <v>9.029999999999999</v>
       </c>
-      <c r="N112" s="14" t="n"/>
-      <c r="O112" s="14" t="n"/>
-      <c r="P112" s="14" t="n"/>
-      <c r="Q112" s="14" t="n">
+      <c r="N113" s="14" t="n"/>
+      <c r="O113" s="14" t="n"/>
+      <c r="P113" s="14" t="n"/>
+      <c r="Q113" s="14" t="n">
         <v>263.02</v>
       </c>
-      <c r="R112" s="3" t="inlineStr">
+      <c r="R113" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="113" outlineLevel="2">
-      <c r="A113" s="11" t="inlineStr">
+    <row r="114" outlineLevel="2">
+      <c r="A114" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C113" s="11" t="inlineStr">
+      <c r="C114" s="11" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D113" s="11" t="inlineStr">
+      <c r="D114" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E113" s="11" t="inlineStr">
+      <c r="E114" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F113" s="11" t="n"/>
-      <c r="G113" s="12" t="n">
+      <c r="F114" s="11" t="n"/>
+      <c r="G114" s="12" t="n">
         <v>665.5</v>
       </c>
-      <c r="H113" s="12" t="n">
+      <c r="H114" s="12" t="n">
         <v>670</v>
       </c>
-      <c r="I113" s="12" t="n">
+      <c r="I114" s="12" t="n">
         <v>503.86</v>
       </c>
-      <c r="J113" s="12" t="n">
+      <c r="J114" s="12" t="n">
         <v>161.88</v>
       </c>
-      <c r="K113" s="12" t="n">
+      <c r="K114" s="12" t="n">
         <v>548</v>
       </c>
-      <c r="L113" s="12" t="n">
+      <c r="L114" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="M113" s="12" t="n">
+      <c r="M114" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="N113" s="12" t="n">
+      <c r="N114" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="O113" s="12" t="n"/>
-      <c r="P113" s="12" t="n"/>
-      <c r="Q113" s="12" t="n">
+      <c r="O114" s="12" t="n"/>
+      <c r="P114" s="12" t="n"/>
+      <c r="Q114" s="12" t="n">
         <v>2728.24</v>
       </c>
-      <c r="R113" s="3" t="inlineStr">
+      <c r="R114" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="114" outlineLevel="2">
-      <c r="A114" s="13" t="inlineStr">
+    <row r="115" outlineLevel="2">
+      <c r="A115" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B114" s="13" t="inlineStr">
+      <c r="B115" s="13" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C114" s="13" t="inlineStr">
+      <c r="C115" s="13" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D114" s="13" t="inlineStr">
+      <c r="D115" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E114" s="13" t="inlineStr">
+      <c r="E115" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F114" s="13" t="inlineStr">
+      <c r="F115" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G114" s="14" t="n">
+      <c r="G115" s="14" t="n">
         <v>48.83</v>
       </c>
-      <c r="H114" s="14" t="n">
+      <c r="H115" s="14" t="n">
         <v>46.9</v>
       </c>
-      <c r="I114" s="14" t="n">
+      <c r="I115" s="14" t="n">
         <v>31.49</v>
       </c>
-      <c r="J114" s="14" t="n">
+      <c r="J115" s="14" t="n">
         <v>11.33</v>
       </c>
-      <c r="K114" s="14" t="n">
+      <c r="K115" s="14" t="n">
         <v>38.36</v>
       </c>
-      <c r="L114" s="14" t="n">
+      <c r="L115" s="14" t="n">
         <v>6.51</v>
       </c>
-      <c r="M114" s="14" t="n">
+      <c r="M115" s="14" t="n">
         <v>3.78</v>
       </c>
-      <c r="N114" s="14" t="n">
+      <c r="N115" s="14" t="n">
         <v>1.12</v>
       </c>
-      <c r="O114" s="14" t="n"/>
-      <c r="P114" s="14" t="n"/>
-      <c r="Q114" s="14" t="n">
+      <c r="O115" s="14" t="n"/>
+      <c r="P115" s="14" t="n"/>
+      <c r="Q115" s="14" t="n">
         <v>188.32</v>
       </c>
-      <c r="R114" s="3" t="inlineStr">
+      <c r="R115" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="115" outlineLevel="2">
-      <c r="A115" s="11" t="inlineStr">
+    <row r="116" outlineLevel="2">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C115" s="11" t="inlineStr">
+      <c r="C116" s="11" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D115" s="11" t="inlineStr">
+      <c r="D116" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E115" s="11" t="inlineStr">
+      <c r="E116" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F115" s="11" t="n"/>
-      <c r="G115" s="12" t="n">
+      <c r="F116" s="11" t="n"/>
+      <c r="G116" s="12" t="n">
         <v>351.34</v>
       </c>
-      <c r="H115" s="12" t="n">
+      <c r="H116" s="12" t="n">
         <v>468.88</v>
       </c>
-      <c r="I115" s="12" t="n">
+      <c r="I116" s="12" t="n">
         <v>104.42</v>
       </c>
-      <c r="J115" s="12" t="n">
+      <c r="J116" s="12" t="n">
         <v>948.78</v>
       </c>
-      <c r="K115" s="12" t="n">
+      <c r="K116" s="12" t="n">
         <v>980.15</v>
       </c>
-      <c r="L115" s="12" t="n">
+      <c r="L116" s="12" t="n">
         <v>405.99</v>
       </c>
-      <c r="M115" s="12" t="n">
+      <c r="M116" s="12" t="n">
         <v>66.01000000000001</v>
       </c>
-      <c r="N115" s="12" t="n"/>
-      <c r="O115" s="12" t="n"/>
-      <c r="P115" s="12" t="n"/>
-      <c r="Q115" s="12" t="n">
+      <c r="N116" s="12" t="n"/>
+      <c r="O116" s="12" t="n"/>
+      <c r="P116" s="12" t="n"/>
+      <c r="Q116" s="12" t="n">
         <v>3325.57</v>
       </c>
-      <c r="R115" s="3" t="inlineStr">
+      <c r="R116" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="116" outlineLevel="2">
-      <c r="A116" s="13" t="inlineStr">
+    <row r="117" outlineLevel="2">
+      <c r="A117" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B116" s="13" t="inlineStr">
+      <c r="B117" s="13" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C116" s="13" t="inlineStr">
+      <c r="C117" s="13" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D116" s="13" t="inlineStr">
+      <c r="D117" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E116" s="13" t="inlineStr">
+      <c r="E117" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F116" s="13" t="inlineStr">
+      <c r="F117" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G116" s="14" t="n">
+      <c r="G117" s="14" t="n">
         <v>24.59</v>
       </c>
-      <c r="H116" s="14" t="n">
+      <c r="H117" s="14" t="n">
         <v>32.83</v>
       </c>
-      <c r="I116" s="14" t="n">
+      <c r="I117" s="14" t="n">
         <v>7.31</v>
       </c>
-      <c r="J116" s="14" t="n">
+      <c r="J117" s="14" t="n">
         <v>66.41</v>
       </c>
-      <c r="K116" s="14" t="n">
+      <c r="K117" s="14" t="n">
         <v>68.62</v>
       </c>
-      <c r="L116" s="14" t="n">
+      <c r="L117" s="14" t="n">
         <v>28.42</v>
       </c>
-      <c r="M116" s="14" t="n">
+      <c r="M117" s="14" t="n">
         <v>16.83</v>
       </c>
-      <c r="N116" s="14" t="n">
+      <c r="N117" s="14" t="n">
         <v>17.95</v>
       </c>
-      <c r="O116" s="14" t="n"/>
-      <c r="P116" s="14" t="n"/>
-      <c r="Q116" s="14" t="n">
+      <c r="O117" s="14" t="n"/>
+      <c r="P117" s="14" t="n"/>
+      <c r="Q117" s="14" t="n">
         <v>262.96</v>
       </c>
-      <c r="R116" s="3" t="inlineStr">
+      <c r="R117" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="117" outlineLevel="2">
-      <c r="A117" s="11" t="inlineStr">
+    <row r="118" outlineLevel="2">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C117" s="11" t="inlineStr">
+      <c r="C118" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D117" s="11" t="inlineStr">
+      <c r="D118" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E117" s="11" t="inlineStr">
+      <c r="E118" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F117" s="11" t="n"/>
-      <c r="G117" s="12" t="n">
+      <c r="F118" s="11" t="n"/>
+      <c r="G118" s="12" t="n">
         <v>107.4</v>
       </c>
-      <c r="H117" s="12" t="n">
+      <c r="H118" s="12" t="n">
         <v>123.18</v>
       </c>
-      <c r="I117" s="12" t="n"/>
-      <c r="J117" s="12" t="n"/>
-      <c r="K117" s="12" t="n"/>
-      <c r="L117" s="12" t="n">
+      <c r="I118" s="12" t="n"/>
+      <c r="J118" s="12" t="n"/>
+      <c r="K118" s="12" t="n"/>
+      <c r="L118" s="12" t="n">
         <v>387.44</v>
       </c>
-      <c r="M117" s="12" t="n"/>
-      <c r="N117" s="12" t="n">
+      <c r="M118" s="12" t="n"/>
+      <c r="N118" s="12" t="n">
         <v>157</v>
       </c>
-      <c r="O117" s="12" t="n"/>
-      <c r="P117" s="12" t="n"/>
-      <c r="Q117" s="12" t="n">
+      <c r="O118" s="12" t="n"/>
+      <c r="P118" s="12" t="n"/>
+      <c r="Q118" s="12" t="n">
         <v>775.02</v>
       </c>
-      <c r="R117" s="3" t="inlineStr">
+      <c r="R118" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="118" outlineLevel="2">
-      <c r="A118" s="13" t="inlineStr">
+    <row r="119" outlineLevel="2">
+      <c r="A119" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B118" s="13" t="inlineStr">
+      <c r="B119" s="13" t="inlineStr">
         <is>
           <t>O'SO</t>
         </is>
       </c>
-      <c r="C118" s="13" t="inlineStr">
+      <c r="C119" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D118" s="13" t="inlineStr">
+      <c r="D119" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E118" s="13" t="inlineStr">
+      <c r="E119" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F118" s="13" t="inlineStr">
+      <c r="F119" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G118" s="14" t="n">
+      <c r="G119" s="14" t="n">
         <v>14.07</v>
       </c>
-      <c r="H118" s="14" t="n">
+      <c r="H119" s="14" t="n">
         <v>11.27</v>
       </c>
-      <c r="I118" s="14" t="n">
+      <c r="I119" s="14" t="n">
         <v>2.24</v>
       </c>
-      <c r="J118" s="14" t="n"/>
-      <c r="K118" s="14" t="n">
+      <c r="J119" s="14" t="n"/>
+      <c r="K119" s="14" t="n">
         <v>20.24</v>
       </c>
-      <c r="L118" s="14" t="n">
+      <c r="L119" s="14" t="n">
         <v>30.2</v>
       </c>
-      <c r="M118" s="14" t="n"/>
-      <c r="N118" s="14" t="n">
+      <c r="M119" s="14" t="n"/>
+      <c r="N119" s="14" t="n">
         <v>14.35</v>
       </c>
-      <c r="O118" s="14" t="n"/>
-      <c r="P118" s="14" t="n"/>
-      <c r="Q118" s="14" t="n">
+      <c r="O119" s="14" t="n"/>
+      <c r="P119" s="14" t="n"/>
+      <c r="Q119" s="14" t="n">
         <v>92.37</v>
       </c>
-      <c r="R118" s="3" t="inlineStr">
+      <c r="R119" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="119" outlineLevel="1">
-      <c r="A119" s="11" t="inlineStr">
+    <row r="120" outlineLevel="1">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B119" s="11" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C119" s="11" t="n"/>
-      <c r="D119" s="11" t="inlineStr">
+      <c r="C120" s="11" t="n"/>
+      <c r="D120" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E119" s="11" t="n"/>
-      <c r="F119" s="11" t="n"/>
-      <c r="G119" s="12" t="n">
-        <v>11744.34</v>
-      </c>
-      <c r="H119" s="12" t="n">
-        <v>7456.05</v>
-      </c>
-      <c r="I119" s="12" t="n">
-        <v>9033.969999999999</v>
-      </c>
-      <c r="J119" s="12" t="n">
-        <v>26081.7</v>
-      </c>
-      <c r="K119" s="12" t="n">
-        <v>17923.14</v>
-      </c>
-      <c r="L119" s="12" t="n">
-        <v>14640.4</v>
-      </c>
-      <c r="M119" s="12" t="n">
-        <v>6386.02</v>
-      </c>
-      <c r="N119" s="12" t="n">
-        <v>2254</v>
-      </c>
-      <c r="O119" s="12" t="n"/>
-      <c r="P119" s="12" t="n"/>
-      <c r="Q119" s="12" t="n">
-        <v>95519.62</v>
-      </c>
-      <c r="R119" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" outlineLevel="2">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t>Rimath</t>
-        </is>
-      </c>
-      <c r="B120" s="11" t="inlineStr">
-        <is>
-          <t>Thannah</t>
-        </is>
-      </c>
-      <c r="C120" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D120" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E120" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E120" s="11" t="n"/>
       <c r="F120" s="11" t="n"/>
       <c r="G120" s="12" t="n">
-        <v>3133</v>
+        <v>11744.34</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>2398.8</v>
+        <v>7456.05</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>1021.2</v>
+        <v>9033.969999999999</v>
       </c>
       <c r="J120" s="12" t="n">
-        <v>966.8</v>
+        <v>26081.7</v>
       </c>
       <c r="K120" s="12" t="n">
-        <v>3279.4</v>
+        <v>17923.14</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>2579</v>
+        <v>14640.4</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>3199</v>
+        <v>6386.02</v>
       </c>
       <c r="N120" s="12" t="n">
-        <v>1381</v>
+        <v>2254</v>
       </c>
       <c r="O120" s="12" t="n"/>
       <c r="P120" s="12" t="n"/>
       <c r="Q120" s="12" t="n">
+        <v>95519.62</v>
+      </c>
+      <c r="R120" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" outlineLevel="2">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>Rimath</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>Thannah</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="n"/>
+      <c r="G121" s="12" t="n">
+        <v>3133</v>
+      </c>
+      <c r="H121" s="12" t="n">
+        <v>2398.8</v>
+      </c>
+      <c r="I121" s="12" t="n">
+        <v>1021.2</v>
+      </c>
+      <c r="J121" s="12" t="n">
+        <v>966.8</v>
+      </c>
+      <c r="K121" s="12" t="n">
+        <v>3279.4</v>
+      </c>
+      <c r="L121" s="12" t="n">
+        <v>2579</v>
+      </c>
+      <c r="M121" s="12" t="n">
+        <v>3199</v>
+      </c>
+      <c r="N121" s="12" t="n">
+        <v>1381</v>
+      </c>
+      <c r="O121" s="12" t="n"/>
+      <c r="P121" s="12" t="n"/>
+      <c r="Q121" s="12" t="n">
         <v>17958.2</v>
       </c>
-      <c r="R120" s="3" t="inlineStr">
+      <c r="R121" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="121" outlineLevel="2">
-      <c r="A121" s="13" t="inlineStr">
+    <row r="122" outlineLevel="2">
+      <c r="A122" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B121" s="13" t="inlineStr">
+      <c r="B122" s="13" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C121" s="13" t="inlineStr">
+      <c r="C122" s="13" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D121" s="13" t="inlineStr">
+      <c r="D122" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E121" s="13" t="inlineStr">
+      <c r="E122" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F121" s="13" t="inlineStr">
+      <c r="F122" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G121" s="14" t="n">
+      <c r="G122" s="14" t="n">
         <v>219.87</v>
       </c>
-      <c r="H121" s="14" t="n">
+      <c r="H122" s="14" t="n">
         <v>169.76</v>
       </c>
-      <c r="I121" s="14" t="n">
+      <c r="I122" s="14" t="n">
         <v>71.48</v>
       </c>
-      <c r="J121" s="14" t="n">
+      <c r="J122" s="14" t="n">
         <v>67.63</v>
       </c>
-      <c r="K121" s="14" t="n">
+      <c r="K122" s="14" t="n">
         <v>226.55</v>
       </c>
-      <c r="L121" s="14" t="n">
+      <c r="L122" s="14" t="n">
         <v>183.54</v>
       </c>
-      <c r="M121" s="14" t="n">
+      <c r="M122" s="14" t="n">
         <v>223.93</v>
       </c>
-      <c r="N121" s="14" t="n">
+      <c r="N122" s="14" t="n">
         <v>75.31999999999999</v>
       </c>
-      <c r="O121" s="14" t="n"/>
-      <c r="P121" s="14" t="n"/>
-      <c r="Q121" s="14" t="n">
+      <c r="O122" s="14" t="n"/>
+      <c r="P122" s="14" t="n"/>
+      <c r="Q122" s="14" t="n">
         <v>1238.08</v>
       </c>
-      <c r="R121" s="3" t="inlineStr">
+      <c r="R122" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="122" outlineLevel="2">
-      <c r="A122" s="11" t="inlineStr">
+    <row r="123" outlineLevel="2">
+      <c r="A123" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C122" s="11" t="inlineStr">
+      <c r="C123" s="11" t="inlineStr">
         <is>
           <t>Hungerstation</t>
         </is>
       </c>
-      <c r="D122" s="11" t="inlineStr">
+      <c r="D123" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E122" s="11" t="inlineStr">
+      <c r="E123" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F122" s="11" t="n"/>
-      <c r="G122" s="12" t="n">
+      <c r="F123" s="11" t="n"/>
+      <c r="G123" s="12" t="n">
         <v>714</v>
       </c>
-      <c r="H122" s="12" t="n">
+      <c r="H123" s="12" t="n">
         <v>339</v>
       </c>
-      <c r="I122" s="12" t="n">
+      <c r="I123" s="12" t="n">
         <v>595</v>
       </c>
-      <c r="J122" s="12" t="n"/>
-      <c r="K122" s="12" t="n"/>
-      <c r="L122" s="12" t="n"/>
-      <c r="M122" s="12" t="n"/>
-      <c r="N122" s="12" t="n"/>
-      <c r="O122" s="12" t="n"/>
-      <c r="P122" s="12" t="n"/>
-      <c r="Q122" s="12" t="n">
+      <c r="J123" s="12" t="n"/>
+      <c r="K123" s="12" t="n"/>
+      <c r="L123" s="12" t="n"/>
+      <c r="M123" s="12" t="n"/>
+      <c r="N123" s="12" t="n"/>
+      <c r="O123" s="12" t="n"/>
+      <c r="P123" s="12" t="n"/>
+      <c r="Q123" s="12" t="n">
         <v>1648</v>
       </c>
-      <c r="R122" s="3" t="inlineStr">
+      <c r="R123" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="123" outlineLevel="2">
-      <c r="A123" s="13" t="inlineStr">
+    <row r="124" outlineLevel="2">
+      <c r="A124" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B123" s="13" t="inlineStr">
+      <c r="B124" s="13" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C123" s="13" t="inlineStr">
+      <c r="C124" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D123" s="13" t="inlineStr">
+      <c r="D124" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E123" s="13" t="inlineStr">
+      <c r="E124" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F123" s="13" t="inlineStr">
+      <c r="F124" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G123" s="14" t="n">
+      <c r="G124" s="14" t="n">
         <v>162.47</v>
       </c>
-      <c r="H123" s="14" t="n">
+      <c r="H124" s="14" t="n">
         <v>101.5</v>
       </c>
-      <c r="I123" s="14" t="n">
+      <c r="I124" s="14" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="J123" s="14" t="n">
+      <c r="J124" s="14" t="n">
         <v>15.6</v>
       </c>
-      <c r="K123" s="14" t="n"/>
-      <c r="L123" s="14" t="n">
+      <c r="K124" s="14" t="n"/>
+      <c r="L124" s="14" t="n">
         <v>6.74</v>
       </c>
-      <c r="M123" s="14" t="n">
+      <c r="M124" s="14" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="N123" s="14" t="n"/>
-      <c r="O123" s="14" t="n"/>
-      <c r="P123" s="14" t="n"/>
-      <c r="Q123" s="14" t="n">
+      <c r="N124" s="14" t="n"/>
+      <c r="O124" s="14" t="n"/>
+      <c r="P124" s="14" t="n"/>
+      <c r="Q124" s="14" t="n">
         <v>369.95</v>
       </c>
-      <c r="R123" s="3" t="inlineStr">
+      <c r="R124" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" outlineLevel="2">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t>Rimath</t>
-        </is>
-      </c>
-      <c r="B124" s="11" t="inlineStr">
-        <is>
-          <t>Thannah</t>
-        </is>
-      </c>
-      <c r="C124" s="11" t="inlineStr">
-        <is>
-          <t>Jahez</t>
-        </is>
-      </c>
-      <c r="D124" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E124" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F124" s="11" t="n"/>
-      <c r="G124" s="12" t="n">
-        <v>1601</v>
-      </c>
-      <c r="H124" s="12" t="n">
-        <v>869</v>
-      </c>
-      <c r="I124" s="12" t="n">
-        <v>465</v>
-      </c>
-      <c r="J124" s="12" t="n">
-        <v>222.88</v>
-      </c>
-      <c r="K124" s="12" t="n"/>
-      <c r="L124" s="12" t="n">
-        <v>96.31999999999999</v>
-      </c>
-      <c r="M124" s="12" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="N124" s="12" t="n"/>
-      <c r="O124" s="12" t="n"/>
-      <c r="P124" s="12" t="n"/>
-      <c r="Q124" s="12" t="n">
-        <v>3369</v>
-      </c>
-      <c r="R124" s="3" t="inlineStr">
-        <is>
-          <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
@@ -11488,7 +11571,7 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Noon</t>
+          <t>Jahez</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
@@ -11503,1421 +11586,1427 @@
       </c>
       <c r="F125" s="11" t="n"/>
       <c r="G125" s="12" t="n">
-        <v>43</v>
+        <v>1601</v>
       </c>
       <c r="H125" s="12" t="n">
-        <v>666</v>
+        <v>869</v>
       </c>
       <c r="I125" s="12" t="n">
-        <v>316</v>
+        <v>465</v>
       </c>
       <c r="J125" s="12" t="n">
-        <v>1320.29</v>
-      </c>
-      <c r="K125" s="12" t="n">
-        <v>166</v>
-      </c>
+        <v>222.88</v>
+      </c>
+      <c r="K125" s="12" t="n"/>
       <c r="L125" s="12" t="n">
-        <v>200</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>338.8</v>
-      </c>
-      <c r="N125" s="12" t="n">
-        <v>467</v>
-      </c>
+        <v>114.8</v>
+      </c>
+      <c r="N125" s="12" t="n"/>
       <c r="O125" s="12" t="n"/>
       <c r="P125" s="12" t="n"/>
       <c r="Q125" s="12" t="n">
+        <v>3369</v>
+      </c>
+      <c r="R125" s="3" t="inlineStr">
+        <is>
+          <t>Nasam platform — revenue view</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" outlineLevel="2">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>Rimath</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>Thannah</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>Noon</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="n"/>
+      <c r="G126" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="H126" s="12" t="n">
+        <v>666</v>
+      </c>
+      <c r="I126" s="12" t="n">
+        <v>316</v>
+      </c>
+      <c r="J126" s="12" t="n">
+        <v>1320.29</v>
+      </c>
+      <c r="K126" s="12" t="n">
+        <v>166</v>
+      </c>
+      <c r="L126" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="M126" s="12" t="n">
+        <v>338.8</v>
+      </c>
+      <c r="N126" s="12" t="n">
+        <v>467</v>
+      </c>
+      <c r="O126" s="12" t="n"/>
+      <c r="P126" s="12" t="n"/>
+      <c r="Q126" s="12" t="n">
         <v>3517.09</v>
       </c>
-      <c r="R125" s="3" t="inlineStr">
+      <c r="R126" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="126" outlineLevel="2">
-      <c r="A126" s="13" t="inlineStr">
+    <row r="127" outlineLevel="2">
+      <c r="A127" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B126" s="13" t="inlineStr">
+      <c r="B127" s="13" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C126" s="13" t="inlineStr">
+      <c r="C127" s="13" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D126" s="13" t="inlineStr">
+      <c r="D127" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E126" s="13" t="inlineStr">
+      <c r="E127" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F126" s="13" t="inlineStr">
+      <c r="F127" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G126" s="14" t="n">
+      <c r="G127" s="14" t="n">
         <v>3.01</v>
       </c>
-      <c r="H126" s="14" t="n">
+      <c r="H127" s="14" t="n">
         <v>46.62</v>
       </c>
-      <c r="I126" s="14" t="n">
+      <c r="I127" s="14" t="n">
         <v>19.6</v>
       </c>
-      <c r="J126" s="14" t="n">
+      <c r="J127" s="14" t="n">
         <v>92.42</v>
       </c>
-      <c r="K126" s="14" t="n">
+      <c r="K127" s="14" t="n">
         <v>20.44</v>
       </c>
-      <c r="L126" s="14" t="n">
+      <c r="L127" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="M126" s="14" t="n">
+      <c r="M127" s="14" t="n">
         <v>26.31</v>
       </c>
-      <c r="N126" s="14" t="n">
+      <c r="N127" s="14" t="n">
         <v>23.8</v>
       </c>
-      <c r="O126" s="14" t="n"/>
-      <c r="P126" s="14" t="n"/>
-      <c r="Q126" s="14" t="n">
+      <c r="O127" s="14" t="n"/>
+      <c r="P127" s="14" t="n"/>
+      <c r="Q127" s="14" t="n">
         <v>246.2</v>
       </c>
-      <c r="R126" s="3" t="inlineStr">
+      <c r="R127" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="127" outlineLevel="2">
-      <c r="A127" s="11" t="inlineStr">
+    <row r="128" outlineLevel="2">
+      <c r="A128" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C127" s="11" t="inlineStr">
+      <c r="C128" s="11" t="inlineStr">
         <is>
           <t>NoonFood</t>
         </is>
       </c>
-      <c r="D127" s="11" t="inlineStr">
+      <c r="D128" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E127" s="11" t="inlineStr">
+      <c r="E128" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F127" s="11" t="n"/>
-      <c r="G127" s="12" t="n"/>
-      <c r="H127" s="12" t="n">
+      <c r="F128" s="11" t="n"/>
+      <c r="G128" s="12" t="n"/>
+      <c r="H128" s="12" t="n">
         <v>242</v>
       </c>
-      <c r="I127" s="12" t="n"/>
-      <c r="J127" s="12" t="n"/>
-      <c r="K127" s="12" t="n"/>
-      <c r="L127" s="12" t="n"/>
-      <c r="M127" s="12" t="n"/>
-      <c r="N127" s="12" t="n"/>
-      <c r="O127" s="12" t="n"/>
-      <c r="P127" s="12" t="n"/>
-      <c r="Q127" s="12" t="n">
+      <c r="I128" s="12" t="n"/>
+      <c r="J128" s="12" t="n"/>
+      <c r="K128" s="12" t="n"/>
+      <c r="L128" s="12" t="n"/>
+      <c r="M128" s="12" t="n"/>
+      <c r="N128" s="12" t="n"/>
+      <c r="O128" s="12" t="n"/>
+      <c r="P128" s="12" t="n"/>
+      <c r="Q128" s="12" t="n">
         <v>242</v>
       </c>
-      <c r="R127" s="3" t="inlineStr">
+      <c r="R128" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="128" outlineLevel="2">
-      <c r="A128" s="13" t="inlineStr">
+    <row r="129" outlineLevel="2">
+      <c r="A129" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B128" s="13" t="inlineStr">
+      <c r="B129" s="13" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C128" s="13" t="inlineStr">
+      <c r="C129" s="13" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="D128" s="13" t="inlineStr">
+      <c r="D129" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E128" s="13" t="inlineStr">
+      <c r="E129" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F128" s="13" t="inlineStr"/>
-      <c r="G128" s="14" t="n"/>
-      <c r="H128" s="14" t="n"/>
-      <c r="I128" s="14" t="n"/>
-      <c r="J128" s="14" t="n"/>
-      <c r="K128" s="14" t="n"/>
-      <c r="L128" s="14" t="n"/>
-      <c r="M128" s="14" t="n"/>
-      <c r="N128" s="14" t="n">
+      <c r="F129" s="13" t="inlineStr"/>
+      <c r="G129" s="14" t="n"/>
+      <c r="H129" s="14" t="n"/>
+      <c r="I129" s="14" t="n"/>
+      <c r="J129" s="14" t="n"/>
+      <c r="K129" s="14" t="n"/>
+      <c r="L129" s="14" t="n"/>
+      <c r="M129" s="14" t="n"/>
+      <c r="N129" s="14" t="n">
         <v>862.6799999999999</v>
       </c>
-      <c r="O128" s="14" t="n"/>
-      <c r="P128" s="14" t="n"/>
-      <c r="Q128" s="14" t="n">
+      <c r="O129" s="14" t="n"/>
+      <c r="P129" s="14" t="n"/>
+      <c r="Q129" s="14" t="n">
         <v>862.6799999999999</v>
       </c>
-      <c r="R128" s="3" t="inlineStr">
+      <c r="R129" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="129" outlineLevel="2">
-      <c r="A129" s="11" t="inlineStr">
+    <row r="130" outlineLevel="2">
+      <c r="A130" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C129" s="11" t="inlineStr">
+      <c r="C130" s="11" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D129" s="11" t="inlineStr">
+      <c r="D130" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E129" s="11" t="inlineStr">
+      <c r="E130" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F129" s="11" t="n"/>
-      <c r="G129" s="12" t="n">
+      <c r="F130" s="11" t="n"/>
+      <c r="G130" s="12" t="n">
         <v>4949.84</v>
       </c>
-      <c r="H129" s="12" t="n">
+      <c r="H130" s="12" t="n">
         <v>2430.39</v>
       </c>
-      <c r="I129" s="12" t="n">
+      <c r="I130" s="12" t="n">
         <v>6636.77</v>
       </c>
-      <c r="J129" s="12" t="n">
+      <c r="J130" s="12" t="n">
         <v>23571.73</v>
       </c>
-      <c r="K129" s="12" t="n">
+      <c r="K130" s="12" t="n">
         <v>14335.79</v>
       </c>
-      <c r="L129" s="12" t="n">
+      <c r="L130" s="12" t="n">
         <v>11615.48</v>
       </c>
-      <c r="M129" s="12" t="n">
+      <c r="M130" s="12" t="n">
         <v>2340.42</v>
       </c>
-      <c r="N129" s="12" t="n"/>
-      <c r="O129" s="12" t="n"/>
-      <c r="P129" s="12" t="n"/>
-      <c r="Q129" s="12" t="n">
+      <c r="N130" s="12" t="n"/>
+      <c r="O130" s="12" t="n"/>
+      <c r="P130" s="12" t="n"/>
+      <c r="Q130" s="12" t="n">
         <v>65880.42</v>
       </c>
-      <c r="R129" s="3" t="inlineStr">
+      <c r="R130" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="130" outlineLevel="2">
-      <c r="A130" s="13" t="inlineStr">
+    <row r="131" outlineLevel="2">
+      <c r="A131" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B130" s="13" t="inlineStr">
+      <c r="B131" s="13" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C130" s="13" t="inlineStr">
+      <c r="C131" s="13" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D130" s="13" t="inlineStr">
+      <c r="D131" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E130" s="13" t="inlineStr">
+      <c r="E131" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F130" s="13" t="inlineStr">
+      <c r="F131" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G130" s="14" t="n">
+      <c r="G131" s="14" t="n">
         <v>346.49</v>
       </c>
-      <c r="H130" s="14" t="n">
+      <c r="H131" s="14" t="n">
         <v>170.13</v>
       </c>
-      <c r="I130" s="14" t="n">
+      <c r="I131" s="14" t="n">
         <v>464.57</v>
       </c>
-      <c r="J130" s="14" t="n">
+      <c r="J131" s="14" t="n">
         <v>1633.71</v>
       </c>
-      <c r="K130" s="14" t="n">
+      <c r="K131" s="14" t="n">
         <v>1003.51</v>
       </c>
-      <c r="L130" s="14" t="n">
+      <c r="L131" s="14" t="n">
         <v>813.08</v>
       </c>
-      <c r="M130" s="14" t="n">
+      <c r="M131" s="14" t="n">
         <v>288.49</v>
       </c>
-      <c r="N130" s="14" t="n">
+      <c r="N131" s="14" t="n">
         <v>226.89</v>
       </c>
-      <c r="O130" s="14" t="n"/>
-      <c r="P130" s="14" t="n"/>
-      <c r="Q130" s="14" t="n">
+      <c r="O131" s="14" t="n"/>
+      <c r="P131" s="14" t="n"/>
+      <c r="Q131" s="14" t="n">
         <v>4946.87</v>
       </c>
-      <c r="R130" s="3" t="inlineStr">
+      <c r="R131" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="131" outlineLevel="2">
-      <c r="A131" s="11" t="inlineStr">
+    <row r="132" outlineLevel="2">
+      <c r="A132" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C131" s="11" t="inlineStr">
+      <c r="C132" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D131" s="11" t="inlineStr">
+      <c r="D132" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E131" s="11" t="inlineStr">
+      <c r="E132" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F131" s="11" t="n"/>
-      <c r="G131" s="12" t="n">
+      <c r="F132" s="11" t="n"/>
+      <c r="G132" s="12" t="n">
         <v>1303.5</v>
       </c>
-      <c r="H131" s="12" t="n">
+      <c r="H132" s="12" t="n">
         <v>510.86</v>
       </c>
-      <c r="I131" s="12" t="n"/>
-      <c r="J131" s="12" t="n"/>
-      <c r="K131" s="12" t="n">
+      <c r="I132" s="12" t="n"/>
+      <c r="J132" s="12" t="n"/>
+      <c r="K132" s="12" t="n">
         <v>141.95</v>
       </c>
-      <c r="L131" s="12" t="n">
+      <c r="L132" s="12" t="n">
         <v>149.6</v>
       </c>
-      <c r="M131" s="12" t="n">
+      <c r="M132" s="12" t="n">
         <v>393</v>
       </c>
-      <c r="N131" s="12" t="n">
+      <c r="N132" s="12" t="n">
         <v>406</v>
       </c>
-      <c r="O131" s="12" t="n"/>
-      <c r="P131" s="12" t="n"/>
-      <c r="Q131" s="12" t="n">
+      <c r="O132" s="12" t="n"/>
+      <c r="P132" s="12" t="n"/>
+      <c r="Q132" s="12" t="n">
         <v>2904.91</v>
       </c>
-      <c r="R131" s="3" t="inlineStr">
+      <c r="R132" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="132" outlineLevel="2">
-      <c r="A132" s="13" t="inlineStr">
+    <row r="133" outlineLevel="2">
+      <c r="A133" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B132" s="13" t="inlineStr">
+      <c r="B133" s="13" t="inlineStr">
         <is>
           <t>Thannah</t>
         </is>
       </c>
-      <c r="C132" s="13" t="inlineStr">
+      <c r="C133" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D132" s="13" t="inlineStr">
+      <c r="D133" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E132" s="13" t="inlineStr">
+      <c r="E133" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F132" s="13" t="inlineStr">
+      <c r="F133" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G132" s="14" t="n">
+      <c r="G133" s="14" t="n">
         <v>98.39</v>
       </c>
-      <c r="H132" s="14" t="n">
+      <c r="H133" s="14" t="n">
         <v>41.79</v>
       </c>
-      <c r="I132" s="14" t="n"/>
-      <c r="J132" s="14" t="n"/>
-      <c r="K132" s="14" t="n">
+      <c r="I133" s="14" t="n"/>
+      <c r="J133" s="14" t="n"/>
+      <c r="K133" s="14" t="n">
         <v>9.93</v>
       </c>
-      <c r="L132" s="14" t="n">
+      <c r="L133" s="14" t="n">
         <v>10.47</v>
       </c>
-      <c r="M132" s="14" t="n">
+      <c r="M133" s="14" t="n">
         <v>27.51</v>
       </c>
-      <c r="N132" s="14" t="n">
+      <c r="N133" s="14" t="n">
         <v>28.07</v>
       </c>
-      <c r="O132" s="14" t="n"/>
-      <c r="P132" s="14" t="n"/>
-      <c r="Q132" s="14" t="n">
+      <c r="O133" s="14" t="n"/>
+      <c r="P133" s="14" t="n"/>
+      <c r="Q133" s="14" t="n">
         <v>216.16</v>
       </c>
-      <c r="R132" s="3" t="inlineStr">
+      <c r="R133" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="133" outlineLevel="1">
-      <c r="A133" s="11" t="inlineStr">
+    <row r="134" outlineLevel="1">
+      <c r="A134" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B134" s="11" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C133" s="11" t="n"/>
-      <c r="D133" s="11" t="inlineStr">
+      <c r="C134" s="11" t="n"/>
+      <c r="D134" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E133" s="11" t="n"/>
-      <c r="F133" s="11" t="n"/>
-      <c r="G133" s="12" t="n">
-        <v>17966.96</v>
-      </c>
-      <c r="H133" s="12" t="n">
-        <v>12215.09</v>
-      </c>
-      <c r="I133" s="12" t="n">
-        <v>19733.81</v>
-      </c>
-      <c r="J133" s="12" t="n">
-        <v>19995.25</v>
-      </c>
-      <c r="K133" s="12" t="n">
-        <v>14622.86</v>
-      </c>
-      <c r="L133" s="12" t="n">
-        <v>15131.7</v>
-      </c>
-      <c r="M133" s="12" t="n">
-        <v>6146.65</v>
-      </c>
-      <c r="N133" s="12" t="n">
-        <v>2282</v>
-      </c>
-      <c r="O133" s="12" t="n"/>
-      <c r="P133" s="12" t="n"/>
-      <c r="Q133" s="12" t="n">
-        <v>108094.32</v>
-      </c>
-      <c r="R133" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" outlineLevel="2">
-      <c r="A134" s="11" t="inlineStr">
-        <is>
-          <t>Rimath</t>
-        </is>
-      </c>
-      <c r="B134" s="11" t="inlineStr">
-        <is>
-          <t>iOUD</t>
-        </is>
-      </c>
-      <c r="C134" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D134" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E134" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E134" s="11" t="n"/>
       <c r="F134" s="11" t="n"/>
       <c r="G134" s="12" t="n">
-        <v>2893.12</v>
+        <v>17966.96</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>805.8</v>
+        <v>12215.09</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>1930.64</v>
+        <v>19733.81</v>
       </c>
       <c r="J134" s="12" t="n">
-        <v>2215.64</v>
+        <v>19995.25</v>
       </c>
       <c r="K134" s="12" t="n">
-        <v>496.92</v>
+        <v>14622.86</v>
       </c>
       <c r="L134" s="12" t="n">
-        <v>1919</v>
-      </c>
-      <c r="M134" s="12" t="n"/>
+        <v>15131.7</v>
+      </c>
+      <c r="M134" s="12" t="n">
+        <v>6146.65</v>
+      </c>
       <c r="N134" s="12" t="n">
-        <v>378</v>
+        <v>2282</v>
       </c>
       <c r="O134" s="12" t="n"/>
       <c r="P134" s="12" t="n"/>
       <c r="Q134" s="12" t="n">
+        <v>108094.32</v>
+      </c>
+      <c r="R134" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" outlineLevel="2">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>Rimath</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>iOUD</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="n"/>
+      <c r="G135" s="12" t="n">
+        <v>2893.12</v>
+      </c>
+      <c r="H135" s="12" t="n">
+        <v>805.8</v>
+      </c>
+      <c r="I135" s="12" t="n">
+        <v>1930.64</v>
+      </c>
+      <c r="J135" s="12" t="n">
+        <v>2215.64</v>
+      </c>
+      <c r="K135" s="12" t="n">
+        <v>496.92</v>
+      </c>
+      <c r="L135" s="12" t="n">
+        <v>1919</v>
+      </c>
+      <c r="M135" s="12" t="n"/>
+      <c r="N135" s="12" t="n">
+        <v>378</v>
+      </c>
+      <c r="O135" s="12" t="n"/>
+      <c r="P135" s="12" t="n"/>
+      <c r="Q135" s="12" t="n">
         <v>10639.12</v>
       </c>
-      <c r="R134" s="3" t="inlineStr">
+      <c r="R135" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="135" outlineLevel="2">
-      <c r="A135" s="13" t="inlineStr">
+    <row r="136" outlineLevel="2">
+      <c r="A136" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B135" s="13" t="inlineStr">
+      <c r="B136" s="13" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C135" s="13" t="inlineStr">
+      <c r="C136" s="13" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D135" s="13" t="inlineStr">
+      <c r="D136" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E135" s="13" t="inlineStr">
+      <c r="E136" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F135" s="13" t="inlineStr">
+      <c r="F136" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G135" s="14" t="n">
+      <c r="G136" s="14" t="n">
         <v>176.96</v>
       </c>
-      <c r="H135" s="14" t="n">
+      <c r="H136" s="14" t="n">
         <v>56.41</v>
       </c>
-      <c r="I135" s="14" t="n">
+      <c r="I136" s="14" t="n">
         <v>135.14</v>
       </c>
-      <c r="J135" s="14" t="n">
+      <c r="J136" s="14" t="n">
         <v>154.82</v>
       </c>
-      <c r="K135" s="14" t="n">
+      <c r="K136" s="14" t="n">
         <v>52.34</v>
       </c>
-      <c r="L135" s="14" t="n">
+      <c r="L136" s="14" t="n">
         <v>134.33</v>
       </c>
-      <c r="M135" s="14" t="n"/>
-      <c r="N135" s="14" t="n">
+      <c r="M136" s="14" t="n"/>
+      <c r="N136" s="14" t="n">
         <v>17.85</v>
       </c>
-      <c r="O135" s="14" t="n"/>
-      <c r="P135" s="14" t="n"/>
-      <c r="Q135" s="14" t="n">
+      <c r="O136" s="14" t="n"/>
+      <c r="P136" s="14" t="n"/>
+      <c r="Q136" s="14" t="n">
         <v>727.85</v>
       </c>
-      <c r="R135" s="3" t="inlineStr">
+      <c r="R136" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="136" outlineLevel="2">
-      <c r="A136" s="11" t="inlineStr">
+    <row r="137" outlineLevel="2">
+      <c r="A137" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C136" s="11" t="inlineStr">
+      <c r="C137" s="11" t="inlineStr">
         <is>
           <t>Jahez</t>
         </is>
       </c>
-      <c r="D136" s="11" t="inlineStr">
+      <c r="D137" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E136" s="11" t="inlineStr">
+      <c r="E137" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F136" s="11" t="n"/>
-      <c r="G136" s="12" t="n"/>
-      <c r="H136" s="12" t="n"/>
-      <c r="I136" s="12" t="n"/>
-      <c r="J136" s="12" t="n"/>
-      <c r="K136" s="12" t="n"/>
-      <c r="L136" s="12" t="n">
+      <c r="F137" s="11" t="n"/>
+      <c r="G137" s="12" t="n"/>
+      <c r="H137" s="12" t="n"/>
+      <c r="I137" s="12" t="n"/>
+      <c r="J137" s="12" t="n"/>
+      <c r="K137" s="12" t="n"/>
+      <c r="L137" s="12" t="n">
         <v>306</v>
       </c>
-      <c r="M136" s="12" t="n"/>
-      <c r="N136" s="12" t="n"/>
-      <c r="O136" s="12" t="n"/>
-      <c r="P136" s="12" t="n"/>
-      <c r="Q136" s="12" t="n">
+      <c r="M137" s="12" t="n"/>
+      <c r="N137" s="12" t="n"/>
+      <c r="O137" s="12" t="n"/>
+      <c r="P137" s="12" t="n"/>
+      <c r="Q137" s="12" t="n">
         <v>306</v>
       </c>
-      <c r="R136" s="3" t="inlineStr">
+      <c r="R137" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="137" outlineLevel="2">
-      <c r="A137" s="13" t="inlineStr">
+    <row r="138" outlineLevel="2">
+      <c r="A138" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B137" s="13" t="inlineStr">
+      <c r="B138" s="13" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C137" s="13" t="inlineStr">
+      <c r="C138" s="13" t="inlineStr">
         <is>
           <t>Quick-commerce</t>
         </is>
       </c>
-      <c r="D137" s="13" t="inlineStr">
+      <c r="D138" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E137" s="13" t="inlineStr">
+      <c r="E138" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F137" s="13" t="inlineStr">
+      <c r="F138" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G137" s="14" t="n"/>
-      <c r="H137" s="14" t="n"/>
-      <c r="I137" s="14" t="n"/>
-      <c r="J137" s="14" t="n"/>
-      <c r="K137" s="14" t="n"/>
-      <c r="L137" s="14" t="n">
+      <c r="G138" s="14" t="n"/>
+      <c r="H138" s="14" t="n"/>
+      <c r="I138" s="14" t="n"/>
+      <c r="J138" s="14" t="n"/>
+      <c r="K138" s="14" t="n"/>
+      <c r="L138" s="14" t="n">
         <v>21.42</v>
       </c>
-      <c r="M137" s="14" t="n"/>
-      <c r="N137" s="14" t="n"/>
-      <c r="O137" s="14" t="n"/>
-      <c r="P137" s="14" t="n"/>
-      <c r="Q137" s="14" t="n">
+      <c r="M138" s="14" t="n"/>
+      <c r="N138" s="14" t="n"/>
+      <c r="O138" s="14" t="n"/>
+      <c r="P138" s="14" t="n"/>
+      <c r="Q138" s="14" t="n">
         <v>21.42</v>
       </c>
-      <c r="R137" s="3" t="inlineStr">
+      <c r="R138" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="138" outlineLevel="2">
-      <c r="A138" s="11" t="inlineStr">
+    <row r="139" outlineLevel="2">
+      <c r="A139" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B139" s="11" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C138" s="11" t="inlineStr">
+      <c r="C139" s="11" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D138" s="11" t="inlineStr">
+      <c r="D139" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E138" s="11" t="inlineStr">
+      <c r="E139" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F138" s="11" t="n"/>
-      <c r="G138" s="12" t="n">
+      <c r="F139" s="11" t="n"/>
+      <c r="G139" s="12" t="n">
         <v>1930.6</v>
       </c>
-      <c r="H138" s="12" t="n">
+      <c r="H139" s="12" t="n">
         <v>1857</v>
       </c>
-      <c r="I138" s="12" t="n">
+      <c r="I139" s="12" t="n">
         <v>1037.52</v>
       </c>
-      <c r="J138" s="12" t="n">
+      <c r="J139" s="12" t="n">
         <v>2488.96</v>
       </c>
-      <c r="K138" s="12" t="n">
+      <c r="K139" s="12" t="n">
         <v>1688</v>
       </c>
-      <c r="L138" s="12" t="n">
+      <c r="L139" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="M138" s="12" t="n">
+      <c r="M139" s="12" t="n">
         <v>283</v>
       </c>
-      <c r="N138" s="12" t="n">
+      <c r="N139" s="12" t="n">
         <v>1904</v>
       </c>
-      <c r="O138" s="12" t="n"/>
-      <c r="P138" s="12" t="n"/>
-      <c r="Q138" s="12" t="n">
+      <c r="O139" s="12" t="n"/>
+      <c r="P139" s="12" t="n"/>
+      <c r="Q139" s="12" t="n">
         <v>11349.08</v>
       </c>
-      <c r="R138" s="3" t="inlineStr">
+      <c r="R139" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="139" outlineLevel="2">
-      <c r="A139" s="13" t="inlineStr">
+    <row r="140" outlineLevel="2">
+      <c r="A140" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B139" s="13" t="inlineStr">
+      <c r="B140" s="13" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C139" s="13" t="inlineStr">
+      <c r="C140" s="13" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D139" s="13" t="inlineStr">
+      <c r="D140" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E139" s="13" t="inlineStr">
+      <c r="E140" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F139" s="13" t="inlineStr">
+      <c r="F140" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G139" s="14" t="n">
+      <c r="G140" s="14" t="n">
         <v>135.14</v>
       </c>
-      <c r="H139" s="14" t="n">
+      <c r="H140" s="14" t="n">
         <v>129.99</v>
       </c>
-      <c r="I139" s="14" t="n">
+      <c r="I140" s="14" t="n">
         <v>55.06</v>
       </c>
-      <c r="J139" s="14" t="n">
+      <c r="J140" s="14" t="n">
         <v>165.62</v>
       </c>
-      <c r="K139" s="14" t="n">
+      <c r="K140" s="14" t="n">
         <v>118.16</v>
       </c>
-      <c r="L139" s="14" t="n">
+      <c r="L140" s="14" t="n">
         <v>11.2</v>
       </c>
-      <c r="M139" s="14" t="n">
+      <c r="M140" s="14" t="n">
         <v>19.81</v>
       </c>
-      <c r="N139" s="14" t="n">
+      <c r="N140" s="14" t="n">
         <v>117.53</v>
       </c>
-      <c r="O139" s="14" t="n"/>
-      <c r="P139" s="14" t="n"/>
-      <c r="Q139" s="14" t="n">
+      <c r="O140" s="14" t="n"/>
+      <c r="P140" s="14" t="n"/>
+      <c r="Q140" s="14" t="n">
         <v>752.51</v>
       </c>
-      <c r="R139" s="3" t="inlineStr">
+      <c r="R140" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="140" outlineLevel="2">
-      <c r="A140" s="11" t="inlineStr">
+    <row r="141" outlineLevel="2">
+      <c r="A141" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B140" s="11" t="inlineStr">
+      <c r="B141" s="11" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C140" s="11" t="inlineStr">
+      <c r="C141" s="11" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D140" s="11" t="inlineStr">
+      <c r="D141" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E140" s="11" t="inlineStr">
+      <c r="E141" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F140" s="11" t="n"/>
-      <c r="G140" s="12" t="n">
+      <c r="F141" s="11" t="n"/>
+      <c r="G141" s="12" t="n">
         <v>11857.63</v>
       </c>
-      <c r="H140" s="12" t="n">
+      <c r="H141" s="12" t="n">
         <v>9312.950000000001</v>
       </c>
-      <c r="I140" s="12" t="n">
+      <c r="I141" s="12" t="n">
         <v>16765.65</v>
       </c>
-      <c r="J140" s="12" t="n">
+      <c r="J141" s="12" t="n">
         <v>15290.65</v>
       </c>
-      <c r="K140" s="12" t="n">
+      <c r="K141" s="12" t="n">
         <v>11946.93</v>
       </c>
-      <c r="L140" s="12" t="n">
+      <c r="L141" s="12" t="n">
         <v>12677.13</v>
       </c>
-      <c r="M140" s="12" t="n">
+      <c r="M141" s="12" t="n">
         <v>5740.65</v>
       </c>
-      <c r="N140" s="12" t="n"/>
-      <c r="O140" s="12" t="n"/>
-      <c r="P140" s="12" t="n"/>
-      <c r="Q140" s="12" t="n">
+      <c r="N141" s="12" t="n"/>
+      <c r="O141" s="12" t="n"/>
+      <c r="P141" s="12" t="n"/>
+      <c r="Q141" s="12" t="n">
         <v>83591.59</v>
       </c>
-      <c r="R140" s="3" t="inlineStr">
+      <c r="R141" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="141" outlineLevel="2">
-      <c r="A141" s="13" t="inlineStr">
+    <row r="142" outlineLevel="2">
+      <c r="A142" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B141" s="13" t="inlineStr">
+      <c r="B142" s="13" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C141" s="13" t="inlineStr">
+      <c r="C142" s="13" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="D141" s="13" t="inlineStr">
+      <c r="D142" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E141" s="13" t="inlineStr">
+      <c r="E142" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F141" s="13" t="inlineStr">
+      <c r="F142" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G141" s="14" t="n">
+      <c r="G142" s="14" t="n">
         <v>830.03</v>
       </c>
-      <c r="H141" s="14" t="n">
+      <c r="H142" s="14" t="n">
         <v>651.91</v>
       </c>
-      <c r="I141" s="14" t="n">
+      <c r="I142" s="14" t="n">
         <v>1173.6</v>
       </c>
-      <c r="J141" s="14" t="n">
+      <c r="J142" s="14" t="n">
         <v>997.98</v>
       </c>
-      <c r="K141" s="14" t="n">
+      <c r="K142" s="14" t="n">
         <v>836.29</v>
       </c>
-      <c r="L141" s="14" t="n">
+      <c r="L142" s="14" t="n">
         <v>853.52</v>
       </c>
-      <c r="M141" s="14" t="n">
+      <c r="M142" s="14" t="n">
         <v>912.28</v>
       </c>
-      <c r="N141" s="14" t="n">
+      <c r="N142" s="14" t="n">
         <v>283.88</v>
       </c>
-      <c r="O141" s="14" t="n"/>
-      <c r="P141" s="14" t="n"/>
-      <c r="Q141" s="14" t="n">
+      <c r="O142" s="14" t="n"/>
+      <c r="P142" s="14" t="n"/>
+      <c r="Q142" s="14" t="n">
         <v>6539.49</v>
       </c>
-      <c r="R141" s="3" t="inlineStr">
+      <c r="R142" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="142" outlineLevel="2">
-      <c r="A142" s="11" t="inlineStr">
+    <row r="143" outlineLevel="2">
+      <c r="A143" s="11" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B142" s="11" t="inlineStr">
+      <c r="B143" s="11" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C142" s="11" t="inlineStr">
+      <c r="C143" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D142" s="11" t="inlineStr">
+      <c r="D143" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E142" s="11" t="inlineStr">
+      <c r="E143" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F142" s="11" t="n"/>
-      <c r="G142" s="12" t="n">
+      <c r="F143" s="11" t="n"/>
+      <c r="G143" s="12" t="n">
         <v>1285.61</v>
       </c>
-      <c r="H142" s="12" t="n">
+      <c r="H143" s="12" t="n">
         <v>239.34</v>
       </c>
-      <c r="I142" s="12" t="n"/>
-      <c r="J142" s="12" t="n"/>
-      <c r="K142" s="12" t="n">
+      <c r="I143" s="12" t="n"/>
+      <c r="J143" s="12" t="n"/>
+      <c r="K143" s="12" t="n">
         <v>491.01</v>
       </c>
-      <c r="L142" s="12" t="n">
+      <c r="L143" s="12" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="M142" s="12" t="n">
+      <c r="M143" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="N142" s="12" t="n"/>
-      <c r="O142" s="12" t="n"/>
-      <c r="P142" s="12" t="n"/>
-      <c r="Q142" s="12" t="n">
+      <c r="N143" s="12" t="n"/>
+      <c r="O143" s="12" t="n"/>
+      <c r="P143" s="12" t="n"/>
+      <c r="Q143" s="12" t="n">
         <v>2208.53</v>
       </c>
-      <c r="R142" s="3" t="inlineStr">
+      <c r="R143" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="143" outlineLevel="2">
-      <c r="A143" s="13" t="inlineStr">
+    <row r="144" outlineLevel="2">
+      <c r="A144" s="13" t="inlineStr">
         <is>
           <t>Rimath</t>
         </is>
       </c>
-      <c r="B143" s="13" t="inlineStr">
+      <c r="B144" s="13" t="inlineStr">
         <is>
           <t>iOUD</t>
         </is>
       </c>
-      <c r="C143" s="13" t="inlineStr">
+      <c r="C144" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D143" s="13" t="inlineStr">
+      <c r="D144" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E143" s="13" t="inlineStr">
+      <c r="E144" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F143" s="13" t="inlineStr">
+      <c r="F144" s="13" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="G143" s="14" t="n">
+      <c r="G144" s="14" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="H143" s="14" t="n">
+      <c r="H144" s="14" t="n">
         <v>16.75</v>
       </c>
-      <c r="I143" s="14" t="n"/>
-      <c r="J143" s="14" t="n"/>
-      <c r="K143" s="14" t="n">
+      <c r="I144" s="14" t="n"/>
+      <c r="J144" s="14" t="n"/>
+      <c r="K144" s="14" t="n">
         <v>34.37</v>
       </c>
-      <c r="L143" s="14" t="n">
+      <c r="L144" s="14" t="n">
         <v>4.87</v>
       </c>
-      <c r="M143" s="14" t="n">
+      <c r="M144" s="14" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="N143" s="14" t="n"/>
-      <c r="O143" s="14" t="n"/>
-      <c r="P143" s="14" t="n"/>
-      <c r="Q143" s="14" t="n">
-        <v>163.2</v>
-      </c>
-      <c r="R143" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" outlineLevel="1">
-      <c r="A144" s="13" t="inlineStr">
-        <is>
-          <t>Rimath</t>
-        </is>
-      </c>
-      <c r="B144" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C144" s="13" t="n"/>
-      <c r="D144" s="13" t="inlineStr">
-        <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E144" s="13" t="n"/>
-      <c r="F144" s="13" t="n"/>
-      <c r="G144" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H144" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I144" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J144" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K144" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L144" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="M144" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="N144" s="14" t="n">
-        <v>1149.99</v>
-      </c>
+      <c r="N144" s="14" t="n"/>
       <c r="O144" s="14" t="n"/>
       <c r="P144" s="14" t="n"/>
       <c r="Q144" s="14" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="R144" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" outlineLevel="1">
+      <c r="A145" s="13" t="inlineStr">
+        <is>
+          <t>Rimath</t>
+        </is>
+      </c>
+      <c r="B145" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C145" s="13" t="n"/>
+      <c r="D145" s="13" t="inlineStr">
+        <is>
+          <t>Monthly fee</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="n"/>
+      <c r="F145" s="13" t="n"/>
+      <c r="G145" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H145" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I145" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J145" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K145" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L145" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M145" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N145" s="14" t="n">
+        <v>1149.99</v>
+      </c>
+      <c r="O145" s="14" t="n"/>
+      <c r="P145" s="14" t="n"/>
+      <c r="Q145" s="14" t="n">
         <v>11649.99</v>
       </c>
-      <c r="R144" s="3" t="inlineStr">
+      <c r="R145" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · Card 1,500 = 500 × 3 brands</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="9" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya  (churned 2026-05)</t>
         </is>
       </c>
-      <c r="B146" s="9" t="n"/>
-      <c r="C146" s="9" t="n"/>
-      <c r="D146" s="9" t="inlineStr">
+      <c r="B147" s="9" t="n"/>
+      <c r="C147" s="9" t="n"/>
+      <c r="D147" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E146" s="9" t="n"/>
-      <c r="F146" s="9" t="n"/>
-      <c r="G146" s="10" t="n">
+      <c r="E147" s="9" t="n"/>
+      <c r="F147" s="9" t="n"/>
+      <c r="G147" s="10" t="n">
         <v>3041.76</v>
       </c>
-      <c r="H146" s="10" t="n">
+      <c r="H147" s="10" t="n">
         <v>2097.12</v>
       </c>
-      <c r="I146" s="10" t="n">
+      <c r="I147" s="10" t="n">
         <v>2292.39</v>
       </c>
-      <c r="J146" s="10" t="n">
+      <c r="J147" s="10" t="n">
         <v>2880.71</v>
       </c>
-      <c r="K146" s="10" t="n">
+      <c r="K147" s="10" t="n">
         <v>2981.2</v>
       </c>
-      <c r="L146" s="10" t="n">
+      <c r="L147" s="10" t="n">
         <v>2360.37</v>
       </c>
-      <c r="M146" s="10" t="n">
+      <c r="M147" s="10" t="n">
         <v>1670.7</v>
       </c>
-      <c r="N146" s="10" t="n"/>
-      <c r="O146" s="10" t="n"/>
-      <c r="P146" s="10" t="n"/>
-      <c r="Q146" s="10" t="n">
+      <c r="N147" s="10" t="n"/>
+      <c r="O147" s="10" t="n"/>
+      <c r="P147" s="10" t="n"/>
+      <c r="Q147" s="10" t="n">
         <v>17324.25</v>
       </c>
-      <c r="R146" s="3" t="inlineStr">
+      <c r="R147" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · Card: 4% + 1,500/mo</t>
         </is>
       </c>
     </row>
-    <row r="147" outlineLevel="1">
-      <c r="A147" s="11" t="inlineStr">
+    <row r="148" outlineLevel="1">
+      <c r="A148" s="11" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="B147" s="11" t="inlineStr">
+      <c r="B148" s="11" t="inlineStr">
         <is>
           <t>Ancy</t>
         </is>
       </c>
-      <c r="C147" s="11" t="n"/>
-      <c r="D147" s="11" t="inlineStr">
+      <c r="C148" s="11" t="n"/>
+      <c r="D148" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E147" s="11" t="n"/>
-      <c r="F147" s="11" t="n"/>
-      <c r="G147" s="12" t="n">
-        <v>20126.2</v>
-      </c>
-      <c r="H147" s="12" t="n">
-        <v>11164.52</v>
-      </c>
-      <c r="I147" s="12" t="n">
-        <v>11654.13</v>
-      </c>
-      <c r="J147" s="12" t="n">
-        <v>10923.98</v>
-      </c>
-      <c r="K147" s="12" t="n">
-        <v>14516.31</v>
-      </c>
-      <c r="L147" s="12" t="n">
-        <v>13262.43</v>
-      </c>
-      <c r="M147" s="12" t="n">
-        <v>80462.35000000001</v>
-      </c>
-      <c r="N147" s="12" t="n"/>
-      <c r="O147" s="12" t="n"/>
-      <c r="P147" s="12" t="n"/>
-      <c r="Q147" s="12" t="n">
-        <v>162109.92</v>
-      </c>
-      <c r="R147" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" outlineLevel="2">
-      <c r="A148" s="11" t="inlineStr">
-        <is>
-          <t>Ancy &amp; Shaya</t>
-        </is>
-      </c>
-      <c r="B148" s="11" t="inlineStr">
-        <is>
-          <t>Ancy</t>
-        </is>
-      </c>
-      <c r="C148" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D148" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E148" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
+      <c r="E148" s="11" t="n"/>
       <c r="F148" s="11" t="n"/>
       <c r="G148" s="12" t="n">
-        <v>199</v>
+        <v>20126.2</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>4577</v>
+        <v>11164.52</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>6507</v>
+        <v>11654.13</v>
       </c>
       <c r="J148" s="12" t="n">
         <v>10923.98</v>
       </c>
       <c r="K148" s="12" t="n">
-        <v>12112.97</v>
+        <v>14516.31</v>
       </c>
       <c r="L148" s="12" t="n">
-        <v>12715.8</v>
+        <v>13262.43</v>
       </c>
       <c r="M148" s="12" t="n">
-        <v>8243.5</v>
+        <v>80462.35000000001</v>
       </c>
       <c r="N148" s="12" t="n"/>
       <c r="O148" s="12" t="n"/>
       <c r="P148" s="12" t="n"/>
       <c r="Q148" s="12" t="n">
+        <v>162109.92</v>
+      </c>
+      <c r="R148" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" outlineLevel="2">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>Ancy &amp; Shaya</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>Ancy</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F149" s="11" t="n"/>
+      <c r="G149" s="12" t="n">
+        <v>199</v>
+      </c>
+      <c r="H149" s="12" t="n">
+        <v>4577</v>
+      </c>
+      <c r="I149" s="12" t="n">
+        <v>6507</v>
+      </c>
+      <c r="J149" s="12" t="n">
+        <v>10923.98</v>
+      </c>
+      <c r="K149" s="12" t="n">
+        <v>12112.97</v>
+      </c>
+      <c r="L149" s="12" t="n">
+        <v>12715.8</v>
+      </c>
+      <c r="M149" s="12" t="n">
+        <v>8243.5</v>
+      </c>
+      <c r="N149" s="12" t="n"/>
+      <c r="O149" s="12" t="n"/>
+      <c r="P149" s="12" t="n"/>
+      <c r="Q149" s="12" t="n">
         <v>55279.25</v>
       </c>
-      <c r="R148" s="3" t="inlineStr">
+      <c r="R149" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="149" outlineLevel="2">
-      <c r="A149" s="13" t="inlineStr">
+    <row r="150" outlineLevel="2">
+      <c r="A150" s="13" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="B149" s="13" t="inlineStr">
+      <c r="B150" s="13" t="inlineStr">
         <is>
           <t>Ancy ≈</t>
         </is>
       </c>
-      <c r="C149" s="13" t="inlineStr">
+      <c r="C150" s="13" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D149" s="13" t="inlineStr">
+      <c r="D150" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E149" s="13" t="inlineStr">
+      <c r="E150" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F149" s="13" t="inlineStr">
+      <c r="F150" s="13" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="G149" s="14" t="n"/>
-      <c r="H149" s="14" t="n">
+      <c r="G150" s="14" t="n"/>
+      <c r="H150" s="14" t="n">
         <v>183.08</v>
       </c>
-      <c r="I149" s="14" t="n">
+      <c r="I150" s="14" t="n">
         <v>260.28</v>
       </c>
-      <c r="J149" s="14" t="n">
+      <c r="J150" s="14" t="n">
         <v>437.78</v>
       </c>
-      <c r="K149" s="14" t="n">
+      <c r="K150" s="14" t="n">
         <v>475.14</v>
       </c>
-      <c r="L149" s="14" t="n">
+      <c r="L150" s="14" t="n">
         <v>521.03</v>
       </c>
-      <c r="M149" s="14" t="n">
+      <c r="M150" s="14" t="n">
         <v>328.37</v>
       </c>
-      <c r="N149" s="14" t="n"/>
-      <c r="O149" s="14" t="n"/>
-      <c r="P149" s="14" t="n"/>
-      <c r="Q149" s="14" t="n">
+      <c r="N150" s="14" t="n"/>
+      <c r="O150" s="14" t="n"/>
+      <c r="P150" s="14" t="n"/>
+      <c r="Q150" s="14" t="n">
         <v>2205.69</v>
       </c>
-      <c r="R149" s="3" t="inlineStr">
+      <c r="R150" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" outlineLevel="2">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t>Ancy &amp; Shaya</t>
-        </is>
-      </c>
-      <c r="B150" s="11" t="inlineStr">
-        <is>
-          <t>Ancy</t>
-        </is>
-      </c>
-      <c r="C150" s="11" t="inlineStr">
-        <is>
-          <t>Noon</t>
-        </is>
-      </c>
-      <c r="D150" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E150" s="11" t="inlineStr">
-        <is>
-          <t>SaaS</t>
-        </is>
-      </c>
-      <c r="F150" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G150" s="12" t="n"/>
-      <c r="H150" s="12" t="n"/>
-      <c r="I150" s="12" t="n"/>
-      <c r="J150" s="12" t="n"/>
-      <c r="K150" s="12" t="n"/>
-      <c r="L150" s="12" t="n"/>
-      <c r="M150" s="12" t="n">
-        <v>70029.97</v>
-      </c>
-      <c r="N150" s="12" t="n"/>
-      <c r="O150" s="12" t="n"/>
-      <c r="P150" s="12" t="n"/>
-      <c r="Q150" s="12" t="n">
-        <v>70029.97</v>
-      </c>
-      <c r="R150" s="3" t="inlineStr">
-        <is>
-          <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
@@ -12934,7 +13023,7 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Trendyol</t>
+          <t>Noon</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
@@ -12944,320 +13033,320 @@
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F151" s="11" t="n"/>
-      <c r="G151" s="12" t="n">
-        <v>19927.2</v>
-      </c>
-      <c r="H151" s="12" t="n">
-        <v>6587.52</v>
-      </c>
-      <c r="I151" s="12" t="n">
-        <v>5147.13</v>
-      </c>
+          <t>SaaS</t>
+        </is>
+      </c>
+      <c r="F151" s="11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G151" s="12" t="n"/>
+      <c r="H151" s="12" t="n"/>
+      <c r="I151" s="12" t="n"/>
       <c r="J151" s="12" t="n"/>
-      <c r="K151" s="12" t="n">
-        <v>2403.34</v>
-      </c>
-      <c r="L151" s="12" t="n">
-        <v>546.63</v>
-      </c>
+      <c r="K151" s="12" t="n"/>
+      <c r="L151" s="12" t="n"/>
       <c r="M151" s="12" t="n">
-        <v>2188.88</v>
+        <v>70029.97</v>
       </c>
       <c r="N151" s="12" t="n"/>
       <c r="O151" s="12" t="n"/>
       <c r="P151" s="12" t="n"/>
       <c r="Q151" s="12" t="n">
+        <v>70029.97</v>
+      </c>
+      <c r="R151" s="3" t="inlineStr">
+        <is>
+          <t>Nasam platform — revenue view</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" outlineLevel="2">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>Ancy &amp; Shaya</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>Ancy</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="inlineStr">
+        <is>
+          <t>Trendyol</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="n"/>
+      <c r="G152" s="12" t="n">
+        <v>19927.2</v>
+      </c>
+      <c r="H152" s="12" t="n">
+        <v>6587.52</v>
+      </c>
+      <c r="I152" s="12" t="n">
+        <v>5147.13</v>
+      </c>
+      <c r="J152" s="12" t="n"/>
+      <c r="K152" s="12" t="n">
+        <v>2403.34</v>
+      </c>
+      <c r="L152" s="12" t="n">
+        <v>546.63</v>
+      </c>
+      <c r="M152" s="12" t="n">
+        <v>2188.88</v>
+      </c>
+      <c r="N152" s="12" t="n"/>
+      <c r="O152" s="12" t="n"/>
+      <c r="P152" s="12" t="n"/>
+      <c r="Q152" s="12" t="n">
         <v>36800.7</v>
       </c>
-      <c r="R151" s="3" t="inlineStr">
+      <c r="R152" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="152" outlineLevel="2">
-      <c r="A152" s="13" t="inlineStr">
+    <row r="153" outlineLevel="2">
+      <c r="A153" s="13" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="B152" s="13" t="inlineStr">
+      <c r="B153" s="13" t="inlineStr">
         <is>
           <t>Ancy ≈</t>
         </is>
       </c>
-      <c r="C152" s="13" t="inlineStr">
+      <c r="C153" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D152" s="13" t="inlineStr">
+      <c r="D153" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E152" s="13" t="inlineStr">
+      <c r="E153" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F152" s="13" t="inlineStr">
+      <c r="F153" s="13" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="G152" s="14" t="n">
+      <c r="G153" s="14" t="n">
         <v>795.64</v>
       </c>
-      <c r="H152" s="14" t="n">
+      <c r="H153" s="14" t="n">
         <v>263.5</v>
       </c>
-      <c r="I152" s="14" t="n">
+      <c r="I153" s="14" t="n">
         <v>272.5</v>
       </c>
-      <c r="J152" s="14" t="n"/>
-      <c r="K152" s="14" t="n">
+      <c r="J153" s="14" t="n"/>
+      <c r="K153" s="14" t="n">
         <v>101.98</v>
       </c>
-      <c r="L152" s="14" t="n">
+      <c r="L153" s="14" t="n">
         <v>22.22</v>
       </c>
-      <c r="M152" s="14" t="n">
+      <c r="M153" s="14" t="n">
         <v>97.12</v>
       </c>
-      <c r="N152" s="14" t="n"/>
-      <c r="O152" s="14" t="n"/>
-      <c r="P152" s="14" t="n"/>
-      <c r="Q152" s="14" t="n">
+      <c r="N153" s="14" t="n"/>
+      <c r="O153" s="14" t="n"/>
+      <c r="P153" s="14" t="n"/>
+      <c r="Q153" s="14" t="n">
         <v>1552.96</v>
       </c>
-      <c r="R152" s="3" t="inlineStr">
+      <c r="R153" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
-    <row r="153" outlineLevel="1">
-      <c r="A153" s="11" t="inlineStr">
+    <row r="154" outlineLevel="1">
+      <c r="A154" s="11" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="B153" s="11" t="inlineStr">
+      <c r="B154" s="11" t="inlineStr">
         <is>
           <t>Shaya</t>
         </is>
       </c>
-      <c r="C153" s="11" t="n"/>
-      <c r="D153" s="11" t="inlineStr">
+      <c r="C154" s="11" t="n"/>
+      <c r="D154" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E153" s="11" t="n"/>
-      <c r="F153" s="11" t="n"/>
-      <c r="G153" s="12" t="n">
+      <c r="E154" s="11" t="n"/>
+      <c r="F154" s="11" t="n"/>
+      <c r="G154" s="12" t="n">
         <v>16003.24</v>
       </c>
-      <c r="H153" s="12" t="n">
+      <c r="H154" s="12" t="n">
         <v>3763.58</v>
       </c>
-      <c r="I153" s="12" t="n">
+      <c r="I154" s="12" t="n">
         <v>5839.63</v>
       </c>
-      <c r="J153" s="12" t="n">
+      <c r="J154" s="12" t="n">
         <v>13744.33</v>
       </c>
-      <c r="K153" s="12" t="n">
+      <c r="K154" s="12" t="n">
         <v>21709.24</v>
       </c>
-      <c r="L153" s="12" t="n">
+      <c r="L154" s="12" t="n">
         <v>7779.17</v>
       </c>
-      <c r="M153" s="12" t="n">
+      <c r="M154" s="12" t="n">
         <v>52659.24</v>
-      </c>
-      <c r="N153" s="12" t="n"/>
-      <c r="O153" s="12" t="n"/>
-      <c r="P153" s="12" t="n"/>
-      <c r="Q153" s="12" t="n">
-        <v>121498.43</v>
-      </c>
-      <c r="R153" s="3" t="inlineStr">
-        <is>
-          <t>Sum of channel sales below</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" outlineLevel="2">
-      <c r="A154" s="11" t="inlineStr">
-        <is>
-          <t>Ancy &amp; Shaya</t>
-        </is>
-      </c>
-      <c r="B154" s="11" t="inlineStr">
-        <is>
-          <t>Shaya</t>
-        </is>
-      </c>
-      <c r="C154" s="11" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D154" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E154" s="11" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F154" s="11" t="n"/>
-      <c r="G154" s="12" t="n"/>
-      <c r="H154" s="12" t="n"/>
-      <c r="I154" s="12" t="n">
-        <v>3829</v>
-      </c>
-      <c r="J154" s="12" t="n">
-        <v>9830.799999999999</v>
-      </c>
-      <c r="K154" s="12" t="n">
-        <v>5344.2</v>
-      </c>
-      <c r="L154" s="12" t="n">
-        <v>2746</v>
-      </c>
-      <c r="M154" s="12" t="n">
-        <v>3585</v>
       </c>
       <c r="N154" s="12" t="n"/>
       <c r="O154" s="12" t="n"/>
       <c r="P154" s="12" t="n"/>
       <c r="Q154" s="12" t="n">
+        <v>121498.43</v>
+      </c>
+      <c r="R154" s="3" t="inlineStr">
+        <is>
+          <t>Sum of channel sales below</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" outlineLevel="2">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>Ancy &amp; Shaya</t>
+        </is>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>Shaya</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="n"/>
+      <c r="G155" s="12" t="n"/>
+      <c r="H155" s="12" t="n"/>
+      <c r="I155" s="12" t="n">
+        <v>3829</v>
+      </c>
+      <c r="J155" s="12" t="n">
+        <v>9830.799999999999</v>
+      </c>
+      <c r="K155" s="12" t="n">
+        <v>5344.2</v>
+      </c>
+      <c r="L155" s="12" t="n">
+        <v>2746</v>
+      </c>
+      <c r="M155" s="12" t="n">
+        <v>3585</v>
+      </c>
+      <c r="N155" s="12" t="n"/>
+      <c r="O155" s="12" t="n"/>
+      <c r="P155" s="12" t="n"/>
+      <c r="Q155" s="12" t="n">
         <v>25335</v>
       </c>
-      <c r="R154" s="3" t="inlineStr">
+      <c r="R155" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="155" outlineLevel="2">
-      <c r="A155" s="13" t="inlineStr">
+    <row r="156" outlineLevel="2">
+      <c r="A156" s="13" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="B155" s="13" t="inlineStr">
+      <c r="B156" s="13" t="inlineStr">
         <is>
           <t>Shaya ≈</t>
         </is>
       </c>
-      <c r="C155" s="13" t="inlineStr">
+      <c r="C156" s="13" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D155" s="13" t="inlineStr">
+      <c r="D156" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E155" s="13" t="inlineStr">
+      <c r="E156" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F155" s="13" t="inlineStr">
+      <c r="F156" s="13" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="G155" s="14" t="n"/>
-      <c r="H155" s="14" t="n"/>
-      <c r="I155" s="14" t="n">
+      <c r="G156" s="14" t="n"/>
+      <c r="H156" s="14" t="n"/>
+      <c r="I156" s="14" t="n">
         <v>153.16</v>
       </c>
-      <c r="J155" s="14" t="n">
+      <c r="J156" s="14" t="n">
         <v>393.98</v>
       </c>
-      <c r="K155" s="14" t="n">
+      <c r="K156" s="14" t="n">
         <v>209.63</v>
       </c>
-      <c r="L155" s="14" t="n">
+      <c r="L156" s="14" t="n">
         <v>112.52</v>
       </c>
-      <c r="M155" s="14" t="n">
+      <c r="M156" s="14" t="n">
         <v>142.81</v>
       </c>
-      <c r="N155" s="14" t="n"/>
-      <c r="O155" s="14" t="n"/>
-      <c r="P155" s="14" t="n"/>
-      <c r="Q155" s="14" t="n">
+      <c r="N156" s="14" t="n"/>
+      <c r="O156" s="14" t="n"/>
+      <c r="P156" s="14" t="n"/>
+      <c r="Q156" s="14" t="n">
         <v>1012.09</v>
       </c>
-      <c r="R155" s="3" t="inlineStr">
+      <c r="R156" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" outlineLevel="2">
-      <c r="A156" s="11" t="inlineStr">
-        <is>
-          <t>Ancy &amp; Shaya</t>
-        </is>
-      </c>
-      <c r="B156" s="11" t="inlineStr">
-        <is>
-          <t>Shaya</t>
-        </is>
-      </c>
-      <c r="C156" s="11" t="inlineStr">
-        <is>
-          <t>Noon</t>
-        </is>
-      </c>
-      <c r="D156" s="11" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E156" s="11" t="inlineStr">
-        <is>
-          <t>SaaS</t>
-        </is>
-      </c>
-      <c r="F156" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G156" s="12" t="n"/>
-      <c r="H156" s="12" t="n"/>
-      <c r="I156" s="12" t="n"/>
-      <c r="J156" s="12" t="n"/>
-      <c r="K156" s="12" t="n"/>
-      <c r="L156" s="12" t="n"/>
-      <c r="M156" s="12" t="n">
-        <v>44948.37</v>
-      </c>
-      <c r="N156" s="12" t="n"/>
-      <c r="O156" s="12" t="n"/>
-      <c r="P156" s="12" t="n"/>
-      <c r="Q156" s="12" t="n">
-        <v>44948.37</v>
-      </c>
-      <c r="R156" s="3" t="inlineStr">
-        <is>
-          <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
@@ -13274,7 +13363,7 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>Trendyol</t>
+          <t>Noon</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr">
@@ -13284,152 +13373,156 @@
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F157" s="11" t="n"/>
-      <c r="G157" s="12" t="n">
-        <v>16003.24</v>
-      </c>
-      <c r="H157" s="12" t="n">
-        <v>3763.58</v>
-      </c>
-      <c r="I157" s="12" t="n">
-        <v>2010.63</v>
-      </c>
-      <c r="J157" s="12" t="n">
-        <v>3913.53</v>
-      </c>
-      <c r="K157" s="12" t="n">
-        <v>16365.04</v>
-      </c>
-      <c r="L157" s="12" t="n">
-        <v>5033.17</v>
-      </c>
+          <t>SaaS</t>
+        </is>
+      </c>
+      <c r="F157" s="11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G157" s="12" t="n"/>
+      <c r="H157" s="12" t="n"/>
+      <c r="I157" s="12" t="n"/>
+      <c r="J157" s="12" t="n"/>
+      <c r="K157" s="12" t="n"/>
+      <c r="L157" s="12" t="n"/>
       <c r="M157" s="12" t="n">
-        <v>4125.87</v>
+        <v>44948.37</v>
       </c>
       <c r="N157" s="12" t="n"/>
       <c r="O157" s="12" t="n"/>
       <c r="P157" s="12" t="n"/>
       <c r="Q157" s="12" t="n">
+        <v>44948.37</v>
+      </c>
+      <c r="R157" s="3" t="inlineStr">
+        <is>
+          <t>Nasam platform — revenue view</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" outlineLevel="2">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>Ancy &amp; Shaya</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t>Shaya</t>
+        </is>
+      </c>
+      <c r="C158" s="11" t="inlineStr">
+        <is>
+          <t>Trendyol</t>
+        </is>
+      </c>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E158" s="11" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F158" s="11" t="n"/>
+      <c r="G158" s="12" t="n">
+        <v>16003.24</v>
+      </c>
+      <c r="H158" s="12" t="n">
+        <v>3763.58</v>
+      </c>
+      <c r="I158" s="12" t="n">
+        <v>2010.63</v>
+      </c>
+      <c r="J158" s="12" t="n">
+        <v>3913.53</v>
+      </c>
+      <c r="K158" s="12" t="n">
+        <v>16365.04</v>
+      </c>
+      <c r="L158" s="12" t="n">
+        <v>5033.17</v>
+      </c>
+      <c r="M158" s="12" t="n">
+        <v>4125.87</v>
+      </c>
+      <c r="N158" s="12" t="n"/>
+      <c r="O158" s="12" t="n"/>
+      <c r="P158" s="12" t="n"/>
+      <c r="Q158" s="12" t="n">
         <v>51215.06</v>
       </c>
-      <c r="R157" s="3" t="inlineStr">
+      <c r="R158" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="158" outlineLevel="2">
-      <c r="A158" s="13" t="inlineStr">
+    <row r="159" outlineLevel="2">
+      <c r="A159" s="13" t="inlineStr">
         <is>
           <t>Ancy &amp; Shaya</t>
         </is>
       </c>
-      <c r="B158" s="13" t="inlineStr">
+      <c r="B159" s="13" t="inlineStr">
         <is>
           <t>Shaya ≈</t>
         </is>
       </c>
-      <c r="C158" s="13" t="inlineStr">
+      <c r="C159" s="13" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D158" s="13" t="inlineStr">
+      <c r="D159" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E158" s="13" t="inlineStr">
+      <c r="E159" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F158" s="13" t="inlineStr">
+      <c r="F159" s="13" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="G158" s="14" t="n">
+      <c r="G159" s="14" t="n">
         <v>638.97</v>
       </c>
-      <c r="H158" s="14" t="n">
+      <c r="H159" s="14" t="n">
         <v>150.54</v>
       </c>
-      <c r="I158" s="14" t="n">
+      <c r="I159" s="14" t="n">
         <v>106.45</v>
       </c>
-      <c r="J158" s="14" t="n">
+      <c r="J159" s="14" t="n">
         <v>548.95</v>
       </c>
-      <c r="K158" s="14" t="n">
+      <c r="K159" s="14" t="n">
         <v>694.45</v>
       </c>
-      <c r="L158" s="14" t="n">
+      <c r="L159" s="14" t="n">
         <v>204.6</v>
       </c>
-      <c r="M158" s="14" t="n">
+      <c r="M159" s="14" t="n">
         <v>183.05</v>
       </c>
-      <c r="N158" s="14" t="n"/>
-      <c r="O158" s="14" t="n"/>
-      <c r="P158" s="14" t="n"/>
-      <c r="Q158" s="14" t="n">
-        <v>2527.01</v>
-      </c>
-      <c r="R158" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" outlineLevel="1">
-      <c r="A159" s="13" t="inlineStr">
-        <is>
-          <t>Ancy &amp; Shaya</t>
-        </is>
-      </c>
-      <c r="B159" s="13" t="inlineStr">
-        <is>
-          <t>— all brands</t>
-        </is>
-      </c>
-      <c r="C159" s="13" t="inlineStr">
-        <is>
-          <t>Amazon Retail</t>
-        </is>
-      </c>
-      <c r="D159" s="13" t="inlineStr">
-        <is>
-          <t>Commission (billed)</t>
-        </is>
-      </c>
-      <c r="E159" s="13" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F159" s="13" t="inlineStr"/>
-      <c r="G159" s="14" t="n">
-        <v>107.15</v>
-      </c>
-      <c r="H159" s="14" t="n"/>
-      <c r="I159" s="14" t="n"/>
-      <c r="J159" s="14" t="n"/>
-      <c r="K159" s="14" t="n"/>
-      <c r="L159" s="14" t="n"/>
-      <c r="M159" s="14" t="n"/>
       <c r="N159" s="14" t="n"/>
       <c r="O159" s="14" t="n"/>
       <c r="P159" s="14" t="n"/>
       <c r="Q159" s="14" t="n">
-        <v>107.15</v>
+        <v>2527.01</v>
       </c>
       <c r="R159" s="3" t="inlineStr">
         <is>
-          <t>Wafeq invoice export</t>
+          <t>Wafeq invoice export · brand split pro-rata platform GMV</t>
         </is>
       </c>
     </row>
@@ -13441,147 +13534,137 @@
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C160" s="13" t="n"/>
+          <t>— all brands</t>
+        </is>
+      </c>
+      <c r="C160" s="13" t="inlineStr">
+        <is>
+          <t>Amazon Retail</t>
+        </is>
+      </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E160" s="13" t="n"/>
-      <c r="F160" s="13" t="n"/>
+          <t>Commission (billed)</t>
+        </is>
+      </c>
+      <c r="E160" s="13" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F160" s="13" t="inlineStr"/>
       <c r="G160" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H160" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I160" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J160" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K160" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L160" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="M160" s="14" t="n">
-        <v>919.35</v>
-      </c>
+        <v>107.15</v>
+      </c>
+      <c r="H160" s="14" t="n"/>
+      <c r="I160" s="14" t="n"/>
+      <c r="J160" s="14" t="n"/>
+      <c r="K160" s="14" t="n"/>
+      <c r="L160" s="14" t="n"/>
+      <c r="M160" s="14" t="n"/>
       <c r="N160" s="14" t="n"/>
       <c r="O160" s="14" t="n"/>
       <c r="P160" s="14" t="n"/>
       <c r="Q160" s="14" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="R160" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" outlineLevel="1">
+      <c r="A161" s="13" t="inlineStr">
+        <is>
+          <t>Ancy &amp; Shaya</t>
+        </is>
+      </c>
+      <c r="B161" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C161" s="13" t="n"/>
+      <c r="D161" s="13" t="inlineStr">
+        <is>
+          <t>Monthly fee</t>
+        </is>
+      </c>
+      <c r="E161" s="13" t="n"/>
+      <c r="F161" s="13" t="n"/>
+      <c r="G161" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H161" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I161" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J161" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K161" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L161" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M161" s="14" t="n">
+        <v>919.35</v>
+      </c>
+      <c r="N161" s="14" t="n"/>
+      <c r="O161" s="14" t="n"/>
+      <c r="P161" s="14" t="n"/>
+      <c r="Q161" s="14" t="n">
         <v>9919.35</v>
       </c>
-      <c r="R160" s="3" t="inlineStr">
+      <c r="R161" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="9" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="9" t="inlineStr">
         <is>
           <t>Gamesir  (churned 2026-02)</t>
         </is>
       </c>
-      <c r="B162" s="9" t="n"/>
-      <c r="C162" s="9" t="n"/>
-      <c r="D162" s="9" t="inlineStr">
+      <c r="B163" s="9" t="n"/>
+      <c r="C163" s="9" t="n"/>
+      <c r="D163" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E162" s="9" t="n"/>
-      <c r="F162" s="9" t="n"/>
-      <c r="G162" s="10" t="n">
+      <c r="E163" s="9" t="n"/>
+      <c r="F163" s="9" t="n"/>
+      <c r="G163" s="10" t="n">
         <v>3161.37</v>
       </c>
-      <c r="H162" s="10" t="n">
+      <c r="H163" s="10" t="n">
         <v>2732.77</v>
       </c>
-      <c r="I162" s="10" t="n">
+      <c r="I163" s="10" t="n">
         <v>5143.07</v>
       </c>
-      <c r="J162" s="10" t="n">
+      <c r="J163" s="10" t="n">
         <v>512.96</v>
       </c>
-      <c r="K162" s="10" t="n"/>
-      <c r="L162" s="10" t="n"/>
-      <c r="M162" s="10" t="n"/>
-      <c r="N162" s="10" t="n"/>
-      <c r="O162" s="10" t="n"/>
-      <c r="P162" s="10" t="n"/>
-      <c r="Q162" s="10" t="n">
+      <c r="K163" s="10" t="n"/>
+      <c r="L163" s="10" t="n"/>
+      <c r="M163" s="10" t="n"/>
+      <c r="N163" s="10" t="n"/>
+      <c r="O163" s="10" t="n"/>
+      <c r="P163" s="10" t="n"/>
+      <c r="Q163" s="10" t="n">
         <v>11550.17</v>
       </c>
-      <c r="R162" s="3" t="inlineStr">
+      <c r="R163" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · Card: 1.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" outlineLevel="1">
-      <c r="A163" s="13" t="inlineStr">
-        <is>
-          <t>Gamesir</t>
-        </is>
-      </c>
-      <c r="B163" s="13" t="inlineStr">
-        <is>
-          <t>— (no platform brand)</t>
-        </is>
-      </c>
-      <c r="C163" s="13" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D163" s="13" t="inlineStr">
-        <is>
-          <t>Commission (billed)</t>
-        </is>
-      </c>
-      <c r="E163" s="13" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F163" s="13" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G163" s="14" t="n">
-        <v>141.12</v>
-      </c>
-      <c r="H163" s="14" t="n">
-        <v>497.2</v>
-      </c>
-      <c r="I163" s="14" t="n">
-        <v>3143.07</v>
-      </c>
-      <c r="J163" s="14" t="n">
-        <v>227.25</v>
-      </c>
-      <c r="K163" s="14" t="n"/>
-      <c r="L163" s="14" t="n"/>
-      <c r="M163" s="14" t="n"/>
-      <c r="N163" s="14" t="n"/>
-      <c r="O163" s="14" t="n"/>
-      <c r="P163" s="14" t="n"/>
-      <c r="Q163" s="14" t="n">
-        <v>4008.64</v>
-      </c>
-      <c r="R163" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
@@ -13598,7 +13681,7 @@
       </c>
       <c r="C164" s="13" t="inlineStr">
         <is>
-          <t>Noon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D164" s="13" t="inlineStr">
@@ -13611,15 +13694,23 @@
           <t>FAM</t>
         </is>
       </c>
-      <c r="F164" s="13" t="inlineStr"/>
+      <c r="F164" s="13" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
       <c r="G164" s="14" t="n">
-        <v>53.58</v>
+        <v>141.12</v>
       </c>
       <c r="H164" s="14" t="n">
-        <v>235.57</v>
-      </c>
-      <c r="I164" s="14" t="n"/>
-      <c r="J164" s="14" t="n"/>
+        <v>497.2</v>
+      </c>
+      <c r="I164" s="14" t="n">
+        <v>3143.07</v>
+      </c>
+      <c r="J164" s="14" t="n">
+        <v>227.25</v>
+      </c>
       <c r="K164" s="14" t="n"/>
       <c r="L164" s="14" t="n"/>
       <c r="M164" s="14" t="n"/>
@@ -13627,7 +13718,7 @@
       <c r="O164" s="14" t="n"/>
       <c r="P164" s="14" t="n"/>
       <c r="Q164" s="14" t="n">
-        <v>289.15</v>
+        <v>4008.64</v>
       </c>
       <c r="R164" s="3" t="inlineStr">
         <is>
@@ -13643,29 +13734,33 @@
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C165" s="13" t="n"/>
+          <t>— (no platform brand)</t>
+        </is>
+      </c>
+      <c r="C165" s="13" t="inlineStr">
+        <is>
+          <t>Noon</t>
+        </is>
+      </c>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E165" s="13" t="n"/>
-      <c r="F165" s="13" t="n"/>
+          <t>Commission (billed)</t>
+        </is>
+      </c>
+      <c r="E165" s="13" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F165" s="13" t="inlineStr"/>
       <c r="G165" s="14" t="n">
-        <v>2466.67</v>
+        <v>53.58</v>
       </c>
       <c r="H165" s="14" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I165" s="14" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J165" s="14" t="n">
-        <v>285.71</v>
-      </c>
+        <v>235.57</v>
+      </c>
+      <c r="I165" s="14" t="n"/>
+      <c r="J165" s="14" t="n"/>
       <c r="K165" s="14" t="n"/>
       <c r="L165" s="14" t="n"/>
       <c r="M165" s="14" t="n"/>
@@ -13673,7 +13768,7 @@
       <c r="O165" s="14" t="n"/>
       <c r="P165" s="14" t="n"/>
       <c r="Q165" s="14" t="n">
-        <v>6752.38</v>
+        <v>289.15</v>
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
@@ -13695,17 +13790,23 @@
       <c r="C166" s="13" t="n"/>
       <c r="D166" s="13" t="inlineStr">
         <is>
-          <t>Setup / one-time</t>
+          <t>Monthly fee</t>
         </is>
       </c>
       <c r="E166" s="13" t="n"/>
       <c r="F166" s="13" t="n"/>
       <c r="G166" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="H166" s="14" t="n"/>
-      <c r="I166" s="14" t="n"/>
-      <c r="J166" s="14" t="n"/>
+        <v>2466.67</v>
+      </c>
+      <c r="H166" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I166" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J166" s="14" t="n">
+        <v>285.71</v>
+      </c>
       <c r="K166" s="14" t="n"/>
       <c r="L166" s="14" t="n"/>
       <c r="M166" s="14" t="n"/>
@@ -13713,165 +13814,147 @@
       <c r="O166" s="14" t="n"/>
       <c r="P166" s="14" t="n"/>
       <c r="Q166" s="14" t="n">
+        <v>6752.38</v>
+      </c>
+      <c r="R166" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" outlineLevel="1">
+      <c r="A167" s="13" t="inlineStr">
+        <is>
+          <t>Gamesir</t>
+        </is>
+      </c>
+      <c r="B167" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C167" s="13" t="n"/>
+      <c r="D167" s="13" t="inlineStr">
+        <is>
+          <t>Setup / one-time</t>
+        </is>
+      </c>
+      <c r="E167" s="13" t="n"/>
+      <c r="F167" s="13" t="n"/>
+      <c r="G167" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="R166" s="3" t="inlineStr">
+      <c r="H167" s="14" t="n"/>
+      <c r="I167" s="14" t="n"/>
+      <c r="J167" s="14" t="n"/>
+      <c r="K167" s="14" t="n"/>
+      <c r="L167" s="14" t="n"/>
+      <c r="M167" s="14" t="n"/>
+      <c r="N167" s="14" t="n"/>
+      <c r="O167" s="14" t="n"/>
+      <c r="P167" s="14" t="n"/>
+      <c r="Q167" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="R167" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="9" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="9" t="inlineStr">
         <is>
           <t>Safwat Aljouf  (churned 2026-02)</t>
         </is>
       </c>
-      <c r="B168" s="9" t="n"/>
-      <c r="C168" s="9" t="n"/>
-      <c r="D168" s="9" t="inlineStr">
+      <c r="B169" s="9" t="n"/>
+      <c r="C169" s="9" t="n"/>
+      <c r="D169" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E168" s="9" t="n"/>
-      <c r="F168" s="9" t="n"/>
-      <c r="G168" s="10" t="n">
+      <c r="E169" s="9" t="n"/>
+      <c r="F169" s="9" t="n"/>
+      <c r="G169" s="10" t="n">
         <v>3585.43</v>
       </c>
-      <c r="H168" s="10" t="n">
+      <c r="H169" s="10" t="n">
         <v>2564.26</v>
       </c>
-      <c r="I168" s="10" t="n">
+      <c r="I169" s="10" t="n">
         <v>2607.58</v>
       </c>
-      <c r="J168" s="10" t="n">
+      <c r="J169" s="10" t="n">
         <v>837.29</v>
       </c>
-      <c r="K168" s="10" t="n"/>
-      <c r="L168" s="10" t="n"/>
-      <c r="M168" s="10" t="n"/>
-      <c r="N168" s="10" t="n"/>
-      <c r="O168" s="10" t="n"/>
-      <c r="P168" s="10" t="n"/>
-      <c r="Q168" s="10" t="n">
+      <c r="K169" s="10" t="n"/>
+      <c r="L169" s="10" t="n"/>
+      <c r="M169" s="10" t="n"/>
+      <c r="N169" s="10" t="n"/>
+      <c r="O169" s="10" t="n"/>
+      <c r="P169" s="10" t="n"/>
+      <c r="Q169" s="10" t="n">
         <v>9594.559999999999</v>
       </c>
-      <c r="R168" s="3" t="inlineStr">
+      <c r="R169" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · Card: 6%</t>
         </is>
       </c>
     </row>
-    <row r="169" outlineLevel="1">
-      <c r="A169" s="11" t="inlineStr">
+    <row r="170" outlineLevel="1">
+      <c r="A170" s="11" t="inlineStr">
         <is>
           <t>Safwat Aljouf</t>
         </is>
       </c>
-      <c r="B169" s="11" t="inlineStr">
+      <c r="B170" s="11" t="inlineStr">
         <is>
           <t>Safwat Aljawf</t>
         </is>
       </c>
-      <c r="C169" s="11" t="inlineStr">
+      <c r="C170" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D169" s="11" t="inlineStr">
+      <c r="D170" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E169" s="11" t="inlineStr">
+      <c r="E170" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F169" s="11" t="n"/>
-      <c r="G169" s="12" t="n">
+      <c r="F170" s="11" t="n"/>
+      <c r="G170" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="H169" s="12" t="n">
+      <c r="H170" s="12" t="n">
         <v>1071</v>
       </c>
-      <c r="I169" s="12" t="n">
+      <c r="I170" s="12" t="n">
         <v>2033</v>
       </c>
-      <c r="J169" s="12" t="n">
+      <c r="J170" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="K169" s="12" t="n"/>
-      <c r="L169" s="12" t="n"/>
-      <c r="M169" s="12" t="n"/>
-      <c r="N169" s="12" t="n"/>
-      <c r="O169" s="12" t="n"/>
-      <c r="P169" s="12" t="n"/>
-      <c r="Q169" s="12" t="n">
+      <c r="K170" s="12" t="n"/>
+      <c r="L170" s="12" t="n"/>
+      <c r="M170" s="12" t="n"/>
+      <c r="N170" s="12" t="n"/>
+      <c r="O170" s="12" t="n"/>
+      <c r="P170" s="12" t="n"/>
+      <c r="Q170" s="12" t="n">
         <v>3205</v>
       </c>
-      <c r="R169" s="3" t="inlineStr">
+      <c r="R170" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" outlineLevel="1">
-      <c r="A170" s="13" t="inlineStr">
-        <is>
-          <t>Safwat Aljouf</t>
-        </is>
-      </c>
-      <c r="B170" s="13" t="inlineStr">
-        <is>
-          <t>Safwat Aljawf</t>
-        </is>
-      </c>
-      <c r="C170" s="13" t="inlineStr">
-        <is>
-          <t>Trendyol</t>
-        </is>
-      </c>
-      <c r="D170" s="13" t="inlineStr">
-        <is>
-          <t>Commission (billed)</t>
-        </is>
-      </c>
-      <c r="E170" s="13" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F170" s="13" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="G170" s="14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H170" s="14" t="n">
-        <v>64.26000000000001</v>
-      </c>
-      <c r="I170" s="14" t="n">
-        <v>107.58</v>
-      </c>
-      <c r="J170" s="14" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="K170" s="14" t="n"/>
-      <c r="L170" s="14" t="n"/>
-      <c r="M170" s="14" t="n"/>
-      <c r="N170" s="14" t="n"/>
-      <c r="O170" s="14" t="n"/>
-      <c r="P170" s="14" t="n"/>
-      <c r="Q170" s="14" t="n">
-        <v>177.9</v>
-      </c>
-      <c r="R170" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
@@ -13883,28 +13966,40 @@
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C171" s="13" t="n"/>
+          <t>Safwat Aljawf</t>
+        </is>
+      </c>
+      <c r="C171" s="13" t="inlineStr">
+        <is>
+          <t>Trendyol</t>
+        </is>
+      </c>
       <c r="D171" s="13" t="inlineStr">
         <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E171" s="13" t="n"/>
-      <c r="F171" s="13" t="n"/>
+          <t>Commission (billed)</t>
+        </is>
+      </c>
+      <c r="E171" s="13" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F171" s="13" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
       <c r="G171" s="14" t="n">
-        <v>1083.33</v>
+        <v>2.1</v>
       </c>
       <c r="H171" s="14" t="n">
-        <v>2500</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I171" s="14" t="n">
-        <v>2500</v>
+        <v>107.58</v>
       </c>
       <c r="J171" s="14" t="n">
-        <v>833.33</v>
+        <v>3.96</v>
       </c>
       <c r="K171" s="14" t="n"/>
       <c r="L171" s="14" t="n"/>
@@ -13913,7 +14008,7 @@
       <c r="O171" s="14" t="n"/>
       <c r="P171" s="14" t="n"/>
       <c r="Q171" s="14" t="n">
-        <v>6916.66</v>
+        <v>177.9</v>
       </c>
       <c r="R171" s="3" t="inlineStr">
         <is>
@@ -13935,17 +14030,23 @@
       <c r="C172" s="13" t="n"/>
       <c r="D172" s="13" t="inlineStr">
         <is>
-          <t>Setup / one-time</t>
+          <t>Monthly fee</t>
         </is>
       </c>
       <c r="E172" s="13" t="n"/>
       <c r="F172" s="13" t="n"/>
       <c r="G172" s="14" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="H172" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="H172" s="14" t="n"/>
-      <c r="I172" s="14" t="n"/>
-      <c r="J172" s="14" t="n"/>
+      <c r="I172" s="14" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J172" s="14" t="n">
+        <v>833.33</v>
+      </c>
       <c r="K172" s="14" t="n"/>
       <c r="L172" s="14" t="n"/>
       <c r="M172" s="14" t="n"/>
@@ -13953,271 +14054,253 @@
       <c r="O172" s="14" t="n"/>
       <c r="P172" s="14" t="n"/>
       <c r="Q172" s="14" t="n">
+        <v>6916.66</v>
+      </c>
+      <c r="R172" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" outlineLevel="1">
+      <c r="A173" s="13" t="inlineStr">
+        <is>
+          <t>Safwat Aljouf</t>
+        </is>
+      </c>
+      <c r="B173" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C173" s="13" t="n"/>
+      <c r="D173" s="13" t="inlineStr">
+        <is>
+          <t>Setup / one-time</t>
+        </is>
+      </c>
+      <c r="E173" s="13" t="n"/>
+      <c r="F173" s="13" t="n"/>
+      <c r="G173" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="R172" s="3" t="inlineStr">
+      <c r="H173" s="14" t="n"/>
+      <c r="I173" s="14" t="n"/>
+      <c r="J173" s="14" t="n"/>
+      <c r="K173" s="14" t="n"/>
+      <c r="L173" s="14" t="n"/>
+      <c r="M173" s="14" t="n"/>
+      <c r="N173" s="14" t="n"/>
+      <c r="O173" s="14" t="n"/>
+      <c r="P173" s="14" t="n"/>
+      <c r="Q173" s="14" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R173" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="9" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="9" t="inlineStr">
         <is>
           <t>Reetal  (churned 2026-06)</t>
         </is>
       </c>
-      <c r="B174" s="9" t="n"/>
-      <c r="C174" s="9" t="n"/>
-      <c r="D174" s="9" t="inlineStr">
+      <c r="B175" s="9" t="n"/>
+      <c r="C175" s="9" t="n"/>
+      <c r="D175" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E174" s="9" t="n"/>
-      <c r="F174" s="9" t="n"/>
-      <c r="G174" s="10" t="n"/>
-      <c r="H174" s="10" t="n"/>
-      <c r="I174" s="10" t="n"/>
-      <c r="J174" s="10" t="n"/>
-      <c r="K174" s="10" t="n">
+      <c r="E175" s="9" t="n"/>
+      <c r="F175" s="9" t="n"/>
+      <c r="G175" s="10" t="n"/>
+      <c r="H175" s="10" t="n"/>
+      <c r="I175" s="10" t="n"/>
+      <c r="J175" s="10" t="n"/>
+      <c r="K175" s="10" t="n">
         <v>4492.3</v>
       </c>
-      <c r="L174" s="10" t="n">
+      <c r="L175" s="10" t="n">
         <v>1033.1</v>
       </c>
-      <c r="M174" s="10" t="n">
+      <c r="M175" s="10" t="n">
         <v>1799.32</v>
       </c>
-      <c r="N174" s="10" t="n">
+      <c r="N175" s="10" t="n">
         <v>684.49</v>
       </c>
-      <c r="O174" s="10" t="n"/>
-      <c r="P174" s="10" t="n"/>
-      <c r="Q174" s="10" t="n">
+      <c r="O175" s="10" t="n"/>
+      <c r="P175" s="10" t="n"/>
+      <c r="Q175" s="10" t="n">
         <v>8009.21</v>
       </c>
-      <c r="R174" s="3" t="inlineStr">
+      <c r="R175" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="175" outlineLevel="1">
-      <c r="A175" s="11" t="inlineStr">
+    <row r="176" outlineLevel="1">
+      <c r="A176" s="11" t="inlineStr">
         <is>
           <t>Reetal</t>
         </is>
       </c>
-      <c r="B175" s="11" t="inlineStr">
+      <c r="B176" s="11" t="inlineStr">
         <is>
           <t>Reetal</t>
         </is>
       </c>
-      <c r="C175" s="11" t="inlineStr">
+      <c r="C176" s="11" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D175" s="11" t="inlineStr">
+      <c r="D176" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E175" s="11" t="inlineStr">
+      <c r="E176" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F175" s="11" t="n"/>
-      <c r="G175" s="12" t="n"/>
-      <c r="H175" s="12" t="n"/>
-      <c r="I175" s="12" t="n"/>
-      <c r="J175" s="12" t="n"/>
-      <c r="K175" s="12" t="n"/>
-      <c r="L175" s="12" t="n">
+      <c r="F176" s="11" t="n"/>
+      <c r="G176" s="12" t="n"/>
+      <c r="H176" s="12" t="n"/>
+      <c r="I176" s="12" t="n"/>
+      <c r="J176" s="12" t="n"/>
+      <c r="K176" s="12" t="n"/>
+      <c r="L176" s="12" t="n">
         <v>280</v>
       </c>
-      <c r="M175" s="12" t="n">
+      <c r="M176" s="12" t="n">
         <v>4670</v>
       </c>
-      <c r="N175" s="12" t="n">
+      <c r="N176" s="12" t="n">
         <v>1150</v>
       </c>
-      <c r="O175" s="12" t="n"/>
-      <c r="P175" s="12" t="n"/>
-      <c r="Q175" s="12" t="n">
+      <c r="O176" s="12" t="n"/>
+      <c r="P176" s="12" t="n"/>
+      <c r="Q176" s="12" t="n">
         <v>6100</v>
       </c>
-      <c r="R175" s="3" t="inlineStr">
+      <c r="R176" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
         </is>
       </c>
     </row>
-    <row r="176" outlineLevel="1">
-      <c r="A176" s="13" t="inlineStr">
+    <row r="177" outlineLevel="1">
+      <c r="A177" s="13" t="inlineStr">
         <is>
           <t>Reetal</t>
         </is>
       </c>
-      <c r="B176" s="13" t="inlineStr">
+      <c r="B177" s="13" t="inlineStr">
         <is>
           <t>Reetal</t>
         </is>
       </c>
-      <c r="C176" s="13" t="inlineStr">
+      <c r="C177" s="13" t="inlineStr">
         <is>
           <t>Noon</t>
         </is>
       </c>
-      <c r="D176" s="13" t="inlineStr">
+      <c r="D177" s="13" t="inlineStr">
         <is>
           <t>Commission (billed)</t>
         </is>
       </c>
-      <c r="E176" s="13" t="inlineStr">
+      <c r="E177" s="13" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F176" s="13" t="inlineStr">
+      <c r="F177" s="13" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="G176" s="14" t="n"/>
-      <c r="H176" s="14" t="n"/>
-      <c r="I176" s="14" t="n"/>
-      <c r="J176" s="14" t="n"/>
-      <c r="K176" s="14" t="n"/>
-      <c r="L176" s="14" t="n">
+      <c r="G177" s="14" t="n"/>
+      <c r="H177" s="14" t="n"/>
+      <c r="I177" s="14" t="n"/>
+      <c r="J177" s="14" t="n"/>
+      <c r="K177" s="14" t="n"/>
+      <c r="L177" s="14" t="n">
         <v>11.2</v>
       </c>
-      <c r="M176" s="14" t="n">
+      <c r="M177" s="14" t="n">
         <v>189.8</v>
       </c>
-      <c r="N176" s="14" t="n">
+      <c r="N177" s="14" t="n">
         <v>72.5</v>
       </c>
-      <c r="O176" s="14" t="n"/>
-      <c r="P176" s="14" t="n"/>
-      <c r="Q176" s="14" t="n">
+      <c r="O177" s="14" t="n"/>
+      <c r="P177" s="14" t="n"/>
+      <c r="Q177" s="14" t="n">
         <v>273.5</v>
       </c>
-      <c r="R176" s="3" t="inlineStr">
+      <c r="R177" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="177" outlineLevel="1">
-      <c r="A177" s="11" t="inlineStr">
+    <row r="178" outlineLevel="1">
+      <c r="A178" s="11" t="inlineStr">
         <is>
           <t>Reetal</t>
         </is>
       </c>
-      <c r="B177" s="11" t="inlineStr">
+      <c r="B178" s="11" t="inlineStr">
         <is>
           <t>Reetal</t>
         </is>
       </c>
-      <c r="C177" s="11" t="inlineStr">
+      <c r="C178" s="11" t="inlineStr">
         <is>
           <t>Trendyol</t>
         </is>
       </c>
-      <c r="D177" s="11" t="inlineStr">
+      <c r="D178" s="11" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="E177" s="11" t="inlineStr">
+      <c r="E178" s="11" t="inlineStr">
         <is>
           <t>FAM</t>
         </is>
       </c>
-      <c r="F177" s="11" t="n"/>
-      <c r="G177" s="12" t="n"/>
-      <c r="H177" s="12" t="n"/>
-      <c r="I177" s="12" t="n"/>
-      <c r="J177" s="12" t="n"/>
-      <c r="K177" s="12" t="n"/>
-      <c r="L177" s="12" t="n">
+      <c r="F178" s="11" t="n"/>
+      <c r="G178" s="12" t="n"/>
+      <c r="H178" s="12" t="n"/>
+      <c r="I178" s="12" t="n"/>
+      <c r="J178" s="12" t="n"/>
+      <c r="K178" s="12" t="n"/>
+      <c r="L178" s="12" t="n">
         <v>547.46</v>
       </c>
-      <c r="M177" s="12" t="n">
+      <c r="M178" s="12" t="n">
         <v>614.85</v>
       </c>
-      <c r="N177" s="12" t="n">
+      <c r="N178" s="12" t="n">
         <v>223.04</v>
       </c>
-      <c r="O177" s="12" t="n"/>
-      <c r="P177" s="12" t="n"/>
-      <c r="Q177" s="12" t="n">
+      <c r="O178" s="12" t="n"/>
+      <c r="P178" s="12" t="n"/>
+      <c r="Q178" s="12" t="n">
         <v>1385.35</v>
       </c>
-      <c r="R177" s="3" t="inlineStr">
+      <c r="R178" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — revenue view</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" outlineLevel="1">
-      <c r="A178" s="13" t="inlineStr">
-        <is>
-          <t>Reetal</t>
-        </is>
-      </c>
-      <c r="B178" s="13" t="inlineStr">
-        <is>
-          <t>Reetal</t>
-        </is>
-      </c>
-      <c r="C178" s="13" t="inlineStr">
-        <is>
-          <t>Trendyol</t>
-        </is>
-      </c>
-      <c r="D178" s="13" t="inlineStr">
-        <is>
-          <t>Commission (billed)</t>
-        </is>
-      </c>
-      <c r="E178" s="13" t="inlineStr">
-        <is>
-          <t>FAM</t>
-        </is>
-      </c>
-      <c r="F178" s="13" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="G178" s="14" t="n"/>
-      <c r="H178" s="14" t="n"/>
-      <c r="I178" s="14" t="n"/>
-      <c r="J178" s="14" t="n"/>
-      <c r="K178" s="14" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="L178" s="14" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M178" s="14" t="n">
-        <v>28.92</v>
-      </c>
-      <c r="N178" s="14" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="O178" s="14" t="n"/>
-      <c r="P178" s="14" t="n"/>
-      <c r="Q178" s="14" t="n">
-        <v>71.23999999999999</v>
-      </c>
-      <c r="R178" s="3" t="inlineStr">
-        <is>
-          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
@@ -14229,41 +14312,53 @@
       </c>
       <c r="B179" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C179" s="13" t="n"/>
+          <t>Reetal</t>
+        </is>
+      </c>
+      <c r="C179" s="13" t="inlineStr">
+        <is>
+          <t>Trendyol</t>
+        </is>
+      </c>
       <c r="D179" s="13" t="inlineStr">
         <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="E179" s="13" t="n"/>
-      <c r="F179" s="13" t="n"/>
+          <t>Commission (billed)</t>
+        </is>
+      </c>
+      <c r="E179" s="13" t="inlineStr">
+        <is>
+          <t>FAM</t>
+        </is>
+      </c>
+      <c r="F179" s="13" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="G179" s="14" t="n"/>
       <c r="H179" s="14" t="n"/>
       <c r="I179" s="14" t="n"/>
       <c r="J179" s="14" t="n"/>
       <c r="K179" s="14" t="n">
-        <v>1483.87</v>
+        <v>8.43</v>
       </c>
       <c r="L179" s="14" t="n">
-        <v>2000</v>
+        <v>21.9</v>
       </c>
       <c r="M179" s="14" t="n">
-        <v>1580.6</v>
+        <v>28.92</v>
       </c>
       <c r="N179" s="14" t="n">
-        <v>600</v>
+        <v>11.99</v>
       </c>
       <c r="O179" s="14" t="n"/>
       <c r="P179" s="14" t="n"/>
       <c r="Q179" s="14" t="n">
-        <v>5664.47</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="R179" s="3" t="inlineStr">
         <is>
-          <t>Wafeq invoice export · Card 5% + 1,000; billed 4% + 2,000 under setup-period arrangement</t>
+          <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14376,7 @@
       <c r="C180" s="13" t="n"/>
       <c r="D180" s="13" t="inlineStr">
         <is>
-          <t>Setup / one-time</t>
+          <t>Monthly fee</t>
         </is>
       </c>
       <c r="E180" s="13" t="n"/>
@@ -14291,19 +14386,25 @@
       <c r="I180" s="14" t="n"/>
       <c r="J180" s="14" t="n"/>
       <c r="K180" s="14" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L180" s="14" t="n"/>
-      <c r="M180" s="14" t="n"/>
-      <c r="N180" s="14" t="n"/>
+        <v>1483.87</v>
+      </c>
+      <c r="L180" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M180" s="14" t="n">
+        <v>1580.6</v>
+      </c>
+      <c r="N180" s="14" t="n">
+        <v>600</v>
+      </c>
       <c r="O180" s="14" t="n"/>
       <c r="P180" s="14" t="n"/>
       <c r="Q180" s="14" t="n">
-        <v>3000</v>
+        <v>5664.47</v>
       </c>
       <c r="R180" s="3" t="inlineStr">
         <is>
-          <t>Wafeq invoice export</t>
+          <t>Wafeq invoice export · Card 5% + 1,000; billed 4% + 2,000 under setup-period arrangement</t>
         </is>
       </c>
     </row>
@@ -14321,7 +14422,7 @@
       <c r="C181" s="13" t="n"/>
       <c r="D181" s="13" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>Setup / one-time</t>
         </is>
       </c>
       <c r="E181" s="13" t="n"/>
@@ -14330,242 +14431,282 @@
       <c r="H181" s="14" t="n"/>
       <c r="I181" s="14" t="n"/>
       <c r="J181" s="14" t="n"/>
-      <c r="K181" s="14" t="n"/>
-      <c r="L181" s="14" t="n">
-        <v>-1000</v>
-      </c>
+      <c r="K181" s="14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L181" s="14" t="n"/>
       <c r="M181" s="14" t="n"/>
       <c r="N181" s="14" t="n"/>
       <c r="O181" s="14" t="n"/>
       <c r="P181" s="14" t="n"/>
       <c r="Q181" s="14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="R181" s="3" t="inlineStr">
+        <is>
+          <t>Wafeq invoice export</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" outlineLevel="1">
+      <c r="A182" s="13" t="inlineStr">
+        <is>
+          <t>Reetal</t>
+        </is>
+      </c>
+      <c r="B182" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C182" s="13" t="n"/>
+      <c r="D182" s="13" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="E182" s="13" t="n"/>
+      <c r="F182" s="13" t="n"/>
+      <c r="G182" s="14" t="n"/>
+      <c r="H182" s="14" t="n"/>
+      <c r="I182" s="14" t="n"/>
+      <c r="J182" s="14" t="n"/>
+      <c r="K182" s="14" t="n"/>
+      <c r="L182" s="14" t="n">
         <v>-1000</v>
       </c>
-      <c r="R181" s="3" t="inlineStr">
+      <c r="M182" s="14" t="n"/>
+      <c r="N182" s="14" t="n"/>
+      <c r="O182" s="14" t="n"/>
+      <c r="P182" s="14" t="n"/>
+      <c r="Q182" s="14" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="R182" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export · setup-period 50% AM fee / agreed reduction / pricing error</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="9" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="9" t="inlineStr">
         <is>
           <t>House Mart  (churned 2026-04)</t>
         </is>
       </c>
-      <c r="B183" s="9" t="n"/>
-      <c r="C183" s="9" t="n"/>
-      <c r="D183" s="9" t="inlineStr">
+      <c r="B184" s="9" t="n"/>
+      <c r="C184" s="9" t="n"/>
+      <c r="D184" s="9" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E183" s="9" t="n"/>
-      <c r="F183" s="9" t="n"/>
-      <c r="G183" s="10" t="n">
+      <c r="E184" s="9" t="n"/>
+      <c r="F184" s="9" t="n"/>
+      <c r="G184" s="10" t="n">
         <v>6750</v>
       </c>
-      <c r="H183" s="10" t="n"/>
-      <c r="I183" s="10" t="n"/>
-      <c r="J183" s="10" t="n"/>
-      <c r="K183" s="10" t="n"/>
-      <c r="L183" s="10" t="n">
+      <c r="H184" s="10" t="n"/>
+      <c r="I184" s="10" t="n"/>
+      <c r="J184" s="10" t="n"/>
+      <c r="K184" s="10" t="n"/>
+      <c r="L184" s="10" t="n">
         <v>8800.5</v>
       </c>
-      <c r="M183" s="10" t="n"/>
-      <c r="N183" s="10" t="n"/>
-      <c r="O183" s="10" t="n"/>
-      <c r="P183" s="10" t="n"/>
-      <c r="Q183" s="10" t="n">
+      <c r="M184" s="10" t="n"/>
+      <c r="N184" s="10" t="n"/>
+      <c r="O184" s="10" t="n"/>
+      <c r="P184" s="10" t="n"/>
+      <c r="Q184" s="10" t="n">
         <v>15550.5</v>
       </c>
-      <c r="R183" s="3" t="inlineStr">
+      <c r="R184" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="184" outlineLevel="1">
-      <c r="A184" s="13" t="inlineStr">
+    <row r="185" outlineLevel="1">
+      <c r="A185" s="13" t="inlineStr">
         <is>
           <t>House Mart</t>
         </is>
       </c>
-      <c r="B184" s="13" t="inlineStr">
+      <c r="B185" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C184" s="13" t="n"/>
-      <c r="D184" s="13" t="inlineStr">
+      <c r="C185" s="13" t="n"/>
+      <c r="D185" s="13" t="inlineStr">
         <is>
           <t>Setup / one-time</t>
         </is>
       </c>
-      <c r="E184" s="13" t="n"/>
-      <c r="F184" s="13" t="n"/>
-      <c r="G184" s="14" t="n">
+      <c r="E185" s="13" t="n"/>
+      <c r="F185" s="13" t="n"/>
+      <c r="G185" s="14" t="n">
         <v>6750</v>
       </c>
-      <c r="H184" s="14" t="n"/>
-      <c r="I184" s="14" t="n"/>
-      <c r="J184" s="14" t="n"/>
-      <c r="K184" s="14" t="n"/>
-      <c r="L184" s="14" t="n">
+      <c r="H185" s="14" t="n"/>
+      <c r="I185" s="14" t="n"/>
+      <c r="J185" s="14" t="n"/>
+      <c r="K185" s="14" t="n"/>
+      <c r="L185" s="14" t="n">
         <v>8800.5</v>
       </c>
-      <c r="M184" s="14" t="n"/>
-      <c r="N184" s="14" t="n"/>
-      <c r="O184" s="14" t="n"/>
-      <c r="P184" s="14" t="n"/>
-      <c r="Q184" s="14" t="n">
+      <c r="M185" s="14" t="n"/>
+      <c r="N185" s="14" t="n"/>
+      <c r="O185" s="14" t="n"/>
+      <c r="P185" s="14" t="n"/>
+      <c r="Q185" s="14" t="n">
         <v>15550.5</v>
       </c>
-      <c r="R184" s="3" t="inlineStr">
+      <c r="R185" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="6" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
         <is>
           <t>ALL CLIENTS</t>
         </is>
       </c>
-      <c r="B186" s="6" t="n"/>
-      <c r="C186" s="6" t="n"/>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="B187" s="6" t="n"/>
+      <c r="C187" s="6" t="n"/>
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>Billed revenue</t>
         </is>
       </c>
-      <c r="E186" s="6" t="n"/>
-      <c r="F186" s="6" t="n"/>
-      <c r="G186" s="18" t="n">
+      <c r="E187" s="6" t="n"/>
+      <c r="F187" s="6" t="n"/>
+      <c r="G187" s="18" t="n">
         <v>31390.44</v>
       </c>
-      <c r="H186" s="18" t="n">
+      <c r="H187" s="18" t="n">
         <v>21947.73</v>
       </c>
-      <c r="I186" s="18" t="n">
+      <c r="I187" s="18" t="n">
         <v>26212.8</v>
       </c>
-      <c r="J186" s="18" t="n">
+      <c r="J187" s="18" t="n">
         <v>19517.67</v>
       </c>
-      <c r="K186" s="18" t="n">
+      <c r="K187" s="18" t="n">
         <v>27125.53</v>
       </c>
-      <c r="L186" s="18" t="n">
+      <c r="L187" s="18" t="n">
         <v>27486.22</v>
       </c>
-      <c r="M186" s="18" t="n">
+      <c r="M187" s="18" t="n">
         <v>21956.43</v>
       </c>
-      <c r="N186" s="18" t="n">
+      <c r="N187" s="18" t="n">
         <v>16243.45</v>
       </c>
-      <c r="O186" s="18" t="n">
+      <c r="O187" s="18" t="n">
         <v>7298.95</v>
       </c>
-      <c r="P186" s="18" t="n">
+      <c r="P187" s="18" t="n">
         <v>12694.6</v>
       </c>
-      <c r="Q186" s="18" t="n">
+      <c r="Q187" s="18" t="n">
         <v>211873.82</v>
       </c>
-      <c r="R186" s="3" t="inlineStr">
+      <c r="R187" s="3" t="inlineStr">
         <is>
           <t>Wafeq invoice export</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="16" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="16" t="inlineStr">
         <is>
           <t>ALL CLIENTS</t>
         </is>
       </c>
-      <c r="B187" s="16" t="n"/>
-      <c r="C187" s="16" t="n"/>
-      <c r="D187" s="16" t="inlineStr">
+      <c r="B188" s="16" t="n"/>
+      <c r="C188" s="16" t="n"/>
+      <c r="D188" s="16" t="inlineStr">
         <is>
           <t>Commission (to invoice)</t>
         </is>
       </c>
-      <c r="E187" s="16" t="n"/>
-      <c r="F187" s="16" t="n"/>
-      <c r="G187" s="17" t="n"/>
-      <c r="H187" s="17" t="n"/>
-      <c r="I187" s="17" t="n"/>
-      <c r="J187" s="17" t="n"/>
-      <c r="K187" s="17" t="n"/>
-      <c r="L187" s="17" t="n"/>
-      <c r="M187" s="17" t="n"/>
-      <c r="N187" s="17" t="n"/>
-      <c r="O187" s="17" t="n"/>
-      <c r="P187" s="17" t="n">
+      <c r="E188" s="16" t="n"/>
+      <c r="F188" s="16" t="n"/>
+      <c r="G188" s="17" t="n"/>
+      <c r="H188" s="17" t="n"/>
+      <c r="I188" s="17" t="n"/>
+      <c r="J188" s="17" t="n"/>
+      <c r="K188" s="17" t="n"/>
+      <c r="L188" s="17" t="n"/>
+      <c r="M188" s="17" t="n"/>
+      <c r="N188" s="17" t="n"/>
+      <c r="O188" s="17" t="n"/>
+      <c r="P188" s="17" t="n">
         <v>17.14</v>
       </c>
-      <c r="Q187" s="17" t="n">
+      <c r="Q188" s="17" t="n">
         <v>17.14</v>
       </c>
-      <c r="R187" s="3" t="inlineStr">
+      <c r="R188" s="3" t="inlineStr">
         <is>
           <t>Nasam platform — closed POs</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="6" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="6" t="inlineStr">
         <is>
           <t>ALL CLIENTS</t>
         </is>
       </c>
-      <c r="B188" s="6" t="n"/>
-      <c r="C188" s="6" t="n"/>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="B189" s="6" t="n"/>
+      <c r="C189" s="6" t="n"/>
+      <c r="D189" s="6" t="inlineStr">
         <is>
           <t>TOTAL incl. to-invoice</t>
         </is>
       </c>
-      <c r="E188" s="6" t="n"/>
-      <c r="F188" s="6" t="n"/>
-      <c r="G188" s="18" t="n">
+      <c r="E189" s="6" t="n"/>
+      <c r="F189" s="6" t="n"/>
+      <c r="G189" s="18" t="n">
         <v>31390.44</v>
       </c>
-      <c r="H188" s="18" t="n">
+      <c r="H189" s="18" t="n">
         <v>21947.73</v>
       </c>
-      <c r="I188" s="18" t="n">
+      <c r="I189" s="18" t="n">
         <v>26212.8</v>
       </c>
-      <c r="J188" s="18" t="n">
+      <c r="J189" s="18" t="n">
         <v>19517.67</v>
       </c>
-      <c r="K188" s="18" t="n">
+      <c r="K189" s="18" t="n">
         <v>27125.53</v>
       </c>
-      <c r="L188" s="18" t="n">
+      <c r="L189" s="18" t="n">
         <v>27486.22</v>
       </c>
-      <c r="M188" s="18" t="n">
+      <c r="M189" s="18" t="n">
         <v>21956.43</v>
       </c>
-      <c r="N188" s="18" t="n">
+      <c r="N189" s="18" t="n">
         <v>16243.45</v>
       </c>
-      <c r="O188" s="18" t="n">
+      <c r="O189" s="18" t="n">
         <v>7298.95</v>
       </c>
-      <c r="P188" s="18" t="n">
+      <c r="P189" s="18" t="n">
         <v>12711.74</v>
       </c>
-      <c r="Q188" s="18" t="n">
+      <c r="Q189" s="18" t="n">
         <v>211890.96</v>
       </c>
-      <c r="R188" s="3" t="inlineStr">
+      <c r="R189" s="3" t="inlineStr">
         <is>
           <t>Billed + closed-PO commission</t>
         </is>
